--- a/examples/DB_Supermercado.xlsx
+++ b/examples/DB_Supermercado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EducacionIT\Documents\office\Excel\xls-mj15\examples\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{291F1920-4C96-46FD-A1BF-BE0A3BCDE154}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{632115F4-9157-413A-8187-B5E009F3A67D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/examples/DB_Supermercado.xlsx
+++ b/examples/DB_Supermercado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EducacionIT\Documents\office\Excel\xls-mj15\examples\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EBFB6C6-6254-479A-9441-8A016063E92F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEF55D92-8FFC-40C6-98B9-EBAB1C7FC01B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7173,7 +7173,7 @@
         <v>3230017545</v>
       </c>
       <c r="AI14" s="95">
-        <f t="shared" ref="AI14:AN14" si="23">SUM(AI10:AI13)</f>
+        <f t="shared" ref="AI14:AM14" si="23">SUM(AI10:AI13)</f>
         <v>9072</v>
       </c>
       <c r="AJ14" s="51">
@@ -7332,23 +7332,23 @@
         <v>645115066</v>
       </c>
       <c r="E17" s="82">
-        <f>SUMIFS(ventas_unidades,ventas_vendedor,$A17,ventas_producto,E$16)</f>
+        <f t="shared" ref="E17:I22" si="27">SUMIFS(ventas_unidades,ventas_vendedor,$A17,ventas_producto,E$16)</f>
         <v>23075</v>
       </c>
       <c r="F17" s="17">
-        <f>SUMIFS(ventas_unidades,ventas_vendedor,$A17,ventas_producto,F$16)</f>
+        <f t="shared" si="27"/>
         <v>14026</v>
       </c>
       <c r="G17" s="17">
-        <f>SUMIFS(ventas_unidades,ventas_vendedor,$A17,ventas_producto,G$16)</f>
+        <f t="shared" si="27"/>
         <v>37242</v>
       </c>
       <c r="H17" s="17">
-        <f>SUMIFS(ventas_unidades,ventas_vendedor,$A17,ventas_producto,H$16)</f>
+        <f t="shared" si="27"/>
         <v>34352</v>
       </c>
       <c r="I17" s="17">
-        <f>SUMIFS(ventas_unidades,ventas_vendedor,$A17,ventas_producto,I$16)</f>
+        <f t="shared" si="27"/>
         <v>12970</v>
       </c>
       <c r="J17" s="17">
@@ -7356,23 +7356,23 @@
         <v>121665</v>
       </c>
       <c r="L17" s="97">
-        <f>SUMIFS(ventas_total,ventas_vendedor,$A17,ventas_producto,L$16)</f>
+        <f t="shared" ref="L17:P22" si="28">SUMIFS(ventas_total,ventas_vendedor,$A17,ventas_producto,L$16)</f>
         <v>109144041</v>
       </c>
       <c r="M17" s="59">
-        <f>SUMIFS(ventas_total,ventas_vendedor,$A17,ventas_producto,M$16)</f>
+        <f t="shared" si="28"/>
         <v>53223672</v>
       </c>
       <c r="N17" s="59">
-        <f>SUMIFS(ventas_total,ventas_vendedor,$A17,ventas_producto,N$16)</f>
+        <f t="shared" si="28"/>
         <v>240818885</v>
       </c>
       <c r="O17" s="59">
-        <f>SUMIFS(ventas_total,ventas_vendedor,$A17,ventas_producto,O$16)</f>
+        <f t="shared" si="28"/>
         <v>169977929</v>
       </c>
       <c r="P17" s="59">
-        <f>SUMIFS(ventas_total,ventas_vendedor,$A17,ventas_producto,P$16)</f>
+        <f t="shared" si="28"/>
         <v>71950539</v>
       </c>
       <c r="Q17" s="59">
@@ -7394,23 +7394,23 @@
       <c r="AF17" s="68"/>
       <c r="AG17" s="68"/>
       <c r="AI17" s="82">
-        <f t="shared" ref="AI17:AM22" si="27">SUMIFS(ventas_unidades,ventas_vendedor,$A17,ventas_region,AI$16)</f>
+        <f t="shared" ref="AI17:AM22" si="29">SUMIFS(ventas_unidades,ventas_vendedor,$A17,ventas_region,AI$16)</f>
         <v>23075</v>
       </c>
       <c r="AJ17" s="17">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>7195</v>
       </c>
       <c r="AK17" s="17">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>39170</v>
       </c>
       <c r="AL17" s="17">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>39255</v>
       </c>
       <c r="AM17" s="17">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>12970</v>
       </c>
       <c r="AN17" s="17">
@@ -7418,23 +7418,23 @@
         <v>121665</v>
       </c>
       <c r="AP17" s="97">
-        <f t="shared" ref="AP17:AT22" si="28">SUMIFS(ventas_total,ventas_vendedor,$A17,ventas_region,AP$16)</f>
+        <f t="shared" ref="AP17:AT22" si="30">SUMIFS(ventas_total,ventas_vendedor,$A17,ventas_region,AP$16)</f>
         <v>109144041</v>
       </c>
       <c r="AQ17" s="59">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>52631529</v>
       </c>
       <c r="AR17" s="59">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>240927099</v>
       </c>
       <c r="AS17" s="59">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>170461858</v>
       </c>
       <c r="AT17" s="59">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>71950539</v>
       </c>
       <c r="AU17" s="59">
@@ -7455,51 +7455,51 @@
         <v>761464717</v>
       </c>
       <c r="E18" s="83">
-        <f>SUMIFS(ventas_unidades,ventas_vendedor,$A18,ventas_producto,E$16)</f>
+        <f t="shared" si="27"/>
         <v>27346</v>
       </c>
       <c r="F18" s="18">
-        <f>SUMIFS(ventas_unidades,ventas_vendedor,$A18,ventas_producto,F$16)</f>
+        <f t="shared" si="27"/>
         <v>51553</v>
       </c>
       <c r="G18" s="18">
-        <f>SUMIFS(ventas_unidades,ventas_vendedor,$A18,ventas_producto,G$16)</f>
+        <f t="shared" si="27"/>
         <v>19565</v>
       </c>
       <c r="H18" s="18">
-        <f>SUMIFS(ventas_unidades,ventas_vendedor,$A18,ventas_producto,H$16)</f>
+        <f t="shared" si="27"/>
         <v>12991</v>
       </c>
       <c r="I18" s="18">
-        <f>SUMIFS(ventas_unidades,ventas_vendedor,$A18,ventas_producto,I$16)</f>
+        <f t="shared" si="27"/>
         <v>14165</v>
       </c>
       <c r="J18" s="18">
-        <f t="shared" ref="J18:J22" si="29">SUM(E18:I18)</f>
+        <f t="shared" ref="J18:J22" si="31">SUM(E18:I18)</f>
         <v>125620</v>
       </c>
       <c r="L18" s="98">
-        <f>SUMIFS(ventas_total,ventas_vendedor,$A18,ventas_producto,L$16)</f>
+        <f t="shared" si="28"/>
         <v>193222871</v>
       </c>
       <c r="M18" s="60">
-        <f>SUMIFS(ventas_total,ventas_vendedor,$A18,ventas_producto,M$16)</f>
+        <f t="shared" si="28"/>
         <v>271532147</v>
       </c>
       <c r="N18" s="60">
-        <f>SUMIFS(ventas_total,ventas_vendedor,$A18,ventas_producto,N$16)</f>
+        <f t="shared" si="28"/>
         <v>131950052</v>
       </c>
       <c r="O18" s="60">
-        <f>SUMIFS(ventas_total,ventas_vendedor,$A18,ventas_producto,O$16)</f>
+        <f t="shared" si="28"/>
         <v>75839132</v>
       </c>
       <c r="P18" s="60">
-        <f>SUMIFS(ventas_total,ventas_vendedor,$A18,ventas_producto,P$16)</f>
+        <f t="shared" si="28"/>
         <v>88920515</v>
       </c>
       <c r="Q18" s="60">
-        <f t="shared" ref="Q18:Q22" si="30">SUM(L18:P18)</f>
+        <f t="shared" ref="Q18:Q22" si="32">SUM(L18:P18)</f>
         <v>761464717</v>
       </c>
       <c r="S18" s="94"/>
@@ -7517,51 +7517,51 @@
       <c r="AF18" s="68"/>
       <c r="AG18" s="68"/>
       <c r="AI18" s="83">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>27346</v>
       </c>
       <c r="AJ18" s="18">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>51553</v>
       </c>
       <c r="AK18" s="18">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>19565</v>
       </c>
       <c r="AL18" s="18">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>12991</v>
       </c>
       <c r="AM18" s="18">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>14165</v>
       </c>
       <c r="AN18" s="18">
-        <f t="shared" ref="AN18:AN22" si="31">SUM(AI18:AM18)</f>
+        <f t="shared" ref="AN18:AN22" si="33">SUM(AI18:AM18)</f>
         <v>125620</v>
       </c>
       <c r="AP18" s="98">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>193222871</v>
       </c>
       <c r="AQ18" s="60">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>271532147</v>
       </c>
       <c r="AR18" s="60">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>131950052</v>
       </c>
       <c r="AS18" s="60">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>75839132</v>
       </c>
       <c r="AT18" s="60">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>88920515</v>
       </c>
       <c r="AU18" s="60">
-        <f t="shared" ref="AU18:AU22" si="32">SUM(AP18:AT18)</f>
+        <f t="shared" ref="AU18:AU22" si="34">SUM(AP18:AT18)</f>
         <v>761464717</v>
       </c>
     </row>
@@ -7578,51 +7578,51 @@
         <v>226722785</v>
       </c>
       <c r="E19" s="84">
-        <f>SUMIFS(ventas_unidades,ventas_vendedor,$A19,ventas_producto,E$16)</f>
+        <f t="shared" si="27"/>
         <v>9125</v>
       </c>
       <c r="F19" s="19">
-        <f>SUMIFS(ventas_unidades,ventas_vendedor,$A19,ventas_producto,F$16)</f>
+        <f t="shared" si="27"/>
         <v>9023</v>
       </c>
       <c r="G19" s="19">
-        <f>SUMIFS(ventas_unidades,ventas_vendedor,$A19,ventas_producto,G$16)</f>
+        <f t="shared" si="27"/>
         <v>6969</v>
       </c>
       <c r="H19" s="19">
-        <f>SUMIFS(ventas_unidades,ventas_vendedor,$A19,ventas_producto,H$16)</f>
+        <f t="shared" si="27"/>
         <v>2096</v>
       </c>
       <c r="I19" s="19">
-        <f>SUMIFS(ventas_unidades,ventas_vendedor,$A19,ventas_producto,I$16)</f>
+        <f t="shared" si="27"/>
         <v>5143</v>
       </c>
       <c r="J19" s="19">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>32356</v>
       </c>
       <c r="L19" s="99">
-        <f>SUMIFS(ventas_total,ventas_vendedor,$A19,ventas_producto,L$16)</f>
+        <f t="shared" si="28"/>
         <v>59797810</v>
       </c>
       <c r="M19" s="61">
-        <f>SUMIFS(ventas_total,ventas_vendedor,$A19,ventas_producto,M$16)</f>
+        <f t="shared" si="28"/>
         <v>63246530</v>
       </c>
       <c r="N19" s="61">
-        <f>SUMIFS(ventas_total,ventas_vendedor,$A19,ventas_producto,N$16)</f>
+        <f t="shared" si="28"/>
         <v>40433106</v>
       </c>
       <c r="O19" s="61">
-        <f>SUMIFS(ventas_total,ventas_vendedor,$A19,ventas_producto,O$16)</f>
+        <f t="shared" si="28"/>
         <v>31378227</v>
       </c>
       <c r="P19" s="61">
-        <f>SUMIFS(ventas_total,ventas_vendedor,$A19,ventas_producto,P$16)</f>
+        <f t="shared" si="28"/>
         <v>31867112</v>
       </c>
       <c r="Q19" s="61">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>226722785</v>
       </c>
       <c r="S19" s="94"/>
@@ -7640,51 +7640,51 @@
       <c r="AF19" s="68"/>
       <c r="AG19" s="68"/>
       <c r="AI19" s="84">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>9125</v>
       </c>
       <c r="AJ19" s="19">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>9023</v>
       </c>
       <c r="AK19" s="19">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>6969</v>
       </c>
       <c r="AL19" s="19">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>2096</v>
       </c>
       <c r="AM19" s="19">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>5143</v>
       </c>
       <c r="AN19" s="19">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>32356</v>
       </c>
       <c r="AP19" s="99">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>59797810</v>
       </c>
       <c r="AQ19" s="61">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>63246530</v>
       </c>
       <c r="AR19" s="61">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>40433106</v>
       </c>
       <c r="AS19" s="61">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>31378227</v>
       </c>
       <c r="AT19" s="61">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>31867112</v>
       </c>
       <c r="AU19" s="61">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>226722785</v>
       </c>
     </row>
@@ -7701,51 +7701,51 @@
         <v>312257691</v>
       </c>
       <c r="E20" s="83">
-        <f>SUMIFS(ventas_unidades,ventas_vendedor,$A20,ventas_producto,E$16)</f>
+        <f t="shared" si="27"/>
         <v>21722</v>
       </c>
       <c r="F20" s="18">
-        <f>SUMIFS(ventas_unidades,ventas_vendedor,$A20,ventas_producto,F$16)</f>
+        <f t="shared" si="27"/>
         <v>197836</v>
       </c>
       <c r="G20" s="18">
-        <f>SUMIFS(ventas_unidades,ventas_vendedor,$A20,ventas_producto,G$16)</f>
+        <f t="shared" si="27"/>
         <v>18868</v>
       </c>
       <c r="H20" s="18">
-        <f>SUMIFS(ventas_unidades,ventas_vendedor,$A20,ventas_producto,H$16)</f>
+        <f t="shared" si="27"/>
         <v>5457</v>
       </c>
       <c r="I20" s="18">
-        <f>SUMIFS(ventas_unidades,ventas_vendedor,$A20,ventas_producto,I$16)</f>
+        <f t="shared" si="27"/>
         <v>112414</v>
       </c>
       <c r="J20" s="18">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>356297</v>
       </c>
       <c r="L20" s="98">
-        <f>SUMIFS(ventas_total,ventas_vendedor,$A20,ventas_producto,L$16)</f>
+        <f t="shared" si="28"/>
         <v>135280108</v>
       </c>
       <c r="M20" s="60">
-        <f>SUMIFS(ventas_total,ventas_vendedor,$A20,ventas_producto,M$16)</f>
+        <f t="shared" si="28"/>
         <v>45710704</v>
       </c>
       <c r="N20" s="60">
-        <f>SUMIFS(ventas_total,ventas_vendedor,$A20,ventas_producto,N$16)</f>
+        <f t="shared" si="28"/>
         <v>31481567</v>
       </c>
       <c r="O20" s="60">
-        <f>SUMIFS(ventas_total,ventas_vendedor,$A20,ventas_producto,O$16)</f>
+        <f t="shared" si="28"/>
         <v>23001252</v>
       </c>
       <c r="P20" s="60">
-        <f>SUMIFS(ventas_total,ventas_vendedor,$A20,ventas_producto,P$16)</f>
+        <f t="shared" si="28"/>
         <v>76784060</v>
       </c>
       <c r="Q20" s="60">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>312257691</v>
       </c>
       <c r="S20" s="94"/>
@@ -7763,51 +7763,51 @@
       <c r="AF20" s="68"/>
       <c r="AG20" s="68"/>
       <c r="AI20" s="83">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>30665</v>
       </c>
       <c r="AJ20" s="18">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>103585</v>
       </c>
       <c r="AK20" s="18">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>9925</v>
       </c>
       <c r="AL20" s="18">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>197831</v>
       </c>
       <c r="AM20" s="18">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>14291</v>
       </c>
       <c r="AN20" s="18">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>356297</v>
       </c>
       <c r="AP20" s="98">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>139608342</v>
       </c>
       <c r="AQ20" s="60">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>44964557</v>
       </c>
       <c r="AR20" s="60">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>27153333</v>
       </c>
       <c r="AS20" s="60">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>23830600</v>
       </c>
       <c r="AT20" s="60">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>76700859</v>
       </c>
       <c r="AU20" s="60">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>312257691</v>
       </c>
     </row>
@@ -7824,51 +7824,51 @@
         <v>722503562</v>
       </c>
       <c r="E21" s="84">
-        <f>SUMIFS(ventas_unidades,ventas_vendedor,$A21,ventas_producto,E$16)</f>
+        <f t="shared" si="27"/>
         <v>18175</v>
       </c>
       <c r="F21" s="19">
-        <f>SUMIFS(ventas_unidades,ventas_vendedor,$A21,ventas_producto,F$16)</f>
+        <f t="shared" si="27"/>
         <v>15576</v>
       </c>
       <c r="G21" s="19">
-        <f>SUMIFS(ventas_unidades,ventas_vendedor,$A21,ventas_producto,G$16)</f>
+        <f t="shared" si="27"/>
         <v>10706</v>
       </c>
       <c r="H21" s="19">
-        <f>SUMIFS(ventas_unidades,ventas_vendedor,$A21,ventas_producto,H$16)</f>
+        <f t="shared" si="27"/>
         <v>55164</v>
       </c>
       <c r="I21" s="19">
-        <f>SUMIFS(ventas_unidades,ventas_vendedor,$A21,ventas_producto,I$16)</f>
+        <f t="shared" si="27"/>
         <v>22674</v>
       </c>
       <c r="J21" s="19">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>122295</v>
       </c>
       <c r="L21" s="99">
-        <f>SUMIFS(ventas_total,ventas_vendedor,$A21,ventas_producto,L$16)</f>
+        <f t="shared" si="28"/>
         <v>103659911</v>
       </c>
       <c r="M21" s="61">
-        <f>SUMIFS(ventas_total,ventas_vendedor,$A21,ventas_producto,M$16)</f>
+        <f t="shared" si="28"/>
         <v>93604609</v>
       </c>
       <c r="N21" s="61">
-        <f>SUMIFS(ventas_total,ventas_vendedor,$A21,ventas_producto,N$16)</f>
+        <f t="shared" si="28"/>
         <v>77744662</v>
       </c>
       <c r="O21" s="61">
-        <f>SUMIFS(ventas_total,ventas_vendedor,$A21,ventas_producto,O$16)</f>
+        <f t="shared" si="28"/>
         <v>336958448</v>
       </c>
       <c r="P21" s="61">
-        <f>SUMIFS(ventas_total,ventas_vendedor,$A21,ventas_producto,P$16)</f>
+        <f t="shared" si="28"/>
         <v>110535932</v>
       </c>
       <c r="Q21" s="61">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>722503562</v>
       </c>
       <c r="S21" s="94"/>
@@ -7886,51 +7886,51 @@
       <c r="AF21" s="68"/>
       <c r="AG21" s="68"/>
       <c r="AI21" s="84">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>11047</v>
       </c>
       <c r="AJ21" s="19">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>25399</v>
       </c>
       <c r="AK21" s="19">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>12633</v>
       </c>
       <c r="AL21" s="19">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>53237</v>
       </c>
       <c r="AM21" s="19">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>19979</v>
       </c>
       <c r="AN21" s="19">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>122295</v>
       </c>
       <c r="AP21" s="99">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>94535993</v>
       </c>
       <c r="AQ21" s="61">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>93622843</v>
       </c>
       <c r="AR21" s="61">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>78668644</v>
       </c>
       <c r="AS21" s="61">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>336034466</v>
       </c>
       <c r="AT21" s="61">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>119641616</v>
       </c>
       <c r="AU21" s="61">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>722503562</v>
       </c>
     </row>
@@ -7947,51 +7947,51 @@
         <v>561953724</v>
       </c>
       <c r="E22" s="88">
-        <f>SUMIFS(ventas_unidades,ventas_vendedor,$A22,ventas_producto,E$16)</f>
+        <f t="shared" si="27"/>
         <v>11460</v>
       </c>
       <c r="F22" s="52">
-        <f>SUMIFS(ventas_unidades,ventas_vendedor,$A22,ventas_producto,F$16)</f>
+        <f t="shared" si="27"/>
         <v>16505</v>
       </c>
       <c r="G22" s="52">
-        <f>SUMIFS(ventas_unidades,ventas_vendedor,$A22,ventas_producto,G$16)</f>
+        <f t="shared" si="27"/>
         <v>25030</v>
       </c>
       <c r="H22" s="52">
-        <f>SUMIFS(ventas_unidades,ventas_vendedor,$A22,ventas_producto,H$16)</f>
+        <f t="shared" si="27"/>
         <v>5584</v>
       </c>
       <c r="I22" s="52">
-        <f>SUMIFS(ventas_unidades,ventas_vendedor,$A22,ventas_producto,I$16)</f>
+        <f t="shared" si="27"/>
         <v>41415</v>
       </c>
       <c r="J22" s="52">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>99994</v>
       </c>
       <c r="L22" s="102">
-        <f>SUMIFS(ventas_total,ventas_vendedor,$A22,ventas_producto,L$16)</f>
+        <f t="shared" si="28"/>
         <v>49438827</v>
       </c>
       <c r="M22" s="58">
-        <f>SUMIFS(ventas_total,ventas_vendedor,$A22,ventas_producto,M$16)</f>
+        <f t="shared" si="28"/>
         <v>50806730</v>
       </c>
       <c r="N22" s="58">
-        <f>SUMIFS(ventas_total,ventas_vendedor,$A22,ventas_producto,N$16)</f>
+        <f t="shared" si="28"/>
         <v>167729464</v>
       </c>
       <c r="O22" s="58">
-        <f>SUMIFS(ventas_total,ventas_vendedor,$A22,ventas_producto,O$16)</f>
+        <f t="shared" si="28"/>
         <v>17788927</v>
       </c>
       <c r="P22" s="58">
-        <f>SUMIFS(ventas_total,ventas_vendedor,$A22,ventas_producto,P$16)</f>
+        <f t="shared" si="28"/>
         <v>276189776</v>
       </c>
       <c r="Q22" s="58">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>561953724</v>
       </c>
       <c r="S22" s="94"/>
@@ -8009,51 +8009,51 @@
       <c r="AF22" s="68"/>
       <c r="AG22" s="68"/>
       <c r="AI22" s="83">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>8851</v>
       </c>
       <c r="AJ22" s="18">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>16505</v>
       </c>
       <c r="AK22" s="18">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>27768</v>
       </c>
       <c r="AL22" s="18">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>7382</v>
       </c>
       <c r="AM22" s="18">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>39488</v>
       </c>
       <c r="AN22" s="18">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>99994</v>
       </c>
       <c r="AP22" s="98">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>49797905</v>
       </c>
       <c r="AQ22" s="60">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>50806730</v>
       </c>
       <c r="AR22" s="60">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>168574296</v>
       </c>
       <c r="AS22" s="60">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>17133409</v>
       </c>
       <c r="AT22" s="60">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>275641384</v>
       </c>
       <c r="AU22" s="60">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>561953724</v>
       </c>
     </row>
@@ -8074,23 +8074,23 @@
         <v>110903</v>
       </c>
       <c r="F23" s="51">
-        <f t="shared" ref="F23:J23" si="33">SUM(F17:F22)</f>
+        <f t="shared" ref="F23:J23" si="35">SUM(F17:F22)</f>
         <v>304519</v>
       </c>
       <c r="G23" s="51">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>118380</v>
       </c>
       <c r="H23" s="51">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>115644</v>
       </c>
       <c r="I23" s="51">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>208781</v>
       </c>
       <c r="J23" s="118">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>858227</v>
       </c>
       <c r="L23" s="109">
@@ -8098,23 +8098,23 @@
         <v>650543568</v>
       </c>
       <c r="M23" s="69">
-        <f t="shared" ref="M23:Q23" si="34">SUM(M17:M22)</f>
+        <f t="shared" ref="M23:Q23" si="36">SUM(M17:M22)</f>
         <v>578124392</v>
       </c>
       <c r="N23" s="69">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>690157736</v>
       </c>
       <c r="O23" s="69">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>654943915</v>
       </c>
       <c r="P23" s="69">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>656247934</v>
       </c>
       <c r="Q23" s="115">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>3230017545</v>
       </c>
       <c r="S23" s="94"/>
@@ -8136,23 +8136,23 @@
         <v>110109</v>
       </c>
       <c r="AJ23" s="51">
-        <f t="shared" ref="AJ23:AN23" si="35">SUM(AJ17:AJ22)</f>
+        <f t="shared" ref="AJ23:AN23" si="37">SUM(AJ17:AJ22)</f>
         <v>213260</v>
       </c>
       <c r="AK23" s="51">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>116030</v>
       </c>
       <c r="AL23" s="51">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>312792</v>
       </c>
       <c r="AM23" s="51">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>106036</v>
       </c>
       <c r="AN23" s="118">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>858227</v>
       </c>
       <c r="AP23" s="109">
@@ -8160,23 +8160,23 @@
         <v>646106962</v>
       </c>
       <c r="AQ23" s="69">
-        <f t="shared" ref="AQ23" si="36">SUM(AQ17:AQ22)</f>
+        <f t="shared" ref="AQ23" si="38">SUM(AQ17:AQ22)</f>
         <v>576804336</v>
       </c>
       <c r="AR23" s="69">
-        <f t="shared" ref="AR23" si="37">SUM(AR17:AR22)</f>
+        <f t="shared" ref="AR23" si="39">SUM(AR17:AR22)</f>
         <v>687706530</v>
       </c>
       <c r="AS23" s="69">
-        <f t="shared" ref="AS23" si="38">SUM(AS17:AS22)</f>
+        <f t="shared" ref="AS23" si="40">SUM(AS17:AS22)</f>
         <v>654677692</v>
       </c>
       <c r="AT23" s="69">
-        <f t="shared" ref="AT23" si="39">SUM(AT17:AT22)</f>
+        <f t="shared" ref="AT23" si="41">SUM(AT17:AT22)</f>
         <v>664722025</v>
       </c>
       <c r="AU23" s="115">
-        <f t="shared" ref="AU23" si="40">SUM(AU17:AU22)</f>
+        <f t="shared" ref="AU23" si="42">SUM(AU17:AU22)</f>
         <v>3230017545</v>
       </c>
     </row>
@@ -8295,23 +8295,23 @@
         <v>646106962</v>
       </c>
       <c r="E26" s="82">
-        <f>SUMIFS(ventas_unidades,ventas_region,$A26,ventas_producto,E$25)</f>
+        <f t="shared" ref="E26:I30" si="43">SUMIFS(ventas_unidades,ventas_region,$A26,ventas_producto,E$25)</f>
         <v>101037</v>
       </c>
       <c r="F26" s="17">
-        <f>SUMIFS(ventas_unidades,ventas_region,$A26,ventas_producto,F$25)</f>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="G26" s="17">
-        <f>SUMIFS(ventas_unidades,ventas_region,$A26,ventas_producto,G$25)</f>
+        <f t="shared" si="43"/>
         <v>8943</v>
       </c>
       <c r="H26" s="17">
-        <f>SUMIFS(ventas_unidades,ventas_region,$A26,ventas_producto,H$25)</f>
+        <f t="shared" si="43"/>
         <v>129</v>
       </c>
       <c r="I26" s="17">
-        <f>SUMIFS(ventas_unidades,ventas_region,$A26,ventas_producto,I$25)</f>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="J26" s="17">
@@ -8319,23 +8319,23 @@
         <v>858227</v>
       </c>
       <c r="L26" s="97">
-        <f>SUMIFS(ventas_total,ventas_region,$A26,ventas_producto,L$25)</f>
+        <f t="shared" ref="L26:P30" si="44">SUMIFS(ventas_total,ventas_region,$A26,ventas_producto,L$25)</f>
         <v>640574818</v>
       </c>
       <c r="M26" s="59">
-        <f>SUMIFS(ventas_total,ventas_region,$A26,ventas_producto,M$25)</f>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="N26" s="59">
-        <f>SUMIFS(ventas_total,ventas_region,$A26,ventas_producto,N$25)</f>
+        <f t="shared" si="44"/>
         <v>4328234</v>
       </c>
       <c r="O26" s="59">
-        <f>SUMIFS(ventas_total,ventas_region,$A26,ventas_producto,O$25)</f>
+        <f t="shared" si="44"/>
         <v>1203910</v>
       </c>
       <c r="P26" s="59">
-        <f>SUMIFS(ventas_total,ventas_region,$A26,ventas_producto,P$25)</f>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="Q26" s="59">
@@ -8343,27 +8343,27 @@
         <v>646106962</v>
       </c>
       <c r="S26" s="82">
-        <f t="shared" ref="S26:X30" si="41">SUMIFS(ventas_unidades,ventas_region,$A26,ventas_vendedor,S$25)</f>
+        <f t="shared" ref="S26:X30" si="45">SUMIFS(ventas_unidades,ventas_region,$A26,ventas_vendedor,S$25)</f>
         <v>23075</v>
       </c>
       <c r="T26" s="29">
-        <f t="shared" si="41"/>
+        <f t="shared" si="45"/>
         <v>27346</v>
       </c>
       <c r="U26" s="29">
-        <f t="shared" si="41"/>
+        <f t="shared" si="45"/>
         <v>9125</v>
       </c>
       <c r="V26" s="17">
-        <f t="shared" si="41"/>
+        <f t="shared" si="45"/>
         <v>30665</v>
       </c>
       <c r="W26" s="29">
-        <f t="shared" si="41"/>
+        <f t="shared" si="45"/>
         <v>11047</v>
       </c>
       <c r="X26" s="29">
-        <f t="shared" si="41"/>
+        <f t="shared" si="45"/>
         <v>8851</v>
       </c>
       <c r="Y26" s="17">
@@ -8371,27 +8371,27 @@
         <v>110109</v>
       </c>
       <c r="AA26" s="97">
-        <f t="shared" ref="AA26:AF30" si="42">SUMIFS(ventas_total,ventas_region,$A26,ventas_vendedor,AA$25)</f>
+        <f t="shared" ref="AA26:AF30" si="46">SUMIFS(ventas_total,ventas_region,$A26,ventas_vendedor,AA$25)</f>
         <v>109144041</v>
       </c>
       <c r="AB26" s="64">
-        <f t="shared" si="42"/>
+        <f t="shared" si="46"/>
         <v>193222871</v>
       </c>
       <c r="AC26" s="64">
-        <f t="shared" si="42"/>
+        <f t="shared" si="46"/>
         <v>59797810</v>
       </c>
       <c r="AD26" s="59">
-        <f t="shared" si="42"/>
+        <f t="shared" si="46"/>
         <v>139608342</v>
       </c>
       <c r="AE26" s="64">
-        <f t="shared" si="42"/>
+        <f t="shared" si="46"/>
         <v>94535993</v>
       </c>
       <c r="AF26" s="64">
-        <f t="shared" si="42"/>
+        <f t="shared" si="46"/>
         <v>49797905</v>
       </c>
       <c r="AG26" s="59">
@@ -8424,107 +8424,107 @@
         <v>576804336</v>
       </c>
       <c r="E27" s="83">
-        <f>SUMIFS(ventas_unidades,ventas_region,$A27,ventas_producto,E$25)</f>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="F27" s="18">
-        <f>SUMIFS(ventas_unidades,ventas_region,$A27,ventas_producto,F$25)</f>
+        <f t="shared" si="43"/>
         <v>105314</v>
       </c>
       <c r="G27" s="18">
-        <f>SUMIFS(ventas_unidades,ventas_region,$A27,ventas_producto,G$25)</f>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="H27" s="18">
-        <f>SUMIFS(ventas_unidades,ventas_region,$A27,ventas_producto,H$25)</f>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="I27" s="18">
-        <f>SUMIFS(ventas_unidades,ventas_region,$A27,ventas_producto,I$25)</f>
+        <f t="shared" si="43"/>
         <v>107946</v>
       </c>
       <c r="J27" s="18">
-        <f t="shared" ref="J27:J30" si="43">SUM(E27:I31)</f>
+        <f t="shared" ref="J27:J30" si="47">SUM(E27:I31)</f>
         <v>1606345</v>
       </c>
       <c r="L27" s="98">
-        <f>SUMIFS(ventas_total,ventas_region,$A27,ventas_producto,L$25)</f>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="M27" s="60">
-        <f>SUMIFS(ventas_total,ventas_region,$A27,ventas_producto,M$25)</f>
+        <f t="shared" si="44"/>
         <v>576702901</v>
       </c>
       <c r="N27" s="60">
-        <f>SUMIFS(ventas_total,ventas_region,$A27,ventas_producto,N$25)</f>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="O27" s="60">
-        <f>SUMIFS(ventas_total,ventas_region,$A27,ventas_producto,O$25)</f>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="P27" s="60">
-        <f>SUMIFS(ventas_total,ventas_region,$A27,ventas_producto,P$25)</f>
+        <f t="shared" si="44"/>
         <v>101435</v>
       </c>
       <c r="Q27" s="60">
-        <f t="shared" ref="Q27:Q30" si="44">SUM(L27:P27)</f>
+        <f t="shared" ref="Q27:Q30" si="48">SUM(L27:P27)</f>
         <v>576804336</v>
       </c>
       <c r="S27" s="91">
-        <f t="shared" si="41"/>
+        <f t="shared" si="45"/>
         <v>7195</v>
       </c>
       <c r="T27" s="30">
-        <f t="shared" si="41"/>
+        <f t="shared" si="45"/>
         <v>51553</v>
       </c>
       <c r="U27" s="30">
-        <f t="shared" si="41"/>
+        <f t="shared" si="45"/>
         <v>9023</v>
       </c>
       <c r="V27" s="30">
-        <f t="shared" si="41"/>
+        <f t="shared" si="45"/>
         <v>103585</v>
       </c>
       <c r="W27" s="30">
-        <f t="shared" si="41"/>
+        <f t="shared" si="45"/>
         <v>25399</v>
       </c>
       <c r="X27" s="30">
-        <f t="shared" si="41"/>
+        <f t="shared" si="45"/>
         <v>16505</v>
       </c>
       <c r="Y27" s="30">
-        <f t="shared" ref="Y27:Y30" si="45">SUM(S27:X27)</f>
+        <f t="shared" ref="Y27:Y30" si="49">SUM(S27:X27)</f>
         <v>213260</v>
       </c>
       <c r="AA27" s="105">
-        <f t="shared" si="42"/>
+        <f t="shared" si="46"/>
         <v>52631529</v>
       </c>
       <c r="AB27" s="65">
-        <f t="shared" si="42"/>
+        <f t="shared" si="46"/>
         <v>271532147</v>
       </c>
       <c r="AC27" s="65">
-        <f t="shared" si="42"/>
+        <f t="shared" si="46"/>
         <v>63246530</v>
       </c>
       <c r="AD27" s="65">
-        <f t="shared" si="42"/>
+        <f t="shared" si="46"/>
         <v>44964557</v>
       </c>
       <c r="AE27" s="65">
-        <f t="shared" si="42"/>
+        <f t="shared" si="46"/>
         <v>93622843</v>
       </c>
       <c r="AF27" s="65">
-        <f t="shared" si="42"/>
+        <f t="shared" si="46"/>
         <v>50806730</v>
       </c>
       <c r="AG27" s="65">
-        <f t="shared" ref="AG27:AG30" si="46">SUM(AA27:AF27)</f>
+        <f t="shared" ref="AG27:AG30" si="50">SUM(AA27:AF27)</f>
         <v>576804336</v>
       </c>
       <c r="AI27" s="94"/>
@@ -8553,107 +8553,107 @@
         <v>687706530</v>
       </c>
       <c r="E28" s="84">
-        <f>SUMIFS(ventas_unidades,ventas_region,$A28,ventas_producto,E$25)</f>
+        <f t="shared" si="43"/>
         <v>2738</v>
       </c>
       <c r="F28" s="19">
-        <f>SUMIFS(ventas_unidades,ventas_region,$A28,ventas_producto,F$25)</f>
+        <f t="shared" si="43"/>
         <v>1928</v>
       </c>
       <c r="G28" s="19">
-        <f>SUMIFS(ventas_unidades,ventas_region,$A28,ventas_producto,G$25)</f>
+        <f t="shared" si="43"/>
         <v>109437</v>
       </c>
       <c r="H28" s="19">
-        <f>SUMIFS(ventas_unidades,ventas_region,$A28,ventas_producto,H$25)</f>
+        <f t="shared" si="43"/>
         <v>1927</v>
       </c>
       <c r="I28" s="19">
-        <f>SUMIFS(ventas_unidades,ventas_region,$A28,ventas_producto,I$25)</f>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="J28" s="19">
-        <f t="shared" si="43"/>
+        <f t="shared" si="47"/>
         <v>1393085</v>
       </c>
       <c r="L28" s="99">
-        <f>SUMIFS(ventas_total,ventas_region,$A28,ventas_producto,L$25)</f>
+        <f t="shared" si="44"/>
         <v>844832</v>
       </c>
       <c r="M28" s="61">
-        <f>SUMIFS(ventas_total,ventas_region,$A28,ventas_producto,M$25)</f>
+        <f t="shared" si="44"/>
         <v>108214</v>
       </c>
       <c r="N28" s="61">
-        <f>SUMIFS(ventas_total,ventas_region,$A28,ventas_producto,N$25)</f>
+        <f t="shared" si="44"/>
         <v>685829502</v>
       </c>
       <c r="O28" s="61">
-        <f>SUMIFS(ventas_total,ventas_region,$A28,ventas_producto,O$25)</f>
+        <f t="shared" si="44"/>
         <v>923982</v>
       </c>
       <c r="P28" s="61">
-        <f>SUMIFS(ventas_total,ventas_region,$A28,ventas_producto,P$25)</f>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="Q28" s="61">
-        <f t="shared" si="44"/>
+        <f t="shared" si="48"/>
         <v>687706530</v>
       </c>
       <c r="S28" s="92">
-        <f t="shared" si="41"/>
+        <f t="shared" si="45"/>
         <v>39170</v>
       </c>
       <c r="T28" s="31">
-        <f t="shared" si="41"/>
+        <f t="shared" si="45"/>
         <v>19565</v>
       </c>
       <c r="U28" s="31">
-        <f t="shared" si="41"/>
+        <f t="shared" si="45"/>
         <v>6969</v>
       </c>
       <c r="V28" s="31">
-        <f t="shared" si="41"/>
+        <f t="shared" si="45"/>
         <v>9925</v>
       </c>
       <c r="W28" s="31">
-        <f t="shared" si="41"/>
+        <f t="shared" si="45"/>
         <v>12633</v>
       </c>
       <c r="X28" s="31">
-        <f t="shared" si="41"/>
+        <f t="shared" si="45"/>
         <v>27768</v>
       </c>
       <c r="Y28" s="31">
-        <f t="shared" si="45"/>
+        <f t="shared" si="49"/>
         <v>116030</v>
       </c>
       <c r="AA28" s="106">
-        <f t="shared" si="42"/>
+        <f t="shared" si="46"/>
         <v>240927099</v>
       </c>
       <c r="AB28" s="66">
-        <f t="shared" si="42"/>
+        <f t="shared" si="46"/>
         <v>131950052</v>
       </c>
       <c r="AC28" s="66">
-        <f t="shared" si="42"/>
+        <f t="shared" si="46"/>
         <v>40433106</v>
       </c>
       <c r="AD28" s="66">
-        <f t="shared" si="42"/>
+        <f t="shared" si="46"/>
         <v>27153333</v>
       </c>
       <c r="AE28" s="66">
-        <f t="shared" si="42"/>
+        <f t="shared" si="46"/>
         <v>78668644</v>
       </c>
       <c r="AF28" s="66">
-        <f t="shared" si="42"/>
+        <f t="shared" si="46"/>
         <v>168574296</v>
       </c>
       <c r="AG28" s="66">
-        <f t="shared" si="46"/>
+        <f t="shared" si="50"/>
         <v>687706530</v>
       </c>
       <c r="AI28" s="94"/>
@@ -8682,107 +8682,107 @@
         <v>654677692</v>
       </c>
       <c r="E29" s="83">
-        <f>SUMIFS(ventas_unidades,ventas_region,$A29,ventas_producto,E$25)</f>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="F29" s="18">
-        <f>SUMIFS(ventas_unidades,ventas_region,$A29,ventas_producto,F$25)</f>
+        <f t="shared" si="43"/>
         <v>197277</v>
       </c>
       <c r="G29" s="18">
-        <f>SUMIFS(ventas_unidades,ventas_region,$A29,ventas_producto,G$25)</f>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="H29" s="18">
-        <f>SUMIFS(ventas_unidades,ventas_region,$A29,ventas_producto,H$25)</f>
+        <f t="shared" si="43"/>
         <v>113588</v>
       </c>
       <c r="I29" s="18">
-        <f>SUMIFS(ventas_unidades,ventas_region,$A29,ventas_producto,I$25)</f>
+        <f t="shared" si="43"/>
         <v>1927</v>
       </c>
       <c r="J29" s="18">
-        <f t="shared" si="43"/>
+        <f t="shared" si="47"/>
         <v>1277055</v>
       </c>
       <c r="L29" s="98">
-        <f>SUMIFS(ventas_total,ventas_region,$A29,ventas_producto,L$25)</f>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="M29" s="60">
-        <f>SUMIFS(ventas_total,ventas_region,$A29,ventas_producto,M$25)</f>
+        <f t="shared" si="44"/>
         <v>1313277</v>
       </c>
       <c r="N29" s="60">
-        <f>SUMIFS(ventas_total,ventas_region,$A29,ventas_producto,N$25)</f>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="O29" s="60">
-        <f>SUMIFS(ventas_total,ventas_region,$A29,ventas_producto,O$25)</f>
+        <f t="shared" si="44"/>
         <v>652816023</v>
       </c>
       <c r="P29" s="60">
-        <f>SUMIFS(ventas_total,ventas_region,$A29,ventas_producto,P$25)</f>
+        <f t="shared" si="44"/>
         <v>548392</v>
       </c>
       <c r="Q29" s="60">
-        <f t="shared" si="44"/>
+        <f t="shared" si="48"/>
         <v>654677692</v>
       </c>
       <c r="S29" s="91">
-        <f t="shared" si="41"/>
+        <f t="shared" si="45"/>
         <v>39255</v>
       </c>
       <c r="T29" s="30">
-        <f t="shared" si="41"/>
+        <f t="shared" si="45"/>
         <v>12991</v>
       </c>
       <c r="U29" s="30">
-        <f t="shared" si="41"/>
+        <f t="shared" si="45"/>
         <v>2096</v>
       </c>
       <c r="V29" s="30">
-        <f t="shared" si="41"/>
+        <f t="shared" si="45"/>
         <v>197831</v>
       </c>
       <c r="W29" s="30">
-        <f t="shared" si="41"/>
+        <f t="shared" si="45"/>
         <v>53237</v>
       </c>
       <c r="X29" s="30">
-        <f t="shared" si="41"/>
+        <f t="shared" si="45"/>
         <v>7382</v>
       </c>
       <c r="Y29" s="30">
-        <f t="shared" si="45"/>
+        <f t="shared" si="49"/>
         <v>312792</v>
       </c>
       <c r="AA29" s="105">
-        <f t="shared" si="42"/>
+        <f t="shared" si="46"/>
         <v>170461858</v>
       </c>
       <c r="AB29" s="65">
-        <f t="shared" si="42"/>
+        <f t="shared" si="46"/>
         <v>75839132</v>
       </c>
       <c r="AC29" s="65">
-        <f t="shared" si="42"/>
+        <f t="shared" si="46"/>
         <v>31378227</v>
       </c>
       <c r="AD29" s="65">
-        <f t="shared" si="42"/>
+        <f t="shared" si="46"/>
         <v>23830600</v>
       </c>
       <c r="AE29" s="65">
-        <f t="shared" si="42"/>
+        <f t="shared" si="46"/>
         <v>336034466</v>
       </c>
       <c r="AF29" s="65">
-        <f t="shared" si="42"/>
+        <f t="shared" si="46"/>
         <v>17133409</v>
       </c>
       <c r="AG29" s="65">
-        <f t="shared" si="46"/>
+        <f t="shared" si="50"/>
         <v>654677692</v>
       </c>
       <c r="AI29" s="94"/>
@@ -8811,107 +8811,107 @@
         <v>664722025</v>
       </c>
       <c r="E30" s="84">
-        <f>SUMIFS(ventas_unidades,ventas_region,$A30,ventas_producto,E$25)</f>
+        <f t="shared" si="43"/>
         <v>7128</v>
       </c>
       <c r="F30" s="19">
-        <f>SUMIFS(ventas_unidades,ventas_region,$A30,ventas_producto,F$25)</f>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="G30" s="19">
-        <f>SUMIFS(ventas_unidades,ventas_region,$A30,ventas_producto,G$25)</f>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="H30" s="19">
-        <f>SUMIFS(ventas_unidades,ventas_region,$A30,ventas_producto,H$25)</f>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="I30" s="19">
-        <f>SUMIFS(ventas_unidades,ventas_region,$A30,ventas_producto,I$25)</f>
+        <f t="shared" si="43"/>
         <v>98908</v>
       </c>
       <c r="J30" s="19">
-        <f t="shared" si="43"/>
+        <f t="shared" si="47"/>
         <v>1146245</v>
       </c>
       <c r="L30" s="99">
-        <f>SUMIFS(ventas_total,ventas_region,$A30,ventas_producto,L$25)</f>
+        <f t="shared" si="44"/>
         <v>9123918</v>
       </c>
       <c r="M30" s="61">
-        <f>SUMIFS(ventas_total,ventas_region,$A30,ventas_producto,M$25)</f>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="N30" s="61">
-        <f>SUMIFS(ventas_total,ventas_region,$A30,ventas_producto,N$25)</f>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="O30" s="61">
-        <f>SUMIFS(ventas_total,ventas_region,$A30,ventas_producto,O$25)</f>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="P30" s="61">
-        <f>SUMIFS(ventas_total,ventas_region,$A30,ventas_producto,P$25)</f>
+        <f t="shared" si="44"/>
         <v>655598107</v>
       </c>
       <c r="Q30" s="61">
-        <f t="shared" si="44"/>
+        <f t="shared" si="48"/>
         <v>664722025</v>
       </c>
       <c r="S30" s="92">
-        <f t="shared" si="41"/>
+        <f t="shared" si="45"/>
         <v>12970</v>
       </c>
       <c r="T30" s="31">
-        <f t="shared" si="41"/>
+        <f t="shared" si="45"/>
         <v>14165</v>
       </c>
       <c r="U30" s="31">
-        <f t="shared" si="41"/>
+        <f t="shared" si="45"/>
         <v>5143</v>
       </c>
       <c r="V30" s="31">
-        <f t="shared" si="41"/>
+        <f t="shared" si="45"/>
         <v>14291</v>
       </c>
       <c r="W30" s="31">
-        <f t="shared" si="41"/>
+        <f t="shared" si="45"/>
         <v>19979</v>
       </c>
       <c r="X30" s="31">
-        <f t="shared" si="41"/>
+        <f t="shared" si="45"/>
         <v>39488</v>
       </c>
       <c r="Y30" s="31">
-        <f t="shared" si="45"/>
+        <f t="shared" si="49"/>
         <v>106036</v>
       </c>
       <c r="AA30" s="106">
-        <f t="shared" si="42"/>
+        <f t="shared" si="46"/>
         <v>71950539</v>
       </c>
       <c r="AB30" s="66">
-        <f t="shared" si="42"/>
+        <f t="shared" si="46"/>
         <v>88920515</v>
       </c>
       <c r="AC30" s="66">
-        <f t="shared" si="42"/>
+        <f t="shared" si="46"/>
         <v>31867112</v>
       </c>
       <c r="AD30" s="66">
-        <f t="shared" si="42"/>
+        <f t="shared" si="46"/>
         <v>76700859</v>
       </c>
       <c r="AE30" s="66">
-        <f t="shared" si="42"/>
+        <f t="shared" si="46"/>
         <v>119641616</v>
       </c>
       <c r="AF30" s="66">
-        <f t="shared" si="42"/>
+        <f t="shared" si="46"/>
         <v>275641384</v>
       </c>
       <c r="AG30" s="66">
-        <f t="shared" si="46"/>
+        <f t="shared" si="50"/>
         <v>664722025</v>
       </c>
       <c r="AI30" s="94"/>
@@ -8944,23 +8944,23 @@
         <v>110903</v>
       </c>
       <c r="F31" s="51">
-        <f t="shared" ref="F31:J31" si="47">SUM(F26:F30)</f>
+        <f t="shared" ref="F31:J31" si="51">SUM(F26:F30)</f>
         <v>304519</v>
       </c>
       <c r="G31" s="51">
-        <f t="shared" si="47"/>
+        <f t="shared" si="51"/>
         <v>118380</v>
       </c>
       <c r="H31" s="51">
-        <f t="shared" si="47"/>
+        <f t="shared" si="51"/>
         <v>115644</v>
       </c>
       <c r="I31" s="51">
-        <f t="shared" si="47"/>
+        <f t="shared" si="51"/>
         <v>208781</v>
       </c>
       <c r="J31" s="118">
-        <f t="shared" si="47"/>
+        <f t="shared" si="51"/>
         <v>6280957</v>
       </c>
       <c r="L31" s="109">
@@ -8968,23 +8968,23 @@
         <v>650543568</v>
       </c>
       <c r="M31" s="69">
-        <f t="shared" ref="M31" si="48">SUM(M26:M30)</f>
+        <f t="shared" ref="M31" si="52">SUM(M26:M30)</f>
         <v>578124392</v>
       </c>
       <c r="N31" s="69">
-        <f t="shared" ref="N31" si="49">SUM(N26:N30)</f>
+        <f t="shared" ref="N31" si="53">SUM(N26:N30)</f>
         <v>690157736</v>
       </c>
       <c r="O31" s="69">
-        <f t="shared" ref="O31" si="50">SUM(O26:O30)</f>
+        <f t="shared" ref="O31" si="54">SUM(O26:O30)</f>
         <v>654943915</v>
       </c>
       <c r="P31" s="69">
-        <f t="shared" ref="P31" si="51">SUM(P26:P30)</f>
+        <f t="shared" ref="P31" si="55">SUM(P26:P30)</f>
         <v>656247934</v>
       </c>
       <c r="Q31" s="115">
-        <f t="shared" ref="Q31" si="52">SUM(Q26:Q30)</f>
+        <f t="shared" ref="Q31" si="56">SUM(Q26:Q30)</f>
         <v>3230017545</v>
       </c>
       <c r="S31" s="93">
@@ -8992,27 +8992,27 @@
         <v>121665</v>
       </c>
       <c r="T31" s="40">
-        <f t="shared" ref="T31:Y31" si="53">SUM(T26:T30)</f>
+        <f t="shared" ref="T31:Y31" si="57">SUM(T26:T30)</f>
         <v>125620</v>
       </c>
       <c r="U31" s="40">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v>32356</v>
       </c>
       <c r="V31" s="40">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v>356297</v>
       </c>
       <c r="W31" s="40">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v>122295</v>
       </c>
       <c r="X31" s="40">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v>99994</v>
       </c>
       <c r="Y31" s="40">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v>858227</v>
       </c>
       <c r="AA31" s="107">
@@ -9020,27 +9020,27 @@
         <v>645115066</v>
       </c>
       <c r="AB31" s="67">
-        <f t="shared" ref="AB31" si="54">SUM(AB26:AB30)</f>
+        <f t="shared" ref="AB31" si="58">SUM(AB26:AB30)</f>
         <v>761464717</v>
       </c>
       <c r="AC31" s="67">
-        <f t="shared" ref="AC31" si="55">SUM(AC26:AC30)</f>
+        <f t="shared" ref="AC31" si="59">SUM(AC26:AC30)</f>
         <v>226722785</v>
       </c>
       <c r="AD31" s="67">
-        <f t="shared" ref="AD31" si="56">SUM(AD26:AD30)</f>
+        <f t="shared" ref="AD31" si="60">SUM(AD26:AD30)</f>
         <v>312257691</v>
       </c>
       <c r="AE31" s="67">
-        <f t="shared" ref="AE31" si="57">SUM(AE26:AE30)</f>
+        <f t="shared" ref="AE31" si="61">SUM(AE26:AE30)</f>
         <v>722503562</v>
       </c>
       <c r="AF31" s="67">
-        <f t="shared" ref="AF31" si="58">SUM(AF26:AF30)</f>
+        <f t="shared" ref="AF31" si="62">SUM(AF26:AF30)</f>
         <v>561953724</v>
       </c>
       <c r="AG31" s="115">
-        <f t="shared" ref="AG31" si="59">SUM(AG26:AG30)</f>
+        <f t="shared" ref="AG31" si="63">SUM(AG26:AG30)</f>
         <v>3230017545</v>
       </c>
       <c r="AI31" s="94"/>
@@ -9195,23 +9195,23 @@
         <v>1007244151</v>
       </c>
       <c r="E34" s="82">
-        <f>SUMIFS(ventas_unidades,ventas_año,$A34,ventas_producto,E$25)</f>
+        <f t="shared" ref="E34:I38" si="64">SUMIFS(ventas_unidades,ventas_año,$A34,ventas_producto,E$25)</f>
         <v>33032</v>
       </c>
       <c r="F34" s="17">
-        <f>SUMIFS(ventas_unidades,ventas_año,$A34,ventas_producto,F$25)</f>
+        <f t="shared" si="64"/>
         <v>32696</v>
       </c>
       <c r="G34" s="17">
-        <f>SUMIFS(ventas_unidades,ventas_año,$A34,ventas_producto,G$25)</f>
+        <f t="shared" si="64"/>
         <v>39124</v>
       </c>
       <c r="H34" s="17">
-        <f>SUMIFS(ventas_unidades,ventas_año,$A34,ventas_producto,H$25)</f>
+        <f t="shared" si="64"/>
         <v>40573</v>
       </c>
       <c r="I34" s="17">
-        <f>SUMIFS(ventas_unidades,ventas_año,$A34,ventas_producto,I$25)</f>
+        <f t="shared" si="64"/>
         <v>36557</v>
       </c>
       <c r="J34" s="17">
@@ -9219,23 +9219,23 @@
         <v>858227</v>
       </c>
       <c r="L34" s="97">
-        <f>SUMIFS(ventas_total,ventas_año,$A34,ventas_producto,L$25)</f>
+        <f t="shared" ref="L34:P38" si="65">SUMIFS(ventas_total,ventas_año,$A34,ventas_producto,L$25)</f>
         <v>218669111</v>
       </c>
       <c r="M34" s="59">
-        <f>SUMIFS(ventas_total,ventas_año,$A34,ventas_producto,M$25)</f>
+        <f t="shared" si="65"/>
         <v>160364763</v>
       </c>
       <c r="N34" s="59">
-        <f>SUMIFS(ventas_total,ventas_año,$A34,ventas_producto,N$25)</f>
+        <f t="shared" si="65"/>
         <v>220801841</v>
       </c>
       <c r="O34" s="59">
-        <f>SUMIFS(ventas_total,ventas_año,$A34,ventas_producto,O$25)</f>
+        <f t="shared" si="65"/>
         <v>190929354</v>
       </c>
       <c r="P34" s="59">
-        <f>SUMIFS(ventas_total,ventas_año,$A34,ventas_producto,P$25)</f>
+        <f t="shared" si="65"/>
         <v>216479082</v>
       </c>
       <c r="Q34" s="59">
@@ -9243,27 +9243,27 @@
         <v>1007244151</v>
       </c>
       <c r="S34" s="90">
-        <f t="shared" ref="S34:X38" si="60">SUMIFS(ventas_unidades,ventas_año,$A34,ventas_vendedor,S$33)</f>
+        <f t="shared" ref="S34:X38" si="66">SUMIFS(ventas_unidades,ventas_año,$A34,ventas_vendedor,S$33)</f>
         <v>33623</v>
       </c>
       <c r="T34" s="29">
-        <f t="shared" si="60"/>
+        <f t="shared" si="66"/>
         <v>45235</v>
       </c>
       <c r="U34" s="29">
-        <f t="shared" si="60"/>
+        <f t="shared" si="66"/>
         <v>12423</v>
       </c>
       <c r="V34" s="29">
-        <f t="shared" si="60"/>
+        <f t="shared" si="66"/>
         <v>20990</v>
       </c>
       <c r="W34" s="29">
-        <f t="shared" si="60"/>
+        <f t="shared" si="66"/>
         <v>44558</v>
       </c>
       <c r="X34" s="29">
-        <f t="shared" si="60"/>
+        <f t="shared" si="66"/>
         <v>25153</v>
       </c>
       <c r="Y34" s="29">
@@ -9271,27 +9271,27 @@
         <v>181982</v>
       </c>
       <c r="AA34" s="104">
-        <f t="shared" ref="AA34:AF38" si="61">SUMIFS(ventas_unidades,ventas_año,$A34,ventas_vendedor,AA$33)</f>
+        <f t="shared" ref="AA34:AF38" si="67">SUMIFS(ventas_unidades,ventas_año,$A34,ventas_vendedor,AA$33)</f>
         <v>33623</v>
       </c>
       <c r="AB34" s="64">
-        <f t="shared" si="61"/>
+        <f t="shared" si="67"/>
         <v>45235</v>
       </c>
       <c r="AC34" s="64">
-        <f t="shared" si="61"/>
+        <f t="shared" si="67"/>
         <v>12423</v>
       </c>
       <c r="AD34" s="64">
-        <f t="shared" si="61"/>
+        <f t="shared" si="67"/>
         <v>20990</v>
       </c>
       <c r="AE34" s="64">
-        <f t="shared" si="61"/>
+        <f t="shared" si="67"/>
         <v>44558</v>
       </c>
       <c r="AF34" s="64">
-        <f t="shared" si="61"/>
+        <f t="shared" si="67"/>
         <v>25153</v>
       </c>
       <c r="AG34" s="64">
@@ -9299,23 +9299,23 @@
         <v>181982</v>
       </c>
       <c r="AI34" s="82">
-        <f t="shared" ref="AI34:AM38" si="62">SUMIFS(ventas_unidades,ventas_año,$A34,ventas_region,AI$33)</f>
+        <f t="shared" ref="AI34:AM38" si="68">SUMIFS(ventas_unidades,ventas_año,$A34,ventas_region,AI$33)</f>
         <v>33032</v>
       </c>
       <c r="AJ34" s="17">
-        <f t="shared" si="62"/>
+        <f t="shared" si="68"/>
         <v>32696</v>
       </c>
       <c r="AK34" s="17">
-        <f t="shared" si="62"/>
+        <f t="shared" si="68"/>
         <v>39124</v>
       </c>
       <c r="AL34" s="17">
-        <f t="shared" si="62"/>
+        <f t="shared" si="68"/>
         <v>40573</v>
       </c>
       <c r="AM34" s="17">
-        <f t="shared" si="62"/>
+        <f t="shared" si="68"/>
         <v>36557</v>
       </c>
       <c r="AN34" s="17">
@@ -9323,23 +9323,23 @@
         <v>181982</v>
       </c>
       <c r="AP34" s="111">
-        <f t="shared" ref="AP34:AT38" si="63">SUMIFS(ventas_total,ventas_año,$A34,ventas_region,AP$33)</f>
+        <f t="shared" ref="AP34:AT38" si="69">SUMIFS(ventas_total,ventas_año,$A34,ventas_region,AP$33)</f>
         <v>218669111</v>
       </c>
       <c r="AQ34" s="41">
-        <f t="shared" si="63"/>
+        <f t="shared" si="69"/>
         <v>160364763</v>
       </c>
       <c r="AR34" s="41">
-        <f t="shared" si="63"/>
+        <f t="shared" si="69"/>
         <v>220801841</v>
       </c>
       <c r="AS34" s="41">
-        <f t="shared" si="63"/>
+        <f t="shared" si="69"/>
         <v>190929354</v>
       </c>
       <c r="AT34" s="41">
-        <f t="shared" si="63"/>
+        <f t="shared" si="69"/>
         <v>216479082</v>
       </c>
       <c r="AU34" s="41">
@@ -9360,155 +9360,155 @@
         <v>1106846472</v>
       </c>
       <c r="E35" s="83">
-        <f>SUMIFS(ventas_unidades,ventas_año,$A35,ventas_producto,E$25)</f>
+        <f t="shared" si="64"/>
         <v>32671</v>
       </c>
       <c r="F35" s="18">
-        <f>SUMIFS(ventas_unidades,ventas_año,$A35,ventas_producto,F$25)</f>
+        <f t="shared" si="64"/>
         <v>31651</v>
       </c>
       <c r="G35" s="18">
-        <f>SUMIFS(ventas_unidades,ventas_año,$A35,ventas_producto,G$25)</f>
+        <f t="shared" si="64"/>
         <v>34000</v>
       </c>
       <c r="H35" s="18">
-        <f>SUMIFS(ventas_unidades,ventas_año,$A35,ventas_producto,H$25)</f>
+        <f t="shared" si="64"/>
         <v>39442</v>
       </c>
       <c r="I35" s="18">
-        <f>SUMIFS(ventas_unidades,ventas_año,$A35,ventas_producto,I$25)</f>
+        <f t="shared" si="64"/>
         <v>28900</v>
       </c>
       <c r="J35" s="18">
-        <f t="shared" ref="J35:J38" si="64">SUM(E35:I39)</f>
+        <f t="shared" ref="J35:J38" si="70">SUM(E35:I39)</f>
         <v>1534472</v>
       </c>
       <c r="L35" s="98">
-        <f>SUMIFS(ventas_total,ventas_año,$A35,ventas_producto,L$25)</f>
+        <f t="shared" si="65"/>
         <v>203341463</v>
       </c>
       <c r="M35" s="60">
-        <f>SUMIFS(ventas_total,ventas_año,$A35,ventas_producto,M$25)</f>
+        <f t="shared" si="65"/>
         <v>201880917</v>
       </c>
       <c r="N35" s="60">
-        <f>SUMIFS(ventas_total,ventas_año,$A35,ventas_producto,N$25)</f>
+        <f t="shared" si="65"/>
         <v>239992813</v>
       </c>
       <c r="O35" s="60">
-        <f>SUMIFS(ventas_total,ventas_año,$A35,ventas_producto,O$25)</f>
+        <f t="shared" si="65"/>
         <v>221383553</v>
       </c>
       <c r="P35" s="60">
-        <f>SUMIFS(ventas_total,ventas_año,$A35,ventas_producto,P$25)</f>
+        <f t="shared" si="65"/>
         <v>240247726</v>
       </c>
       <c r="Q35" s="60">
-        <f t="shared" ref="Q35:Q38" si="65">SUM(L35:P35)</f>
+        <f t="shared" ref="Q35:Q38" si="71">SUM(L35:P35)</f>
         <v>1106846472</v>
       </c>
       <c r="S35" s="91">
-        <f t="shared" si="60"/>
+        <f t="shared" si="66"/>
         <v>42339</v>
       </c>
       <c r="T35" s="30">
-        <f t="shared" si="60"/>
+        <f t="shared" si="66"/>
         <v>39435</v>
       </c>
       <c r="U35" s="30">
-        <f t="shared" si="60"/>
+        <f t="shared" si="66"/>
         <v>12194</v>
       </c>
       <c r="V35" s="30">
-        <f t="shared" si="60"/>
+        <f t="shared" si="66"/>
         <v>11750</v>
       </c>
       <c r="W35" s="30">
-        <f t="shared" si="60"/>
+        <f t="shared" si="66"/>
         <v>27319</v>
       </c>
       <c r="X35" s="30">
-        <f t="shared" si="60"/>
+        <f t="shared" si="66"/>
         <v>33627</v>
       </c>
       <c r="Y35" s="30">
-        <f t="shared" ref="Y35:Y38" si="66">SUM(S35:X35)</f>
+        <f t="shared" ref="Y35:Y38" si="72">SUM(S35:X35)</f>
         <v>166664</v>
       </c>
       <c r="AA35" s="105">
-        <f t="shared" si="61"/>
+        <f t="shared" si="67"/>
         <v>42339</v>
       </c>
       <c r="AB35" s="65">
-        <f t="shared" si="61"/>
+        <f t="shared" si="67"/>
         <v>39435</v>
       </c>
       <c r="AC35" s="65">
-        <f t="shared" si="61"/>
+        <f t="shared" si="67"/>
         <v>12194</v>
       </c>
       <c r="AD35" s="65">
-        <f t="shared" si="61"/>
+        <f t="shared" si="67"/>
         <v>11750</v>
       </c>
       <c r="AE35" s="65">
-        <f t="shared" si="61"/>
+        <f t="shared" si="67"/>
         <v>27319</v>
       </c>
       <c r="AF35" s="65">
-        <f t="shared" si="61"/>
+        <f t="shared" si="67"/>
         <v>33627</v>
       </c>
       <c r="AG35" s="65">
-        <f t="shared" ref="AG35:AG38" si="67">SUM(AA35:AF35)</f>
+        <f t="shared" ref="AG35:AG38" si="73">SUM(AA35:AF35)</f>
         <v>166664</v>
       </c>
       <c r="AI35" s="83">
-        <f t="shared" si="62"/>
+        <f t="shared" si="68"/>
         <v>32671</v>
       </c>
       <c r="AJ35" s="18">
-        <f t="shared" si="62"/>
+        <f t="shared" si="68"/>
         <v>31651</v>
       </c>
       <c r="AK35" s="18">
-        <f t="shared" si="62"/>
+        <f t="shared" si="68"/>
         <v>34000</v>
       </c>
       <c r="AL35" s="18">
-        <f t="shared" si="62"/>
+        <f t="shared" si="68"/>
         <v>39442</v>
       </c>
       <c r="AM35" s="18">
-        <f t="shared" si="62"/>
+        <f t="shared" si="68"/>
         <v>28900</v>
       </c>
       <c r="AN35" s="18">
-        <f t="shared" ref="AN35:AN38" si="68">SUM(AI35:AM35)</f>
+        <f t="shared" ref="AN35:AN38" si="74">SUM(AI35:AM35)</f>
         <v>166664</v>
       </c>
       <c r="AP35" s="112">
-        <f t="shared" si="63"/>
+        <f t="shared" si="69"/>
         <v>203341463</v>
       </c>
       <c r="AQ35" s="45">
-        <f t="shared" si="63"/>
+        <f t="shared" si="69"/>
         <v>201880917</v>
       </c>
       <c r="AR35" s="45">
-        <f t="shared" si="63"/>
+        <f t="shared" si="69"/>
         <v>239992813</v>
       </c>
       <c r="AS35" s="45">
-        <f t="shared" si="63"/>
+        <f t="shared" si="69"/>
         <v>221383553</v>
       </c>
       <c r="AT35" s="45">
-        <f t="shared" si="63"/>
+        <f t="shared" si="69"/>
         <v>240247726</v>
       </c>
       <c r="AU35" s="45">
-        <f t="shared" ref="AU35:AU38" si="69">SUM(AP35:AT35)</f>
+        <f t="shared" ref="AU35:AU38" si="75">SUM(AP35:AT35)</f>
         <v>1106846472</v>
       </c>
     </row>
@@ -9525,155 +9525,155 @@
         <v>1089310347</v>
       </c>
       <c r="E36" s="84">
-        <f>SUMIFS(ventas_unidades,ventas_año,$A36,ventas_producto,E$25)</f>
+        <f t="shared" si="64"/>
         <v>35334</v>
       </c>
       <c r="F36" s="19">
-        <f>SUMIFS(ventas_unidades,ventas_año,$A36,ventas_producto,F$25)</f>
+        <f t="shared" si="64"/>
         <v>40967</v>
       </c>
       <c r="G36" s="19">
-        <f>SUMIFS(ventas_unidades,ventas_año,$A36,ventas_producto,G$25)</f>
+        <f t="shared" si="64"/>
         <v>31330</v>
       </c>
       <c r="H36" s="19">
-        <f>SUMIFS(ventas_unidades,ventas_año,$A36,ventas_producto,H$25)</f>
+        <f t="shared" si="64"/>
         <v>33573</v>
       </c>
       <c r="I36" s="19">
-        <f>SUMIFS(ventas_unidades,ventas_año,$A36,ventas_producto,I$25)</f>
+        <f t="shared" si="64"/>
         <v>33451</v>
       </c>
       <c r="J36" s="19">
-        <f t="shared" si="64"/>
+        <f t="shared" si="70"/>
         <v>1367808</v>
       </c>
       <c r="L36" s="99">
-        <f>SUMIFS(ventas_total,ventas_año,$A36,ventas_producto,L$25)</f>
+        <f t="shared" si="65"/>
         <v>218564244</v>
       </c>
       <c r="M36" s="61">
-        <f>SUMIFS(ventas_total,ventas_año,$A36,ventas_producto,M$25)</f>
+        <f t="shared" si="65"/>
         <v>214457221</v>
       </c>
       <c r="N36" s="61">
-        <f>SUMIFS(ventas_total,ventas_año,$A36,ventas_producto,N$25)</f>
+        <f t="shared" si="65"/>
         <v>216914467</v>
       </c>
       <c r="O36" s="61">
-        <f>SUMIFS(ventas_total,ventas_año,$A36,ventas_producto,O$25)</f>
+        <f t="shared" si="65"/>
         <v>240503116</v>
       </c>
       <c r="P36" s="61">
-        <f>SUMIFS(ventas_total,ventas_año,$A36,ventas_producto,P$25)</f>
+        <f t="shared" si="65"/>
         <v>198871299</v>
       </c>
       <c r="Q36" s="61">
-        <f t="shared" si="65"/>
+        <f t="shared" si="71"/>
         <v>1089310347</v>
       </c>
       <c r="S36" s="92">
-        <f t="shared" si="60"/>
+        <f t="shared" si="66"/>
         <v>33889</v>
       </c>
       <c r="T36" s="31">
-        <f t="shared" si="60"/>
+        <f t="shared" si="66"/>
         <v>40950</v>
       </c>
       <c r="U36" s="31">
-        <f t="shared" si="60"/>
+        <f t="shared" si="66"/>
         <v>7739</v>
       </c>
       <c r="V36" s="31">
-        <f t="shared" si="60"/>
+        <f t="shared" si="66"/>
         <v>24117</v>
       </c>
       <c r="W36" s="31">
-        <f t="shared" si="60"/>
+        <f t="shared" si="66"/>
         <v>31540</v>
       </c>
       <c r="X36" s="31">
-        <f t="shared" si="60"/>
+        <f t="shared" si="66"/>
         <v>36420</v>
       </c>
       <c r="Y36" s="31">
-        <f t="shared" si="66"/>
+        <f t="shared" si="72"/>
         <v>174655</v>
       </c>
       <c r="AA36" s="106">
-        <f t="shared" si="61"/>
+        <f t="shared" si="67"/>
         <v>33889</v>
       </c>
       <c r="AB36" s="66">
-        <f t="shared" si="61"/>
+        <f t="shared" si="67"/>
         <v>40950</v>
       </c>
       <c r="AC36" s="66">
-        <f t="shared" si="61"/>
+        <f t="shared" si="67"/>
         <v>7739</v>
       </c>
       <c r="AD36" s="66">
-        <f t="shared" si="61"/>
+        <f t="shared" si="67"/>
         <v>24117</v>
       </c>
       <c r="AE36" s="66">
-        <f t="shared" si="61"/>
+        <f t="shared" si="67"/>
         <v>31540</v>
       </c>
       <c r="AF36" s="66">
-        <f t="shared" si="61"/>
+        <f t="shared" si="67"/>
         <v>36420</v>
       </c>
       <c r="AG36" s="66">
-        <f t="shared" si="67"/>
+        <f t="shared" si="73"/>
         <v>174655</v>
       </c>
       <c r="AI36" s="84">
-        <f t="shared" si="62"/>
+        <f t="shared" si="68"/>
         <v>35334</v>
       </c>
       <c r="AJ36" s="19">
-        <f t="shared" si="62"/>
+        <f t="shared" si="68"/>
         <v>40967</v>
       </c>
       <c r="AK36" s="19">
-        <f t="shared" si="62"/>
+        <f t="shared" si="68"/>
         <v>31330</v>
       </c>
       <c r="AL36" s="19">
-        <f t="shared" si="62"/>
+        <f t="shared" si="68"/>
         <v>33573</v>
       </c>
       <c r="AM36" s="19">
-        <f t="shared" si="62"/>
+        <f t="shared" si="68"/>
         <v>33451</v>
       </c>
       <c r="AN36" s="19">
-        <f t="shared" si="68"/>
+        <f t="shared" si="74"/>
         <v>174655</v>
       </c>
       <c r="AP36" s="113">
-        <f t="shared" si="63"/>
+        <f t="shared" si="69"/>
         <v>218564244</v>
       </c>
       <c r="AQ36" s="46">
-        <f t="shared" si="63"/>
+        <f t="shared" si="69"/>
         <v>214457221</v>
       </c>
       <c r="AR36" s="46">
-        <f t="shared" si="63"/>
+        <f t="shared" si="69"/>
         <v>216914467</v>
       </c>
       <c r="AS36" s="46">
-        <f t="shared" si="63"/>
+        <f t="shared" si="69"/>
         <v>240503116</v>
       </c>
       <c r="AT36" s="46">
-        <f t="shared" si="63"/>
+        <f t="shared" si="69"/>
         <v>198871299</v>
       </c>
       <c r="AU36" s="46">
-        <f t="shared" si="69"/>
+        <f t="shared" si="75"/>
         <v>1089310347</v>
       </c>
     </row>
@@ -9690,155 +9690,155 @@
         <v>15082721</v>
       </c>
       <c r="E37" s="83">
-        <f>SUMIFS(ventas_unidades,ventas_año,$A37,ventas_producto,E$25)</f>
+        <f t="shared" si="64"/>
         <v>2738</v>
       </c>
       <c r="F37" s="18">
-        <f>SUMIFS(ventas_unidades,ventas_año,$A37,ventas_producto,F$25)</f>
+        <f t="shared" si="64"/>
         <v>4903</v>
       </c>
       <c r="G37" s="18">
-        <f>SUMIFS(ventas_unidades,ventas_año,$A37,ventas_producto,G$25)</f>
+        <f t="shared" si="64"/>
         <v>13926</v>
       </c>
       <c r="H37" s="18">
-        <f>SUMIFS(ventas_unidades,ventas_año,$A37,ventas_producto,H$25)</f>
+        <f t="shared" si="64"/>
         <v>129</v>
       </c>
       <c r="I37" s="18">
-        <f>SUMIFS(ventas_unidades,ventas_año,$A37,ventas_producto,I$25)</f>
+        <f t="shared" si="64"/>
         <v>107946</v>
       </c>
       <c r="J37" s="18">
-        <f t="shared" si="64"/>
+        <f t="shared" si="70"/>
         <v>1193153</v>
       </c>
       <c r="L37" s="98">
-        <f>SUMIFS(ventas_total,ventas_año,$A37,ventas_producto,L$25)</f>
+        <f t="shared" si="65"/>
         <v>844832</v>
       </c>
       <c r="M37" s="60">
-        <f>SUMIFS(ventas_total,ventas_año,$A37,ventas_producto,M$25)</f>
+        <f t="shared" si="65"/>
         <v>483929</v>
       </c>
       <c r="N37" s="60">
-        <f>SUMIFS(ventas_total,ventas_año,$A37,ventas_producto,N$25)</f>
+        <f t="shared" si="65"/>
         <v>12448615</v>
       </c>
       <c r="O37" s="60">
-        <f>SUMIFS(ventas_total,ventas_año,$A37,ventas_producto,O$25)</f>
+        <f t="shared" si="65"/>
         <v>1203910</v>
       </c>
       <c r="P37" s="60">
-        <f>SUMIFS(ventas_total,ventas_año,$A37,ventas_producto,P$25)</f>
+        <f t="shared" si="65"/>
         <v>101435</v>
       </c>
       <c r="Q37" s="60">
-        <f t="shared" si="65"/>
+        <f t="shared" si="71"/>
         <v>15082721</v>
       </c>
       <c r="S37" s="91">
-        <f t="shared" si="60"/>
+        <f t="shared" si="66"/>
         <v>9886</v>
       </c>
       <c r="T37" s="30">
-        <f t="shared" si="60"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="U37" s="30">
-        <f t="shared" si="60"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="V37" s="30">
-        <f t="shared" si="60"/>
+        <f t="shared" si="66"/>
         <v>107066</v>
       </c>
       <c r="W37" s="30">
-        <f t="shared" si="60"/>
+        <f t="shared" si="66"/>
         <v>9823</v>
       </c>
       <c r="X37" s="30">
-        <f t="shared" si="60"/>
+        <f t="shared" si="66"/>
         <v>2867</v>
       </c>
       <c r="Y37" s="30">
-        <f t="shared" si="66"/>
+        <f t="shared" si="72"/>
         <v>129642</v>
       </c>
       <c r="AA37" s="105">
-        <f t="shared" si="61"/>
+        <f t="shared" si="67"/>
         <v>9886</v>
       </c>
       <c r="AB37" s="65">
-        <f t="shared" si="61"/>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="AC37" s="65">
-        <f t="shared" si="61"/>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="AD37" s="65">
-        <f t="shared" si="61"/>
+        <f t="shared" si="67"/>
         <v>107066</v>
       </c>
       <c r="AE37" s="65">
-        <f t="shared" si="61"/>
+        <f t="shared" si="67"/>
         <v>9823</v>
       </c>
       <c r="AF37" s="65">
-        <f t="shared" si="61"/>
+        <f t="shared" si="67"/>
         <v>2867</v>
       </c>
       <c r="AG37" s="65">
-        <f t="shared" si="67"/>
+        <f t="shared" si="73"/>
         <v>129642</v>
       </c>
       <c r="AI37" s="83">
-        <f t="shared" si="62"/>
+        <f t="shared" si="68"/>
         <v>9072</v>
       </c>
       <c r="AJ37" s="18">
-        <f t="shared" si="62"/>
+        <f t="shared" si="68"/>
         <v>107946</v>
       </c>
       <c r="AK37" s="18">
-        <f t="shared" si="62"/>
+        <f t="shared" si="68"/>
         <v>7721</v>
       </c>
       <c r="AL37" s="18">
-        <f t="shared" si="62"/>
+        <f t="shared" si="68"/>
         <v>4903</v>
       </c>
       <c r="AM37" s="18">
-        <f t="shared" si="62"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="AN37" s="18">
-        <f t="shared" si="68"/>
+        <f t="shared" si="74"/>
         <v>129642</v>
       </c>
       <c r="AP37" s="112">
-        <f t="shared" si="63"/>
+        <f t="shared" si="69"/>
         <v>5532144</v>
       </c>
       <c r="AQ37" s="45">
-        <f t="shared" si="63"/>
+        <f t="shared" si="69"/>
         <v>101435</v>
       </c>
       <c r="AR37" s="45">
-        <f t="shared" si="63"/>
+        <f t="shared" si="69"/>
         <v>8965213</v>
       </c>
       <c r="AS37" s="45">
-        <f t="shared" si="63"/>
+        <f t="shared" si="69"/>
         <v>483929</v>
       </c>
       <c r="AT37" s="45">
-        <f t="shared" si="63"/>
+        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="AU37" s="45">
-        <f t="shared" si="69"/>
+        <f t="shared" si="75"/>
         <v>15082721</v>
       </c>
     </row>
@@ -9855,155 +9855,155 @@
         <v>11533854</v>
       </c>
       <c r="E38" s="84">
-        <f>SUMIFS(ventas_unidades,ventas_año,$A38,ventas_producto,E$25)</f>
+        <f t="shared" si="64"/>
         <v>7128</v>
       </c>
       <c r="F38" s="19">
-        <f>SUMIFS(ventas_unidades,ventas_año,$A38,ventas_producto,F$25)</f>
+        <f t="shared" si="64"/>
         <v>194302</v>
       </c>
       <c r="G38" s="19">
-        <f>SUMIFS(ventas_unidades,ventas_año,$A38,ventas_producto,G$25)</f>
+        <f t="shared" si="64"/>
         <v>0</v>
       </c>
       <c r="H38" s="19">
-        <f>SUMIFS(ventas_unidades,ventas_año,$A38,ventas_producto,H$25)</f>
+        <f t="shared" si="64"/>
         <v>1927</v>
       </c>
       <c r="I38" s="19">
-        <f>SUMIFS(ventas_unidades,ventas_año,$A38,ventas_producto,I$25)</f>
+        <f t="shared" si="64"/>
         <v>1927</v>
       </c>
       <c r="J38" s="19">
-        <f t="shared" si="64"/>
+        <f t="shared" si="70"/>
         <v>1063511</v>
       </c>
       <c r="L38" s="99">
-        <f>SUMIFS(ventas_total,ventas_año,$A38,ventas_producto,L$25)</f>
+        <f t="shared" si="65"/>
         <v>9123918</v>
       </c>
       <c r="M38" s="61">
-        <f>SUMIFS(ventas_total,ventas_año,$A38,ventas_producto,M$25)</f>
+        <f t="shared" si="65"/>
         <v>937562</v>
       </c>
       <c r="N38" s="61">
-        <f>SUMIFS(ventas_total,ventas_año,$A38,ventas_producto,N$25)</f>
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="O38" s="61">
-        <f>SUMIFS(ventas_total,ventas_año,$A38,ventas_producto,O$25)</f>
+        <f t="shared" si="65"/>
         <v>923982</v>
       </c>
       <c r="P38" s="61">
-        <f>SUMIFS(ventas_total,ventas_año,$A38,ventas_producto,P$25)</f>
+        <f t="shared" si="65"/>
         <v>548392</v>
       </c>
       <c r="Q38" s="61">
-        <f t="shared" si="65"/>
+        <f t="shared" si="71"/>
         <v>11533854</v>
       </c>
       <c r="S38" s="92">
-        <f t="shared" si="60"/>
+        <f t="shared" si="66"/>
         <v>1928</v>
       </c>
       <c r="T38" s="31">
-        <f t="shared" si="60"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="U38" s="31">
-        <f t="shared" si="60"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="V38" s="31">
-        <f t="shared" si="60"/>
+        <f t="shared" si="66"/>
         <v>192374</v>
       </c>
       <c r="W38" s="31">
-        <f t="shared" si="60"/>
+        <f t="shared" si="66"/>
         <v>9055</v>
       </c>
       <c r="X38" s="31">
-        <f t="shared" si="60"/>
+        <f t="shared" si="66"/>
         <v>1927</v>
       </c>
       <c r="Y38" s="31">
-        <f t="shared" si="66"/>
+        <f t="shared" si="72"/>
         <v>205284</v>
       </c>
       <c r="AA38" s="106">
-        <f t="shared" si="61"/>
+        <f t="shared" si="67"/>
         <v>1928</v>
       </c>
       <c r="AB38" s="66">
-        <f t="shared" si="61"/>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="AC38" s="66">
-        <f t="shared" si="61"/>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="AD38" s="66">
-        <f t="shared" si="61"/>
+        <f t="shared" si="67"/>
         <v>192374</v>
       </c>
       <c r="AE38" s="66">
-        <f t="shared" si="61"/>
+        <f t="shared" si="67"/>
         <v>9055</v>
       </c>
       <c r="AF38" s="66">
-        <f t="shared" si="61"/>
+        <f t="shared" si="67"/>
         <v>1927</v>
       </c>
       <c r="AG38" s="66">
-        <f t="shared" si="67"/>
+        <f t="shared" si="73"/>
         <v>205284</v>
       </c>
       <c r="AI38" s="84">
-        <f t="shared" si="62"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="AJ38" s="19">
-        <f t="shared" si="62"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="AK38" s="19">
-        <f t="shared" si="62"/>
+        <f t="shared" si="68"/>
         <v>3855</v>
       </c>
       <c r="AL38" s="19">
-        <f t="shared" si="62"/>
+        <f t="shared" si="68"/>
         <v>194301</v>
       </c>
       <c r="AM38" s="19">
-        <f t="shared" si="62"/>
+        <f t="shared" si="68"/>
         <v>7128</v>
       </c>
       <c r="AN38" s="19">
-        <f t="shared" si="68"/>
+        <f t="shared" si="74"/>
         <v>205284</v>
       </c>
       <c r="AP38" s="113">
-        <f t="shared" si="63"/>
+        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="AQ38" s="46">
-        <f t="shared" si="63"/>
+        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="AR38" s="46">
-        <f t="shared" si="63"/>
+        <f t="shared" si="69"/>
         <v>1032196</v>
       </c>
       <c r="AS38" s="46">
-        <f t="shared" si="63"/>
+        <f t="shared" si="69"/>
         <v>1377740</v>
       </c>
       <c r="AT38" s="46">
-        <f t="shared" si="63"/>
+        <f t="shared" si="69"/>
         <v>9123918</v>
       </c>
       <c r="AU38" s="46">
-        <f t="shared" si="69"/>
+        <f t="shared" si="75"/>
         <v>11533854</v>
       </c>
     </row>
@@ -10024,23 +10024,23 @@
         <v>110903</v>
       </c>
       <c r="F39" s="51">
-        <f t="shared" ref="F39" si="70">SUM(F34:F38)</f>
+        <f t="shared" ref="F39" si="76">SUM(F34:F38)</f>
         <v>304519</v>
       </c>
       <c r="G39" s="51">
-        <f t="shared" ref="G39" si="71">SUM(G34:G38)</f>
+        <f t="shared" ref="G39" si="77">SUM(G34:G38)</f>
         <v>118380</v>
       </c>
       <c r="H39" s="51">
-        <f t="shared" ref="H39" si="72">SUM(H34:H38)</f>
+        <f t="shared" ref="H39" si="78">SUM(H34:H38)</f>
         <v>115644</v>
       </c>
       <c r="I39" s="51">
-        <f t="shared" ref="I39" si="73">SUM(I34:I38)</f>
+        <f t="shared" ref="I39" si="79">SUM(I34:I38)</f>
         <v>208781</v>
       </c>
       <c r="J39" s="118">
-        <f t="shared" ref="J39" si="74">SUM(J34:J38)</f>
+        <f t="shared" ref="J39" si="80">SUM(J34:J38)</f>
         <v>6017171</v>
       </c>
       <c r="L39" s="109">
@@ -10048,19 +10048,19 @@
         <v>650543568</v>
       </c>
       <c r="M39" s="69">
-        <f t="shared" ref="M39" si="75">SUM(M34:M38)</f>
+        <f t="shared" ref="M39" si="81">SUM(M34:M38)</f>
         <v>578124392</v>
       </c>
       <c r="N39" s="69">
-        <f t="shared" ref="N39" si="76">SUM(N34:N38)</f>
+        <f t="shared" ref="N39" si="82">SUM(N34:N38)</f>
         <v>690157736</v>
       </c>
       <c r="O39" s="69">
-        <f t="shared" ref="O39" si="77">SUM(O34:O38)</f>
+        <f t="shared" ref="O39" si="83">SUM(O34:O38)</f>
         <v>654943915</v>
       </c>
       <c r="P39" s="69">
-        <f t="shared" ref="P39" si="78">SUM(P34:P38)</f>
+        <f t="shared" ref="P39" si="84">SUM(P34:P38)</f>
         <v>656247934</v>
       </c>
       <c r="Q39" s="115">
@@ -10072,27 +10072,27 @@
         <v>121665</v>
       </c>
       <c r="T39" s="40">
-        <f t="shared" ref="T39:Y39" si="79">SUM(T34:T38)</f>
+        <f t="shared" ref="T39:Y39" si="85">SUM(T34:T38)</f>
         <v>125620</v>
       </c>
       <c r="U39" s="40">
-        <f t="shared" si="79"/>
+        <f t="shared" si="85"/>
         <v>32356</v>
       </c>
       <c r="V39" s="40">
-        <f t="shared" si="79"/>
+        <f t="shared" si="85"/>
         <v>356297</v>
       </c>
       <c r="W39" s="40">
-        <f t="shared" si="79"/>
+        <f t="shared" si="85"/>
         <v>122295</v>
       </c>
       <c r="X39" s="40">
-        <f t="shared" si="79"/>
+        <f t="shared" si="85"/>
         <v>99994</v>
       </c>
       <c r="Y39" s="40">
-        <f t="shared" si="79"/>
+        <f t="shared" si="85"/>
         <v>858227</v>
       </c>
       <c r="AA39" s="107">
@@ -10100,27 +10100,27 @@
         <v>121665</v>
       </c>
       <c r="AB39" s="67">
-        <f t="shared" ref="AB39" si="80">SUM(AB34:AB38)</f>
+        <f t="shared" ref="AB39" si="86">SUM(AB34:AB38)</f>
         <v>125620</v>
       </c>
       <c r="AC39" s="67">
-        <f t="shared" ref="AC39" si="81">SUM(AC34:AC38)</f>
+        <f t="shared" ref="AC39" si="87">SUM(AC34:AC38)</f>
         <v>32356</v>
       </c>
       <c r="AD39" s="67">
-        <f t="shared" ref="AD39" si="82">SUM(AD34:AD38)</f>
+        <f t="shared" ref="AD39" si="88">SUM(AD34:AD38)</f>
         <v>356297</v>
       </c>
       <c r="AE39" s="67">
-        <f t="shared" ref="AE39" si="83">SUM(AE34:AE38)</f>
+        <f t="shared" ref="AE39" si="89">SUM(AE34:AE38)</f>
         <v>122295</v>
       </c>
       <c r="AF39" s="67">
-        <f t="shared" ref="AF39" si="84">SUM(AF34:AF38)</f>
+        <f t="shared" ref="AF39" si="90">SUM(AF34:AF38)</f>
         <v>99994</v>
       </c>
       <c r="AG39" s="115">
-        <f t="shared" ref="AG39" si="85">SUM(AG34:AG38)</f>
+        <f t="shared" ref="AG39" si="91">SUM(AG34:AG38)</f>
         <v>858227</v>
       </c>
       <c r="AI39" s="95">
@@ -10128,23 +10128,23 @@
         <v>110109</v>
       </c>
       <c r="AJ39" s="51">
-        <f t="shared" ref="AJ39:AN39" si="86">SUM(AJ34:AJ38)</f>
+        <f t="shared" ref="AJ39:AN39" si="92">SUM(AJ34:AJ38)</f>
         <v>213260</v>
       </c>
       <c r="AK39" s="51">
-        <f t="shared" si="86"/>
+        <f t="shared" si="92"/>
         <v>116030</v>
       </c>
       <c r="AL39" s="51">
-        <f t="shared" si="86"/>
+        <f t="shared" si="92"/>
         <v>312792</v>
       </c>
       <c r="AM39" s="51">
-        <f t="shared" si="86"/>
+        <f t="shared" si="92"/>
         <v>106036</v>
       </c>
       <c r="AN39" s="118">
-        <f t="shared" si="86"/>
+        <f t="shared" si="92"/>
         <v>858227</v>
       </c>
       <c r="AP39" s="114">
@@ -10152,23 +10152,23 @@
         <v>646106962</v>
       </c>
       <c r="AQ39" s="49">
-        <f t="shared" ref="AQ39" si="87">SUM(AQ34:AQ38)</f>
+        <f t="shared" ref="AQ39" si="93">SUM(AQ34:AQ38)</f>
         <v>576804336</v>
       </c>
       <c r="AR39" s="49">
-        <f t="shared" ref="AR39" si="88">SUM(AR34:AR38)</f>
+        <f t="shared" ref="AR39" si="94">SUM(AR34:AR38)</f>
         <v>687706530</v>
       </c>
       <c r="AS39" s="49">
-        <f t="shared" ref="AS39" si="89">SUM(AS34:AS38)</f>
+        <f t="shared" ref="AS39" si="95">SUM(AS34:AS38)</f>
         <v>654677692</v>
       </c>
       <c r="AT39" s="49">
-        <f t="shared" ref="AT39" si="90">SUM(AT34:AT38)</f>
+        <f t="shared" ref="AT39" si="96">SUM(AT34:AT38)</f>
         <v>664722025</v>
       </c>
       <c r="AU39" s="119">
-        <f t="shared" ref="AU39" si="91">SUM(AU34:AU38)</f>
+        <f t="shared" ref="AU39" si="97">SUM(AU34:AU38)</f>
         <v>3230017545</v>
       </c>
     </row>

--- a/examples/DB_Supermercado.xlsx
+++ b/examples/DB_Supermercado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EducacionIT\Documents\office\Excel\xls-mj15\examples\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEF55D92-8FFC-40C6-98B9-EBAB1C7FC01B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30A3AA43-0965-484F-88A4-DE87CEE6109D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="983" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="989" uniqueCount="49">
   <si>
     <t>Mes</t>
   </si>
@@ -223,7 +223,7 @@
     <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -284,8 +284,14 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -309,8 +315,14 @@
         <fgColor theme="8"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -411,6 +423,15 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -418,7 +439,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="124">
+  <cellXfs count="136">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -463,7 +484,6 @@
     <xf numFmtId="44" fontId="2" fillId="3" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="164" fontId="6" fillId="3" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="6" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="44" fontId="2" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -551,6 +571,19 @@
     <xf numFmtId="164" fontId="7" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="7" fillId="4" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="8" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="4" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="10" fillId="5" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="10" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Énfasis5" xfId="3" builtinId="45"/>
@@ -906,13 +939,13 @@
       <c r="G1" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="I1" s="76" t="s">
+      <c r="I1" s="75" t="s">
         <v>41</v>
       </c>
-      <c r="J1" s="76" t="s">
+      <c r="J1" s="75" t="s">
         <v>48</v>
       </c>
-      <c r="K1" s="76" t="s">
+      <c r="K1" s="75" t="s">
         <v>39</v>
       </c>
     </row>
@@ -938,15 +971,15 @@
       <c r="G2" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="I2" s="73">
+      <c r="I2" s="72">
         <f>COUNT(ventas_unidades)</f>
         <v>192</v>
       </c>
-      <c r="J2" s="74">
+      <c r="J2" s="73">
         <f>SUM(ventas_unidades)</f>
         <v>858227</v>
       </c>
-      <c r="K2" s="75">
+      <c r="K2" s="74">
         <f>SUM(ventas_total)</f>
         <v>3230017545</v>
       </c>
@@ -5468,47 +5501,55 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C55B143F-BB66-4B35-BD7B-8E64426316F6}">
-  <dimension ref="A1:AU39"/>
+  <dimension ref="A1:BI39"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.21875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="3.44140625" customWidth="1"/>
-    <col min="5" max="5" width="8.88671875" style="88" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="8.88671875" style="52" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.88671875" style="52" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.88671875" style="52" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.44140625" style="52" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.88671875" style="87" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="8.88671875" style="51" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.88671875" style="51" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.88671875" style="51" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.44140625" style="51" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="3.44140625" customWidth="1"/>
-    <col min="12" max="12" width="13.88671875" style="102" bestFit="1" customWidth="1"/>
-    <col min="13" max="16" width="13.88671875" style="58" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="16.5546875" style="58" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.88671875" style="101" bestFit="1" customWidth="1"/>
+    <col min="13" max="16" width="13.88671875" style="57" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="16.5546875" style="57" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="3.44140625" customWidth="1"/>
-    <col min="19" max="19" width="10.109375" style="88" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="8.88671875" style="52" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="9" style="52" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="8.88671875" style="52" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="9.21875" style="52" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="8.88671875" style="52" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.109375" style="87" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="8.88671875" style="51" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="9" style="51" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="8.88671875" style="51" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="9.21875" style="51" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="8.88671875" style="51" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="3.44140625" customWidth="1"/>
-    <col min="27" max="27" width="13.88671875" style="102" bestFit="1" customWidth="1"/>
-    <col min="28" max="32" width="13.88671875" style="58" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="15.44140625" style="58" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="13.88671875" style="101" bestFit="1" customWidth="1"/>
+    <col min="28" max="32" width="13.88671875" style="57" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="15.44140625" style="57" bestFit="1" customWidth="1"/>
     <col min="34" max="34" width="3.44140625" customWidth="1"/>
-    <col min="35" max="35" width="8.88671875" style="88" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="8.88671875" style="52" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="12.77734375" style="52" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="10.5546875" style="52" bestFit="1" customWidth="1"/>
-    <col min="39" max="40" width="8.88671875" style="52" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="8.88671875" style="87" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="8.88671875" style="51" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="12.77734375" style="51" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="10.5546875" style="51" bestFit="1" customWidth="1"/>
+    <col min="39" max="40" width="8.88671875" style="51" bestFit="1" customWidth="1"/>
     <col min="41" max="41" width="3.44140625" customWidth="1"/>
-    <col min="42" max="42" width="16.44140625" style="86" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="16.44140625" style="85" bestFit="1" customWidth="1"/>
     <col min="43" max="46" width="16.44140625" bestFit="1" customWidth="1"/>
     <col min="47" max="47" width="18.109375" bestFit="1" customWidth="1"/>
     <col min="48" max="48" width="3.44140625" customWidth="1"/>
+    <col min="49" max="49" width="11.44140625" style="85" bestFit="1" customWidth="1"/>
+    <col min="50" max="51" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="52" max="54" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="3.44140625" customWidth="1"/>
+    <col min="56" max="56" width="15.44140625" style="85" bestFit="1" customWidth="1"/>
+    <col min="57" max="58" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="59" max="60" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="61" max="61" width="15.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:47" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:61" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="7" t="s">
         <v>46</v>
       </c>
@@ -5518,107 +5559,139 @@
       <c r="C1" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="E1" s="87" t="s">
+      <c r="E1" s="86" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="53" t="s">
+      <c r="F1" s="52" t="s">
         <v>33</v>
       </c>
-      <c r="G1" s="53" t="s">
+      <c r="G1" s="52" t="s">
         <v>15</v>
       </c>
-      <c r="H1" s="53" t="s">
+      <c r="H1" s="52" t="s">
         <v>18</v>
       </c>
-      <c r="I1" s="53" t="s">
+      <c r="I1" s="52" t="s">
         <v>47</v>
       </c>
-      <c r="J1" s="120"/>
-      <c r="L1" s="101" t="s">
+      <c r="J1" s="119"/>
+      <c r="L1" s="100" t="s">
         <v>6</v>
       </c>
-      <c r="M1" s="57" t="s">
+      <c r="M1" s="56" t="s">
         <v>33</v>
       </c>
-      <c r="N1" s="57" t="s">
+      <c r="N1" s="56" t="s">
         <v>15</v>
       </c>
-      <c r="O1" s="57" t="s">
+      <c r="O1" s="56" t="s">
         <v>18</v>
       </c>
-      <c r="P1" s="57" t="s">
+      <c r="P1" s="56" t="s">
         <v>47</v>
       </c>
-      <c r="Q1" s="122"/>
-      <c r="S1" s="87" t="s">
+      <c r="Q1" s="121"/>
+      <c r="S1" s="86" t="s">
         <v>28</v>
       </c>
-      <c r="T1" s="53" t="s">
+      <c r="T1" s="52" t="s">
         <v>8</v>
       </c>
-      <c r="U1" s="53" t="s">
+      <c r="U1" s="52" t="s">
         <v>11</v>
       </c>
-      <c r="V1" s="53" t="s">
+      <c r="V1" s="52" t="s">
         <v>13</v>
       </c>
-      <c r="W1" s="53" t="s">
+      <c r="W1" s="52" t="s">
         <v>29</v>
       </c>
-      <c r="X1" s="53" t="s">
+      <c r="X1" s="52" t="s">
         <v>30</v>
       </c>
-      <c r="AA1" s="101" t="s">
+      <c r="AA1" s="100" t="s">
         <v>28</v>
       </c>
-      <c r="AB1" s="57" t="s">
+      <c r="AB1" s="56" t="s">
         <v>8</v>
       </c>
-      <c r="AC1" s="57" t="s">
+      <c r="AC1" s="56" t="s">
         <v>11</v>
       </c>
-      <c r="AD1" s="57" t="s">
+      <c r="AD1" s="56" t="s">
         <v>13</v>
       </c>
-      <c r="AE1" s="57" t="s">
+      <c r="AE1" s="56" t="s">
         <v>29</v>
       </c>
-      <c r="AF1" s="57" t="s">
+      <c r="AF1" s="56" t="s">
         <v>30</v>
       </c>
-      <c r="AI1" s="87" t="s">
+      <c r="AI1" s="86" t="s">
         <v>31</v>
       </c>
-      <c r="AJ1" s="53" t="s">
+      <c r="AJ1" s="52" t="s">
         <v>9</v>
       </c>
-      <c r="AK1" s="53" t="s">
+      <c r="AK1" s="52" t="s">
         <v>16</v>
       </c>
-      <c r="AL1" s="53" t="s">
+      <c r="AL1" s="52" t="s">
         <v>19</v>
       </c>
-      <c r="AM1" s="53" t="s">
+      <c r="AM1" s="52" t="s">
         <v>21</v>
       </c>
       <c r="AN1"/>
-      <c r="AP1" s="87" t="s">
+      <c r="AP1" s="86" t="s">
         <v>31</v>
       </c>
-      <c r="AQ1" s="53" t="s">
+      <c r="AQ1" s="52" t="s">
         <v>9</v>
       </c>
-      <c r="AR1" s="53" t="s">
+      <c r="AR1" s="52" t="s">
         <v>16</v>
       </c>
-      <c r="AS1" s="53" t="s">
+      <c r="AS1" s="52" t="s">
         <v>19</v>
       </c>
-      <c r="AT1" s="53" t="s">
+      <c r="AT1" s="52" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="2" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AW1" s="125">
+        <v>2008</v>
+      </c>
+      <c r="AX1" s="21">
+        <v>2009</v>
+      </c>
+      <c r="AY1" s="21">
+        <v>2010</v>
+      </c>
+      <c r="AZ1" s="21">
+        <v>2011</v>
+      </c>
+      <c r="BA1" s="21">
+        <v>2012</v>
+      </c>
+      <c r="BB1" s="2"/>
+      <c r="BC1" s="2"/>
+      <c r="BD1" s="125">
+        <v>2008</v>
+      </c>
+      <c r="BE1" s="21">
+        <v>2009</v>
+      </c>
+      <c r="BF1" s="21">
+        <v>2010</v>
+      </c>
+      <c r="BG1" s="21">
+        <v>2011</v>
+      </c>
+      <c r="BH1" s="21">
+        <v>2012</v>
+      </c>
+    </row>
+    <row r="2" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
         <v>35</v>
       </c>
@@ -5630,7 +5703,7 @@
         <f>MIN(ventas_total)</f>
         <v>18234</v>
       </c>
-      <c r="E2" s="82">
+      <c r="E2" s="81">
         <f>_xlfn.MINIFS(ventas_unidades,ventas_producto,E$1)</f>
         <v>951</v>
       </c>
@@ -5650,29 +5723,29 @@
         <f>_xlfn.MINIFS(ventas_unidades,ventas_producto,I$1)</f>
         <v>933</v>
       </c>
-      <c r="J2" s="78"/>
-      <c r="L2" s="97">
+      <c r="J2" s="77"/>
+      <c r="L2" s="96">
         <f>_xlfn.MINIFS(ventas_total,ventas_producto,L$1)</f>
         <v>844832</v>
       </c>
-      <c r="M2" s="59">
+      <c r="M2" s="58">
         <f>_xlfn.MINIFS(ventas_total,ventas_producto,M$1)</f>
         <v>108214</v>
       </c>
-      <c r="N2" s="59">
+      <c r="N2" s="58">
         <f>_xlfn.MINIFS(ventas_total,ventas_producto,N$1)</f>
         <v>4328234</v>
       </c>
-      <c r="O2" s="59">
+      <c r="O2" s="58">
         <f>_xlfn.MINIFS(ventas_total,ventas_producto,O$1)</f>
         <v>923982</v>
       </c>
-      <c r="P2" s="59">
+      <c r="P2" s="58">
         <f>_xlfn.MINIFS(ventas_total,ventas_producto,P$1)</f>
         <v>18234</v>
       </c>
-      <c r="Q2" s="77"/>
-      <c r="S2" s="82">
+      <c r="Q2" s="76"/>
+      <c r="S2" s="81">
         <f t="shared" ref="S2:X2" si="0">_xlfn.MINIFS(ventas_unidades,ventas_vendedor,S$1)</f>
         <v>928</v>
       </c>
@@ -5696,31 +5769,31 @@
         <f t="shared" si="0"/>
         <v>129</v>
       </c>
-      <c r="AA2" s="97">
+      <c r="AA2" s="96">
         <f t="shared" ref="AA2:AF2" si="1">_xlfn.MINIFS(ventas_total,ventas_vendedor,AA$1)</f>
         <v>108214</v>
       </c>
-      <c r="AB2" s="59">
+      <c r="AB2" s="58">
         <f t="shared" si="1"/>
         <v>7474946</v>
       </c>
-      <c r="AC2" s="59">
+      <c r="AC2" s="58">
         <f t="shared" si="1"/>
         <v>6788991</v>
       </c>
-      <c r="AD2" s="59">
+      <c r="AD2" s="58">
         <f t="shared" si="1"/>
         <v>83201</v>
       </c>
-      <c r="AE2" s="59">
+      <c r="AE2" s="58">
         <f t="shared" si="1"/>
         <v>18234</v>
       </c>
-      <c r="AF2" s="59">
+      <c r="AF2" s="58">
         <f t="shared" si="1"/>
         <v>548392</v>
       </c>
-      <c r="AI2" s="82">
+      <c r="AI2" s="81">
         <f>_xlfn.MINIFS(ventas_unidades,ventas_region,AI$1)</f>
         <v>129</v>
       </c>
@@ -5741,28 +5814,68 @@
         <v>933</v>
       </c>
       <c r="AN2"/>
-      <c r="AP2" s="97">
+      <c r="AP2" s="96">
         <f>_xlfn.MINIFS(ventas_total,ventas_region,AP$1)</f>
         <v>1203910</v>
       </c>
-      <c r="AQ2" s="59">
+      <c r="AQ2" s="58">
         <f>_xlfn.MINIFS(ventas_total,ventas_region,AQ$1)</f>
         <v>18234</v>
       </c>
-      <c r="AR2" s="59">
+      <c r="AR2" s="58">
         <f>_xlfn.MINIFS(ventas_total,ventas_region,AR$1)</f>
         <v>108214</v>
       </c>
-      <c r="AS2" s="59">
+      <c r="AS2" s="58">
         <f>_xlfn.MINIFS(ventas_total,ventas_region,AS$1)</f>
         <v>483929</v>
       </c>
-      <c r="AT2" s="59">
+      <c r="AT2" s="58">
         <f>_xlfn.MINIFS(ventas_total,ventas_region,AT$1)</f>
         <v>5126450</v>
       </c>
-    </row>
-    <row r="3" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AW2" s="81">
+        <f>_xlfn.MINIFS(ventas_unidades,ventas_año,AW$1)</f>
+        <v>928</v>
+      </c>
+      <c r="AX2" s="17">
+        <f>_xlfn.MINIFS(ventas_unidades,ventas_año,AX$1)</f>
+        <v>932</v>
+      </c>
+      <c r="AY2" s="17">
+        <f>_xlfn.MINIFS(ventas_unidades,ventas_año,AY$1)</f>
+        <v>933</v>
+      </c>
+      <c r="AZ2" s="17">
+        <f>_xlfn.MINIFS(ventas_unidades,ventas_año,AZ$1)</f>
+        <v>129</v>
+      </c>
+      <c r="BA2" s="17">
+        <f>_xlfn.MINIFS(ventas_unidades,ventas_año,BA$1)</f>
+        <v>1927</v>
+      </c>
+      <c r="BD2" s="96">
+        <f>_xlfn.MINIFS(ventas_total,ventas_año,BD$1)</f>
+        <v>5090135</v>
+      </c>
+      <c r="BE2" s="58">
+        <f>_xlfn.MINIFS(ventas_total,ventas_año,BE$1)</f>
+        <v>5126450</v>
+      </c>
+      <c r="BF2" s="58">
+        <f>_xlfn.MINIFS(ventas_total,ventas_año,BF$1)</f>
+        <v>5608677</v>
+      </c>
+      <c r="BG2" s="58">
+        <f>_xlfn.MINIFS(ventas_total,ventas_año,BG$1)</f>
+        <v>18234</v>
+      </c>
+      <c r="BH2" s="58">
+        <f>_xlfn.MINIFS(ventas_total,ventas_año,BH$1)</f>
+        <v>108214</v>
+      </c>
+    </row>
+    <row r="3" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>36</v>
       </c>
@@ -5774,7 +5887,7 @@
         <f>MAX(ventas_total)</f>
         <v>31939624</v>
       </c>
-      <c r="E3" s="83">
+      <c r="E3" s="82">
         <f>_xlfn.MAXIFS(ventas_unidades,ventas_producto,E$1)</f>
         <v>7128</v>
       </c>
@@ -5794,29 +5907,29 @@
         <f>_xlfn.MAXIFS(ventas_unidades,ventas_producto,I$1)</f>
         <v>98123</v>
       </c>
-      <c r="J3" s="78"/>
-      <c r="L3" s="98">
+      <c r="J3" s="77"/>
+      <c r="L3" s="97">
         <f>_xlfn.MAXIFS(ventas_total,ventas_producto,L$1)</f>
         <v>31075727</v>
       </c>
-      <c r="M3" s="60">
+      <c r="M3" s="59">
         <f>_xlfn.MAXIFS(ventas_total,ventas_producto,M$1)</f>
         <v>31939624</v>
       </c>
-      <c r="N3" s="60">
+      <c r="N3" s="59">
         <f>_xlfn.MAXIFS(ventas_total,ventas_producto,N$1)</f>
         <v>31929296</v>
       </c>
-      <c r="O3" s="60">
+      <c r="O3" s="59">
         <f>_xlfn.MAXIFS(ventas_total,ventas_producto,O$1)</f>
         <v>31378227</v>
       </c>
-      <c r="P3" s="60">
+      <c r="P3" s="59">
         <f>_xlfn.MAXIFS(ventas_total,ventas_producto,P$1)</f>
         <v>31553984</v>
       </c>
-      <c r="Q3" s="77"/>
-      <c r="S3" s="83">
+      <c r="Q3" s="76"/>
+      <c r="S3" s="82">
         <f t="shared" ref="S3:X3" si="2">_xlfn.MAXIFS(ventas_unidades,ventas_vendedor,S$1)</f>
         <v>4983</v>
       </c>
@@ -5840,31 +5953,31 @@
         <f t="shared" si="2"/>
         <v>4859</v>
       </c>
-      <c r="AA3" s="98">
+      <c r="AA3" s="97">
         <f t="shared" ref="AA3:AF3" si="3">_xlfn.MAXIFS(ventas_total,ventas_vendedor,AA$1)</f>
         <v>31929296</v>
       </c>
-      <c r="AB3" s="60">
+      <c r="AB3" s="59">
         <f t="shared" si="3"/>
         <v>31939624</v>
       </c>
-      <c r="AC3" s="60">
+      <c r="AC3" s="59">
         <f t="shared" si="3"/>
         <v>31378227</v>
       </c>
-      <c r="AD3" s="60">
+      <c r="AD3" s="59">
         <f t="shared" si="3"/>
         <v>31204355</v>
       </c>
-      <c r="AE3" s="60">
+      <c r="AE3" s="59">
         <f t="shared" si="3"/>
         <v>31553984</v>
       </c>
-      <c r="AF3" s="60">
+      <c r="AF3" s="59">
         <f t="shared" si="3"/>
         <v>29657237</v>
       </c>
-      <c r="AI3" s="83">
+      <c r="AI3" s="82">
         <f>_xlfn.MAXIFS(ventas_unidades,ventas_region,AI$1)</f>
         <v>8943</v>
       </c>
@@ -5885,28 +5998,68 @@
         <v>7128</v>
       </c>
       <c r="AN3"/>
-      <c r="AP3" s="98">
+      <c r="AP3" s="97">
         <f>_xlfn.MAXIFS(ventas_total,ventas_region,AP$1)</f>
         <v>31075727</v>
       </c>
-      <c r="AQ3" s="65">
+      <c r="AQ3" s="64">
         <f>_xlfn.MAXIFS(ventas_total,ventas_region,AQ$1)</f>
         <v>31939624</v>
       </c>
-      <c r="AR3" s="65">
+      <c r="AR3" s="64">
         <f>_xlfn.MAXIFS(ventas_total,ventas_region,AR$1)</f>
         <v>31929296</v>
       </c>
-      <c r="AS3" s="60">
+      <c r="AS3" s="59">
         <f>_xlfn.MAXIFS(ventas_total,ventas_region,AS$1)</f>
         <v>31378227</v>
       </c>
-      <c r="AT3" s="65">
+      <c r="AT3" s="64">
         <f>_xlfn.MAXIFS(ventas_total,ventas_region,AT$1)</f>
         <v>31553984</v>
       </c>
-    </row>
-    <row r="4" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AW3" s="82">
+        <f>_xlfn.MAXIFS(ventas_unidades,ventas_año,AW$1)</f>
+        <v>4991</v>
+      </c>
+      <c r="AX3" s="30">
+        <f>_xlfn.MAXIFS(ventas_unidades,ventas_año,AX$1)</f>
+        <v>4983</v>
+      </c>
+      <c r="AY3" s="30">
+        <f>_xlfn.MAXIFS(ventas_unidades,ventas_año,AY$1)</f>
+        <v>4859</v>
+      </c>
+      <c r="AZ3" s="18">
+        <f>_xlfn.MAXIFS(ventas_unidades,ventas_año,AZ$1)</f>
+        <v>98123</v>
+      </c>
+      <c r="BA3" s="30">
+        <f>_xlfn.MAXIFS(ventas_unidades,ventas_año,BA$1)</f>
+        <v>192374</v>
+      </c>
+      <c r="BD3" s="97">
+        <f>_xlfn.MAXIFS(ventas_total,ventas_año,BD$1)</f>
+        <v>31929296</v>
+      </c>
+      <c r="BE3" s="64">
+        <f>_xlfn.MAXIFS(ventas_total,ventas_año,BE$1)</f>
+        <v>31553984</v>
+      </c>
+      <c r="BF3" s="64">
+        <f>_xlfn.MAXIFS(ventas_total,ventas_año,BF$1)</f>
+        <v>31939624</v>
+      </c>
+      <c r="BG3" s="59">
+        <f>_xlfn.MAXIFS(ventas_total,ventas_año,BG$1)</f>
+        <v>8120381</v>
+      </c>
+      <c r="BH3" s="64">
+        <f>_xlfn.MAXIFS(ventas_total,ventas_año,BH$1)</f>
+        <v>9123918</v>
+      </c>
+    </row>
+    <row r="4" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>37</v>
       </c>
@@ -5918,7 +6071,7 @@
         <f>MEDIAN(ventas_total)</f>
         <v>17050822.5</v>
       </c>
-      <c r="E4" s="84" cm="1">
+      <c r="E4" s="83" cm="1">
         <f t="array" ref="E4">MEDIAN(IF(ventas_producto=E$1,ventas_unidades))</f>
         <v>2698.5</v>
       </c>
@@ -5938,29 +6091,29 @@
         <f t="array" ref="I4">MEDIAN(IF(ventas_producto=I$1,ventas_unidades))</f>
         <v>2754</v>
       </c>
-      <c r="J4" s="79"/>
-      <c r="L4" s="99" cm="1">
+      <c r="J4" s="78"/>
+      <c r="L4" s="98" cm="1">
         <f t="array" ref="L4">MEDIAN(IF(ventas_producto=L$1,ventas_total))</f>
         <v>16191526</v>
       </c>
-      <c r="M4" s="61" cm="1">
+      <c r="M4" s="60" cm="1">
         <f t="array" ref="M4">MEDIAN(IF(ventas_producto=M$1,ventas_total))</f>
         <v>13677001</v>
       </c>
-      <c r="N4" s="61" cm="1">
+      <c r="N4" s="60" cm="1">
         <f t="array" ref="N4">MEDIAN(IF(ventas_producto=N$1,ventas_total))</f>
         <v>18201953</v>
       </c>
-      <c r="O4" s="61" cm="1">
+      <c r="O4" s="60" cm="1">
         <f t="array" ref="O4">MEDIAN(IF(ventas_producto=O$1,ventas_total))</f>
         <v>17464872</v>
       </c>
-      <c r="P4" s="61" cm="1">
+      <c r="P4" s="60" cm="1">
         <f t="array" ref="P4">MEDIAN(IF(ventas_producto=P$1,ventas_total))</f>
         <v>17785852</v>
       </c>
-      <c r="Q4" s="77"/>
-      <c r="S4" s="84" cm="1">
+      <c r="Q4" s="76"/>
+      <c r="S4" s="83" cm="1">
         <f t="array" ref="S4">MEDIAN(IF(ventas_vendedor=S$1,ventas_unidades))</f>
         <v>3299.5</v>
       </c>
@@ -5984,31 +6137,31 @@
         <f t="array" ref="X4">MEDIAN(IF(ventas_vendedor=X$1,ventas_unidades))</f>
         <v>2578.5</v>
       </c>
-      <c r="AA4" s="99" cm="1">
+      <c r="AA4" s="98" cm="1">
         <f t="array" ref="AA4">MEDIAN(IF(ventas_vendedor=AA$1,ventas_total))</f>
         <v>18058448.5</v>
       </c>
-      <c r="AB4" s="61" cm="1">
+      <c r="AB4" s="60" cm="1">
         <f t="array" ref="AB4">MEDIAN(IF(ventas_vendedor=AB$1,ventas_total))</f>
         <v>21187434</v>
       </c>
-      <c r="AC4" s="61" cm="1">
+      <c r="AC4" s="60" cm="1">
         <f t="array" ref="AC4">MEDIAN(IF(ventas_vendedor=AC$1,ventas_total))</f>
         <v>15867065</v>
       </c>
-      <c r="AD4" s="61" cm="1">
+      <c r="AD4" s="60" cm="1">
         <f t="array" ref="AD4">MEDIAN(IF(ventas_vendedor=AD$1,ventas_total))</f>
         <v>11257947</v>
       </c>
-      <c r="AE4" s="61" cm="1">
+      <c r="AE4" s="60" cm="1">
         <f t="array" ref="AE4">MEDIAN(IF(ventas_vendedor=AE$1,ventas_total))</f>
         <v>19652115.5</v>
       </c>
-      <c r="AF4" s="61" cm="1">
+      <c r="AF4" s="60" cm="1">
         <f t="array" ref="AF4">MEDIAN(IF(ventas_vendedor=AF$1,ventas_total))</f>
         <v>13579772.5</v>
       </c>
-      <c r="AI4" s="84" cm="1">
+      <c r="AI4" s="83" cm="1">
         <f t="array" ref="AI4">MEDIAN(IF(ventas_region=AI$1,ventas_unidades))</f>
         <v>2612.5</v>
       </c>
@@ -6029,28 +6182,68 @@
         <v>2754</v>
       </c>
       <c r="AN4"/>
-      <c r="AP4" s="99" cm="1">
+      <c r="AP4" s="98" cm="1">
         <f t="array" ref="AP4">MEDIAN(IF(ventas_region=AP$1,ventas_total))</f>
         <v>16191526</v>
       </c>
-      <c r="AQ4" s="61" cm="1">
+      <c r="AQ4" s="60" cm="1">
         <f t="array" ref="AQ4">MEDIAN(IF(ventas_region=AQ$1,ventas_total))</f>
         <v>14080030.5</v>
       </c>
-      <c r="AR4" s="61" cm="1">
+      <c r="AR4" s="60" cm="1">
         <f t="array" ref="AR4">MEDIAN(IF(ventas_region=AR$1,ventas_total))</f>
         <v>18076571.5</v>
       </c>
-      <c r="AS4" s="61" cm="1">
+      <c r="AS4" s="60" cm="1">
         <f t="array" ref="AS4">MEDIAN(IF(ventas_region=AS$1,ventas_total))</f>
         <v>16927126</v>
       </c>
-      <c r="AT4" s="61" cm="1">
+      <c r="AT4" s="60" cm="1">
         <f t="array" ref="AT4">MEDIAN(IF(ventas_region=AT$1,ventas_total))</f>
         <v>18114279</v>
       </c>
-    </row>
-    <row r="5" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AW4" s="83" cm="1">
+        <f t="array" ref="AW4">MEDIAN(IF(ventas_año=AW$1,ventas_unidades))</f>
+        <v>3022</v>
+      </c>
+      <c r="AX4" s="19" cm="1">
+        <f t="array" ref="AX4">MEDIAN(IF(ventas_año=AX$1,ventas_unidades))</f>
+        <v>2702</v>
+      </c>
+      <c r="AY4" s="19" cm="1">
+        <f t="array" ref="AY4">MEDIAN(IF(ventas_año=AY$1,ventas_unidades))</f>
+        <v>3020.5</v>
+      </c>
+      <c r="AZ4" s="19" cm="1">
+        <f t="array" ref="AZ4">MEDIAN(IF(ventas_año=AZ$1,ventas_unidades))</f>
+        <v>4983</v>
+      </c>
+      <c r="BA4" s="19" cm="1">
+        <f t="array" ref="BA4">MEDIAN(IF(ventas_año=BA$1,ventas_unidades))</f>
+        <v>1928</v>
+      </c>
+      <c r="BD4" s="98" cm="1">
+        <f t="array" ref="BD4">MEDIAN(IF(ventas_año=BD$1,ventas_total))</f>
+        <v>16523964</v>
+      </c>
+      <c r="BE4" s="60" cm="1">
+        <f t="array" ref="BE4">MEDIAN(IF(ventas_año=BE$1,ventas_total))</f>
+        <v>18016546</v>
+      </c>
+      <c r="BF4" s="60" cm="1">
+        <f t="array" ref="BF4">MEDIAN(IF(ventas_año=BF$1,ventas_total))</f>
+        <v>18201953</v>
+      </c>
+      <c r="BG4" s="60" cm="1">
+        <f t="array" ref="BG4">MEDIAN(IF(ventas_año=BG$1,ventas_total))</f>
+        <v>844832</v>
+      </c>
+      <c r="BH4" s="60" cm="1">
+        <f t="array" ref="BH4">MEDIAN(IF(ventas_año=BH$1,ventas_total))</f>
+        <v>829348</v>
+      </c>
+    </row>
+    <row r="5" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>38</v>
       </c>
@@ -6062,7 +6255,7 @@
         <f>AVERAGE(ventas_total)</f>
         <v>16823008.046875</v>
       </c>
-      <c r="E5" s="83">
+      <c r="E5" s="82">
         <f>AVERAGEIF(ventas_producto,E$1, ventas_unidades)</f>
         <v>2918.5</v>
       </c>
@@ -6082,29 +6275,29 @@
         <f>AVERAGEIF(ventas_producto,I$1, ventas_unidades)</f>
         <v>5353.3589743589746</v>
       </c>
-      <c r="J5" s="78"/>
-      <c r="L5" s="98">
+      <c r="J5" s="77"/>
+      <c r="L5" s="97">
         <f>AVERAGEIF(ventas_producto,L$1, ventas_total)</f>
         <v>17119567.578947369</v>
       </c>
-      <c r="M5" s="60">
+      <c r="M5" s="59">
         <f>AVERAGEIF(ventas_producto,M$1, ventas_total)</f>
         <v>14823702.358974358</v>
       </c>
-      <c r="N5" s="60">
+      <c r="N5" s="59">
         <f>AVERAGEIF(ventas_producto,N$1, ventas_total)</f>
         <v>18162045.684210528</v>
       </c>
-      <c r="O5" s="60">
+      <c r="O5" s="59">
         <f>AVERAGEIF(ventas_producto,O$1, ventas_total)</f>
         <v>17235366.184210528</v>
       </c>
-      <c r="P5" s="60">
+      <c r="P5" s="59">
         <f>AVERAGEIF(ventas_producto,P$1, ventas_total)</f>
         <v>16826870.102564104</v>
       </c>
-      <c r="Q5" s="77"/>
-      <c r="S5" s="83">
+      <c r="Q5" s="76"/>
+      <c r="S5" s="82">
         <f t="shared" ref="S5:X5" si="4">AVERAGEIF(ventas_vendedor,S$1, ventas_unidades)</f>
         <v>3201.7105263157896</v>
       </c>
@@ -6128,31 +6321,31 @@
         <f t="shared" si="4"/>
         <v>2631.4210526315787</v>
       </c>
-      <c r="AA5" s="98">
+      <c r="AA5" s="97">
         <f t="shared" ref="AA5:AF5" si="5">AVERAGEIF(ventas_vendedor,AA$1, ventas_total)</f>
         <v>16976712.263157893</v>
       </c>
-      <c r="AB5" s="60">
+      <c r="AB5" s="59">
         <f t="shared" si="5"/>
         <v>20038545.184210528</v>
       </c>
-      <c r="AC5" s="60">
+      <c r="AC5" s="59">
         <f t="shared" si="5"/>
         <v>17440214.230769232</v>
       </c>
-      <c r="AD5" s="60">
+      <c r="AD5" s="59">
         <f t="shared" si="5"/>
         <v>12490307.640000001</v>
       </c>
-      <c r="AE5" s="60">
+      <c r="AE5" s="59">
         <f t="shared" si="5"/>
         <v>18062589.050000001</v>
       </c>
-      <c r="AF5" s="60">
+      <c r="AF5" s="59">
         <f t="shared" si="5"/>
         <v>14788255.894736841</v>
       </c>
-      <c r="AI5" s="83">
+      <c r="AI5" s="82">
         <f>AVERAGEIF(ventas_region,AI$1, ventas_unidades)</f>
         <v>2897.6052631578946</v>
       </c>
@@ -6173,40 +6366,80 @@
         <v>2865.8378378378379</v>
       </c>
       <c r="AN5"/>
-      <c r="AP5" s="98">
+      <c r="AP5" s="97">
         <f>AVERAGEIF(ventas_region,AP$1, ventas_total)</f>
         <v>17002814.789473683</v>
       </c>
-      <c r="AQ5" s="65">
+      <c r="AQ5" s="64">
         <f>AVERAGEIF(ventas_region,AQ$1, ventas_total)</f>
         <v>15179061.47368421</v>
       </c>
-      <c r="AR5" s="65">
+      <c r="AR5" s="64">
         <f>AVERAGEIF(ventas_region,AR$1, ventas_total)</f>
         <v>17192663.25</v>
       </c>
-      <c r="AS5" s="60">
+      <c r="AS5" s="59">
         <f>AVERAGEIF(ventas_region,AS$1, ventas_total)</f>
         <v>16786607.487179488</v>
       </c>
-      <c r="AT5" s="65">
+      <c r="AT5" s="64">
         <f>AVERAGEIF(ventas_region,AT$1, ventas_total)</f>
         <v>17965460.135135137</v>
       </c>
-    </row>
-    <row r="6" spans="1:47" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="AW5" s="82">
+        <f>AVERAGEIF(ventas_año,AW$1, ventas_unidades)</f>
+        <v>3033.0333333333333</v>
+      </c>
+      <c r="AX5" s="30">
+        <f>AVERAGEIF(ventas_año,AX$1, ventas_unidades)</f>
+        <v>2777.7333333333331</v>
+      </c>
+      <c r="AY5" s="30">
+        <f>AVERAGEIF(ventas_año,AY$1, ventas_unidades)</f>
+        <v>2910.9166666666665</v>
+      </c>
+      <c r="AZ5" s="18">
+        <f>AVERAGEIF(ventas_año,AZ$1, ventas_unidades)</f>
+        <v>18520.285714285714</v>
+      </c>
+      <c r="BA5" s="30">
+        <f>AVERAGEIF(ventas_año,BA$1, ventas_unidades)</f>
+        <v>41056.800000000003</v>
+      </c>
+      <c r="BD5" s="97">
+        <f>AVERAGEIF(ventas_año,BD$1, ventas_total)</f>
+        <v>16787402.516666666</v>
+      </c>
+      <c r="BE5" s="64">
+        <f>AVERAGEIF(ventas_año,BE$1, ventas_total)</f>
+        <v>18447441.199999999</v>
+      </c>
+      <c r="BF5" s="64">
+        <f>AVERAGEIF(ventas_año,BF$1, ventas_total)</f>
+        <v>18155172.449999999</v>
+      </c>
+      <c r="BG5" s="59">
+        <f>AVERAGEIF(ventas_año,BG$1, ventas_total)</f>
+        <v>2154674.4285714286</v>
+      </c>
+      <c r="BH5" s="64">
+        <f>AVERAGEIF(ventas_año,BH$1, ventas_total)</f>
+        <v>2306770.7999999998</v>
+      </c>
+    </row>
+    <row r="6" spans="1:61" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B6" s="43">
+      <c r="B6" s="123">
         <f>SUM(ventas_unidades)</f>
         <v>858227</v>
       </c>
-      <c r="C6" s="44">
+      <c r="C6" s="124">
         <f>SUM(ventas_total)</f>
         <v>3230017545</v>
       </c>
-      <c r="E6" s="85">
+      <c r="E6" s="84">
         <f>SUMIF(ventas_producto,E$1,ventas_unidades)</f>
         <v>110903</v>
       </c>
@@ -6226,29 +6459,35 @@
         <f>SUMIF(ventas_producto,I$1,ventas_unidades)</f>
         <v>208781</v>
       </c>
-      <c r="J6" s="78"/>
-      <c r="L6" s="100">
+      <c r="J6" s="131">
+        <f>SUM(E6:I6)</f>
+        <v>858227</v>
+      </c>
+      <c r="L6" s="99">
         <f>SUMIF(ventas_producto,L$1,ventas_total)</f>
         <v>650543568</v>
       </c>
-      <c r="M6" s="62">
+      <c r="M6" s="61">
         <f>SUMIF(ventas_producto,M$1,ventas_total)</f>
         <v>578124392</v>
       </c>
-      <c r="N6" s="62">
+      <c r="N6" s="61">
         <f>SUMIF(ventas_producto,N$1,ventas_total)</f>
         <v>690157736</v>
       </c>
-      <c r="O6" s="62">
+      <c r="O6" s="61">
         <f>SUMIF(ventas_producto,O$1,ventas_total)</f>
         <v>654943915</v>
       </c>
-      <c r="P6" s="62">
+      <c r="P6" s="61">
         <f>SUMIF(ventas_producto,P$1,ventas_total)</f>
         <v>656247934</v>
       </c>
-      <c r="Q6" s="77"/>
-      <c r="S6" s="85">
+      <c r="Q6" s="132">
+        <f>SUM(L6:P6)</f>
+        <v>3230017545</v>
+      </c>
+      <c r="S6" s="84">
         <f t="shared" ref="S6:X6" si="6">SUMIF(ventas_vendedor,S$1,ventas_unidades)</f>
         <v>121665</v>
       </c>
@@ -6272,31 +6511,34 @@
         <f t="shared" si="6"/>
         <v>99994</v>
       </c>
-      <c r="AA6" s="100">
+      <c r="Y6" s="131"/>
+      <c r="Z6" s="133"/>
+      <c r="AA6" s="99">
         <f t="shared" ref="AA6:AF6" si="7">SUMIF(ventas_vendedor,AA$1,ventas_total)</f>
         <v>645115066</v>
       </c>
-      <c r="AB6" s="62">
+      <c r="AB6" s="61">
         <f t="shared" si="7"/>
         <v>761464717</v>
       </c>
-      <c r="AC6" s="62">
+      <c r="AC6" s="61">
         <f t="shared" si="7"/>
         <v>226722785</v>
       </c>
-      <c r="AD6" s="62">
+      <c r="AD6" s="61">
         <f t="shared" si="7"/>
         <v>312257691</v>
       </c>
-      <c r="AE6" s="62">
+      <c r="AE6" s="61">
         <f t="shared" si="7"/>
         <v>722503562</v>
       </c>
-      <c r="AF6" s="62">
+      <c r="AF6" s="61">
         <f t="shared" si="7"/>
         <v>561953724</v>
       </c>
-      <c r="AI6" s="85">
+      <c r="AG6" s="132"/>
+      <c r="AI6" s="84">
         <f>SUMIF(ventas_region,AI$1,ventas_unidades)</f>
         <v>110109</v>
       </c>
@@ -6316,30 +6558,82 @@
         <f>SUMIF(ventas_region,AM$1,ventas_unidades)</f>
         <v>106036</v>
       </c>
-      <c r="AN6"/>
-      <c r="AP6" s="100">
+      <c r="AN6" s="134"/>
+      <c r="AP6" s="99">
         <f>SUMIF(ventas_region,AP$1,ventas_total)</f>
         <v>646106962</v>
       </c>
-      <c r="AQ6" s="72">
+      <c r="AQ6" s="71">
         <f>SUMIF(ventas_region,AQ$1,ventas_total)</f>
         <v>576804336</v>
       </c>
-      <c r="AR6" s="72">
+      <c r="AR6" s="71">
         <f>SUMIF(ventas_region,AR$1,ventas_total)</f>
         <v>687706530</v>
       </c>
-      <c r="AS6" s="62">
+      <c r="AS6" s="61">
         <f>SUMIF(ventas_region,AS$1,ventas_total)</f>
         <v>654677692</v>
       </c>
-      <c r="AT6" s="72">
+      <c r="AT6" s="71">
         <f>SUMIF(ventas_region,AT$1,ventas_total)</f>
         <v>664722025</v>
       </c>
-    </row>
-    <row r="7" spans="1:47" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="8" spans="1:47" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="AU6" s="135">
+        <f>SUM(AP6:AT6)</f>
+        <v>3230017545</v>
+      </c>
+      <c r="AW6" s="84">
+        <f>SUMIF(ventas_año,AW$1,ventas_unidades)</f>
+        <v>181982</v>
+      </c>
+      <c r="AX6" s="43">
+        <f>SUMIF(ventas_año,AX$1,ventas_unidades)</f>
+        <v>166664</v>
+      </c>
+      <c r="AY6" s="43">
+        <f>SUMIF(ventas_año,AY$1,ventas_unidades)</f>
+        <v>174655</v>
+      </c>
+      <c r="AZ6" s="20">
+        <f>SUMIF(ventas_año,AZ$1,ventas_unidades)</f>
+        <v>129642</v>
+      </c>
+      <c r="BA6" s="43">
+        <f>SUMIF(ventas_año,BA$1,ventas_unidades)</f>
+        <v>205284</v>
+      </c>
+      <c r="BB6" s="130">
+        <f>SUM(AW6:BA6)</f>
+        <v>858227</v>
+      </c>
+      <c r="BD6" s="99">
+        <f>SUMIF(ventas_año,BD$1,ventas_total)</f>
+        <v>1007244151</v>
+      </c>
+      <c r="BE6" s="71">
+        <f>SUMIF(ventas_año,BE$1,ventas_total)</f>
+        <v>1106846472</v>
+      </c>
+      <c r="BF6" s="71">
+        <f>SUMIF(ventas_año,BF$1,ventas_total)</f>
+        <v>1089310347</v>
+      </c>
+      <c r="BG6" s="61">
+        <f>SUMIF(ventas_año,BG$1,ventas_total)</f>
+        <v>15082721</v>
+      </c>
+      <c r="BH6" s="71">
+        <f>SUMIF(ventas_año,BH$1,ventas_total)</f>
+        <v>11533854</v>
+      </c>
+      <c r="BI6" s="135">
+        <f>SUM(BD6:BH6)</f>
+        <v>3230017545</v>
+      </c>
+    </row>
+    <row r="7" spans="1:61" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="8" spans="1:61" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="7" t="s">
         <v>45</v>
       </c>
@@ -6349,80 +6643,80 @@
       <c r="C8" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="D8" s="80"/>
-      <c r="E8" s="121"/>
-      <c r="F8" s="121"/>
-      <c r="G8" s="121"/>
-      <c r="H8" s="121"/>
-      <c r="I8" s="121"/>
-      <c r="J8" s="121"/>
-      <c r="L8" s="108"/>
-      <c r="M8" s="123"/>
-      <c r="N8" s="123"/>
-      <c r="O8" s="123"/>
-      <c r="P8" s="123"/>
-      <c r="Q8" s="123"/>
-      <c r="S8" s="89" t="s">
+      <c r="D8" s="79"/>
+      <c r="E8" s="120"/>
+      <c r="F8" s="120"/>
+      <c r="G8" s="120"/>
+      <c r="H8" s="120"/>
+      <c r="I8" s="120"/>
+      <c r="J8" s="120"/>
+      <c r="L8" s="107"/>
+      <c r="M8" s="122"/>
+      <c r="N8" s="122"/>
+      <c r="O8" s="122"/>
+      <c r="P8" s="122"/>
+      <c r="Q8" s="122"/>
+      <c r="S8" s="88" t="s">
         <v>28</v>
       </c>
-      <c r="T8" s="55" t="s">
+      <c r="T8" s="54" t="s">
         <v>8</v>
       </c>
-      <c r="U8" s="55" t="s">
+      <c r="U8" s="54" t="s">
         <v>11</v>
       </c>
-      <c r="V8" s="55" t="s">
+      <c r="V8" s="54" t="s">
         <v>13</v>
       </c>
-      <c r="W8" s="55" t="s">
+      <c r="W8" s="54" t="s">
         <v>29</v>
       </c>
-      <c r="X8" s="55" t="s">
+      <c r="X8" s="54" t="s">
         <v>30</v>
       </c>
-      <c r="Y8" s="55" t="s">
+      <c r="Y8" s="54" t="s">
         <v>39</v>
       </c>
-      <c r="AA8" s="103" t="s">
+      <c r="AA8" s="102" t="s">
         <v>28</v>
       </c>
-      <c r="AB8" s="63" t="s">
+      <c r="AB8" s="62" t="s">
         <v>8</v>
       </c>
-      <c r="AC8" s="63" t="s">
+      <c r="AC8" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="AD8" s="63" t="s">
+      <c r="AD8" s="62" t="s">
         <v>13</v>
       </c>
-      <c r="AE8" s="63" t="s">
+      <c r="AE8" s="62" t="s">
         <v>29</v>
       </c>
-      <c r="AF8" s="63" t="s">
+      <c r="AF8" s="62" t="s">
         <v>30</v>
       </c>
-      <c r="AG8" s="63" t="s">
+      <c r="AG8" s="62" t="s">
         <v>39</v>
       </c>
-      <c r="AI8" s="87" t="s">
+      <c r="AI8" s="86" t="s">
         <v>31</v>
       </c>
-      <c r="AJ8" s="53" t="s">
+      <c r="AJ8" s="52" t="s">
         <v>9</v>
       </c>
-      <c r="AK8" s="53" t="s">
+      <c r="AK8" s="52" t="s">
         <v>16</v>
       </c>
-      <c r="AL8" s="53" t="s">
+      <c r="AL8" s="52" t="s">
         <v>19</v>
       </c>
-      <c r="AM8" s="53" t="s">
+      <c r="AM8" s="52" t="s">
         <v>21</v>
       </c>
-      <c r="AN8" s="53" t="s">
+      <c r="AN8" s="52" t="s">
         <v>34</v>
       </c>
-      <c r="AP8" s="81" t="s">
+      <c r="AP8" s="80" t="s">
         <v>31</v>
       </c>
       <c r="AQ8" s="7" t="s">
@@ -6440,8 +6734,45 @@
       <c r="AU8" s="7" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="9" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AW8" s="125">
+        <v>2008</v>
+      </c>
+      <c r="AX8" s="21">
+        <v>2009</v>
+      </c>
+      <c r="AY8" s="21">
+        <v>2010</v>
+      </c>
+      <c r="AZ8" s="21">
+        <v>2011</v>
+      </c>
+      <c r="BA8" s="21">
+        <v>2012</v>
+      </c>
+      <c r="BB8" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="BC8" s="2"/>
+      <c r="BD8" s="125">
+        <v>2008</v>
+      </c>
+      <c r="BE8" s="21">
+        <v>2009</v>
+      </c>
+      <c r="BF8" s="21">
+        <v>2010</v>
+      </c>
+      <c r="BG8" s="21">
+        <v>2011</v>
+      </c>
+      <c r="BH8" s="21">
+        <v>2012</v>
+      </c>
+      <c r="BI8" s="7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A9" s="28" t="s">
         <v>6</v>
       </c>
@@ -6453,20 +6784,20 @@
         <f>SUMIF(ventas_producto,$A9,ventas_total)</f>
         <v>650543568</v>
       </c>
-      <c r="D9" s="80"/>
-      <c r="E9" s="121"/>
-      <c r="F9" s="121"/>
-      <c r="G9" s="121"/>
-      <c r="H9" s="121"/>
-      <c r="I9" s="121"/>
-      <c r="J9" s="121"/>
-      <c r="L9" s="108"/>
-      <c r="M9" s="123"/>
-      <c r="N9" s="123"/>
-      <c r="O9" s="123"/>
-      <c r="P9" s="123"/>
-      <c r="Q9" s="123"/>
-      <c r="S9" s="90">
+      <c r="D9" s="79"/>
+      <c r="E9" s="120"/>
+      <c r="F9" s="120"/>
+      <c r="G9" s="120"/>
+      <c r="H9" s="120"/>
+      <c r="I9" s="120"/>
+      <c r="J9" s="120"/>
+      <c r="L9" s="107"/>
+      <c r="M9" s="122"/>
+      <c r="N9" s="122"/>
+      <c r="O9" s="122"/>
+      <c r="P9" s="122"/>
+      <c r="Q9" s="122"/>
+      <c r="S9" s="89">
         <f t="shared" ref="S9:X13" si="8">SUMIFS(ventas_unidades,ventas_producto,$A9,ventas_vendedor,S$8)</f>
         <v>23075</v>
       </c>
@@ -6494,35 +6825,35 @@
         <f>SUM(S9:X9)</f>
         <v>110903</v>
       </c>
-      <c r="AA9" s="104">
+      <c r="AA9" s="103">
         <f t="shared" ref="AA9:AF13" si="9">SUMIFS(ventas_total,ventas_producto,$A9,ventas_vendedor,AA$8)</f>
         <v>109144041</v>
       </c>
-      <c r="AB9" s="64">
+      <c r="AB9" s="63">
         <f t="shared" si="9"/>
         <v>193222871</v>
       </c>
-      <c r="AC9" s="64">
+      <c r="AC9" s="63">
         <f t="shared" si="9"/>
         <v>59797810</v>
       </c>
-      <c r="AD9" s="64">
+      <c r="AD9" s="63">
         <f t="shared" si="9"/>
         <v>135280108</v>
       </c>
-      <c r="AE9" s="64">
+      <c r="AE9" s="63">
         <f t="shared" si="9"/>
         <v>103659911</v>
       </c>
-      <c r="AF9" s="64">
+      <c r="AF9" s="63">
         <f t="shared" si="9"/>
         <v>49438827</v>
       </c>
-      <c r="AG9" s="64">
+      <c r="AG9" s="63">
         <f>SUM(AA9:AF9)</f>
         <v>650543568</v>
       </c>
-      <c r="AI9" s="82">
+      <c r="AI9" s="81">
         <f t="shared" ref="AI9:AM13" si="10">SUMIFS(ventas_unidades,ventas_producto,$A9,ventas_region,AI$8)</f>
         <v>101037</v>
       </c>
@@ -6546,32 +6877,80 @@
         <f>SUM(AI9:AM9)</f>
         <v>110903</v>
       </c>
-      <c r="AP9" s="97">
+      <c r="AP9" s="96">
         <f t="shared" ref="AP9:AT13" si="11">SUMIFS(ventas_total,ventas_producto,$A9,ventas_region,AP$8)</f>
         <v>640574818</v>
       </c>
-      <c r="AQ9" s="59">
+      <c r="AQ9" s="58">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AR9" s="59">
+      <c r="AR9" s="58">
         <f t="shared" si="11"/>
         <v>844832</v>
       </c>
-      <c r="AS9" s="59">
+      <c r="AS9" s="58">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AT9" s="59">
+      <c r="AT9" s="58">
         <f t="shared" si="11"/>
         <v>9123918</v>
       </c>
-      <c r="AU9" s="59">
+      <c r="AU9" s="58">
         <f>SUM(AP9:AT9)</f>
         <v>650543568</v>
       </c>
-    </row>
-    <row r="10" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AW9" s="81">
+        <f>SUMIFS(ventas_unidades,ventas_producto,$A9,ventas_año,AW$8)</f>
+        <v>33032</v>
+      </c>
+      <c r="AX9" s="17">
+        <f>SUMIFS(ventas_unidades,ventas_producto,$A9,ventas_año,AX$8)</f>
+        <v>32671</v>
+      </c>
+      <c r="AY9" s="17">
+        <f>SUMIFS(ventas_unidades,ventas_producto,$A9,ventas_año,AY$8)</f>
+        <v>35334</v>
+      </c>
+      <c r="AZ9" s="17">
+        <f>SUMIFS(ventas_unidades,ventas_producto,$A9,ventas_año,AZ$8)</f>
+        <v>2738</v>
+      </c>
+      <c r="BA9" s="17">
+        <f>SUMIFS(ventas_unidades,ventas_producto,$A9,ventas_año,BA$8)</f>
+        <v>7128</v>
+      </c>
+      <c r="BB9" s="17">
+        <f>SUM(AW9:BA9)</f>
+        <v>110903</v>
+      </c>
+      <c r="BD9" s="96">
+        <f>SUMIFS(ventas_total,ventas_producto,$A9,ventas_año,BD$8)</f>
+        <v>218669111</v>
+      </c>
+      <c r="BE9" s="58">
+        <f>SUMIFS(ventas_total,ventas_producto,$A9,ventas_año,BE$8)</f>
+        <v>203341463</v>
+      </c>
+      <c r="BF9" s="58">
+        <f>SUMIFS(ventas_total,ventas_producto,$A9,ventas_año,BF$8)</f>
+        <v>218564244</v>
+      </c>
+      <c r="BG9" s="58">
+        <f>SUMIFS(ventas_total,ventas_producto,$A9,ventas_año,BG$8)</f>
+        <v>844832</v>
+      </c>
+      <c r="BH9" s="58">
+        <f>SUMIFS(ventas_total,ventas_producto,$A9,ventas_año,BH$8)</f>
+        <v>9123918</v>
+      </c>
+      <c r="BI9" s="58">
+        <f>SUM(BD9:BH9)</f>
+        <v>650543568</v>
+      </c>
+    </row>
+    <row r="10" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
         <v>33</v>
       </c>
@@ -6583,20 +6962,20 @@
         <f>SUMIF(ventas_producto,$A10,ventas_total)</f>
         <v>578124392</v>
       </c>
-      <c r="D10" s="80"/>
-      <c r="E10" s="121"/>
-      <c r="F10" s="121"/>
-      <c r="G10" s="121"/>
-      <c r="H10" s="121"/>
-      <c r="I10" s="121"/>
-      <c r="J10" s="121"/>
-      <c r="L10" s="108"/>
-      <c r="M10" s="123"/>
-      <c r="N10" s="123"/>
-      <c r="O10" s="123"/>
-      <c r="P10" s="123"/>
-      <c r="Q10" s="123"/>
-      <c r="S10" s="91">
+      <c r="D10" s="79"/>
+      <c r="E10" s="120"/>
+      <c r="F10" s="120"/>
+      <c r="G10" s="120"/>
+      <c r="H10" s="120"/>
+      <c r="I10" s="120"/>
+      <c r="J10" s="120"/>
+      <c r="L10" s="107"/>
+      <c r="M10" s="122"/>
+      <c r="N10" s="122"/>
+      <c r="O10" s="122"/>
+      <c r="P10" s="122"/>
+      <c r="Q10" s="122"/>
+      <c r="S10" s="90">
         <f t="shared" si="8"/>
         <v>14026</v>
       </c>
@@ -6624,84 +7003,132 @@
         <f t="shared" ref="Y10:Y13" si="12">SUM(S10:X10)</f>
         <v>304519</v>
       </c>
-      <c r="AA10" s="105">
+      <c r="AA10" s="104">
         <f t="shared" si="9"/>
         <v>53223672</v>
       </c>
-      <c r="AB10" s="65">
+      <c r="AB10" s="64">
         <f t="shared" si="9"/>
         <v>271532147</v>
       </c>
-      <c r="AC10" s="65">
+      <c r="AC10" s="64">
         <f t="shared" si="9"/>
         <v>63246530</v>
       </c>
-      <c r="AD10" s="65">
+      <c r="AD10" s="64">
         <f t="shared" si="9"/>
         <v>45710704</v>
       </c>
-      <c r="AE10" s="65">
+      <c r="AE10" s="64">
         <f t="shared" si="9"/>
         <v>93604609</v>
       </c>
-      <c r="AF10" s="65">
+      <c r="AF10" s="64">
         <f t="shared" si="9"/>
         <v>50806730</v>
       </c>
-      <c r="AG10" s="65">
+      <c r="AG10" s="64">
         <f t="shared" ref="AG10:AG13" si="13">SUM(AA10:AF10)</f>
         <v>578124392</v>
       </c>
-      <c r="AI10" s="83">
+      <c r="AI10" s="82">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AJ10" s="47">
+      <c r="AJ10" s="46">
         <f t="shared" si="10"/>
         <v>105314</v>
       </c>
-      <c r="AK10" s="47">
+      <c r="AK10" s="46">
         <f t="shared" si="10"/>
         <v>1928</v>
       </c>
-      <c r="AL10" s="47">
+      <c r="AL10" s="46">
         <f t="shared" si="10"/>
         <v>197277</v>
       </c>
-      <c r="AM10" s="47">
+      <c r="AM10" s="46">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AN10" s="47">
+      <c r="AN10" s="46">
         <f t="shared" ref="AN10:AN13" si="14">SUM(AI10:AM10)</f>
         <v>304519</v>
       </c>
-      <c r="AP10" s="98">
+      <c r="AP10" s="97">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AQ10" s="70">
+      <c r="AQ10" s="69">
         <f t="shared" si="11"/>
         <v>576702901</v>
       </c>
-      <c r="AR10" s="70">
+      <c r="AR10" s="69">
         <f t="shared" si="11"/>
         <v>108214</v>
       </c>
-      <c r="AS10" s="70">
+      <c r="AS10" s="69">
         <f t="shared" si="11"/>
         <v>1313277</v>
       </c>
-      <c r="AT10" s="70">
+      <c r="AT10" s="69">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AU10" s="70">
+      <c r="AU10" s="69">
         <f t="shared" ref="AU10:AU13" si="15">SUM(AP10:AT10)</f>
         <v>578124392</v>
       </c>
-    </row>
-    <row r="11" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AW10" s="82">
+        <f>SUMIFS(ventas_unidades,ventas_producto,$A10,ventas_año,AW$8)</f>
+        <v>32696</v>
+      </c>
+      <c r="AX10" s="46">
+        <f>SUMIFS(ventas_unidades,ventas_producto,$A10,ventas_año,AX$8)</f>
+        <v>31651</v>
+      </c>
+      <c r="AY10" s="46">
+        <f>SUMIFS(ventas_unidades,ventas_producto,$A10,ventas_año,AY$8)</f>
+        <v>40967</v>
+      </c>
+      <c r="AZ10" s="46">
+        <f>SUMIFS(ventas_unidades,ventas_producto,$A10,ventas_año,AZ$8)</f>
+        <v>4903</v>
+      </c>
+      <c r="BA10" s="46">
+        <f>SUMIFS(ventas_unidades,ventas_producto,$A10,ventas_año,BA$8)</f>
+        <v>194302</v>
+      </c>
+      <c r="BB10" s="46">
+        <f t="shared" ref="BB10:BB13" si="16">SUM(AW10:BA10)</f>
+        <v>304519</v>
+      </c>
+      <c r="BD10" s="97">
+        <f>SUMIFS(ventas_total,ventas_producto,$A10,ventas_año,BD$8)</f>
+        <v>160364763</v>
+      </c>
+      <c r="BE10" s="69">
+        <f>SUMIFS(ventas_total,ventas_producto,$A10,ventas_año,BE$8)</f>
+        <v>201880917</v>
+      </c>
+      <c r="BF10" s="69">
+        <f>SUMIFS(ventas_total,ventas_producto,$A10,ventas_año,BF$8)</f>
+        <v>214457221</v>
+      </c>
+      <c r="BG10" s="69">
+        <f>SUMIFS(ventas_total,ventas_producto,$A10,ventas_año,BG$8)</f>
+        <v>483929</v>
+      </c>
+      <c r="BH10" s="69">
+        <f>SUMIFS(ventas_total,ventas_producto,$A10,ventas_año,BH$8)</f>
+        <v>937562</v>
+      </c>
+      <c r="BI10" s="69">
+        <f t="shared" ref="BI10:BI13" si="17">SUM(BD10:BH10)</f>
+        <v>578124392</v>
+      </c>
+    </row>
+    <row r="11" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A11" s="27" t="s">
         <v>15</v>
       </c>
@@ -6713,20 +7140,20 @@
         <f>SUMIF(ventas_producto,$A11,ventas_total)</f>
         <v>690157736</v>
       </c>
-      <c r="D11" s="80"/>
-      <c r="E11" s="121"/>
-      <c r="F11" s="121"/>
-      <c r="G11" s="121"/>
-      <c r="H11" s="121"/>
-      <c r="I11" s="121"/>
-      <c r="J11" s="121"/>
-      <c r="L11" s="108"/>
-      <c r="M11" s="123"/>
-      <c r="N11" s="123"/>
-      <c r="O11" s="123"/>
-      <c r="P11" s="123"/>
-      <c r="Q11" s="123"/>
-      <c r="S11" s="92">
+      <c r="D11" s="79"/>
+      <c r="E11" s="120"/>
+      <c r="F11" s="120"/>
+      <c r="G11" s="120"/>
+      <c r="H11" s="120"/>
+      <c r="I11" s="120"/>
+      <c r="J11" s="120"/>
+      <c r="L11" s="107"/>
+      <c r="M11" s="122"/>
+      <c r="N11" s="122"/>
+      <c r="O11" s="122"/>
+      <c r="P11" s="122"/>
+      <c r="Q11" s="122"/>
+      <c r="S11" s="91">
         <f t="shared" si="8"/>
         <v>37242</v>
       </c>
@@ -6754,84 +7181,132 @@
         <f t="shared" si="12"/>
         <v>118380</v>
       </c>
-      <c r="AA11" s="106">
+      <c r="AA11" s="105">
         <f t="shared" si="9"/>
         <v>240818885</v>
       </c>
-      <c r="AB11" s="66">
+      <c r="AB11" s="65">
         <f t="shared" si="9"/>
         <v>131950052</v>
       </c>
-      <c r="AC11" s="66">
+      <c r="AC11" s="65">
         <f t="shared" si="9"/>
         <v>40433106</v>
       </c>
-      <c r="AD11" s="66">
+      <c r="AD11" s="65">
         <f t="shared" si="9"/>
         <v>31481567</v>
       </c>
-      <c r="AE11" s="66">
+      <c r="AE11" s="65">
         <f t="shared" si="9"/>
         <v>77744662</v>
       </c>
-      <c r="AF11" s="66">
+      <c r="AF11" s="65">
         <f t="shared" si="9"/>
         <v>167729464</v>
       </c>
-      <c r="AG11" s="66">
+      <c r="AG11" s="65">
         <f t="shared" si="13"/>
         <v>690157736</v>
       </c>
-      <c r="AI11" s="84">
+      <c r="AI11" s="83">
         <f t="shared" si="10"/>
         <v>8943</v>
       </c>
-      <c r="AJ11" s="48">
+      <c r="AJ11" s="47">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AK11" s="48">
+      <c r="AK11" s="47">
         <f t="shared" si="10"/>
         <v>109437</v>
       </c>
-      <c r="AL11" s="48">
+      <c r="AL11" s="47">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AM11" s="48">
+      <c r="AM11" s="47">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AN11" s="48">
+      <c r="AN11" s="47">
         <f t="shared" si="14"/>
         <v>118380</v>
       </c>
-      <c r="AP11" s="99">
+      <c r="AP11" s="98">
         <f t="shared" si="11"/>
         <v>4328234</v>
       </c>
-      <c r="AQ11" s="71">
+      <c r="AQ11" s="70">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AR11" s="71">
+      <c r="AR11" s="70">
         <f t="shared" si="11"/>
         <v>685829502</v>
       </c>
-      <c r="AS11" s="71">
+      <c r="AS11" s="70">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AT11" s="71">
+      <c r="AT11" s="70">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AU11" s="71">
+      <c r="AU11" s="70">
         <f t="shared" si="15"/>
         <v>690157736</v>
       </c>
-    </row>
-    <row r="12" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AW11" s="83">
+        <f>SUMIFS(ventas_unidades,ventas_producto,$A11,ventas_año,AW$8)</f>
+        <v>39124</v>
+      </c>
+      <c r="AX11" s="47">
+        <f>SUMIFS(ventas_unidades,ventas_producto,$A11,ventas_año,AX$8)</f>
+        <v>34000</v>
+      </c>
+      <c r="AY11" s="47">
+        <f>SUMIFS(ventas_unidades,ventas_producto,$A11,ventas_año,AY$8)</f>
+        <v>31330</v>
+      </c>
+      <c r="AZ11" s="47">
+        <f>SUMIFS(ventas_unidades,ventas_producto,$A11,ventas_año,AZ$8)</f>
+        <v>13926</v>
+      </c>
+      <c r="BA11" s="47">
+        <f>SUMIFS(ventas_unidades,ventas_producto,$A11,ventas_año,BA$8)</f>
+        <v>0</v>
+      </c>
+      <c r="BB11" s="47">
+        <f t="shared" si="16"/>
+        <v>118380</v>
+      </c>
+      <c r="BD11" s="98">
+        <f>SUMIFS(ventas_total,ventas_producto,$A11,ventas_año,BD$8)</f>
+        <v>220801841</v>
+      </c>
+      <c r="BE11" s="70">
+        <f>SUMIFS(ventas_total,ventas_producto,$A11,ventas_año,BE$8)</f>
+        <v>239992813</v>
+      </c>
+      <c r="BF11" s="70">
+        <f>SUMIFS(ventas_total,ventas_producto,$A11,ventas_año,BF$8)</f>
+        <v>216914467</v>
+      </c>
+      <c r="BG11" s="70">
+        <f>SUMIFS(ventas_total,ventas_producto,$A11,ventas_año,BG$8)</f>
+        <v>12448615</v>
+      </c>
+      <c r="BH11" s="70">
+        <f>SUMIFS(ventas_total,ventas_producto,$A11,ventas_año,BH$8)</f>
+        <v>0</v>
+      </c>
+      <c r="BI11" s="70">
+        <f t="shared" si="17"/>
+        <v>690157736</v>
+      </c>
+    </row>
+    <row r="12" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A12" s="26" t="s">
         <v>18</v>
       </c>
@@ -6843,20 +7318,20 @@
         <f>SUMIF(ventas_producto,$A12,ventas_total)</f>
         <v>654943915</v>
       </c>
-      <c r="D12" s="80"/>
-      <c r="E12" s="121"/>
-      <c r="F12" s="121"/>
-      <c r="G12" s="121"/>
-      <c r="H12" s="121"/>
-      <c r="I12" s="121"/>
-      <c r="J12" s="121"/>
-      <c r="L12" s="108"/>
-      <c r="M12" s="123"/>
-      <c r="N12" s="123"/>
-      <c r="O12" s="123"/>
-      <c r="P12" s="123"/>
-      <c r="Q12" s="123"/>
-      <c r="S12" s="91">
+      <c r="D12" s="79"/>
+      <c r="E12" s="120"/>
+      <c r="F12" s="120"/>
+      <c r="G12" s="120"/>
+      <c r="H12" s="120"/>
+      <c r="I12" s="120"/>
+      <c r="J12" s="120"/>
+      <c r="L12" s="107"/>
+      <c r="M12" s="122"/>
+      <c r="N12" s="122"/>
+      <c r="O12" s="122"/>
+      <c r="P12" s="122"/>
+      <c r="Q12" s="122"/>
+      <c r="S12" s="90">
         <f t="shared" si="8"/>
         <v>34352</v>
       </c>
@@ -6884,84 +7359,132 @@
         <f t="shared" si="12"/>
         <v>115644</v>
       </c>
-      <c r="AA12" s="105">
+      <c r="AA12" s="104">
         <f t="shared" si="9"/>
         <v>169977929</v>
       </c>
-      <c r="AB12" s="65">
+      <c r="AB12" s="64">
         <f t="shared" si="9"/>
         <v>75839132</v>
       </c>
-      <c r="AC12" s="65">
+      <c r="AC12" s="64">
         <f t="shared" si="9"/>
         <v>31378227</v>
       </c>
-      <c r="AD12" s="65">
+      <c r="AD12" s="64">
         <f t="shared" si="9"/>
         <v>23001252</v>
       </c>
-      <c r="AE12" s="65">
+      <c r="AE12" s="64">
         <f t="shared" si="9"/>
         <v>336958448</v>
       </c>
-      <c r="AF12" s="65">
+      <c r="AF12" s="64">
         <f t="shared" si="9"/>
         <v>17788927</v>
       </c>
-      <c r="AG12" s="65">
+      <c r="AG12" s="64">
         <f t="shared" si="13"/>
         <v>654943915</v>
       </c>
-      <c r="AI12" s="83">
+      <c r="AI12" s="82">
         <f t="shared" si="10"/>
         <v>129</v>
       </c>
-      <c r="AJ12" s="47">
+      <c r="AJ12" s="46">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AK12" s="47">
+      <c r="AK12" s="46">
         <f t="shared" si="10"/>
         <v>1927</v>
       </c>
-      <c r="AL12" s="47">
+      <c r="AL12" s="46">
         <f t="shared" si="10"/>
         <v>113588</v>
       </c>
-      <c r="AM12" s="47">
+      <c r="AM12" s="46">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AN12" s="47">
+      <c r="AN12" s="46">
         <f t="shared" si="14"/>
         <v>115644</v>
       </c>
-      <c r="AP12" s="98">
+      <c r="AP12" s="97">
         <f t="shared" si="11"/>
         <v>1203910</v>
       </c>
-      <c r="AQ12" s="70">
+      <c r="AQ12" s="69">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AR12" s="70">
+      <c r="AR12" s="69">
         <f t="shared" si="11"/>
         <v>923982</v>
       </c>
-      <c r="AS12" s="70">
+      <c r="AS12" s="69">
         <f t="shared" si="11"/>
         <v>652816023</v>
       </c>
-      <c r="AT12" s="70">
+      <c r="AT12" s="69">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AU12" s="70">
+      <c r="AU12" s="69">
         <f t="shared" si="15"/>
         <v>654943915</v>
       </c>
-    </row>
-    <row r="13" spans="1:47" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="AW12" s="82">
+        <f>SUMIFS(ventas_unidades,ventas_producto,$A12,ventas_año,AW$8)</f>
+        <v>40573</v>
+      </c>
+      <c r="AX12" s="46">
+        <f>SUMIFS(ventas_unidades,ventas_producto,$A12,ventas_año,AX$8)</f>
+        <v>39442</v>
+      </c>
+      <c r="AY12" s="46">
+        <f>SUMIFS(ventas_unidades,ventas_producto,$A12,ventas_año,AY$8)</f>
+        <v>33573</v>
+      </c>
+      <c r="AZ12" s="46">
+        <f>SUMIFS(ventas_unidades,ventas_producto,$A12,ventas_año,AZ$8)</f>
+        <v>129</v>
+      </c>
+      <c r="BA12" s="46">
+        <f>SUMIFS(ventas_unidades,ventas_producto,$A12,ventas_año,BA$8)</f>
+        <v>1927</v>
+      </c>
+      <c r="BB12" s="46">
+        <f t="shared" si="16"/>
+        <v>115644</v>
+      </c>
+      <c r="BD12" s="97">
+        <f>SUMIFS(ventas_total,ventas_producto,$A12,ventas_año,BD$8)</f>
+        <v>190929354</v>
+      </c>
+      <c r="BE12" s="69">
+        <f>SUMIFS(ventas_total,ventas_producto,$A12,ventas_año,BE$8)</f>
+        <v>221383553</v>
+      </c>
+      <c r="BF12" s="69">
+        <f>SUMIFS(ventas_total,ventas_producto,$A12,ventas_año,BF$8)</f>
+        <v>240503116</v>
+      </c>
+      <c r="BG12" s="69">
+        <f>SUMIFS(ventas_total,ventas_producto,$A12,ventas_año,BG$8)</f>
+        <v>1203910</v>
+      </c>
+      <c r="BH12" s="69">
+        <f>SUMIFS(ventas_total,ventas_producto,$A12,ventas_año,BH$8)</f>
+        <v>923982</v>
+      </c>
+      <c r="BI12" s="69">
+        <f t="shared" si="17"/>
+        <v>654943915</v>
+      </c>
+    </row>
+    <row r="13" spans="1:61" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="s">
         <v>47</v>
       </c>
@@ -6973,20 +7496,20 @@
         <f>SUMIF(ventas_producto,$A13,ventas_total)</f>
         <v>656247934</v>
       </c>
-      <c r="D13" s="80"/>
-      <c r="E13" s="121"/>
-      <c r="F13" s="121"/>
-      <c r="G13" s="121"/>
-      <c r="H13" s="121"/>
-      <c r="I13" s="121"/>
-      <c r="J13" s="121"/>
-      <c r="L13" s="108"/>
-      <c r="M13" s="123"/>
-      <c r="N13" s="123"/>
-      <c r="O13" s="123"/>
-      <c r="P13" s="123"/>
-      <c r="Q13" s="123"/>
-      <c r="S13" s="92">
+      <c r="D13" s="79"/>
+      <c r="E13" s="120"/>
+      <c r="F13" s="120"/>
+      <c r="G13" s="120"/>
+      <c r="H13" s="120"/>
+      <c r="I13" s="120"/>
+      <c r="J13" s="120"/>
+      <c r="L13" s="107"/>
+      <c r="M13" s="122"/>
+      <c r="N13" s="122"/>
+      <c r="O13" s="122"/>
+      <c r="P13" s="122"/>
+      <c r="Q13" s="122"/>
+      <c r="S13" s="91">
         <f t="shared" si="8"/>
         <v>12970</v>
       </c>
@@ -7014,215 +7537,311 @@
         <f t="shared" si="12"/>
         <v>208781</v>
       </c>
-      <c r="AA13" s="106">
+      <c r="AA13" s="105">
         <f t="shared" si="9"/>
         <v>71950539</v>
       </c>
-      <c r="AB13" s="66">
+      <c r="AB13" s="65">
         <f t="shared" si="9"/>
         <v>88920515</v>
       </c>
-      <c r="AC13" s="66">
+      <c r="AC13" s="65">
         <f t="shared" si="9"/>
         <v>31867112</v>
       </c>
-      <c r="AD13" s="66">
+      <c r="AD13" s="65">
         <f t="shared" si="9"/>
         <v>76784060</v>
       </c>
-      <c r="AE13" s="66">
+      <c r="AE13" s="65">
         <f t="shared" si="9"/>
         <v>110535932</v>
       </c>
-      <c r="AF13" s="66">
+      <c r="AF13" s="65">
         <f t="shared" si="9"/>
         <v>276189776</v>
       </c>
-      <c r="AG13" s="66">
+      <c r="AG13" s="65">
         <f t="shared" si="13"/>
         <v>656247934</v>
       </c>
-      <c r="AI13" s="84">
+      <c r="AI13" s="83">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AJ13" s="48">
+      <c r="AJ13" s="47">
         <f t="shared" si="10"/>
         <v>107946</v>
       </c>
-      <c r="AK13" s="48">
+      <c r="AK13" s="47">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AL13" s="48">
+      <c r="AL13" s="47">
         <f t="shared" si="10"/>
         <v>1927</v>
       </c>
-      <c r="AM13" s="48">
+      <c r="AM13" s="47">
         <f t="shared" si="10"/>
         <v>98908</v>
       </c>
-      <c r="AN13" s="48">
+      <c r="AN13" s="47">
         <f t="shared" si="14"/>
         <v>208781</v>
       </c>
-      <c r="AP13" s="99">
+      <c r="AP13" s="98">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AQ13" s="71">
+      <c r="AQ13" s="70">
         <f t="shared" si="11"/>
         <v>101435</v>
       </c>
-      <c r="AR13" s="71">
+      <c r="AR13" s="70">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AS13" s="71">
+      <c r="AS13" s="70">
         <f t="shared" si="11"/>
         <v>548392</v>
       </c>
-      <c r="AT13" s="71">
+      <c r="AT13" s="70">
         <f t="shared" si="11"/>
         <v>655598107</v>
       </c>
-      <c r="AU13" s="71">
+      <c r="AU13" s="70">
         <f t="shared" si="15"/>
         <v>656247934</v>
       </c>
-    </row>
-    <row r="14" spans="1:47" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="AW13" s="83">
+        <f>SUMIFS(ventas_unidades,ventas_producto,$A13,ventas_año,AW$8)</f>
+        <v>36557</v>
+      </c>
+      <c r="AX13" s="47">
+        <f>SUMIFS(ventas_unidades,ventas_producto,$A13,ventas_año,AX$8)</f>
+        <v>28900</v>
+      </c>
+      <c r="AY13" s="47">
+        <f>SUMIFS(ventas_unidades,ventas_producto,$A13,ventas_año,AY$8)</f>
+        <v>33451</v>
+      </c>
+      <c r="AZ13" s="47">
+        <f>SUMIFS(ventas_unidades,ventas_producto,$A13,ventas_año,AZ$8)</f>
+        <v>107946</v>
+      </c>
+      <c r="BA13" s="47">
+        <f>SUMIFS(ventas_unidades,ventas_producto,$A13,ventas_año,BA$8)</f>
+        <v>1927</v>
+      </c>
+      <c r="BB13" s="47">
+        <f t="shared" si="16"/>
+        <v>208781</v>
+      </c>
+      <c r="BD13" s="98">
+        <f>SUMIFS(ventas_total,ventas_producto,$A13,ventas_año,BD$8)</f>
+        <v>216479082</v>
+      </c>
+      <c r="BE13" s="70">
+        <f>SUMIFS(ventas_total,ventas_producto,$A13,ventas_año,BE$8)</f>
+        <v>240247726</v>
+      </c>
+      <c r="BF13" s="70">
+        <f>SUMIFS(ventas_total,ventas_producto,$A13,ventas_año,BF$8)</f>
+        <v>198871299</v>
+      </c>
+      <c r="BG13" s="70">
+        <f>SUMIFS(ventas_total,ventas_producto,$A13,ventas_año,BG$8)</f>
+        <v>101435</v>
+      </c>
+      <c r="BH13" s="70">
+        <f>SUMIFS(ventas_total,ventas_producto,$A13,ventas_año,BH$8)</f>
+        <v>548392</v>
+      </c>
+      <c r="BI13" s="70">
+        <f t="shared" si="17"/>
+        <v>656247934</v>
+      </c>
+    </row>
+    <row r="14" spans="1:61" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="36" t="s">
         <v>34</v>
       </c>
-      <c r="B14" s="117">
+      <c r="B14" s="116">
         <f>SUM(B9:B13)</f>
         <v>858227</v>
       </c>
-      <c r="C14" s="116">
+      <c r="C14" s="115">
         <f>SUBTOTAL(109,estadisticas!$C$9:$C$13)</f>
         <v>3230017545</v>
       </c>
-      <c r="D14" s="80"/>
-      <c r="E14" s="121"/>
-      <c r="F14" s="121"/>
-      <c r="G14" s="121"/>
-      <c r="H14" s="121"/>
-      <c r="I14" s="121"/>
-      <c r="J14" s="121"/>
-      <c r="L14" s="108"/>
-      <c r="M14" s="123"/>
-      <c r="N14" s="123"/>
-      <c r="O14" s="123"/>
-      <c r="P14" s="123"/>
-      <c r="Q14" s="123"/>
-      <c r="S14" s="93">
+      <c r="D14" s="79"/>
+      <c r="E14" s="120"/>
+      <c r="F14" s="120"/>
+      <c r="G14" s="120"/>
+      <c r="H14" s="120"/>
+      <c r="I14" s="120"/>
+      <c r="J14" s="120"/>
+      <c r="L14" s="107"/>
+      <c r="M14" s="122"/>
+      <c r="N14" s="122"/>
+      <c r="O14" s="122"/>
+      <c r="P14" s="122"/>
+      <c r="Q14" s="122"/>
+      <c r="S14" s="92">
         <f>SUM(S9:S13)</f>
         <v>121665</v>
       </c>
       <c r="T14" s="40">
-        <f t="shared" ref="T14:X14" si="16">SUM(T9:T13)</f>
+        <f t="shared" ref="T14:X14" si="18">SUM(T9:T13)</f>
         <v>125620</v>
       </c>
       <c r="U14" s="40">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>32356</v>
       </c>
       <c r="V14" s="40">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>356297</v>
       </c>
       <c r="W14" s="40">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>122295</v>
       </c>
       <c r="X14" s="40">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>99994</v>
       </c>
-      <c r="Y14" s="118">
+      <c r="Y14" s="117">
         <f>SUM(Y9:Y13)</f>
         <v>858227</v>
       </c>
-      <c r="AA14" s="107">
+      <c r="AA14" s="106">
         <f>SUM(AA9:AA13)</f>
         <v>645115066</v>
       </c>
-      <c r="AB14" s="67">
-        <f t="shared" ref="AB14" si="17">SUM(AB9:AB13)</f>
+      <c r="AB14" s="66">
+        <f t="shared" ref="AB14" si="19">SUM(AB9:AB13)</f>
         <v>761464717</v>
       </c>
-      <c r="AC14" s="67">
-        <f t="shared" ref="AC14" si="18">SUM(AC9:AC13)</f>
+      <c r="AC14" s="66">
+        <f t="shared" ref="AC14" si="20">SUM(AC9:AC13)</f>
         <v>226722785</v>
       </c>
-      <c r="AD14" s="67">
-        <f t="shared" ref="AD14" si="19">SUM(AD9:AD13)</f>
+      <c r="AD14" s="66">
+        <f t="shared" ref="AD14" si="21">SUM(AD9:AD13)</f>
         <v>312257691</v>
       </c>
-      <c r="AE14" s="67">
-        <f t="shared" ref="AE14" si="20">SUM(AE9:AE13)</f>
+      <c r="AE14" s="66">
+        <f t="shared" ref="AE14" si="22">SUM(AE9:AE13)</f>
         <v>722503562</v>
       </c>
-      <c r="AF14" s="67">
-        <f t="shared" ref="AF14" si="21">SUM(AF9:AF13)</f>
+      <c r="AF14" s="66">
+        <f t="shared" ref="AF14" si="23">SUM(AF9:AF13)</f>
         <v>561953724</v>
       </c>
-      <c r="AG14" s="115">
-        <f t="shared" ref="AG14" si="22">SUM(AG9:AG13)</f>
+      <c r="AG14" s="114">
+        <f t="shared" ref="AG14" si="24">SUM(AG9:AG13)</f>
         <v>3230017545</v>
       </c>
-      <c r="AI14" s="95">
-        <f t="shared" ref="AI14:AM14" si="23">SUM(AI10:AI13)</f>
+      <c r="AI14" s="94">
+        <f t="shared" ref="AI14:AM14" si="25">SUM(AI10:AI13)</f>
         <v>9072</v>
       </c>
-      <c r="AJ14" s="51">
-        <f t="shared" si="23"/>
+      <c r="AJ14" s="50">
+        <f t="shared" si="25"/>
         <v>213260</v>
       </c>
-      <c r="AK14" s="51">
-        <f t="shared" si="23"/>
+      <c r="AK14" s="50">
+        <f t="shared" si="25"/>
         <v>113292</v>
       </c>
-      <c r="AL14" s="51">
-        <f t="shared" si="23"/>
+      <c r="AL14" s="50">
+        <f t="shared" si="25"/>
         <v>312792</v>
       </c>
-      <c r="AM14" s="51">
-        <f t="shared" si="23"/>
+      <c r="AM14" s="50">
+        <f t="shared" si="25"/>
         <v>98908</v>
       </c>
-      <c r="AN14" s="118">
+      <c r="AN14" s="117">
         <f>SUM(AN9:AN13)</f>
         <v>858227</v>
       </c>
-      <c r="AP14" s="109">
+      <c r="AP14" s="108">
         <f>SUM(AP9:AP13)</f>
         <v>646106962</v>
       </c>
-      <c r="AQ14" s="69">
-        <f t="shared" ref="AQ14:AU14" si="24">SUM(AQ9:AQ13)</f>
+      <c r="AQ14" s="68">
+        <f t="shared" ref="AQ14:AU14" si="26">SUM(AQ9:AQ13)</f>
         <v>576804336</v>
       </c>
-      <c r="AR14" s="69">
-        <f t="shared" si="24"/>
+      <c r="AR14" s="68">
+        <f t="shared" si="26"/>
         <v>687706530</v>
       </c>
-      <c r="AS14" s="69">
-        <f t="shared" si="24"/>
+      <c r="AS14" s="68">
+        <f t="shared" si="26"/>
         <v>654677692</v>
       </c>
-      <c r="AT14" s="69">
-        <f t="shared" si="24"/>
+      <c r="AT14" s="68">
+        <f t="shared" si="26"/>
         <v>664722025</v>
       </c>
-      <c r="AU14" s="115">
-        <f t="shared" si="24"/>
+      <c r="AU14" s="114">
+        <f t="shared" si="26"/>
         <v>3230017545</v>
       </c>
-    </row>
-    <row r="15" spans="1:47" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="16" spans="1:47" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="AW14" s="94">
+        <f t="shared" ref="AW14:BA14" si="27">SUM(AW10:AW13)</f>
+        <v>148950</v>
+      </c>
+      <c r="AX14" s="50">
+        <f t="shared" si="27"/>
+        <v>133993</v>
+      </c>
+      <c r="AY14" s="50">
+        <f t="shared" si="27"/>
+        <v>139321</v>
+      </c>
+      <c r="AZ14" s="50">
+        <f t="shared" si="27"/>
+        <v>126904</v>
+      </c>
+      <c r="BA14" s="50">
+        <f t="shared" si="27"/>
+        <v>198156</v>
+      </c>
+      <c r="BB14" s="117">
+        <f>SUM(BB9:BB13)</f>
+        <v>858227</v>
+      </c>
+      <c r="BD14" s="108">
+        <f>SUM(BD9:BD13)</f>
+        <v>1007244151</v>
+      </c>
+      <c r="BE14" s="68">
+        <f t="shared" ref="BE14:BI14" si="28">SUM(BE9:BE13)</f>
+        <v>1106846472</v>
+      </c>
+      <c r="BF14" s="68">
+        <f t="shared" si="28"/>
+        <v>1089310347</v>
+      </c>
+      <c r="BG14" s="68">
+        <f t="shared" si="28"/>
+        <v>15082721</v>
+      </c>
+      <c r="BH14" s="68">
+        <f t="shared" si="28"/>
+        <v>11533854</v>
+      </c>
+      <c r="BI14" s="114">
+        <f t="shared" si="28"/>
+        <v>3230017545</v>
+      </c>
+    </row>
+    <row r="15" spans="1:61" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="16" spans="1:61" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="7" t="s">
         <v>44</v>
       </c>
@@ -7232,75 +7851,75 @@
       <c r="C16" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="E16" s="87" t="s">
+      <c r="E16" s="86" t="s">
         <v>6</v>
       </c>
-      <c r="F16" s="53" t="s">
+      <c r="F16" s="52" t="s">
         <v>33</v>
       </c>
-      <c r="G16" s="53" t="s">
+      <c r="G16" s="52" t="s">
         <v>15</v>
       </c>
-      <c r="H16" s="53" t="s">
+      <c r="H16" s="52" t="s">
         <v>18</v>
       </c>
-      <c r="I16" s="53" t="s">
+      <c r="I16" s="52" t="s">
         <v>47</v>
       </c>
-      <c r="J16" s="53" t="s">
+      <c r="J16" s="52" t="s">
         <v>34</v>
       </c>
-      <c r="L16" s="101" t="s">
+      <c r="L16" s="100" t="s">
         <v>6</v>
       </c>
-      <c r="M16" s="57" t="s">
+      <c r="M16" s="56" t="s">
         <v>33</v>
       </c>
-      <c r="N16" s="57" t="s">
+      <c r="N16" s="56" t="s">
         <v>15</v>
       </c>
-      <c r="O16" s="57" t="s">
+      <c r="O16" s="56" t="s">
         <v>18</v>
       </c>
-      <c r="P16" s="57" t="s">
+      <c r="P16" s="56" t="s">
         <v>47</v>
       </c>
-      <c r="Q16" s="57" t="s">
+      <c r="Q16" s="56" t="s">
         <v>34</v>
       </c>
-      <c r="S16" s="94"/>
-      <c r="T16" s="54"/>
-      <c r="U16" s="54"/>
-      <c r="V16" s="54"/>
-      <c r="W16" s="54"/>
-      <c r="X16" s="54"/>
-      <c r="Y16" s="54"/>
-      <c r="AA16" s="108"/>
-      <c r="AB16" s="68"/>
-      <c r="AC16" s="68"/>
-      <c r="AD16" s="68"/>
-      <c r="AE16" s="68"/>
-      <c r="AF16" s="68"/>
-      <c r="AG16" s="68"/>
-      <c r="AI16" s="87" t="s">
+      <c r="S16" s="93"/>
+      <c r="T16" s="53"/>
+      <c r="U16" s="53"/>
+      <c r="V16" s="53"/>
+      <c r="W16" s="53"/>
+      <c r="X16" s="53"/>
+      <c r="Y16" s="53"/>
+      <c r="AA16" s="107"/>
+      <c r="AB16" s="67"/>
+      <c r="AC16" s="67"/>
+      <c r="AD16" s="67"/>
+      <c r="AE16" s="67"/>
+      <c r="AF16" s="67"/>
+      <c r="AG16" s="67"/>
+      <c r="AI16" s="86" t="s">
         <v>31</v>
       </c>
-      <c r="AJ16" s="53" t="s">
+      <c r="AJ16" s="52" t="s">
         <v>9</v>
       </c>
-      <c r="AK16" s="53" t="s">
+      <c r="AK16" s="52" t="s">
         <v>16</v>
       </c>
-      <c r="AL16" s="53" t="s">
+      <c r="AL16" s="52" t="s">
         <v>19</v>
       </c>
-      <c r="AM16" s="53" t="s">
+      <c r="AM16" s="52" t="s">
         <v>21</v>
       </c>
-      <c r="AN16" s="53" t="s">
+      <c r="AN16" s="52" t="s">
         <v>34</v>
       </c>
-      <c r="AP16" s="81" t="s">
+      <c r="AP16" s="80" t="s">
         <v>31</v>
       </c>
       <c r="AQ16" s="7" t="s">
@@ -7318,870 +7937,1244 @@
       <c r="AU16" s="7" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="17" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AW16" s="125">
+        <v>2008</v>
+      </c>
+      <c r="AX16" s="21">
+        <v>2009</v>
+      </c>
+      <c r="AY16" s="21">
+        <v>2010</v>
+      </c>
+      <c r="AZ16" s="21">
+        <v>2011</v>
+      </c>
+      <c r="BA16" s="21">
+        <v>2012</v>
+      </c>
+      <c r="BB16" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="BC16" s="2"/>
+      <c r="BD16" s="125">
+        <v>2008</v>
+      </c>
+      <c r="BE16" s="21">
+        <v>2009</v>
+      </c>
+      <c r="BF16" s="21">
+        <v>2010</v>
+      </c>
+      <c r="BG16" s="21">
+        <v>2011</v>
+      </c>
+      <c r="BH16" s="21">
+        <v>2012</v>
+      </c>
+      <c r="BI16" s="7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="17" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A17" s="28" t="s">
         <v>28</v>
       </c>
       <c r="B17" s="29">
-        <f t="shared" ref="B17:B22" si="25">SUMIF(ventas_vendedor,$A17,ventas_unidades)</f>
+        <f t="shared" ref="B17:B22" si="29">SUMIF(ventas_vendedor,$A17,ventas_unidades)</f>
         <v>121665</v>
       </c>
       <c r="C17" s="37">
-        <f t="shared" ref="C17:C22" si="26">SUMIF(ventas_vendedor,$A17,ventas_total)</f>
+        <f t="shared" ref="C17:C22" si="30">SUMIF(ventas_vendedor,$A17,ventas_total)</f>
         <v>645115066</v>
       </c>
-      <c r="E17" s="82">
-        <f t="shared" ref="E17:I22" si="27">SUMIFS(ventas_unidades,ventas_vendedor,$A17,ventas_producto,E$16)</f>
+      <c r="E17" s="81">
+        <f t="shared" ref="E17:I22" si="31">SUMIFS(ventas_unidades,ventas_vendedor,$A17,ventas_producto,E$16)</f>
         <v>23075</v>
       </c>
       <c r="F17" s="17">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>14026</v>
       </c>
       <c r="G17" s="17">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>37242</v>
       </c>
       <c r="H17" s="17">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>34352</v>
       </c>
       <c r="I17" s="17">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>12970</v>
       </c>
       <c r="J17" s="17">
         <f>SUM(E17:I17)</f>
         <v>121665</v>
       </c>
-      <c r="L17" s="97">
-        <f t="shared" ref="L17:P22" si="28">SUMIFS(ventas_total,ventas_vendedor,$A17,ventas_producto,L$16)</f>
+      <c r="L17" s="96">
+        <f t="shared" ref="L17:P22" si="32">SUMIFS(ventas_total,ventas_vendedor,$A17,ventas_producto,L$16)</f>
         <v>109144041</v>
       </c>
-      <c r="M17" s="59">
-        <f t="shared" si="28"/>
+      <c r="M17" s="58">
+        <f t="shared" si="32"/>
         <v>53223672</v>
       </c>
-      <c r="N17" s="59">
-        <f t="shared" si="28"/>
+      <c r="N17" s="58">
+        <f t="shared" si="32"/>
         <v>240818885</v>
       </c>
-      <c r="O17" s="59">
-        <f t="shared" si="28"/>
+      <c r="O17" s="58">
+        <f t="shared" si="32"/>
         <v>169977929</v>
       </c>
-      <c r="P17" s="59">
-        <f t="shared" si="28"/>
+      <c r="P17" s="58">
+        <f t="shared" si="32"/>
         <v>71950539</v>
       </c>
-      <c r="Q17" s="59">
+      <c r="Q17" s="58">
         <f>SUM(L17:P17)</f>
         <v>645115066</v>
       </c>
-      <c r="S17" s="94"/>
-      <c r="T17" s="54"/>
-      <c r="U17" s="54"/>
-      <c r="V17" s="54"/>
-      <c r="W17" s="54"/>
-      <c r="X17" s="54"/>
-      <c r="Y17" s="54"/>
-      <c r="AA17" s="108"/>
-      <c r="AB17" s="68"/>
-      <c r="AC17" s="68"/>
-      <c r="AD17" s="68"/>
-      <c r="AE17" s="68"/>
-      <c r="AF17" s="68"/>
-      <c r="AG17" s="68"/>
-      <c r="AI17" s="82">
-        <f t="shared" ref="AI17:AM22" si="29">SUMIFS(ventas_unidades,ventas_vendedor,$A17,ventas_region,AI$16)</f>
+      <c r="S17" s="93"/>
+      <c r="T17" s="53"/>
+      <c r="U17" s="53"/>
+      <c r="V17" s="53"/>
+      <c r="W17" s="53"/>
+      <c r="X17" s="53"/>
+      <c r="Y17" s="53"/>
+      <c r="AA17" s="107"/>
+      <c r="AB17" s="67"/>
+      <c r="AC17" s="67"/>
+      <c r="AD17" s="67"/>
+      <c r="AE17" s="67"/>
+      <c r="AF17" s="67"/>
+      <c r="AG17" s="67"/>
+      <c r="AI17" s="81">
+        <f t="shared" ref="AI17:AM22" si="33">SUMIFS(ventas_unidades,ventas_vendedor,$A17,ventas_region,AI$16)</f>
         <v>23075</v>
       </c>
       <c r="AJ17" s="17">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>7195</v>
       </c>
       <c r="AK17" s="17">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>39170</v>
       </c>
       <c r="AL17" s="17">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>39255</v>
       </c>
       <c r="AM17" s="17">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>12970</v>
       </c>
       <c r="AN17" s="17">
         <f>SUM(AI17:AM17)</f>
         <v>121665</v>
       </c>
-      <c r="AP17" s="97">
-        <f t="shared" ref="AP17:AT22" si="30">SUMIFS(ventas_total,ventas_vendedor,$A17,ventas_region,AP$16)</f>
+      <c r="AP17" s="96">
+        <f t="shared" ref="AP17:AT22" si="34">SUMIFS(ventas_total,ventas_vendedor,$A17,ventas_region,AP$16)</f>
         <v>109144041</v>
       </c>
-      <c r="AQ17" s="59">
-        <f t="shared" si="30"/>
+      <c r="AQ17" s="58">
+        <f t="shared" si="34"/>
         <v>52631529</v>
       </c>
-      <c r="AR17" s="59">
-        <f t="shared" si="30"/>
+      <c r="AR17" s="58">
+        <f t="shared" si="34"/>
         <v>240927099</v>
       </c>
-      <c r="AS17" s="59">
-        <f t="shared" si="30"/>
+      <c r="AS17" s="58">
+        <f t="shared" si="34"/>
         <v>170461858</v>
       </c>
-      <c r="AT17" s="59">
-        <f t="shared" si="30"/>
+      <c r="AT17" s="58">
+        <f t="shared" si="34"/>
         <v>71950539</v>
       </c>
-      <c r="AU17" s="59">
+      <c r="AU17" s="58">
         <f>SUM(AP17:AT17)</f>
         <v>645115066</v>
       </c>
-    </row>
-    <row r="18" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AW17" s="81">
+        <f>SUMIFS(ventas_unidades,ventas_vendedor,$A17,ventas_año,AW$16)</f>
+        <v>33623</v>
+      </c>
+      <c r="AX17" s="17">
+        <f>SUMIFS(ventas_unidades,ventas_vendedor,$A17,ventas_año,AX$16)</f>
+        <v>42339</v>
+      </c>
+      <c r="AY17" s="17">
+        <f>SUMIFS(ventas_unidades,ventas_vendedor,$A17,ventas_año,AY$16)</f>
+        <v>33889</v>
+      </c>
+      <c r="AZ17" s="17">
+        <f>SUMIFS(ventas_unidades,ventas_vendedor,$A17,ventas_año,AZ$16)</f>
+        <v>9886</v>
+      </c>
+      <c r="BA17" s="17">
+        <f>SUMIFS(ventas_unidades,ventas_vendedor,$A17,ventas_año,BA$16)</f>
+        <v>1928</v>
+      </c>
+      <c r="BB17" s="17">
+        <f>SUM(AW17:BA17)</f>
+        <v>121665</v>
+      </c>
+      <c r="BD17" s="96">
+        <f>SUMIFS(ventas_total,ventas_vendedor,$A17,ventas_año,BD$8)</f>
+        <v>175048265</v>
+      </c>
+      <c r="BE17" s="58">
+        <f>SUMIFS(ventas_total,ventas_vendedor,$A17,ventas_año,BE$8)</f>
+        <v>244791087</v>
+      </c>
+      <c r="BF17" s="58">
+        <f>SUMIFS(ventas_total,ventas_vendedor,$A17,ventas_año,BF$8)</f>
+        <v>216563190</v>
+      </c>
+      <c r="BG17" s="58">
+        <f>SUMIFS(ventas_total,ventas_vendedor,$A17,ventas_año,BG$8)</f>
+        <v>8604310</v>
+      </c>
+      <c r="BH17" s="58">
+        <f>SUMIFS(ventas_total,ventas_vendedor,$A17,ventas_año,BH$8)</f>
+        <v>108214</v>
+      </c>
+      <c r="BI17" s="58">
+        <f>SUM(BD17:BH17)</f>
+        <v>645115066</v>
+      </c>
+    </row>
+    <row r="18" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A18" s="26" t="s">
         <v>8</v>
       </c>
       <c r="B18" s="30">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>125620</v>
       </c>
       <c r="C18" s="38">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>761464717</v>
       </c>
-      <c r="E18" s="83">
-        <f t="shared" si="27"/>
+      <c r="E18" s="82">
+        <f t="shared" si="31"/>
         <v>27346</v>
       </c>
       <c r="F18" s="18">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>51553</v>
       </c>
       <c r="G18" s="18">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>19565</v>
       </c>
       <c r="H18" s="18">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>12991</v>
       </c>
       <c r="I18" s="18">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>14165</v>
       </c>
       <c r="J18" s="18">
-        <f t="shared" ref="J18:J22" si="31">SUM(E18:I18)</f>
+        <f t="shared" ref="J18:J22" si="35">SUM(E18:I18)</f>
         <v>125620</v>
       </c>
-      <c r="L18" s="98">
-        <f t="shared" si="28"/>
+      <c r="L18" s="97">
+        <f t="shared" si="32"/>
         <v>193222871</v>
       </c>
-      <c r="M18" s="60">
-        <f t="shared" si="28"/>
+      <c r="M18" s="59">
+        <f t="shared" si="32"/>
         <v>271532147</v>
       </c>
-      <c r="N18" s="60">
-        <f t="shared" si="28"/>
+      <c r="N18" s="59">
+        <f t="shared" si="32"/>
         <v>131950052</v>
       </c>
-      <c r="O18" s="60">
-        <f t="shared" si="28"/>
+      <c r="O18" s="59">
+        <f t="shared" si="32"/>
         <v>75839132</v>
       </c>
-      <c r="P18" s="60">
-        <f t="shared" si="28"/>
+      <c r="P18" s="59">
+        <f t="shared" si="32"/>
         <v>88920515</v>
       </c>
-      <c r="Q18" s="60">
-        <f t="shared" ref="Q18:Q22" si="32">SUM(L18:P18)</f>
+      <c r="Q18" s="59">
+        <f t="shared" ref="Q18:Q22" si="36">SUM(L18:P18)</f>
         <v>761464717</v>
       </c>
-      <c r="S18" s="94"/>
-      <c r="T18" s="54"/>
-      <c r="U18" s="54"/>
-      <c r="V18" s="54"/>
-      <c r="W18" s="54"/>
-      <c r="X18" s="54"/>
-      <c r="Y18" s="54"/>
-      <c r="AA18" s="108"/>
-      <c r="AB18" s="68"/>
-      <c r="AC18" s="68"/>
-      <c r="AD18" s="68"/>
-      <c r="AE18" s="68"/>
-      <c r="AF18" s="68"/>
-      <c r="AG18" s="68"/>
-      <c r="AI18" s="83">
-        <f t="shared" si="29"/>
+      <c r="S18" s="93"/>
+      <c r="T18" s="53"/>
+      <c r="U18" s="53"/>
+      <c r="V18" s="53"/>
+      <c r="W18" s="53"/>
+      <c r="X18" s="53"/>
+      <c r="Y18" s="53"/>
+      <c r="AA18" s="107"/>
+      <c r="AB18" s="67"/>
+      <c r="AC18" s="67"/>
+      <c r="AD18" s="67"/>
+      <c r="AE18" s="67"/>
+      <c r="AF18" s="67"/>
+      <c r="AG18" s="67"/>
+      <c r="AI18" s="82">
+        <f t="shared" si="33"/>
         <v>27346</v>
       </c>
       <c r="AJ18" s="18">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>51553</v>
       </c>
       <c r="AK18" s="18">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>19565</v>
       </c>
       <c r="AL18" s="18">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>12991</v>
       </c>
       <c r="AM18" s="18">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>14165</v>
       </c>
       <c r="AN18" s="18">
-        <f t="shared" ref="AN18:AN22" si="33">SUM(AI18:AM18)</f>
+        <f t="shared" ref="AN18:AN22" si="37">SUM(AI18:AM18)</f>
         <v>125620</v>
       </c>
-      <c r="AP18" s="98">
-        <f t="shared" si="30"/>
+      <c r="AP18" s="97">
+        <f t="shared" si="34"/>
         <v>193222871</v>
       </c>
-      <c r="AQ18" s="60">
-        <f t="shared" si="30"/>
+      <c r="AQ18" s="59">
+        <f t="shared" si="34"/>
         <v>271532147</v>
       </c>
-      <c r="AR18" s="60">
-        <f t="shared" si="30"/>
+      <c r="AR18" s="59">
+        <f t="shared" si="34"/>
         <v>131950052</v>
       </c>
-      <c r="AS18" s="60">
-        <f t="shared" si="30"/>
+      <c r="AS18" s="59">
+        <f t="shared" si="34"/>
         <v>75839132</v>
       </c>
-      <c r="AT18" s="60">
-        <f t="shared" si="30"/>
+      <c r="AT18" s="59">
+        <f t="shared" si="34"/>
         <v>88920515</v>
       </c>
-      <c r="AU18" s="60">
-        <f t="shared" ref="AU18:AU22" si="34">SUM(AP18:AT18)</f>
+      <c r="AU18" s="59">
+        <f t="shared" ref="AU18:AU22" si="38">SUM(AP18:AT18)</f>
         <v>761464717</v>
       </c>
-    </row>
-    <row r="19" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AW18" s="82">
+        <f>SUMIFS(ventas_unidades,ventas_vendedor,$A18,ventas_año,AW$16)</f>
+        <v>45235</v>
+      </c>
+      <c r="AX18" s="46">
+        <f>SUMIFS(ventas_unidades,ventas_vendedor,$A18,ventas_año,AX$16)</f>
+        <v>39435</v>
+      </c>
+      <c r="AY18" s="46">
+        <f>SUMIFS(ventas_unidades,ventas_vendedor,$A18,ventas_año,AY$16)</f>
+        <v>40950</v>
+      </c>
+      <c r="AZ18" s="46">
+        <f>SUMIFS(ventas_unidades,ventas_vendedor,$A18,ventas_año,AZ$16)</f>
+        <v>0</v>
+      </c>
+      <c r="BA18" s="46">
+        <f>SUMIFS(ventas_unidades,ventas_vendedor,$A18,ventas_año,BA$16)</f>
+        <v>0</v>
+      </c>
+      <c r="BB18" s="46">
+        <f t="shared" ref="BB18:BB21" si="39">SUM(AW18:BA18)</f>
+        <v>125620</v>
+      </c>
+      <c r="BD18" s="97">
+        <f>SUMIFS(ventas_total,ventas_vendedor,$A18,ventas_año,BD$8)</f>
+        <v>275531995</v>
+      </c>
+      <c r="BE18" s="69">
+        <f>SUMIFS(ventas_total,ventas_vendedor,$A18,ventas_año,BE$8)</f>
+        <v>271002529</v>
+      </c>
+      <c r="BF18" s="69">
+        <f>SUMIFS(ventas_total,ventas_vendedor,$A18,ventas_año,BF$8)</f>
+        <v>214930193</v>
+      </c>
+      <c r="BG18" s="69">
+        <f>SUMIFS(ventas_total,ventas_vendedor,$A18,ventas_año,BG$8)</f>
+        <v>0</v>
+      </c>
+      <c r="BH18" s="69">
+        <f>SUMIFS(ventas_total,ventas_vendedor,$A18,ventas_año,BH$8)</f>
+        <v>0</v>
+      </c>
+      <c r="BI18" s="69">
+        <f t="shared" ref="BI18:BI21" si="40">SUM(BD18:BH18)</f>
+        <v>761464717</v>
+      </c>
+    </row>
+    <row r="19" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A19" s="27" t="s">
         <v>11</v>
       </c>
       <c r="B19" s="31">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>32356</v>
       </c>
       <c r="C19" s="39">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>226722785</v>
       </c>
-      <c r="E19" s="84">
-        <f t="shared" si="27"/>
+      <c r="E19" s="83">
+        <f t="shared" si="31"/>
         <v>9125</v>
       </c>
       <c r="F19" s="19">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>9023</v>
       </c>
       <c r="G19" s="19">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>6969</v>
       </c>
       <c r="H19" s="19">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>2096</v>
       </c>
       <c r="I19" s="19">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>5143</v>
       </c>
       <c r="J19" s="19">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>32356</v>
       </c>
-      <c r="L19" s="99">
-        <f t="shared" si="28"/>
+      <c r="L19" s="98">
+        <f t="shared" si="32"/>
         <v>59797810</v>
       </c>
-      <c r="M19" s="61">
-        <f t="shared" si="28"/>
+      <c r="M19" s="60">
+        <f t="shared" si="32"/>
         <v>63246530</v>
       </c>
-      <c r="N19" s="61">
-        <f t="shared" si="28"/>
+      <c r="N19" s="60">
+        <f t="shared" si="32"/>
         <v>40433106</v>
       </c>
-      <c r="O19" s="61">
-        <f t="shared" si="28"/>
+      <c r="O19" s="60">
+        <f t="shared" si="32"/>
         <v>31378227</v>
       </c>
-      <c r="P19" s="61">
-        <f t="shared" si="28"/>
+      <c r="P19" s="60">
+        <f t="shared" si="32"/>
         <v>31867112</v>
       </c>
-      <c r="Q19" s="61">
-        <f t="shared" si="32"/>
+      <c r="Q19" s="60">
+        <f t="shared" si="36"/>
         <v>226722785</v>
       </c>
-      <c r="S19" s="94"/>
-      <c r="T19" s="54"/>
-      <c r="U19" s="54"/>
-      <c r="V19" s="54"/>
-      <c r="W19" s="54"/>
-      <c r="X19" s="54"/>
-      <c r="Y19" s="54"/>
-      <c r="AA19" s="108"/>
-      <c r="AB19" s="68"/>
-      <c r="AC19" s="68"/>
-      <c r="AD19" s="68"/>
-      <c r="AE19" s="68"/>
-      <c r="AF19" s="68"/>
-      <c r="AG19" s="68"/>
-      <c r="AI19" s="84">
-        <f t="shared" si="29"/>
+      <c r="S19" s="93"/>
+      <c r="T19" s="53"/>
+      <c r="U19" s="53"/>
+      <c r="V19" s="53"/>
+      <c r="W19" s="53"/>
+      <c r="X19" s="53"/>
+      <c r="Y19" s="53"/>
+      <c r="AA19" s="107"/>
+      <c r="AB19" s="67"/>
+      <c r="AC19" s="67"/>
+      <c r="AD19" s="67"/>
+      <c r="AE19" s="67"/>
+      <c r="AF19" s="67"/>
+      <c r="AG19" s="67"/>
+      <c r="AI19" s="83">
+        <f t="shared" si="33"/>
         <v>9125</v>
       </c>
       <c r="AJ19" s="19">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>9023</v>
       </c>
       <c r="AK19" s="19">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>6969</v>
       </c>
       <c r="AL19" s="19">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>2096</v>
       </c>
       <c r="AM19" s="19">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>5143</v>
       </c>
       <c r="AN19" s="19">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>32356</v>
       </c>
-      <c r="AP19" s="99">
-        <f t="shared" si="30"/>
+      <c r="AP19" s="98">
+        <f t="shared" si="34"/>
         <v>59797810</v>
       </c>
-      <c r="AQ19" s="61">
-        <f t="shared" si="30"/>
+      <c r="AQ19" s="60">
+        <f t="shared" si="34"/>
         <v>63246530</v>
       </c>
-      <c r="AR19" s="61">
-        <f t="shared" si="30"/>
+      <c r="AR19" s="60">
+        <f t="shared" si="34"/>
         <v>40433106</v>
       </c>
-      <c r="AS19" s="61">
-        <f t="shared" si="30"/>
+      <c r="AS19" s="60">
+        <f t="shared" si="34"/>
         <v>31378227</v>
       </c>
-      <c r="AT19" s="61">
-        <f t="shared" si="30"/>
+      <c r="AT19" s="60">
+        <f t="shared" si="34"/>
         <v>31867112</v>
       </c>
-      <c r="AU19" s="61">
-        <f t="shared" si="34"/>
+      <c r="AU19" s="60">
+        <f t="shared" si="38"/>
         <v>226722785</v>
       </c>
-    </row>
-    <row r="20" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AW19" s="83">
+        <f>SUMIFS(ventas_unidades,ventas_vendedor,$A19,ventas_año,AW$16)</f>
+        <v>12423</v>
+      </c>
+      <c r="AX19" s="47">
+        <f>SUMIFS(ventas_unidades,ventas_vendedor,$A19,ventas_año,AX$16)</f>
+        <v>12194</v>
+      </c>
+      <c r="AY19" s="47">
+        <f>SUMIFS(ventas_unidades,ventas_vendedor,$A19,ventas_año,AY$16)</f>
+        <v>7739</v>
+      </c>
+      <c r="AZ19" s="47">
+        <f>SUMIFS(ventas_unidades,ventas_vendedor,$A19,ventas_año,AZ$16)</f>
+        <v>0</v>
+      </c>
+      <c r="BA19" s="47">
+        <f>SUMIFS(ventas_unidades,ventas_vendedor,$A19,ventas_año,BA$16)</f>
+        <v>0</v>
+      </c>
+      <c r="BB19" s="47">
+        <f t="shared" si="39"/>
+        <v>32356</v>
+      </c>
+      <c r="BD19" s="98">
+        <f>SUMIFS(ventas_total,ventas_vendedor,$A19,ventas_año,BD$8)</f>
+        <v>48322205</v>
+      </c>
+      <c r="BE19" s="70">
+        <f>SUMIFS(ventas_total,ventas_vendedor,$A19,ventas_año,BE$8)</f>
+        <v>131956162</v>
+      </c>
+      <c r="BF19" s="70">
+        <f>SUMIFS(ventas_total,ventas_vendedor,$A19,ventas_año,BF$8)</f>
+        <v>46444418</v>
+      </c>
+      <c r="BG19" s="70">
+        <f>SUMIFS(ventas_total,ventas_vendedor,$A19,ventas_año,BG$8)</f>
+        <v>0</v>
+      </c>
+      <c r="BH19" s="70">
+        <f>SUMIFS(ventas_total,ventas_vendedor,$A19,ventas_año,BH$8)</f>
+        <v>0</v>
+      </c>
+      <c r="BI19" s="70">
+        <f t="shared" si="40"/>
+        <v>226722785</v>
+      </c>
+    </row>
+    <row r="20" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A20" s="26" t="s">
         <v>13</v>
       </c>
       <c r="B20" s="30">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>356297</v>
       </c>
       <c r="C20" s="38">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>312257691</v>
       </c>
-      <c r="E20" s="83">
-        <f t="shared" si="27"/>
+      <c r="E20" s="82">
+        <f t="shared" si="31"/>
         <v>21722</v>
       </c>
       <c r="F20" s="18">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>197836</v>
       </c>
       <c r="G20" s="18">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>18868</v>
       </c>
       <c r="H20" s="18">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>5457</v>
       </c>
       <c r="I20" s="18">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>112414</v>
       </c>
       <c r="J20" s="18">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>356297</v>
       </c>
-      <c r="L20" s="98">
-        <f t="shared" si="28"/>
+      <c r="L20" s="97">
+        <f t="shared" si="32"/>
         <v>135280108</v>
       </c>
-      <c r="M20" s="60">
-        <f t="shared" si="28"/>
+      <c r="M20" s="59">
+        <f t="shared" si="32"/>
         <v>45710704</v>
       </c>
-      <c r="N20" s="60">
-        <f t="shared" si="28"/>
+      <c r="N20" s="59">
+        <f t="shared" si="32"/>
         <v>31481567</v>
       </c>
-      <c r="O20" s="60">
-        <f t="shared" si="28"/>
+      <c r="O20" s="59">
+        <f t="shared" si="32"/>
         <v>23001252</v>
       </c>
-      <c r="P20" s="60">
-        <f t="shared" si="28"/>
+      <c r="P20" s="59">
+        <f t="shared" si="32"/>
         <v>76784060</v>
       </c>
-      <c r="Q20" s="60">
-        <f t="shared" si="32"/>
+      <c r="Q20" s="59">
+        <f t="shared" si="36"/>
         <v>312257691</v>
       </c>
-      <c r="S20" s="94"/>
-      <c r="T20" s="54"/>
-      <c r="U20" s="54"/>
-      <c r="V20" s="54"/>
-      <c r="W20" s="54"/>
-      <c r="X20" s="54"/>
-      <c r="Y20" s="54"/>
-      <c r="AA20" s="108"/>
-      <c r="AB20" s="68"/>
-      <c r="AC20" s="68"/>
-      <c r="AD20" s="68"/>
-      <c r="AE20" s="68"/>
-      <c r="AF20" s="68"/>
-      <c r="AG20" s="68"/>
-      <c r="AI20" s="83">
-        <f t="shared" si="29"/>
+      <c r="S20" s="93"/>
+      <c r="T20" s="53"/>
+      <c r="U20" s="53"/>
+      <c r="V20" s="53"/>
+      <c r="W20" s="53"/>
+      <c r="X20" s="53"/>
+      <c r="Y20" s="53"/>
+      <c r="AA20" s="107"/>
+      <c r="AB20" s="67"/>
+      <c r="AC20" s="67"/>
+      <c r="AD20" s="67"/>
+      <c r="AE20" s="67"/>
+      <c r="AF20" s="67"/>
+      <c r="AG20" s="67"/>
+      <c r="AI20" s="82">
+        <f t="shared" si="33"/>
         <v>30665</v>
       </c>
       <c r="AJ20" s="18">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>103585</v>
       </c>
       <c r="AK20" s="18">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>9925</v>
       </c>
       <c r="AL20" s="18">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>197831</v>
       </c>
       <c r="AM20" s="18">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>14291</v>
       </c>
       <c r="AN20" s="18">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>356297</v>
       </c>
-      <c r="AP20" s="98">
-        <f t="shared" si="30"/>
+      <c r="AP20" s="97">
+        <f t="shared" si="34"/>
         <v>139608342</v>
       </c>
-      <c r="AQ20" s="60">
-        <f t="shared" si="30"/>
+      <c r="AQ20" s="59">
+        <f t="shared" si="34"/>
         <v>44964557</v>
       </c>
-      <c r="AR20" s="60">
-        <f t="shared" si="30"/>
+      <c r="AR20" s="59">
+        <f t="shared" si="34"/>
         <v>27153333</v>
       </c>
-      <c r="AS20" s="60">
-        <f t="shared" si="30"/>
+      <c r="AS20" s="59">
+        <f t="shared" si="34"/>
         <v>23830600</v>
       </c>
-      <c r="AT20" s="60">
-        <f t="shared" si="30"/>
+      <c r="AT20" s="59">
+        <f t="shared" si="34"/>
         <v>76700859</v>
       </c>
-      <c r="AU20" s="60">
-        <f t="shared" si="34"/>
+      <c r="AU20" s="59">
+        <f t="shared" si="38"/>
         <v>312257691</v>
       </c>
-    </row>
-    <row r="21" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AW20" s="82">
+        <f>SUMIFS(ventas_unidades,ventas_vendedor,$A20,ventas_año,AW$16)</f>
+        <v>20990</v>
+      </c>
+      <c r="AX20" s="46">
+        <f>SUMIFS(ventas_unidades,ventas_vendedor,$A20,ventas_año,AX$16)</f>
+        <v>11750</v>
+      </c>
+      <c r="AY20" s="46">
+        <f>SUMIFS(ventas_unidades,ventas_vendedor,$A20,ventas_año,AY$16)</f>
+        <v>24117</v>
+      </c>
+      <c r="AZ20" s="46">
+        <f>SUMIFS(ventas_unidades,ventas_vendedor,$A20,ventas_año,AZ$16)</f>
+        <v>107066</v>
+      </c>
+      <c r="BA20" s="46">
+        <f>SUMIFS(ventas_unidades,ventas_vendedor,$A20,ventas_año,BA$16)</f>
+        <v>192374</v>
+      </c>
+      <c r="BB20" s="46">
+        <f t="shared" si="39"/>
+        <v>356297</v>
+      </c>
+      <c r="BD20" s="97">
+        <f>SUMIFS(ventas_total,ventas_vendedor,$A20,ventas_año,BD$8)</f>
+        <v>109777406</v>
+      </c>
+      <c r="BE20" s="69">
+        <f>SUMIFS(ventas_total,ventas_vendedor,$A20,ventas_año,BE$8)</f>
+        <v>63876055</v>
+      </c>
+      <c r="BF20" s="69">
+        <f>SUMIFS(ventas_total,ventas_vendedor,$A20,ventas_año,BF$8)</f>
+        <v>133363447</v>
+      </c>
+      <c r="BG20" s="69">
+        <f>SUMIFS(ventas_total,ventas_vendedor,$A20,ventas_año,BG$8)</f>
+        <v>4411435</v>
+      </c>
+      <c r="BH20" s="69">
+        <f>SUMIFS(ventas_total,ventas_vendedor,$A20,ventas_año,BH$8)</f>
+        <v>829348</v>
+      </c>
+      <c r="BI20" s="69">
+        <f t="shared" si="40"/>
+        <v>312257691</v>
+      </c>
+    </row>
+    <row r="21" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A21" s="27" t="s">
         <v>29</v>
       </c>
       <c r="B21" s="31">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>122295</v>
       </c>
       <c r="C21" s="39">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>722503562</v>
       </c>
-      <c r="E21" s="84">
-        <f t="shared" si="27"/>
+      <c r="E21" s="83">
+        <f t="shared" si="31"/>
         <v>18175</v>
       </c>
       <c r="F21" s="19">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>15576</v>
       </c>
       <c r="G21" s="19">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>10706</v>
       </c>
       <c r="H21" s="19">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>55164</v>
       </c>
       <c r="I21" s="19">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>22674</v>
       </c>
       <c r="J21" s="19">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v>122295</v>
       </c>
-      <c r="L21" s="99">
-        <f t="shared" si="28"/>
+      <c r="L21" s="98">
+        <f t="shared" si="32"/>
         <v>103659911</v>
       </c>
-      <c r="M21" s="61">
-        <f t="shared" si="28"/>
+      <c r="M21" s="60">
+        <f t="shared" si="32"/>
         <v>93604609</v>
       </c>
-      <c r="N21" s="61">
-        <f t="shared" si="28"/>
+      <c r="N21" s="60">
+        <f t="shared" si="32"/>
         <v>77744662</v>
       </c>
-      <c r="O21" s="61">
-        <f t="shared" si="28"/>
+      <c r="O21" s="60">
+        <f t="shared" si="32"/>
         <v>336958448</v>
       </c>
-      <c r="P21" s="61">
-        <f t="shared" si="28"/>
+      <c r="P21" s="60">
+        <f t="shared" si="32"/>
         <v>110535932</v>
       </c>
-      <c r="Q21" s="61">
-        <f t="shared" si="32"/>
+      <c r="Q21" s="60">
+        <f t="shared" si="36"/>
         <v>722503562</v>
       </c>
-      <c r="S21" s="94"/>
-      <c r="T21" s="54"/>
-      <c r="U21" s="54"/>
-      <c r="V21" s="54"/>
-      <c r="W21" s="54"/>
-      <c r="X21" s="54"/>
-      <c r="Y21" s="54"/>
-      <c r="AA21" s="108"/>
-      <c r="AB21" s="68"/>
-      <c r="AC21" s="68"/>
-      <c r="AD21" s="68"/>
-      <c r="AE21" s="68"/>
-      <c r="AF21" s="68"/>
-      <c r="AG21" s="68"/>
-      <c r="AI21" s="84">
-        <f t="shared" si="29"/>
+      <c r="S21" s="93"/>
+      <c r="T21" s="53"/>
+      <c r="U21" s="53"/>
+      <c r="V21" s="53"/>
+      <c r="W21" s="53"/>
+      <c r="X21" s="53"/>
+      <c r="Y21" s="53"/>
+      <c r="AA21" s="107"/>
+      <c r="AB21" s="67"/>
+      <c r="AC21" s="67"/>
+      <c r="AD21" s="67"/>
+      <c r="AE21" s="67"/>
+      <c r="AF21" s="67"/>
+      <c r="AG21" s="67"/>
+      <c r="AI21" s="83">
+        <f t="shared" si="33"/>
         <v>11047</v>
       </c>
       <c r="AJ21" s="19">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>25399</v>
       </c>
       <c r="AK21" s="19">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>12633</v>
       </c>
       <c r="AL21" s="19">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>53237</v>
       </c>
       <c r="AM21" s="19">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>19979</v>
       </c>
       <c r="AN21" s="19">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>122295</v>
       </c>
-      <c r="AP21" s="99">
-        <f t="shared" si="30"/>
+      <c r="AP21" s="98">
+        <f t="shared" si="34"/>
         <v>94535993</v>
       </c>
-      <c r="AQ21" s="61">
-        <f t="shared" si="30"/>
+      <c r="AQ21" s="60">
+        <f t="shared" si="34"/>
         <v>93622843</v>
       </c>
-      <c r="AR21" s="61">
-        <f t="shared" si="30"/>
+      <c r="AR21" s="60">
+        <f t="shared" si="34"/>
         <v>78668644</v>
       </c>
-      <c r="AS21" s="61">
-        <f t="shared" si="30"/>
+      <c r="AS21" s="60">
+        <f t="shared" si="34"/>
         <v>336034466</v>
       </c>
-      <c r="AT21" s="61">
-        <f t="shared" si="30"/>
+      <c r="AT21" s="60">
+        <f t="shared" si="34"/>
         <v>119641616</v>
       </c>
-      <c r="AU21" s="61">
-        <f t="shared" si="34"/>
+      <c r="AU21" s="60">
+        <f t="shared" si="38"/>
         <v>722503562</v>
       </c>
-    </row>
-    <row r="22" spans="1:47" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="AW21" s="83">
+        <f>SUMIFS(ventas_unidades,ventas_vendedor,$A21,ventas_año,AW$16)</f>
+        <v>44558</v>
+      </c>
+      <c r="AX21" s="47">
+        <f>SUMIFS(ventas_unidades,ventas_vendedor,$A21,ventas_año,AX$16)</f>
+        <v>27319</v>
+      </c>
+      <c r="AY21" s="47">
+        <f>SUMIFS(ventas_unidades,ventas_vendedor,$A21,ventas_año,AY$16)</f>
+        <v>31540</v>
+      </c>
+      <c r="AZ21" s="47">
+        <f>SUMIFS(ventas_unidades,ventas_vendedor,$A21,ventas_año,AZ$16)</f>
+        <v>9823</v>
+      </c>
+      <c r="BA21" s="47">
+        <f>SUMIFS(ventas_unidades,ventas_vendedor,$A21,ventas_año,BA$16)</f>
+        <v>9055</v>
+      </c>
+      <c r="BB21" s="47">
+        <f t="shared" si="39"/>
+        <v>122295</v>
+      </c>
+      <c r="BD21" s="98">
+        <f>SUMIFS(ventas_total,ventas_vendedor,$A21,ventas_año,BD$8)</f>
+        <v>223098228</v>
+      </c>
+      <c r="BE21" s="70">
+        <f>SUMIFS(ventas_total,ventas_vendedor,$A21,ventas_año,BE$8)</f>
+        <v>217807965</v>
+      </c>
+      <c r="BF21" s="70">
+        <f>SUMIFS(ventas_total,ventas_vendedor,$A21,ventas_año,BF$8)</f>
+        <v>271531235</v>
+      </c>
+      <c r="BG21" s="70">
+        <f>SUMIFS(ventas_total,ventas_vendedor,$A21,ventas_año,BG$8)</f>
+        <v>18234</v>
+      </c>
+      <c r="BH21" s="70">
+        <f>SUMIFS(ventas_total,ventas_vendedor,$A21,ventas_año,BH$8)</f>
+        <v>10047900</v>
+      </c>
+      <c r="BI21" s="70">
+        <f t="shared" si="40"/>
+        <v>722503562</v>
+      </c>
+    </row>
+    <row r="22" spans="1:61" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="26" t="s">
         <v>30</v>
       </c>
       <c r="B22" s="30">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>99994</v>
       </c>
       <c r="C22" s="38">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>561953724</v>
       </c>
-      <c r="E22" s="88">
-        <f t="shared" si="27"/>
+      <c r="E22" s="87">
+        <f t="shared" si="31"/>
         <v>11460</v>
       </c>
-      <c r="F22" s="52">
-        <f t="shared" si="27"/>
+      <c r="F22" s="51">
+        <f t="shared" si="31"/>
         <v>16505</v>
       </c>
-      <c r="G22" s="52">
-        <f t="shared" si="27"/>
+      <c r="G22" s="51">
+        <f t="shared" si="31"/>
         <v>25030</v>
       </c>
-      <c r="H22" s="52">
-        <f t="shared" si="27"/>
+      <c r="H22" s="51">
+        <f t="shared" si="31"/>
         <v>5584</v>
       </c>
-      <c r="I22" s="52">
-        <f t="shared" si="27"/>
+      <c r="I22" s="51">
+        <f t="shared" si="31"/>
         <v>41415</v>
       </c>
-      <c r="J22" s="52">
-        <f t="shared" si="31"/>
+      <c r="J22" s="51">
+        <f t="shared" si="35"/>
         <v>99994</v>
       </c>
-      <c r="L22" s="102">
-        <f t="shared" si="28"/>
+      <c r="L22" s="101">
+        <f t="shared" si="32"/>
         <v>49438827</v>
       </c>
-      <c r="M22" s="58">
-        <f t="shared" si="28"/>
+      <c r="M22" s="57">
+        <f t="shared" si="32"/>
         <v>50806730</v>
       </c>
-      <c r="N22" s="58">
-        <f t="shared" si="28"/>
+      <c r="N22" s="57">
+        <f t="shared" si="32"/>
         <v>167729464</v>
       </c>
-      <c r="O22" s="58">
-        <f t="shared" si="28"/>
+      <c r="O22" s="57">
+        <f t="shared" si="32"/>
         <v>17788927</v>
       </c>
-      <c r="P22" s="58">
-        <f t="shared" si="28"/>
+      <c r="P22" s="57">
+        <f t="shared" si="32"/>
         <v>276189776</v>
       </c>
-      <c r="Q22" s="58">
-        <f t="shared" si="32"/>
+      <c r="Q22" s="57">
+        <f t="shared" si="36"/>
         <v>561953724</v>
       </c>
-      <c r="S22" s="94"/>
-      <c r="T22" s="54"/>
-      <c r="U22" s="54"/>
-      <c r="V22" s="54"/>
-      <c r="W22" s="54"/>
-      <c r="X22" s="54"/>
-      <c r="Y22" s="54"/>
-      <c r="AA22" s="108"/>
-      <c r="AB22" s="68"/>
-      <c r="AC22" s="68"/>
-      <c r="AD22" s="68"/>
-      <c r="AE22" s="68"/>
-      <c r="AF22" s="68"/>
-      <c r="AG22" s="68"/>
-      <c r="AI22" s="83">
-        <f t="shared" si="29"/>
+      <c r="S22" s="93"/>
+      <c r="T22" s="53"/>
+      <c r="U22" s="53"/>
+      <c r="V22" s="53"/>
+      <c r="W22" s="53"/>
+      <c r="X22" s="53"/>
+      <c r="Y22" s="53"/>
+      <c r="AA22" s="107"/>
+      <c r="AB22" s="67"/>
+      <c r="AC22" s="67"/>
+      <c r="AD22" s="67"/>
+      <c r="AE22" s="67"/>
+      <c r="AF22" s="67"/>
+      <c r="AG22" s="67"/>
+      <c r="AI22" s="82">
+        <f t="shared" si="33"/>
         <v>8851</v>
       </c>
       <c r="AJ22" s="18">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>16505</v>
       </c>
       <c r="AK22" s="18">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>27768</v>
       </c>
       <c r="AL22" s="18">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>7382</v>
       </c>
       <c r="AM22" s="18">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v>39488</v>
       </c>
       <c r="AN22" s="18">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>99994</v>
       </c>
-      <c r="AP22" s="98">
-        <f t="shared" si="30"/>
+      <c r="AP22" s="97">
+        <f t="shared" si="34"/>
         <v>49797905</v>
       </c>
-      <c r="AQ22" s="60">
-        <f t="shared" si="30"/>
+      <c r="AQ22" s="59">
+        <f t="shared" si="34"/>
         <v>50806730</v>
       </c>
-      <c r="AR22" s="60">
-        <f t="shared" si="30"/>
+      <c r="AR22" s="59">
+        <f t="shared" si="34"/>
         <v>168574296</v>
       </c>
-      <c r="AS22" s="60">
-        <f t="shared" si="30"/>
+      <c r="AS22" s="59">
+        <f t="shared" si="34"/>
         <v>17133409</v>
       </c>
-      <c r="AT22" s="60">
-        <f t="shared" si="30"/>
+      <c r="AT22" s="59">
+        <f t="shared" si="34"/>
         <v>275641384</v>
       </c>
-      <c r="AU22" s="60">
-        <f t="shared" si="34"/>
+      <c r="AU22" s="59">
+        <f t="shared" si="38"/>
         <v>561953724</v>
       </c>
-    </row>
-    <row r="23" spans="1:47" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="AW22" s="126">
+        <f>SUMIFS(ventas_unidades,ventas_vendedor,$A22,ventas_año,AW$16)</f>
+        <v>25153</v>
+      </c>
+      <c r="AX22" s="78">
+        <f>SUMIFS(ventas_unidades,ventas_vendedor,$A22,ventas_año,AX$16)</f>
+        <v>33627</v>
+      </c>
+      <c r="AY22" s="78">
+        <f>SUMIFS(ventas_unidades,ventas_vendedor,$A22,ventas_año,AY$16)</f>
+        <v>36420</v>
+      </c>
+      <c r="AZ22" s="78">
+        <f>SUMIFS(ventas_unidades,ventas_vendedor,$A22,ventas_año,AZ$16)</f>
+        <v>2867</v>
+      </c>
+      <c r="BA22" s="78">
+        <f>SUMIFS(ventas_unidades,ventas_vendedor,$A22,ventas_año,BA$16)</f>
+        <v>1927</v>
+      </c>
+      <c r="BB22" s="78">
+        <f t="shared" ref="BB22" si="41">SUM(AW22:BA22)</f>
+        <v>99994</v>
+      </c>
+      <c r="BC22" s="127"/>
+      <c r="BD22" s="128">
+        <f>SUMIFS(ventas_total,ventas_vendedor,$A22,ventas_año,BD$8)</f>
+        <v>175466052</v>
+      </c>
+      <c r="BE22" s="129">
+        <f>SUMIFS(ventas_total,ventas_vendedor,$A22,ventas_año,BE$8)</f>
+        <v>177412674</v>
+      </c>
+      <c r="BF22" s="129">
+        <f>SUMIFS(ventas_total,ventas_vendedor,$A22,ventas_año,BF$8)</f>
+        <v>206477864</v>
+      </c>
+      <c r="BG22" s="129">
+        <f>SUMIFS(ventas_total,ventas_vendedor,$A22,ventas_año,BG$8)</f>
+        <v>2048742</v>
+      </c>
+      <c r="BH22" s="129">
+        <f>SUMIFS(ventas_total,ventas_vendedor,$A22,ventas_año,BH$8)</f>
+        <v>548392</v>
+      </c>
+      <c r="BI22" s="129">
+        <f t="shared" ref="BI22" si="42">SUM(BD22:BH22)</f>
+        <v>561953724</v>
+      </c>
+    </row>
+    <row r="23" spans="1:61" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="B23" s="117">
+      <c r="B23" s="116">
         <f>SUM(B17:B22)</f>
         <v>858227</v>
       </c>
-      <c r="C23" s="116">
+      <c r="C23" s="115">
         <f>SUBTOTAL(109,estadisticas!$C$17:$C$22)</f>
         <v>3230017545</v>
       </c>
-      <c r="E23" s="95">
+      <c r="E23" s="94">
         <f>SUM(E17:E22)</f>
         <v>110903</v>
       </c>
-      <c r="F23" s="51">
-        <f t="shared" ref="F23:J23" si="35">SUM(F17:F22)</f>
+      <c r="F23" s="50">
+        <f t="shared" ref="F23:J23" si="43">SUM(F17:F22)</f>
         <v>304519</v>
       </c>
-      <c r="G23" s="51">
-        <f t="shared" si="35"/>
+      <c r="G23" s="50">
+        <f t="shared" si="43"/>
         <v>118380</v>
       </c>
-      <c r="H23" s="51">
-        <f t="shared" si="35"/>
+      <c r="H23" s="50">
+        <f t="shared" si="43"/>
         <v>115644</v>
       </c>
-      <c r="I23" s="51">
-        <f t="shared" si="35"/>
+      <c r="I23" s="50">
+        <f t="shared" si="43"/>
         <v>208781</v>
       </c>
-      <c r="J23" s="118">
-        <f t="shared" si="35"/>
+      <c r="J23" s="117">
+        <f t="shared" si="43"/>
         <v>858227</v>
       </c>
-      <c r="L23" s="109">
+      <c r="L23" s="108">
         <f>SUM(L17:L22)</f>
         <v>650543568</v>
       </c>
-      <c r="M23" s="69">
-        <f t="shared" ref="M23:Q23" si="36">SUM(M17:M22)</f>
+      <c r="M23" s="68">
+        <f t="shared" ref="M23:Q23" si="44">SUM(M17:M22)</f>
         <v>578124392</v>
       </c>
-      <c r="N23" s="69">
-        <f t="shared" si="36"/>
+      <c r="N23" s="68">
+        <f t="shared" si="44"/>
         <v>690157736</v>
       </c>
-      <c r="O23" s="69">
-        <f t="shared" si="36"/>
+      <c r="O23" s="68">
+        <f t="shared" si="44"/>
         <v>654943915</v>
       </c>
-      <c r="P23" s="69">
-        <f t="shared" si="36"/>
+      <c r="P23" s="68">
+        <f t="shared" si="44"/>
         <v>656247934</v>
       </c>
-      <c r="Q23" s="115">
-        <f t="shared" si="36"/>
+      <c r="Q23" s="114">
+        <f t="shared" si="44"/>
         <v>3230017545</v>
       </c>
-      <c r="S23" s="94"/>
-      <c r="T23" s="54"/>
-      <c r="U23" s="54"/>
-      <c r="V23" s="54"/>
-      <c r="W23" s="54"/>
-      <c r="X23" s="54"/>
-      <c r="Y23" s="54"/>
-      <c r="AA23" s="108"/>
-      <c r="AB23" s="68"/>
-      <c r="AC23" s="68"/>
-      <c r="AD23" s="68"/>
-      <c r="AE23" s="68"/>
-      <c r="AF23" s="68"/>
-      <c r="AG23" s="68"/>
-      <c r="AI23" s="95">
+      <c r="S23" s="93"/>
+      <c r="T23" s="53"/>
+      <c r="U23" s="53"/>
+      <c r="V23" s="53"/>
+      <c r="W23" s="53"/>
+      <c r="X23" s="53"/>
+      <c r="Y23" s="53"/>
+      <c r="AA23" s="107"/>
+      <c r="AB23" s="67"/>
+      <c r="AC23" s="67"/>
+      <c r="AD23" s="67"/>
+      <c r="AE23" s="67"/>
+      <c r="AF23" s="67"/>
+      <c r="AG23" s="67"/>
+      <c r="AI23" s="94">
         <f>SUM(AI17:AI22)</f>
         <v>110109</v>
       </c>
-      <c r="AJ23" s="51">
-        <f t="shared" ref="AJ23:AN23" si="37">SUM(AJ17:AJ22)</f>
+      <c r="AJ23" s="50">
+        <f t="shared" ref="AJ23:AN23" si="45">SUM(AJ17:AJ22)</f>
         <v>213260</v>
       </c>
-      <c r="AK23" s="51">
-        <f t="shared" si="37"/>
+      <c r="AK23" s="50">
+        <f t="shared" si="45"/>
         <v>116030</v>
       </c>
-      <c r="AL23" s="51">
-        <f t="shared" si="37"/>
+      <c r="AL23" s="50">
+        <f t="shared" si="45"/>
         <v>312792</v>
       </c>
-      <c r="AM23" s="51">
-        <f t="shared" si="37"/>
+      <c r="AM23" s="50">
+        <f t="shared" si="45"/>
         <v>106036</v>
       </c>
-      <c r="AN23" s="118">
-        <f t="shared" si="37"/>
+      <c r="AN23" s="117">
+        <f t="shared" si="45"/>
         <v>858227</v>
       </c>
-      <c r="AP23" s="109">
+      <c r="AP23" s="108">
         <f>SUM(AP17:AP22)</f>
         <v>646106962</v>
       </c>
-      <c r="AQ23" s="69">
-        <f t="shared" ref="AQ23" si="38">SUM(AQ17:AQ22)</f>
+      <c r="AQ23" s="68">
+        <f t="shared" ref="AQ23" si="46">SUM(AQ17:AQ22)</f>
         <v>576804336</v>
       </c>
-      <c r="AR23" s="69">
-        <f t="shared" ref="AR23" si="39">SUM(AR17:AR22)</f>
+      <c r="AR23" s="68">
+        <f t="shared" ref="AR23" si="47">SUM(AR17:AR22)</f>
         <v>687706530</v>
       </c>
-      <c r="AS23" s="69">
-        <f t="shared" ref="AS23" si="40">SUM(AS17:AS22)</f>
+      <c r="AS23" s="68">
+        <f t="shared" ref="AS23" si="48">SUM(AS17:AS22)</f>
         <v>654677692</v>
       </c>
-      <c r="AT23" s="69">
-        <f t="shared" ref="AT23" si="41">SUM(AT17:AT22)</f>
+      <c r="AT23" s="68">
+        <f t="shared" ref="AT23" si="49">SUM(AT17:AT22)</f>
         <v>664722025</v>
       </c>
-      <c r="AU23" s="115">
-        <f t="shared" ref="AU23" si="42">SUM(AU17:AU22)</f>
+      <c r="AU23" s="114">
+        <f t="shared" ref="AU23" si="50">SUM(AU17:AU22)</f>
         <v>3230017545</v>
       </c>
-    </row>
-    <row r="24" spans="1:47" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="25" spans="1:47" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="AW23" s="94">
+        <f>SUM(AW18:AW21)</f>
+        <v>123206</v>
+      </c>
+      <c r="AX23" s="50">
+        <f>SUM(AX18:AX21)</f>
+        <v>90698</v>
+      </c>
+      <c r="AY23" s="50">
+        <f>SUM(AY18:AY21)</f>
+        <v>104346</v>
+      </c>
+      <c r="AZ23" s="50">
+        <f>SUM(AZ18:AZ21)</f>
+        <v>116889</v>
+      </c>
+      <c r="BA23" s="50">
+        <f>SUM(BA18:BA21)</f>
+        <v>201429</v>
+      </c>
+      <c r="BB23" s="117">
+        <f>SUM(BB17:BB21)</f>
+        <v>758233</v>
+      </c>
+      <c r="BD23" s="108">
+        <f>SUM(BD17:BD21)</f>
+        <v>831778099</v>
+      </c>
+      <c r="BE23" s="68">
+        <f>SUM(BE17:BE21)</f>
+        <v>929433798</v>
+      </c>
+      <c r="BF23" s="68">
+        <f>SUM(BF17:BF21)</f>
+        <v>882832483</v>
+      </c>
+      <c r="BG23" s="68">
+        <f>SUM(BG17:BG21)</f>
+        <v>13033979</v>
+      </c>
+      <c r="BH23" s="68">
+        <f>SUM(BH17:BH21)</f>
+        <v>10985462</v>
+      </c>
+      <c r="BI23" s="114">
+        <f>SUM(BI17:BI21)</f>
+        <v>2668063821</v>
+      </c>
+    </row>
+    <row r="24" spans="1:61" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="25" spans="1:61" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="7" t="s">
         <v>43</v>
       </c>
@@ -8191,98 +9184,135 @@
       <c r="C25" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="E25" s="87" t="s">
+      <c r="E25" s="86" t="s">
         <v>6</v>
       </c>
-      <c r="F25" s="53" t="s">
+      <c r="F25" s="52" t="s">
         <v>33</v>
       </c>
-      <c r="G25" s="53" t="s">
+      <c r="G25" s="52" t="s">
         <v>15</v>
       </c>
-      <c r="H25" s="53" t="s">
+      <c r="H25" s="52" t="s">
         <v>18</v>
       </c>
-      <c r="I25" s="53" t="s">
+      <c r="I25" s="52" t="s">
         <v>47</v>
       </c>
-      <c r="J25" s="53" t="s">
+      <c r="J25" s="52" t="s">
         <v>34</v>
       </c>
-      <c r="L25" s="101" t="s">
+      <c r="L25" s="100" t="s">
         <v>6</v>
       </c>
-      <c r="M25" s="57" t="s">
+      <c r="M25" s="56" t="s">
         <v>33</v>
       </c>
-      <c r="N25" s="57" t="s">
+      <c r="N25" s="56" t="s">
         <v>15</v>
       </c>
-      <c r="O25" s="57" t="s">
+      <c r="O25" s="56" t="s">
         <v>18</v>
       </c>
-      <c r="P25" s="57" t="s">
+      <c r="P25" s="56" t="s">
         <v>47</v>
       </c>
-      <c r="Q25" s="57" t="s">
+      <c r="Q25" s="56" t="s">
         <v>34</v>
       </c>
-      <c r="S25" s="87" t="s">
+      <c r="S25" s="86" t="s">
         <v>28</v>
       </c>
-      <c r="T25" s="53" t="s">
+      <c r="T25" s="52" t="s">
         <v>8</v>
       </c>
-      <c r="U25" s="53" t="s">
+      <c r="U25" s="52" t="s">
         <v>11</v>
       </c>
-      <c r="V25" s="53" t="s">
+      <c r="V25" s="52" t="s">
         <v>13</v>
       </c>
-      <c r="W25" s="53" t="s">
+      <c r="W25" s="52" t="s">
         <v>29</v>
       </c>
-      <c r="X25" s="53" t="s">
+      <c r="X25" s="52" t="s">
         <v>30</v>
       </c>
-      <c r="Y25" s="53" t="s">
+      <c r="Y25" s="52" t="s">
         <v>39</v>
       </c>
-      <c r="AA25" s="101" t="s">
+      <c r="AA25" s="100" t="s">
         <v>28</v>
       </c>
-      <c r="AB25" s="57" t="s">
+      <c r="AB25" s="56" t="s">
         <v>8</v>
       </c>
-      <c r="AC25" s="57" t="s">
+      <c r="AC25" s="56" t="s">
         <v>11</v>
       </c>
-      <c r="AD25" s="57" t="s">
+      <c r="AD25" s="56" t="s">
         <v>13</v>
       </c>
-      <c r="AE25" s="57" t="s">
+      <c r="AE25" s="56" t="s">
         <v>29</v>
       </c>
-      <c r="AF25" s="57" t="s">
+      <c r="AF25" s="56" t="s">
         <v>30</v>
       </c>
-      <c r="AG25" s="57" t="s">
+      <c r="AG25" s="56" t="s">
         <v>39</v>
       </c>
-      <c r="AI25" s="94"/>
-      <c r="AJ25" s="54"/>
-      <c r="AK25" s="54"/>
-      <c r="AL25" s="54"/>
-      <c r="AM25" s="54"/>
-      <c r="AN25" s="54"/>
-      <c r="AP25" s="96"/>
-      <c r="AQ25" s="50"/>
-      <c r="AR25" s="50"/>
-      <c r="AS25" s="50"/>
-      <c r="AT25" s="50"/>
-      <c r="AU25" s="50"/>
-    </row>
-    <row r="26" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AI25" s="93"/>
+      <c r="AJ25" s="53"/>
+      <c r="AK25" s="53"/>
+      <c r="AL25" s="53"/>
+      <c r="AM25" s="53"/>
+      <c r="AN25" s="53"/>
+      <c r="AP25" s="95"/>
+      <c r="AQ25" s="49"/>
+      <c r="AR25" s="49"/>
+      <c r="AS25" s="49"/>
+      <c r="AT25" s="49"/>
+      <c r="AU25" s="49"/>
+      <c r="AW25" s="125">
+        <v>2008</v>
+      </c>
+      <c r="AX25" s="21">
+        <v>2009</v>
+      </c>
+      <c r="AY25" s="21">
+        <v>2010</v>
+      </c>
+      <c r="AZ25" s="21">
+        <v>2011</v>
+      </c>
+      <c r="BA25" s="21">
+        <v>2012</v>
+      </c>
+      <c r="BB25" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="BC25" s="2"/>
+      <c r="BD25" s="125">
+        <v>2008</v>
+      </c>
+      <c r="BE25" s="21">
+        <v>2009</v>
+      </c>
+      <c r="BF25" s="21">
+        <v>2010</v>
+      </c>
+      <c r="BG25" s="21">
+        <v>2011</v>
+      </c>
+      <c r="BH25" s="21">
+        <v>2012</v>
+      </c>
+      <c r="BI25" s="7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="26" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A26" s="10" t="s">
         <v>31</v>
       </c>
@@ -8294,124 +9324,172 @@
         <f>SUMIF(ventas_region,$A26,ventas_total)</f>
         <v>646106962</v>
       </c>
-      <c r="E26" s="82">
-        <f t="shared" ref="E26:I30" si="43">SUMIFS(ventas_unidades,ventas_region,$A26,ventas_producto,E$25)</f>
+      <c r="E26" s="81">
+        <f t="shared" ref="E26:I30" si="51">SUMIFS(ventas_unidades,ventas_region,$A26,ventas_producto,E$25)</f>
         <v>101037</v>
       </c>
       <c r="F26" s="17">
-        <f t="shared" si="43"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="G26" s="17">
-        <f t="shared" si="43"/>
+        <f t="shared" si="51"/>
         <v>8943</v>
       </c>
       <c r="H26" s="17">
-        <f t="shared" si="43"/>
+        <f t="shared" si="51"/>
         <v>129</v>
       </c>
       <c r="I26" s="17">
-        <f t="shared" si="43"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="J26" s="17">
         <f>SUM(E26:I30)</f>
         <v>858227</v>
       </c>
-      <c r="L26" s="97">
-        <f t="shared" ref="L26:P30" si="44">SUMIFS(ventas_total,ventas_region,$A26,ventas_producto,L$25)</f>
+      <c r="L26" s="96">
+        <f t="shared" ref="L26:P30" si="52">SUMIFS(ventas_total,ventas_region,$A26,ventas_producto,L$25)</f>
         <v>640574818</v>
       </c>
-      <c r="M26" s="59">
-        <f t="shared" si="44"/>
+      <c r="M26" s="58">
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
-      <c r="N26" s="59">
-        <f t="shared" si="44"/>
+      <c r="N26" s="58">
+        <f t="shared" si="52"/>
         <v>4328234</v>
       </c>
-      <c r="O26" s="59">
-        <f t="shared" si="44"/>
+      <c r="O26" s="58">
+        <f t="shared" si="52"/>
         <v>1203910</v>
       </c>
-      <c r="P26" s="59">
-        <f t="shared" si="44"/>
+      <c r="P26" s="58">
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
-      <c r="Q26" s="59">
+      <c r="Q26" s="58">
         <f>SUM(L26:P26)</f>
         <v>646106962</v>
       </c>
-      <c r="S26" s="82">
-        <f t="shared" ref="S26:X30" si="45">SUMIFS(ventas_unidades,ventas_region,$A26,ventas_vendedor,S$25)</f>
+      <c r="S26" s="81">
+        <f t="shared" ref="S26:X30" si="53">SUMIFS(ventas_unidades,ventas_region,$A26,ventas_vendedor,S$25)</f>
         <v>23075</v>
       </c>
       <c r="T26" s="29">
-        <f t="shared" si="45"/>
+        <f t="shared" si="53"/>
         <v>27346</v>
       </c>
       <c r="U26" s="29">
-        <f t="shared" si="45"/>
+        <f t="shared" si="53"/>
         <v>9125</v>
       </c>
       <c r="V26" s="17">
-        <f t="shared" si="45"/>
+        <f t="shared" si="53"/>
         <v>30665</v>
       </c>
       <c r="W26" s="29">
-        <f t="shared" si="45"/>
+        <f t="shared" si="53"/>
         <v>11047</v>
       </c>
       <c r="X26" s="29">
-        <f t="shared" si="45"/>
+        <f t="shared" si="53"/>
         <v>8851</v>
       </c>
       <c r="Y26" s="17">
         <f>SUM(S26:X26)</f>
         <v>110109</v>
       </c>
-      <c r="AA26" s="97">
-        <f t="shared" ref="AA26:AF30" si="46">SUMIFS(ventas_total,ventas_region,$A26,ventas_vendedor,AA$25)</f>
+      <c r="AA26" s="96">
+        <f t="shared" ref="AA26:AF30" si="54">SUMIFS(ventas_total,ventas_region,$A26,ventas_vendedor,AA$25)</f>
         <v>109144041</v>
       </c>
-      <c r="AB26" s="64">
-        <f t="shared" si="46"/>
+      <c r="AB26" s="63">
+        <f t="shared" si="54"/>
         <v>193222871</v>
       </c>
-      <c r="AC26" s="64">
-        <f t="shared" si="46"/>
+      <c r="AC26" s="63">
+        <f t="shared" si="54"/>
         <v>59797810</v>
       </c>
-      <c r="AD26" s="59">
-        <f t="shared" si="46"/>
+      <c r="AD26" s="58">
+        <f t="shared" si="54"/>
         <v>139608342</v>
       </c>
-      <c r="AE26" s="64">
-        <f t="shared" si="46"/>
+      <c r="AE26" s="63">
+        <f t="shared" si="54"/>
         <v>94535993</v>
       </c>
-      <c r="AF26" s="64">
-        <f t="shared" si="46"/>
+      <c r="AF26" s="63">
+        <f t="shared" si="54"/>
         <v>49797905</v>
       </c>
-      <c r="AG26" s="59">
+      <c r="AG26" s="58">
         <f>SUM(AA26:AF26)</f>
         <v>646106962</v>
       </c>
-      <c r="AI26" s="94"/>
-      <c r="AJ26" s="54"/>
-      <c r="AK26" s="54"/>
-      <c r="AL26" s="54"/>
-      <c r="AM26" s="54"/>
-      <c r="AN26" s="54"/>
-      <c r="AP26" s="96"/>
-      <c r="AQ26" s="50"/>
-      <c r="AR26" s="50"/>
-      <c r="AS26" s="50"/>
-      <c r="AT26" s="50"/>
-      <c r="AU26" s="50"/>
-    </row>
-    <row r="27" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AI26" s="93"/>
+      <c r="AJ26" s="53"/>
+      <c r="AK26" s="53"/>
+      <c r="AL26" s="53"/>
+      <c r="AM26" s="53"/>
+      <c r="AN26" s="53"/>
+      <c r="AP26" s="95"/>
+      <c r="AQ26" s="49"/>
+      <c r="AR26" s="49"/>
+      <c r="AS26" s="49"/>
+      <c r="AT26" s="49"/>
+      <c r="AU26" s="49"/>
+      <c r="AW26" s="81">
+        <f>SUMIFS(ventas_unidades,ventas_region,$A26,ventas_año,AW$8)</f>
+        <v>33032</v>
+      </c>
+      <c r="AX26" s="17">
+        <f>SUMIFS(ventas_unidades,ventas_region,$A26,ventas_año,AX$8)</f>
+        <v>32671</v>
+      </c>
+      <c r="AY26" s="17">
+        <f>SUMIFS(ventas_unidades,ventas_region,$A26,ventas_año,AY$8)</f>
+        <v>35334</v>
+      </c>
+      <c r="AZ26" s="17">
+        <f>SUMIFS(ventas_unidades,ventas_region,$A26,ventas_año,AZ$8)</f>
+        <v>9072</v>
+      </c>
+      <c r="BA26" s="17">
+        <f>SUMIFS(ventas_unidades,ventas_region,$A26,ventas_año,BA$8)</f>
+        <v>0</v>
+      </c>
+      <c r="BB26" s="17">
+        <f>SUM(AW26:BA26)</f>
+        <v>110109</v>
+      </c>
+      <c r="BD26" s="96">
+        <f>SUMIFS(ventas_total,ventas_region,$A26,ventas_año,BD$8)</f>
+        <v>218669111</v>
+      </c>
+      <c r="BE26" s="58">
+        <f>SUMIFS(ventas_total,ventas_region,$A26,ventas_año,BE$8)</f>
+        <v>203341463</v>
+      </c>
+      <c r="BF26" s="58">
+        <f>SUMIFS(ventas_total,ventas_region,$A26,ventas_año,BF$8)</f>
+        <v>218564244</v>
+      </c>
+      <c r="BG26" s="58">
+        <f>SUMIFS(ventas_total,ventas_region,$A26,ventas_año,BG$8)</f>
+        <v>5532144</v>
+      </c>
+      <c r="BH26" s="58">
+        <f>SUMIFS(ventas_total,ventas_region,$A26,ventas_año,BH$8)</f>
+        <v>0</v>
+      </c>
+      <c r="BI26" s="58">
+        <f>SUM(BD26:BH26)</f>
+        <v>646106962</v>
+      </c>
+    </row>
+    <row r="27" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A27" s="26" t="s">
         <v>9</v>
       </c>
@@ -8423,124 +9501,172 @@
         <f>SUMIF(ventas_region,$A27,ventas_total)</f>
         <v>576804336</v>
       </c>
-      <c r="E27" s="83">
-        <f t="shared" si="43"/>
+      <c r="E27" s="82">
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="F27" s="18">
-        <f t="shared" si="43"/>
+        <f t="shared" si="51"/>
         <v>105314</v>
       </c>
       <c r="G27" s="18">
-        <f t="shared" si="43"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="H27" s="18">
-        <f t="shared" si="43"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="I27" s="18">
-        <f t="shared" si="43"/>
+        <f t="shared" si="51"/>
         <v>107946</v>
       </c>
       <c r="J27" s="18">
-        <f t="shared" ref="J27:J30" si="47">SUM(E27:I31)</f>
+        <f t="shared" ref="J27:J30" si="55">SUM(E27:I31)</f>
         <v>1606345</v>
       </c>
-      <c r="L27" s="98">
-        <f t="shared" si="44"/>
+      <c r="L27" s="97">
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
-      <c r="M27" s="60">
-        <f t="shared" si="44"/>
+      <c r="M27" s="59">
+        <f t="shared" si="52"/>
         <v>576702901</v>
       </c>
-      <c r="N27" s="60">
-        <f t="shared" si="44"/>
+      <c r="N27" s="59">
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
-      <c r="O27" s="60">
-        <f t="shared" si="44"/>
+      <c r="O27" s="59">
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
-      <c r="P27" s="60">
-        <f t="shared" si="44"/>
+      <c r="P27" s="59">
+        <f t="shared" si="52"/>
         <v>101435</v>
       </c>
-      <c r="Q27" s="60">
-        <f t="shared" ref="Q27:Q30" si="48">SUM(L27:P27)</f>
+      <c r="Q27" s="59">
+        <f t="shared" ref="Q27:Q30" si="56">SUM(L27:P27)</f>
         <v>576804336</v>
       </c>
-      <c r="S27" s="91">
-        <f t="shared" si="45"/>
+      <c r="S27" s="90">
+        <f t="shared" si="53"/>
         <v>7195</v>
       </c>
       <c r="T27" s="30">
-        <f t="shared" si="45"/>
+        <f t="shared" si="53"/>
         <v>51553</v>
       </c>
       <c r="U27" s="30">
-        <f t="shared" si="45"/>
+        <f t="shared" si="53"/>
         <v>9023</v>
       </c>
       <c r="V27" s="30">
-        <f t="shared" si="45"/>
+        <f t="shared" si="53"/>
         <v>103585</v>
       </c>
       <c r="W27" s="30">
-        <f t="shared" si="45"/>
+        <f t="shared" si="53"/>
         <v>25399</v>
       </c>
       <c r="X27" s="30">
-        <f t="shared" si="45"/>
+        <f t="shared" si="53"/>
         <v>16505</v>
       </c>
       <c r="Y27" s="30">
-        <f t="shared" ref="Y27:Y30" si="49">SUM(S27:X27)</f>
+        <f t="shared" ref="Y27:Y30" si="57">SUM(S27:X27)</f>
         <v>213260</v>
       </c>
-      <c r="AA27" s="105">
-        <f t="shared" si="46"/>
+      <c r="AA27" s="104">
+        <f t="shared" si="54"/>
         <v>52631529</v>
       </c>
-      <c r="AB27" s="65">
-        <f t="shared" si="46"/>
+      <c r="AB27" s="64">
+        <f t="shared" si="54"/>
         <v>271532147</v>
       </c>
-      <c r="AC27" s="65">
-        <f t="shared" si="46"/>
+      <c r="AC27" s="64">
+        <f t="shared" si="54"/>
         <v>63246530</v>
       </c>
-      <c r="AD27" s="65">
-        <f t="shared" si="46"/>
+      <c r="AD27" s="64">
+        <f t="shared" si="54"/>
         <v>44964557</v>
       </c>
-      <c r="AE27" s="65">
-        <f t="shared" si="46"/>
+      <c r="AE27" s="64">
+        <f t="shared" si="54"/>
         <v>93622843</v>
       </c>
-      <c r="AF27" s="65">
-        <f t="shared" si="46"/>
+      <c r="AF27" s="64">
+        <f t="shared" si="54"/>
         <v>50806730</v>
       </c>
-      <c r="AG27" s="65">
-        <f t="shared" ref="AG27:AG30" si="50">SUM(AA27:AF27)</f>
+      <c r="AG27" s="64">
+        <f t="shared" ref="AG27:AG30" si="58">SUM(AA27:AF27)</f>
         <v>576804336</v>
       </c>
-      <c r="AI27" s="94"/>
-      <c r="AJ27" s="54"/>
-      <c r="AK27" s="54"/>
-      <c r="AL27" s="54"/>
-      <c r="AM27" s="54"/>
-      <c r="AN27" s="54"/>
-      <c r="AP27" s="96"/>
-      <c r="AQ27" s="50"/>
-      <c r="AR27" s="50"/>
-      <c r="AS27" s="50"/>
-      <c r="AT27" s="50"/>
-      <c r="AU27" s="50"/>
-    </row>
-    <row r="28" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AI27" s="93"/>
+      <c r="AJ27" s="53"/>
+      <c r="AK27" s="53"/>
+      <c r="AL27" s="53"/>
+      <c r="AM27" s="53"/>
+      <c r="AN27" s="53"/>
+      <c r="AP27" s="95"/>
+      <c r="AQ27" s="49"/>
+      <c r="AR27" s="49"/>
+      <c r="AS27" s="49"/>
+      <c r="AT27" s="49"/>
+      <c r="AU27" s="49"/>
+      <c r="AW27" s="82">
+        <f>SUMIFS(ventas_unidades,ventas_region,$A27,ventas_año,AW$8)</f>
+        <v>32696</v>
+      </c>
+      <c r="AX27" s="46">
+        <f>SUMIFS(ventas_unidades,ventas_region,$A27,ventas_año,AX$8)</f>
+        <v>31651</v>
+      </c>
+      <c r="AY27" s="46">
+        <f>SUMIFS(ventas_unidades,ventas_region,$A27,ventas_año,AY$8)</f>
+        <v>40967</v>
+      </c>
+      <c r="AZ27" s="46">
+        <f>SUMIFS(ventas_unidades,ventas_region,$A27,ventas_año,AZ$8)</f>
+        <v>107946</v>
+      </c>
+      <c r="BA27" s="46">
+        <f>SUMIFS(ventas_unidades,ventas_region,$A27,ventas_año,BA$8)</f>
+        <v>0</v>
+      </c>
+      <c r="BB27" s="46">
+        <f t="shared" ref="BB27:BB30" si="59">SUM(AW27:BA27)</f>
+        <v>213260</v>
+      </c>
+      <c r="BD27" s="97">
+        <f>SUMIFS(ventas_total,ventas_region,$A27,ventas_año,BD$8)</f>
+        <v>160364763</v>
+      </c>
+      <c r="BE27" s="69">
+        <f>SUMIFS(ventas_total,ventas_region,$A27,ventas_año,BE$8)</f>
+        <v>201880917</v>
+      </c>
+      <c r="BF27" s="69">
+        <f>SUMIFS(ventas_total,ventas_region,$A27,ventas_año,BF$8)</f>
+        <v>214457221</v>
+      </c>
+      <c r="BG27" s="69">
+        <f>SUMIFS(ventas_total,ventas_region,$A27,ventas_año,BG$8)</f>
+        <v>101435</v>
+      </c>
+      <c r="BH27" s="69">
+        <f>SUMIFS(ventas_total,ventas_region,$A27,ventas_año,BH$8)</f>
+        <v>0</v>
+      </c>
+      <c r="BI27" s="69">
+        <f t="shared" ref="BI27:BI30" si="60">SUM(BD27:BH27)</f>
+        <v>576804336</v>
+      </c>
+    </row>
+    <row r="28" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A28" s="27" t="s">
         <v>16</v>
       </c>
@@ -8552,124 +9678,172 @@
         <f>SUMIF(ventas_region,$A28,ventas_total)</f>
         <v>687706530</v>
       </c>
-      <c r="E28" s="84">
-        <f t="shared" si="43"/>
+      <c r="E28" s="83">
+        <f t="shared" si="51"/>
         <v>2738</v>
       </c>
       <c r="F28" s="19">
-        <f t="shared" si="43"/>
+        <f t="shared" si="51"/>
         <v>1928</v>
       </c>
       <c r="G28" s="19">
-        <f t="shared" si="43"/>
+        <f t="shared" si="51"/>
         <v>109437</v>
       </c>
       <c r="H28" s="19">
-        <f t="shared" si="43"/>
+        <f t="shared" si="51"/>
         <v>1927</v>
       </c>
       <c r="I28" s="19">
-        <f t="shared" si="43"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="J28" s="19">
-        <f t="shared" si="47"/>
+        <f t="shared" si="55"/>
         <v>1393085</v>
       </c>
-      <c r="L28" s="99">
-        <f t="shared" si="44"/>
+      <c r="L28" s="98">
+        <f t="shared" si="52"/>
         <v>844832</v>
       </c>
-      <c r="M28" s="61">
-        <f t="shared" si="44"/>
+      <c r="M28" s="60">
+        <f t="shared" si="52"/>
         <v>108214</v>
       </c>
-      <c r="N28" s="61">
-        <f t="shared" si="44"/>
+      <c r="N28" s="60">
+        <f t="shared" si="52"/>
         <v>685829502</v>
       </c>
-      <c r="O28" s="61">
-        <f t="shared" si="44"/>
+      <c r="O28" s="60">
+        <f t="shared" si="52"/>
         <v>923982</v>
       </c>
-      <c r="P28" s="61">
-        <f t="shared" si="44"/>
+      <c r="P28" s="60">
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
-      <c r="Q28" s="61">
-        <f t="shared" si="48"/>
+      <c r="Q28" s="60">
+        <f t="shared" si="56"/>
         <v>687706530</v>
       </c>
-      <c r="S28" s="92">
-        <f t="shared" si="45"/>
+      <c r="S28" s="91">
+        <f t="shared" si="53"/>
         <v>39170</v>
       </c>
       <c r="T28" s="31">
-        <f t="shared" si="45"/>
+        <f t="shared" si="53"/>
         <v>19565</v>
       </c>
       <c r="U28" s="31">
-        <f t="shared" si="45"/>
+        <f t="shared" si="53"/>
         <v>6969</v>
       </c>
       <c r="V28" s="31">
-        <f t="shared" si="45"/>
+        <f t="shared" si="53"/>
         <v>9925</v>
       </c>
       <c r="W28" s="31">
-        <f t="shared" si="45"/>
+        <f t="shared" si="53"/>
         <v>12633</v>
       </c>
       <c r="X28" s="31">
-        <f t="shared" si="45"/>
+        <f t="shared" si="53"/>
         <v>27768</v>
       </c>
       <c r="Y28" s="31">
-        <f t="shared" si="49"/>
+        <f t="shared" si="57"/>
         <v>116030</v>
       </c>
-      <c r="AA28" s="106">
-        <f t="shared" si="46"/>
+      <c r="AA28" s="105">
+        <f t="shared" si="54"/>
         <v>240927099</v>
       </c>
-      <c r="AB28" s="66">
-        <f t="shared" si="46"/>
+      <c r="AB28" s="65">
+        <f t="shared" si="54"/>
         <v>131950052</v>
       </c>
-      <c r="AC28" s="66">
-        <f t="shared" si="46"/>
+      <c r="AC28" s="65">
+        <f t="shared" si="54"/>
         <v>40433106</v>
       </c>
-      <c r="AD28" s="66">
-        <f t="shared" si="46"/>
+      <c r="AD28" s="65">
+        <f t="shared" si="54"/>
         <v>27153333</v>
       </c>
-      <c r="AE28" s="66">
-        <f t="shared" si="46"/>
+      <c r="AE28" s="65">
+        <f t="shared" si="54"/>
         <v>78668644</v>
       </c>
-      <c r="AF28" s="66">
-        <f t="shared" si="46"/>
+      <c r="AF28" s="65">
+        <f t="shared" si="54"/>
         <v>168574296</v>
       </c>
-      <c r="AG28" s="66">
-        <f t="shared" si="50"/>
+      <c r="AG28" s="65">
+        <f t="shared" si="58"/>
         <v>687706530</v>
       </c>
-      <c r="AI28" s="94"/>
-      <c r="AJ28" s="54"/>
-      <c r="AK28" s="54"/>
-      <c r="AL28" s="54"/>
-      <c r="AM28" s="54"/>
-      <c r="AN28" s="54"/>
-      <c r="AP28" s="96"/>
-      <c r="AQ28" s="50"/>
-      <c r="AR28" s="50"/>
-      <c r="AS28" s="50"/>
-      <c r="AT28" s="50"/>
-      <c r="AU28" s="50"/>
-    </row>
-    <row r="29" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AI28" s="93"/>
+      <c r="AJ28" s="53"/>
+      <c r="AK28" s="53"/>
+      <c r="AL28" s="53"/>
+      <c r="AM28" s="53"/>
+      <c r="AN28" s="53"/>
+      <c r="AP28" s="95"/>
+      <c r="AQ28" s="49"/>
+      <c r="AR28" s="49"/>
+      <c r="AS28" s="49"/>
+      <c r="AT28" s="49"/>
+      <c r="AU28" s="49"/>
+      <c r="AW28" s="83">
+        <f>SUMIFS(ventas_unidades,ventas_region,$A28,ventas_año,AW$8)</f>
+        <v>39124</v>
+      </c>
+      <c r="AX28" s="47">
+        <f>SUMIFS(ventas_unidades,ventas_region,$A28,ventas_año,AX$8)</f>
+        <v>34000</v>
+      </c>
+      <c r="AY28" s="47">
+        <f>SUMIFS(ventas_unidades,ventas_region,$A28,ventas_año,AY$8)</f>
+        <v>31330</v>
+      </c>
+      <c r="AZ28" s="47">
+        <f>SUMIFS(ventas_unidades,ventas_region,$A28,ventas_año,AZ$8)</f>
+        <v>7721</v>
+      </c>
+      <c r="BA28" s="47">
+        <f>SUMIFS(ventas_unidades,ventas_region,$A28,ventas_año,BA$8)</f>
+        <v>3855</v>
+      </c>
+      <c r="BB28" s="47">
+        <f t="shared" si="59"/>
+        <v>116030</v>
+      </c>
+      <c r="BD28" s="98">
+        <f>SUMIFS(ventas_total,ventas_region,$A28,ventas_año,BD$8)</f>
+        <v>220801841</v>
+      </c>
+      <c r="BE28" s="70">
+        <f>SUMIFS(ventas_total,ventas_region,$A28,ventas_año,BE$8)</f>
+        <v>239992813</v>
+      </c>
+      <c r="BF28" s="70">
+        <f>SUMIFS(ventas_total,ventas_region,$A28,ventas_año,BF$8)</f>
+        <v>216914467</v>
+      </c>
+      <c r="BG28" s="70">
+        <f>SUMIFS(ventas_total,ventas_region,$A28,ventas_año,BG$8)</f>
+        <v>8965213</v>
+      </c>
+      <c r="BH28" s="70">
+        <f>SUMIFS(ventas_total,ventas_region,$A28,ventas_año,BH$8)</f>
+        <v>1032196</v>
+      </c>
+      <c r="BI28" s="70">
+        <f t="shared" si="60"/>
+        <v>687706530</v>
+      </c>
+    </row>
+    <row r="29" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A29" s="26" t="s">
         <v>19</v>
       </c>
@@ -8681,124 +9855,172 @@
         <f>SUMIF(ventas_region,$A29,ventas_total)</f>
         <v>654677692</v>
       </c>
-      <c r="E29" s="83">
-        <f t="shared" si="43"/>
+      <c r="E29" s="82">
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="F29" s="18">
-        <f t="shared" si="43"/>
+        <f t="shared" si="51"/>
         <v>197277</v>
       </c>
       <c r="G29" s="18">
-        <f t="shared" si="43"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="H29" s="18">
-        <f t="shared" si="43"/>
+        <f t="shared" si="51"/>
         <v>113588</v>
       </c>
       <c r="I29" s="18">
-        <f t="shared" si="43"/>
+        <f t="shared" si="51"/>
         <v>1927</v>
       </c>
       <c r="J29" s="18">
-        <f t="shared" si="47"/>
+        <f t="shared" si="55"/>
         <v>1277055</v>
       </c>
-      <c r="L29" s="98">
-        <f t="shared" si="44"/>
+      <c r="L29" s="97">
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
-      <c r="M29" s="60">
-        <f t="shared" si="44"/>
+      <c r="M29" s="59">
+        <f t="shared" si="52"/>
         <v>1313277</v>
       </c>
-      <c r="N29" s="60">
-        <f t="shared" si="44"/>
+      <c r="N29" s="59">
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
-      <c r="O29" s="60">
-        <f t="shared" si="44"/>
+      <c r="O29" s="59">
+        <f t="shared" si="52"/>
         <v>652816023</v>
       </c>
-      <c r="P29" s="60">
-        <f t="shared" si="44"/>
+      <c r="P29" s="59">
+        <f t="shared" si="52"/>
         <v>548392</v>
       </c>
-      <c r="Q29" s="60">
-        <f t="shared" si="48"/>
+      <c r="Q29" s="59">
+        <f t="shared" si="56"/>
         <v>654677692</v>
       </c>
-      <c r="S29" s="91">
-        <f t="shared" si="45"/>
+      <c r="S29" s="90">
+        <f t="shared" si="53"/>
         <v>39255</v>
       </c>
       <c r="T29" s="30">
-        <f t="shared" si="45"/>
+        <f t="shared" si="53"/>
         <v>12991</v>
       </c>
       <c r="U29" s="30">
-        <f t="shared" si="45"/>
+        <f t="shared" si="53"/>
         <v>2096</v>
       </c>
       <c r="V29" s="30">
-        <f t="shared" si="45"/>
+        <f t="shared" si="53"/>
         <v>197831</v>
       </c>
       <c r="W29" s="30">
-        <f t="shared" si="45"/>
+        <f t="shared" si="53"/>
         <v>53237</v>
       </c>
       <c r="X29" s="30">
-        <f t="shared" si="45"/>
+        <f t="shared" si="53"/>
         <v>7382</v>
       </c>
       <c r="Y29" s="30">
-        <f t="shared" si="49"/>
+        <f t="shared" si="57"/>
         <v>312792</v>
       </c>
-      <c r="AA29" s="105">
-        <f t="shared" si="46"/>
+      <c r="AA29" s="104">
+        <f t="shared" si="54"/>
         <v>170461858</v>
       </c>
-      <c r="AB29" s="65">
-        <f t="shared" si="46"/>
+      <c r="AB29" s="64">
+        <f t="shared" si="54"/>
         <v>75839132</v>
       </c>
-      <c r="AC29" s="65">
-        <f t="shared" si="46"/>
+      <c r="AC29" s="64">
+        <f t="shared" si="54"/>
         <v>31378227</v>
       </c>
-      <c r="AD29" s="65">
-        <f t="shared" si="46"/>
+      <c r="AD29" s="64">
+        <f t="shared" si="54"/>
         <v>23830600</v>
       </c>
-      <c r="AE29" s="65">
-        <f t="shared" si="46"/>
+      <c r="AE29" s="64">
+        <f t="shared" si="54"/>
         <v>336034466</v>
       </c>
-      <c r="AF29" s="65">
-        <f t="shared" si="46"/>
+      <c r="AF29" s="64">
+        <f t="shared" si="54"/>
         <v>17133409</v>
       </c>
-      <c r="AG29" s="65">
-        <f t="shared" si="50"/>
+      <c r="AG29" s="64">
+        <f t="shared" si="58"/>
         <v>654677692</v>
       </c>
-      <c r="AI29" s="94"/>
-      <c r="AJ29" s="54"/>
-      <c r="AK29" s="54"/>
-      <c r="AL29" s="54"/>
-      <c r="AM29" s="54"/>
-      <c r="AN29" s="54"/>
-      <c r="AP29" s="96"/>
-      <c r="AQ29" s="50"/>
-      <c r="AR29" s="50"/>
-      <c r="AS29" s="50"/>
-      <c r="AT29" s="50"/>
-      <c r="AU29" s="50"/>
-    </row>
-    <row r="30" spans="1:47" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="AI29" s="93"/>
+      <c r="AJ29" s="53"/>
+      <c r="AK29" s="53"/>
+      <c r="AL29" s="53"/>
+      <c r="AM29" s="53"/>
+      <c r="AN29" s="53"/>
+      <c r="AP29" s="95"/>
+      <c r="AQ29" s="49"/>
+      <c r="AR29" s="49"/>
+      <c r="AS29" s="49"/>
+      <c r="AT29" s="49"/>
+      <c r="AU29" s="49"/>
+      <c r="AW29" s="82">
+        <f>SUMIFS(ventas_unidades,ventas_region,$A29,ventas_año,AW$8)</f>
+        <v>40573</v>
+      </c>
+      <c r="AX29" s="46">
+        <f>SUMIFS(ventas_unidades,ventas_region,$A29,ventas_año,AX$8)</f>
+        <v>39442</v>
+      </c>
+      <c r="AY29" s="46">
+        <f>SUMIFS(ventas_unidades,ventas_region,$A29,ventas_año,AY$8)</f>
+        <v>33573</v>
+      </c>
+      <c r="AZ29" s="46">
+        <f>SUMIFS(ventas_unidades,ventas_region,$A29,ventas_año,AZ$8)</f>
+        <v>4903</v>
+      </c>
+      <c r="BA29" s="46">
+        <f>SUMIFS(ventas_unidades,ventas_region,$A29,ventas_año,BA$8)</f>
+        <v>194301</v>
+      </c>
+      <c r="BB29" s="46">
+        <f t="shared" si="59"/>
+        <v>312792</v>
+      </c>
+      <c r="BD29" s="97">
+        <f>SUMIFS(ventas_total,ventas_region,$A29,ventas_año,BD$8)</f>
+        <v>190929354</v>
+      </c>
+      <c r="BE29" s="69">
+        <f>SUMIFS(ventas_total,ventas_region,$A29,ventas_año,BE$8)</f>
+        <v>221383553</v>
+      </c>
+      <c r="BF29" s="69">
+        <f>SUMIFS(ventas_total,ventas_region,$A29,ventas_año,BF$8)</f>
+        <v>240503116</v>
+      </c>
+      <c r="BG29" s="69">
+        <f>SUMIFS(ventas_total,ventas_region,$A29,ventas_año,BG$8)</f>
+        <v>483929</v>
+      </c>
+      <c r="BH29" s="69">
+        <f>SUMIFS(ventas_total,ventas_region,$A29,ventas_año,BH$8)</f>
+        <v>1377740</v>
+      </c>
+      <c r="BI29" s="69">
+        <f t="shared" si="60"/>
+        <v>654677692</v>
+      </c>
+    </row>
+    <row r="30" spans="1:61" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="27" t="s">
         <v>21</v>
       </c>
@@ -8810,254 +10032,350 @@
         <f>SUMIF(ventas_region,$A30,ventas_total)</f>
         <v>664722025</v>
       </c>
-      <c r="E30" s="84">
-        <f t="shared" si="43"/>
+      <c r="E30" s="83">
+        <f t="shared" si="51"/>
         <v>7128</v>
       </c>
       <c r="F30" s="19">
-        <f t="shared" si="43"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="G30" s="19">
-        <f t="shared" si="43"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="H30" s="19">
-        <f t="shared" si="43"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="I30" s="19">
-        <f t="shared" si="43"/>
+        <f t="shared" si="51"/>
         <v>98908</v>
       </c>
       <c r="J30" s="19">
-        <f t="shared" si="47"/>
+        <f t="shared" si="55"/>
         <v>1146245</v>
       </c>
-      <c r="L30" s="99">
-        <f t="shared" si="44"/>
+      <c r="L30" s="98">
+        <f t="shared" si="52"/>
         <v>9123918</v>
       </c>
-      <c r="M30" s="61">
-        <f t="shared" si="44"/>
+      <c r="M30" s="60">
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
-      <c r="N30" s="61">
-        <f t="shared" si="44"/>
+      <c r="N30" s="60">
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
-      <c r="O30" s="61">
-        <f t="shared" si="44"/>
+      <c r="O30" s="60">
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
-      <c r="P30" s="61">
-        <f t="shared" si="44"/>
+      <c r="P30" s="60">
+        <f t="shared" si="52"/>
         <v>655598107</v>
       </c>
-      <c r="Q30" s="61">
-        <f t="shared" si="48"/>
+      <c r="Q30" s="60">
+        <f t="shared" si="56"/>
         <v>664722025</v>
       </c>
-      <c r="S30" s="92">
-        <f t="shared" si="45"/>
+      <c r="S30" s="91">
+        <f t="shared" si="53"/>
         <v>12970</v>
       </c>
       <c r="T30" s="31">
-        <f t="shared" si="45"/>
+        <f t="shared" si="53"/>
         <v>14165</v>
       </c>
       <c r="U30" s="31">
-        <f t="shared" si="45"/>
+        <f t="shared" si="53"/>
         <v>5143</v>
       </c>
       <c r="V30" s="31">
-        <f t="shared" si="45"/>
+        <f t="shared" si="53"/>
         <v>14291</v>
       </c>
       <c r="W30" s="31">
-        <f t="shared" si="45"/>
+        <f t="shared" si="53"/>
         <v>19979</v>
       </c>
       <c r="X30" s="31">
-        <f t="shared" si="45"/>
+        <f t="shared" si="53"/>
         <v>39488</v>
       </c>
       <c r="Y30" s="31">
-        <f t="shared" si="49"/>
+        <f t="shared" si="57"/>
         <v>106036</v>
       </c>
-      <c r="AA30" s="106">
-        <f t="shared" si="46"/>
+      <c r="AA30" s="105">
+        <f t="shared" si="54"/>
         <v>71950539</v>
       </c>
-      <c r="AB30" s="66">
-        <f t="shared" si="46"/>
+      <c r="AB30" s="65">
+        <f t="shared" si="54"/>
         <v>88920515</v>
       </c>
-      <c r="AC30" s="66">
-        <f t="shared" si="46"/>
+      <c r="AC30" s="65">
+        <f t="shared" si="54"/>
         <v>31867112</v>
       </c>
-      <c r="AD30" s="66">
-        <f t="shared" si="46"/>
+      <c r="AD30" s="65">
+        <f t="shared" si="54"/>
         <v>76700859</v>
       </c>
-      <c r="AE30" s="66">
-        <f t="shared" si="46"/>
+      <c r="AE30" s="65">
+        <f t="shared" si="54"/>
         <v>119641616</v>
       </c>
-      <c r="AF30" s="66">
-        <f t="shared" si="46"/>
+      <c r="AF30" s="65">
+        <f t="shared" si="54"/>
         <v>275641384</v>
       </c>
-      <c r="AG30" s="66">
-        <f t="shared" si="50"/>
+      <c r="AG30" s="65">
+        <f t="shared" si="58"/>
         <v>664722025</v>
       </c>
-      <c r="AI30" s="94"/>
-      <c r="AJ30" s="54"/>
-      <c r="AK30" s="54"/>
-      <c r="AL30" s="54"/>
-      <c r="AM30" s="54"/>
-      <c r="AN30" s="54"/>
-      <c r="AP30" s="96"/>
-      <c r="AQ30" s="50"/>
-      <c r="AR30" s="50"/>
-      <c r="AS30" s="50"/>
-      <c r="AT30" s="50"/>
-      <c r="AU30" s="50"/>
-    </row>
-    <row r="31" spans="1:47" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="AI30" s="93"/>
+      <c r="AJ30" s="53"/>
+      <c r="AK30" s="53"/>
+      <c r="AL30" s="53"/>
+      <c r="AM30" s="53"/>
+      <c r="AN30" s="53"/>
+      <c r="AP30" s="95"/>
+      <c r="AQ30" s="49"/>
+      <c r="AR30" s="49"/>
+      <c r="AS30" s="49"/>
+      <c r="AT30" s="49"/>
+      <c r="AU30" s="49"/>
+      <c r="AW30" s="83">
+        <f>SUMIFS(ventas_unidades,ventas_region,$A30,ventas_año,AW$8)</f>
+        <v>36557</v>
+      </c>
+      <c r="AX30" s="47">
+        <f>SUMIFS(ventas_unidades,ventas_region,$A30,ventas_año,AX$8)</f>
+        <v>28900</v>
+      </c>
+      <c r="AY30" s="47">
+        <f>SUMIFS(ventas_unidades,ventas_region,$A30,ventas_año,AY$8)</f>
+        <v>33451</v>
+      </c>
+      <c r="AZ30" s="47">
+        <f>SUMIFS(ventas_unidades,ventas_region,$A30,ventas_año,AZ$8)</f>
+        <v>0</v>
+      </c>
+      <c r="BA30" s="47">
+        <f>SUMIFS(ventas_unidades,ventas_region,$A30,ventas_año,BA$8)</f>
+        <v>7128</v>
+      </c>
+      <c r="BB30" s="47">
+        <f t="shared" si="59"/>
+        <v>106036</v>
+      </c>
+      <c r="BD30" s="98">
+        <f>SUMIFS(ventas_total,ventas_region,$A30,ventas_año,BD$8)</f>
+        <v>216479082</v>
+      </c>
+      <c r="BE30" s="70">
+        <f>SUMIFS(ventas_total,ventas_region,$A30,ventas_año,BE$8)</f>
+        <v>240247726</v>
+      </c>
+      <c r="BF30" s="70">
+        <f>SUMIFS(ventas_total,ventas_region,$A30,ventas_año,BF$8)</f>
+        <v>198871299</v>
+      </c>
+      <c r="BG30" s="70">
+        <f>SUMIFS(ventas_total,ventas_region,$A30,ventas_año,BG$8)</f>
+        <v>0</v>
+      </c>
+      <c r="BH30" s="70">
+        <f>SUMIFS(ventas_total,ventas_region,$A30,ventas_año,BH$8)</f>
+        <v>9123918</v>
+      </c>
+      <c r="BI30" s="70">
+        <f t="shared" si="60"/>
+        <v>664722025</v>
+      </c>
+    </row>
+    <row r="31" spans="1:61" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="B31" s="117">
+      <c r="B31" s="116">
         <f>SUM(B26:B30)</f>
         <v>858227</v>
       </c>
-      <c r="C31" s="116">
+      <c r="C31" s="115">
         <f>SUBTOTAL(109,estadisticas!$C$26:$C$30)</f>
         <v>3230017545</v>
       </c>
-      <c r="E31" s="95">
+      <c r="E31" s="94">
         <f>SUM(E26:E30)</f>
         <v>110903</v>
       </c>
-      <c r="F31" s="51">
-        <f t="shared" ref="F31:J31" si="51">SUM(F26:F30)</f>
+      <c r="F31" s="50">
+        <f t="shared" ref="F31:J31" si="61">SUM(F26:F30)</f>
         <v>304519</v>
       </c>
-      <c r="G31" s="51">
-        <f t="shared" si="51"/>
+      <c r="G31" s="50">
+        <f t="shared" si="61"/>
         <v>118380</v>
       </c>
-      <c r="H31" s="51">
-        <f t="shared" si="51"/>
+      <c r="H31" s="50">
+        <f t="shared" si="61"/>
         <v>115644</v>
       </c>
-      <c r="I31" s="51">
-        <f t="shared" si="51"/>
+      <c r="I31" s="50">
+        <f t="shared" si="61"/>
         <v>208781</v>
       </c>
-      <c r="J31" s="118">
-        <f t="shared" si="51"/>
+      <c r="J31" s="117">
+        <f t="shared" si="61"/>
         <v>6280957</v>
       </c>
-      <c r="L31" s="109">
+      <c r="L31" s="108">
         <f>SUM(L26:L30)</f>
         <v>650543568</v>
       </c>
-      <c r="M31" s="69">
-        <f t="shared" ref="M31" si="52">SUM(M26:M30)</f>
+      <c r="M31" s="68">
+        <f t="shared" ref="M31" si="62">SUM(M26:M30)</f>
         <v>578124392</v>
       </c>
-      <c r="N31" s="69">
-        <f t="shared" ref="N31" si="53">SUM(N26:N30)</f>
+      <c r="N31" s="68">
+        <f t="shared" ref="N31" si="63">SUM(N26:N30)</f>
         <v>690157736</v>
       </c>
-      <c r="O31" s="69">
-        <f t="shared" ref="O31" si="54">SUM(O26:O30)</f>
+      <c r="O31" s="68">
+        <f t="shared" ref="O31" si="64">SUM(O26:O30)</f>
         <v>654943915</v>
       </c>
-      <c r="P31" s="69">
-        <f t="shared" ref="P31" si="55">SUM(P26:P30)</f>
+      <c r="P31" s="68">
+        <f t="shared" ref="P31" si="65">SUM(P26:P30)</f>
         <v>656247934</v>
       </c>
-      <c r="Q31" s="115">
-        <f t="shared" ref="Q31" si="56">SUM(Q26:Q30)</f>
+      <c r="Q31" s="114">
+        <f t="shared" ref="Q31" si="66">SUM(Q26:Q30)</f>
         <v>3230017545</v>
       </c>
-      <c r="S31" s="93">
+      <c r="S31" s="92">
         <f>SUM(S26:S30)</f>
         <v>121665</v>
       </c>
       <c r="T31" s="40">
-        <f t="shared" ref="T31:Y31" si="57">SUM(T26:T30)</f>
+        <f t="shared" ref="T31:Y31" si="67">SUM(T26:T30)</f>
         <v>125620</v>
       </c>
       <c r="U31" s="40">
-        <f t="shared" si="57"/>
+        <f t="shared" si="67"/>
         <v>32356</v>
       </c>
       <c r="V31" s="40">
-        <f t="shared" si="57"/>
+        <f t="shared" si="67"/>
         <v>356297</v>
       </c>
       <c r="W31" s="40">
-        <f t="shared" si="57"/>
+        <f t="shared" si="67"/>
         <v>122295</v>
       </c>
       <c r="X31" s="40">
-        <f t="shared" si="57"/>
+        <f t="shared" si="67"/>
         <v>99994</v>
       </c>
       <c r="Y31" s="40">
-        <f t="shared" si="57"/>
+        <f t="shared" si="67"/>
         <v>858227</v>
       </c>
-      <c r="AA31" s="107">
+      <c r="AA31" s="106">
         <f>SUM(AA26:AA30)</f>
         <v>645115066</v>
       </c>
-      <c r="AB31" s="67">
-        <f t="shared" ref="AB31" si="58">SUM(AB26:AB30)</f>
+      <c r="AB31" s="66">
+        <f t="shared" ref="AB31" si="68">SUM(AB26:AB30)</f>
         <v>761464717</v>
       </c>
-      <c r="AC31" s="67">
-        <f t="shared" ref="AC31" si="59">SUM(AC26:AC30)</f>
+      <c r="AC31" s="66">
+        <f t="shared" ref="AC31" si="69">SUM(AC26:AC30)</f>
         <v>226722785</v>
       </c>
-      <c r="AD31" s="67">
-        <f t="shared" ref="AD31" si="60">SUM(AD26:AD30)</f>
+      <c r="AD31" s="66">
+        <f t="shared" ref="AD31" si="70">SUM(AD26:AD30)</f>
         <v>312257691</v>
       </c>
-      <c r="AE31" s="67">
-        <f t="shared" ref="AE31" si="61">SUM(AE26:AE30)</f>
+      <c r="AE31" s="66">
+        <f t="shared" ref="AE31" si="71">SUM(AE26:AE30)</f>
         <v>722503562</v>
       </c>
-      <c r="AF31" s="67">
-        <f t="shared" ref="AF31" si="62">SUM(AF26:AF30)</f>
+      <c r="AF31" s="66">
+        <f t="shared" ref="AF31" si="72">SUM(AF26:AF30)</f>
         <v>561953724</v>
       </c>
-      <c r="AG31" s="115">
-        <f t="shared" ref="AG31" si="63">SUM(AG26:AG30)</f>
+      <c r="AG31" s="114">
+        <f t="shared" ref="AG31" si="73">SUM(AG26:AG30)</f>
         <v>3230017545</v>
       </c>
-      <c r="AI31" s="94"/>
-      <c r="AJ31" s="54"/>
-      <c r="AK31" s="54"/>
-      <c r="AL31" s="54"/>
-      <c r="AM31" s="54"/>
-      <c r="AN31" s="54"/>
-      <c r="AP31" s="96"/>
-      <c r="AQ31" s="50"/>
-      <c r="AR31" s="50"/>
-      <c r="AS31" s="50"/>
-      <c r="AT31" s="50"/>
-      <c r="AU31" s="50"/>
-    </row>
-    <row r="32" spans="1:47" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="33" spans="1:47" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="AI31" s="93"/>
+      <c r="AJ31" s="53"/>
+      <c r="AK31" s="53"/>
+      <c r="AL31" s="53"/>
+      <c r="AM31" s="53"/>
+      <c r="AN31" s="53"/>
+      <c r="AP31" s="95"/>
+      <c r="AQ31" s="49"/>
+      <c r="AR31" s="49"/>
+      <c r="AS31" s="49"/>
+      <c r="AT31" s="49"/>
+      <c r="AU31" s="49"/>
+      <c r="AW31" s="94">
+        <f t="shared" ref="AW31:BA31" si="74">SUM(AW27:AW30)</f>
+        <v>148950</v>
+      </c>
+      <c r="AX31" s="50">
+        <f t="shared" si="74"/>
+        <v>133993</v>
+      </c>
+      <c r="AY31" s="50">
+        <f t="shared" si="74"/>
+        <v>139321</v>
+      </c>
+      <c r="AZ31" s="50">
+        <f t="shared" si="74"/>
+        <v>120570</v>
+      </c>
+      <c r="BA31" s="50">
+        <f t="shared" si="74"/>
+        <v>205284</v>
+      </c>
+      <c r="BB31" s="117">
+        <f>SUM(BB26:BB30)</f>
+        <v>858227</v>
+      </c>
+      <c r="BD31" s="108">
+        <f>SUM(BD26:BD30)</f>
+        <v>1007244151</v>
+      </c>
+      <c r="BE31" s="68">
+        <f t="shared" ref="BE31:BI31" si="75">SUM(BE26:BE30)</f>
+        <v>1106846472</v>
+      </c>
+      <c r="BF31" s="68">
+        <f t="shared" si="75"/>
+        <v>1089310347</v>
+      </c>
+      <c r="BG31" s="68">
+        <f t="shared" si="75"/>
+        <v>15082721</v>
+      </c>
+      <c r="BH31" s="68">
+        <f t="shared" si="75"/>
+        <v>11533854</v>
+      </c>
+      <c r="BI31" s="114">
+        <f t="shared" si="75"/>
+        <v>3230017545</v>
+      </c>
+    </row>
+    <row r="32" spans="1:61" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="33" spans="1:61" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="7" t="s">
         <v>42</v>
       </c>
@@ -9067,122 +10385,134 @@
       <c r="C33" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="E33" s="87" t="s">
+      <c r="E33" s="86" t="s">
         <v>6</v>
       </c>
-      <c r="F33" s="53" t="s">
+      <c r="F33" s="52" t="s">
         <v>33</v>
       </c>
-      <c r="G33" s="53" t="s">
+      <c r="G33" s="52" t="s">
         <v>15</v>
       </c>
-      <c r="H33" s="53" t="s">
+      <c r="H33" s="52" t="s">
         <v>18</v>
       </c>
-      <c r="I33" s="53" t="s">
+      <c r="I33" s="52" t="s">
         <v>47</v>
       </c>
-      <c r="J33" s="53" t="s">
+      <c r="J33" s="52" t="s">
         <v>34</v>
       </c>
-      <c r="L33" s="101" t="s">
+      <c r="L33" s="100" t="s">
         <v>6</v>
       </c>
-      <c r="M33" s="57" t="s">
+      <c r="M33" s="56" t="s">
         <v>33</v>
       </c>
-      <c r="N33" s="57" t="s">
+      <c r="N33" s="56" t="s">
         <v>15</v>
       </c>
-      <c r="O33" s="57" t="s">
+      <c r="O33" s="56" t="s">
         <v>18</v>
       </c>
-      <c r="P33" s="57" t="s">
+      <c r="P33" s="56" t="s">
         <v>47</v>
       </c>
-      <c r="Q33" s="57" t="s">
+      <c r="Q33" s="56" t="s">
         <v>34</v>
       </c>
-      <c r="S33" s="87" t="s">
+      <c r="S33" s="86" t="s">
         <v>28</v>
       </c>
-      <c r="T33" s="53" t="s">
+      <c r="T33" s="52" t="s">
         <v>8</v>
       </c>
-      <c r="U33" s="53" t="s">
+      <c r="U33" s="52" t="s">
         <v>11</v>
       </c>
-      <c r="V33" s="53" t="s">
+      <c r="V33" s="52" t="s">
         <v>13</v>
       </c>
-      <c r="W33" s="53" t="s">
+      <c r="W33" s="52" t="s">
         <v>29</v>
       </c>
-      <c r="X33" s="53" t="s">
+      <c r="X33" s="52" t="s">
         <v>30</v>
       </c>
-      <c r="Y33" s="53" t="s">
+      <c r="Y33" s="52" t="s">
         <v>39</v>
       </c>
-      <c r="AA33" s="101" t="s">
+      <c r="AA33" s="100" t="s">
         <v>28</v>
       </c>
-      <c r="AB33" s="57" t="s">
+      <c r="AB33" s="56" t="s">
         <v>8</v>
       </c>
-      <c r="AC33" s="57" t="s">
+      <c r="AC33" s="56" t="s">
         <v>11</v>
       </c>
-      <c r="AD33" s="57" t="s">
+      <c r="AD33" s="56" t="s">
         <v>13</v>
       </c>
-      <c r="AE33" s="57" t="s">
+      <c r="AE33" s="56" t="s">
         <v>29</v>
       </c>
-      <c r="AF33" s="57" t="s">
+      <c r="AF33" s="56" t="s">
         <v>30</v>
       </c>
-      <c r="AG33" s="57" t="s">
+      <c r="AG33" s="56" t="s">
         <v>39</v>
       </c>
-      <c r="AI33" s="87" t="s">
+      <c r="AI33" s="86" t="s">
         <v>31</v>
       </c>
-      <c r="AJ33" s="53" t="s">
+      <c r="AJ33" s="52" t="s">
         <v>9</v>
       </c>
-      <c r="AK33" s="53" t="s">
+      <c r="AK33" s="52" t="s">
         <v>16</v>
       </c>
-      <c r="AL33" s="53" t="s">
+      <c r="AL33" s="52" t="s">
         <v>19</v>
       </c>
-      <c r="AM33" s="53" t="s">
+      <c r="AM33" s="52" t="s">
         <v>21</v>
       </c>
-      <c r="AN33" s="53" t="s">
+      <c r="AN33" s="52" t="s">
         <v>34</v>
       </c>
-      <c r="AP33" s="110" t="s">
+      <c r="AP33" s="109" t="s">
         <v>31</v>
       </c>
-      <c r="AQ33" s="56" t="s">
+      <c r="AQ33" s="55" t="s">
         <v>9</v>
       </c>
-      <c r="AR33" s="56" t="s">
+      <c r="AR33" s="55" t="s">
         <v>16</v>
       </c>
-      <c r="AS33" s="56" t="s">
+      <c r="AS33" s="55" t="s">
         <v>19</v>
       </c>
-      <c r="AT33" s="56" t="s">
+      <c r="AT33" s="55" t="s">
         <v>21</v>
       </c>
-      <c r="AU33" s="56" t="s">
+      <c r="AU33" s="55" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="34" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AW33" s="93"/>
+      <c r="AX33" s="53"/>
+      <c r="AY33" s="53"/>
+      <c r="AZ33" s="53"/>
+      <c r="BA33" s="120"/>
+      <c r="BB33" s="120"/>
+      <c r="BD33" s="93"/>
+      <c r="BE33" s="53"/>
+      <c r="BF33" s="53"/>
+      <c r="BG33" s="53"/>
+      <c r="BH33" s="120"/>
+      <c r="BI33" s="120"/>
+    </row>
+    <row r="34" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A34" s="28">
         <v>2008</v>
       </c>
@@ -9194,160 +10524,172 @@
         <f>SUMIF(ventas_año,$A34,ventas_total)</f>
         <v>1007244151</v>
       </c>
-      <c r="E34" s="82">
-        <f t="shared" ref="E34:I38" si="64">SUMIFS(ventas_unidades,ventas_año,$A34,ventas_producto,E$25)</f>
+      <c r="E34" s="81">
+        <f t="shared" ref="E34:I38" si="76">SUMIFS(ventas_unidades,ventas_año,$A34,ventas_producto,E$25)</f>
         <v>33032</v>
       </c>
       <c r="F34" s="17">
-        <f t="shared" si="64"/>
+        <f t="shared" si="76"/>
         <v>32696</v>
       </c>
       <c r="G34" s="17">
-        <f t="shared" si="64"/>
+        <f t="shared" si="76"/>
         <v>39124</v>
       </c>
       <c r="H34" s="17">
-        <f t="shared" si="64"/>
+        <f t="shared" si="76"/>
         <v>40573</v>
       </c>
       <c r="I34" s="17">
-        <f t="shared" si="64"/>
+        <f t="shared" si="76"/>
         <v>36557</v>
       </c>
       <c r="J34" s="17">
         <f>SUM(E34:I38)</f>
         <v>858227</v>
       </c>
-      <c r="L34" s="97">
-        <f t="shared" ref="L34:P38" si="65">SUMIFS(ventas_total,ventas_año,$A34,ventas_producto,L$25)</f>
+      <c r="L34" s="96">
+        <f t="shared" ref="L34:P38" si="77">SUMIFS(ventas_total,ventas_año,$A34,ventas_producto,L$25)</f>
         <v>218669111</v>
       </c>
-      <c r="M34" s="59">
-        <f t="shared" si="65"/>
+      <c r="M34" s="58">
+        <f t="shared" si="77"/>
         <v>160364763</v>
       </c>
-      <c r="N34" s="59">
-        <f t="shared" si="65"/>
+      <c r="N34" s="58">
+        <f t="shared" si="77"/>
         <v>220801841</v>
       </c>
-      <c r="O34" s="59">
-        <f t="shared" si="65"/>
+      <c r="O34" s="58">
+        <f t="shared" si="77"/>
         <v>190929354</v>
       </c>
-      <c r="P34" s="59">
-        <f t="shared" si="65"/>
+      <c r="P34" s="58">
+        <f t="shared" si="77"/>
         <v>216479082</v>
       </c>
-      <c r="Q34" s="59">
+      <c r="Q34" s="58">
         <f>SUM(L34:P34)</f>
         <v>1007244151</v>
       </c>
-      <c r="S34" s="90">
-        <f t="shared" ref="S34:X38" si="66">SUMIFS(ventas_unidades,ventas_año,$A34,ventas_vendedor,S$33)</f>
+      <c r="S34" s="89">
+        <f t="shared" ref="S34:X38" si="78">SUMIFS(ventas_unidades,ventas_año,$A34,ventas_vendedor,S$33)</f>
         <v>33623</v>
       </c>
       <c r="T34" s="29">
-        <f t="shared" si="66"/>
+        <f t="shared" si="78"/>
         <v>45235</v>
       </c>
       <c r="U34" s="29">
-        <f t="shared" si="66"/>
+        <f t="shared" si="78"/>
         <v>12423</v>
       </c>
       <c r="V34" s="29">
-        <f t="shared" si="66"/>
+        <f t="shared" si="78"/>
         <v>20990</v>
       </c>
       <c r="W34" s="29">
-        <f t="shared" si="66"/>
+        <f t="shared" si="78"/>
         <v>44558</v>
       </c>
       <c r="X34" s="29">
-        <f t="shared" si="66"/>
+        <f t="shared" si="78"/>
         <v>25153</v>
       </c>
       <c r="Y34" s="29">
         <f>SUM(S34:X34)</f>
         <v>181982</v>
       </c>
-      <c r="AA34" s="104">
-        <f t="shared" ref="AA34:AF38" si="67">SUMIFS(ventas_unidades,ventas_año,$A34,ventas_vendedor,AA$33)</f>
+      <c r="AA34" s="103">
+        <f t="shared" ref="AA34:AF38" si="79">SUMIFS(ventas_unidades,ventas_año,$A34,ventas_vendedor,AA$33)</f>
         <v>33623</v>
       </c>
-      <c r="AB34" s="64">
-        <f t="shared" si="67"/>
+      <c r="AB34" s="63">
+        <f t="shared" si="79"/>
         <v>45235</v>
       </c>
-      <c r="AC34" s="64">
-        <f t="shared" si="67"/>
+      <c r="AC34" s="63">
+        <f t="shared" si="79"/>
         <v>12423</v>
       </c>
-      <c r="AD34" s="64">
-        <f t="shared" si="67"/>
+      <c r="AD34" s="63">
+        <f t="shared" si="79"/>
         <v>20990</v>
       </c>
-      <c r="AE34" s="64">
-        <f t="shared" si="67"/>
+      <c r="AE34" s="63">
+        <f t="shared" si="79"/>
         <v>44558</v>
       </c>
-      <c r="AF34" s="64">
-        <f t="shared" si="67"/>
+      <c r="AF34" s="63">
+        <f t="shared" si="79"/>
         <v>25153</v>
       </c>
-      <c r="AG34" s="64">
+      <c r="AG34" s="63">
         <f>SUM(AA34:AF34)</f>
         <v>181982</v>
       </c>
-      <c r="AI34" s="82">
-        <f t="shared" ref="AI34:AM38" si="68">SUMIFS(ventas_unidades,ventas_año,$A34,ventas_region,AI$33)</f>
+      <c r="AI34" s="81">
+        <f t="shared" ref="AI34:AM38" si="80">SUMIFS(ventas_unidades,ventas_año,$A34,ventas_region,AI$33)</f>
         <v>33032</v>
       </c>
       <c r="AJ34" s="17">
-        <f t="shared" si="68"/>
+        <f t="shared" si="80"/>
         <v>32696</v>
       </c>
       <c r="AK34" s="17">
-        <f t="shared" si="68"/>
+        <f t="shared" si="80"/>
         <v>39124</v>
       </c>
       <c r="AL34" s="17">
-        <f t="shared" si="68"/>
+        <f t="shared" si="80"/>
         <v>40573</v>
       </c>
       <c r="AM34" s="17">
-        <f t="shared" si="68"/>
+        <f t="shared" si="80"/>
         <v>36557</v>
       </c>
       <c r="AN34" s="17">
         <f>SUM(AI34:AM34)</f>
         <v>181982</v>
       </c>
-      <c r="AP34" s="111">
-        <f t="shared" ref="AP34:AT38" si="69">SUMIFS(ventas_total,ventas_año,$A34,ventas_region,AP$33)</f>
+      <c r="AP34" s="110">
+        <f t="shared" ref="AP34:AT38" si="81">SUMIFS(ventas_total,ventas_año,$A34,ventas_region,AP$33)</f>
         <v>218669111</v>
       </c>
       <c r="AQ34" s="41">
-        <f t="shared" si="69"/>
+        <f t="shared" si="81"/>
         <v>160364763</v>
       </c>
       <c r="AR34" s="41">
-        <f t="shared" si="69"/>
+        <f t="shared" si="81"/>
         <v>220801841</v>
       </c>
       <c r="AS34" s="41">
-        <f t="shared" si="69"/>
+        <f t="shared" si="81"/>
         <v>190929354</v>
       </c>
       <c r="AT34" s="41">
-        <f t="shared" si="69"/>
+        <f t="shared" si="81"/>
         <v>216479082</v>
       </c>
       <c r="AU34" s="41">
         <f>SUM(AP34:AT34)</f>
         <v>1007244151</v>
       </c>
-    </row>
-    <row r="35" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AW34" s="93"/>
+      <c r="AX34" s="53"/>
+      <c r="AY34" s="53"/>
+      <c r="AZ34" s="53"/>
+      <c r="BA34" s="120"/>
+      <c r="BB34" s="120"/>
+      <c r="BD34" s="93"/>
+      <c r="BE34" s="53"/>
+      <c r="BF34" s="53"/>
+      <c r="BG34" s="53"/>
+      <c r="BH34" s="120"/>
+      <c r="BI34" s="120"/>
+    </row>
+    <row r="35" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A35" s="26">
         <v>2009</v>
       </c>
@@ -9359,160 +10701,172 @@
         <f>SUMIF(ventas_año,$A35,ventas_total)</f>
         <v>1106846472</v>
       </c>
-      <c r="E35" s="83">
-        <f t="shared" si="64"/>
+      <c r="E35" s="82">
+        <f t="shared" si="76"/>
         <v>32671</v>
       </c>
       <c r="F35" s="18">
-        <f t="shared" si="64"/>
+        <f t="shared" si="76"/>
         <v>31651</v>
       </c>
       <c r="G35" s="18">
-        <f t="shared" si="64"/>
+        <f t="shared" si="76"/>
         <v>34000</v>
       </c>
       <c r="H35" s="18">
-        <f t="shared" si="64"/>
+        <f t="shared" si="76"/>
         <v>39442</v>
       </c>
       <c r="I35" s="18">
-        <f t="shared" si="64"/>
+        <f t="shared" si="76"/>
         <v>28900</v>
       </c>
       <c r="J35" s="18">
-        <f t="shared" ref="J35:J38" si="70">SUM(E35:I39)</f>
+        <f t="shared" ref="J35:J38" si="82">SUM(E35:I39)</f>
         <v>1534472</v>
       </c>
-      <c r="L35" s="98">
-        <f t="shared" si="65"/>
+      <c r="L35" s="97">
+        <f t="shared" si="77"/>
         <v>203341463</v>
       </c>
-      <c r="M35" s="60">
-        <f t="shared" si="65"/>
+      <c r="M35" s="59">
+        <f t="shared" si="77"/>
         <v>201880917</v>
       </c>
-      <c r="N35" s="60">
-        <f t="shared" si="65"/>
+      <c r="N35" s="59">
+        <f t="shared" si="77"/>
         <v>239992813</v>
       </c>
-      <c r="O35" s="60">
-        <f t="shared" si="65"/>
+      <c r="O35" s="59">
+        <f t="shared" si="77"/>
         <v>221383553</v>
       </c>
-      <c r="P35" s="60">
-        <f t="shared" si="65"/>
+      <c r="P35" s="59">
+        <f t="shared" si="77"/>
         <v>240247726</v>
       </c>
-      <c r="Q35" s="60">
-        <f t="shared" ref="Q35:Q38" si="71">SUM(L35:P35)</f>
+      <c r="Q35" s="59">
+        <f t="shared" ref="Q35:Q38" si="83">SUM(L35:P35)</f>
         <v>1106846472</v>
       </c>
-      <c r="S35" s="91">
-        <f t="shared" si="66"/>
+      <c r="S35" s="90">
+        <f t="shared" si="78"/>
         <v>42339</v>
       </c>
       <c r="T35" s="30">
-        <f t="shared" si="66"/>
+        <f t="shared" si="78"/>
         <v>39435</v>
       </c>
       <c r="U35" s="30">
-        <f t="shared" si="66"/>
+        <f t="shared" si="78"/>
         <v>12194</v>
       </c>
       <c r="V35" s="30">
-        <f t="shared" si="66"/>
+        <f t="shared" si="78"/>
         <v>11750</v>
       </c>
       <c r="W35" s="30">
-        <f t="shared" si="66"/>
+        <f t="shared" si="78"/>
         <v>27319</v>
       </c>
       <c r="X35" s="30">
-        <f t="shared" si="66"/>
+        <f t="shared" si="78"/>
         <v>33627</v>
       </c>
       <c r="Y35" s="30">
-        <f t="shared" ref="Y35:Y38" si="72">SUM(S35:X35)</f>
+        <f t="shared" ref="Y35:Y38" si="84">SUM(S35:X35)</f>
         <v>166664</v>
       </c>
-      <c r="AA35" s="105">
-        <f t="shared" si="67"/>
+      <c r="AA35" s="104">
+        <f t="shared" si="79"/>
         <v>42339</v>
       </c>
-      <c r="AB35" s="65">
-        <f t="shared" si="67"/>
+      <c r="AB35" s="64">
+        <f t="shared" si="79"/>
         <v>39435</v>
       </c>
-      <c r="AC35" s="65">
-        <f t="shared" si="67"/>
+      <c r="AC35" s="64">
+        <f t="shared" si="79"/>
         <v>12194</v>
       </c>
-      <c r="AD35" s="65">
-        <f t="shared" si="67"/>
+      <c r="AD35" s="64">
+        <f t="shared" si="79"/>
         <v>11750</v>
       </c>
-      <c r="AE35" s="65">
-        <f t="shared" si="67"/>
+      <c r="AE35" s="64">
+        <f t="shared" si="79"/>
         <v>27319</v>
       </c>
-      <c r="AF35" s="65">
-        <f t="shared" si="67"/>
+      <c r="AF35" s="64">
+        <f t="shared" si="79"/>
         <v>33627</v>
       </c>
-      <c r="AG35" s="65">
-        <f t="shared" ref="AG35:AG38" si="73">SUM(AA35:AF35)</f>
+      <c r="AG35" s="64">
+        <f t="shared" ref="AG35:AG38" si="85">SUM(AA35:AF35)</f>
         <v>166664</v>
       </c>
-      <c r="AI35" s="83">
-        <f t="shared" si="68"/>
+      <c r="AI35" s="82">
+        <f t="shared" si="80"/>
         <v>32671</v>
       </c>
       <c r="AJ35" s="18">
-        <f t="shared" si="68"/>
+        <f t="shared" si="80"/>
         <v>31651</v>
       </c>
       <c r="AK35" s="18">
-        <f t="shared" si="68"/>
+        <f t="shared" si="80"/>
         <v>34000</v>
       </c>
       <c r="AL35" s="18">
-        <f t="shared" si="68"/>
+        <f t="shared" si="80"/>
         <v>39442</v>
       </c>
       <c r="AM35" s="18">
-        <f t="shared" si="68"/>
+        <f t="shared" si="80"/>
         <v>28900</v>
       </c>
       <c r="AN35" s="18">
-        <f t="shared" ref="AN35:AN38" si="74">SUM(AI35:AM35)</f>
+        <f t="shared" ref="AN35:AN38" si="86">SUM(AI35:AM35)</f>
         <v>166664</v>
       </c>
-      <c r="AP35" s="112">
-        <f t="shared" si="69"/>
+      <c r="AP35" s="111">
+        <f t="shared" si="81"/>
         <v>203341463</v>
       </c>
-      <c r="AQ35" s="45">
-        <f t="shared" si="69"/>
+      <c r="AQ35" s="44">
+        <f t="shared" si="81"/>
         <v>201880917</v>
       </c>
-      <c r="AR35" s="45">
-        <f t="shared" si="69"/>
+      <c r="AR35" s="44">
+        <f t="shared" si="81"/>
         <v>239992813</v>
       </c>
-      <c r="AS35" s="45">
-        <f t="shared" si="69"/>
+      <c r="AS35" s="44">
+        <f t="shared" si="81"/>
         <v>221383553</v>
       </c>
-      <c r="AT35" s="45">
-        <f t="shared" si="69"/>
+      <c r="AT35" s="44">
+        <f t="shared" si="81"/>
         <v>240247726</v>
       </c>
-      <c r="AU35" s="45">
-        <f t="shared" ref="AU35:AU38" si="75">SUM(AP35:AT35)</f>
+      <c r="AU35" s="44">
+        <f t="shared" ref="AU35:AU38" si="87">SUM(AP35:AT35)</f>
         <v>1106846472</v>
       </c>
-    </row>
-    <row r="36" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AW35" s="93"/>
+      <c r="AX35" s="53"/>
+      <c r="AY35" s="53"/>
+      <c r="AZ35" s="53"/>
+      <c r="BA35" s="120"/>
+      <c r="BB35" s="120"/>
+      <c r="BD35" s="93"/>
+      <c r="BE35" s="53"/>
+      <c r="BF35" s="53"/>
+      <c r="BG35" s="53"/>
+      <c r="BH35" s="120"/>
+      <c r="BI35" s="120"/>
+    </row>
+    <row r="36" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A36" s="27">
         <v>2010</v>
       </c>
@@ -9524,160 +10878,172 @@
         <f>SUMIF(ventas_año,$A36,ventas_total)</f>
         <v>1089310347</v>
       </c>
-      <c r="E36" s="84">
-        <f t="shared" si="64"/>
+      <c r="E36" s="83">
+        <f t="shared" si="76"/>
         <v>35334</v>
       </c>
       <c r="F36" s="19">
-        <f t="shared" si="64"/>
+        <f t="shared" si="76"/>
         <v>40967</v>
       </c>
       <c r="G36" s="19">
-        <f t="shared" si="64"/>
+        <f t="shared" si="76"/>
         <v>31330</v>
       </c>
       <c r="H36" s="19">
-        <f t="shared" si="64"/>
+        <f t="shared" si="76"/>
         <v>33573</v>
       </c>
       <c r="I36" s="19">
-        <f t="shared" si="64"/>
+        <f t="shared" si="76"/>
         <v>33451</v>
       </c>
       <c r="J36" s="19">
-        <f t="shared" si="70"/>
+        <f t="shared" si="82"/>
         <v>1367808</v>
       </c>
-      <c r="L36" s="99">
-        <f t="shared" si="65"/>
+      <c r="L36" s="98">
+        <f t="shared" si="77"/>
         <v>218564244</v>
       </c>
-      <c r="M36" s="61">
-        <f t="shared" si="65"/>
+      <c r="M36" s="60">
+        <f t="shared" si="77"/>
         <v>214457221</v>
       </c>
-      <c r="N36" s="61">
-        <f t="shared" si="65"/>
+      <c r="N36" s="60">
+        <f t="shared" si="77"/>
         <v>216914467</v>
       </c>
-      <c r="O36" s="61">
-        <f t="shared" si="65"/>
+      <c r="O36" s="60">
+        <f t="shared" si="77"/>
         <v>240503116</v>
       </c>
-      <c r="P36" s="61">
-        <f t="shared" si="65"/>
+      <c r="P36" s="60">
+        <f t="shared" si="77"/>
         <v>198871299</v>
       </c>
-      <c r="Q36" s="61">
-        <f t="shared" si="71"/>
+      <c r="Q36" s="60">
+        <f t="shared" si="83"/>
         <v>1089310347</v>
       </c>
-      <c r="S36" s="92">
-        <f t="shared" si="66"/>
+      <c r="S36" s="91">
+        <f t="shared" si="78"/>
         <v>33889</v>
       </c>
       <c r="T36" s="31">
-        <f t="shared" si="66"/>
+        <f t="shared" si="78"/>
         <v>40950</v>
       </c>
       <c r="U36" s="31">
-        <f t="shared" si="66"/>
+        <f t="shared" si="78"/>
         <v>7739</v>
       </c>
       <c r="V36" s="31">
-        <f t="shared" si="66"/>
+        <f t="shared" si="78"/>
         <v>24117</v>
       </c>
       <c r="W36" s="31">
-        <f t="shared" si="66"/>
+        <f t="shared" si="78"/>
         <v>31540</v>
       </c>
       <c r="X36" s="31">
-        <f t="shared" si="66"/>
+        <f t="shared" si="78"/>
         <v>36420</v>
       </c>
       <c r="Y36" s="31">
-        <f t="shared" si="72"/>
+        <f t="shared" si="84"/>
         <v>174655</v>
       </c>
-      <c r="AA36" s="106">
-        <f t="shared" si="67"/>
+      <c r="AA36" s="105">
+        <f t="shared" si="79"/>
         <v>33889</v>
       </c>
-      <c r="AB36" s="66">
-        <f t="shared" si="67"/>
+      <c r="AB36" s="65">
+        <f t="shared" si="79"/>
         <v>40950</v>
       </c>
-      <c r="AC36" s="66">
-        <f t="shared" si="67"/>
+      <c r="AC36" s="65">
+        <f t="shared" si="79"/>
         <v>7739</v>
       </c>
-      <c r="AD36" s="66">
-        <f t="shared" si="67"/>
+      <c r="AD36" s="65">
+        <f t="shared" si="79"/>
         <v>24117</v>
       </c>
-      <c r="AE36" s="66">
-        <f t="shared" si="67"/>
+      <c r="AE36" s="65">
+        <f t="shared" si="79"/>
         <v>31540</v>
       </c>
-      <c r="AF36" s="66">
-        <f t="shared" si="67"/>
+      <c r="AF36" s="65">
+        <f t="shared" si="79"/>
         <v>36420</v>
       </c>
-      <c r="AG36" s="66">
-        <f t="shared" si="73"/>
+      <c r="AG36" s="65">
+        <f t="shared" si="85"/>
         <v>174655</v>
       </c>
-      <c r="AI36" s="84">
-        <f t="shared" si="68"/>
+      <c r="AI36" s="83">
+        <f t="shared" si="80"/>
         <v>35334</v>
       </c>
       <c r="AJ36" s="19">
-        <f t="shared" si="68"/>
+        <f t="shared" si="80"/>
         <v>40967</v>
       </c>
       <c r="AK36" s="19">
-        <f t="shared" si="68"/>
+        <f t="shared" si="80"/>
         <v>31330</v>
       </c>
       <c r="AL36" s="19">
-        <f t="shared" si="68"/>
+        <f t="shared" si="80"/>
         <v>33573</v>
       </c>
       <c r="AM36" s="19">
-        <f t="shared" si="68"/>
+        <f t="shared" si="80"/>
         <v>33451</v>
       </c>
       <c r="AN36" s="19">
-        <f t="shared" si="74"/>
+        <f t="shared" si="86"/>
         <v>174655</v>
       </c>
-      <c r="AP36" s="113">
-        <f t="shared" si="69"/>
+      <c r="AP36" s="112">
+        <f t="shared" si="81"/>
         <v>218564244</v>
       </c>
-      <c r="AQ36" s="46">
-        <f t="shared" si="69"/>
+      <c r="AQ36" s="45">
+        <f t="shared" si="81"/>
         <v>214457221</v>
       </c>
-      <c r="AR36" s="46">
-        <f t="shared" si="69"/>
+      <c r="AR36" s="45">
+        <f t="shared" si="81"/>
         <v>216914467</v>
       </c>
-      <c r="AS36" s="46">
-        <f t="shared" si="69"/>
+      <c r="AS36" s="45">
+        <f t="shared" si="81"/>
         <v>240503116</v>
       </c>
-      <c r="AT36" s="46">
-        <f t="shared" si="69"/>
+      <c r="AT36" s="45">
+        <f t="shared" si="81"/>
         <v>198871299</v>
       </c>
-      <c r="AU36" s="46">
-        <f t="shared" si="75"/>
+      <c r="AU36" s="45">
+        <f t="shared" si="87"/>
         <v>1089310347</v>
       </c>
-    </row>
-    <row r="37" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AW36" s="93"/>
+      <c r="AX36" s="53"/>
+      <c r="AY36" s="53"/>
+      <c r="AZ36" s="53"/>
+      <c r="BA36" s="120"/>
+      <c r="BB36" s="120"/>
+      <c r="BD36" s="93"/>
+      <c r="BE36" s="53"/>
+      <c r="BF36" s="53"/>
+      <c r="BG36" s="53"/>
+      <c r="BH36" s="120"/>
+      <c r="BI36" s="120"/>
+    </row>
+    <row r="37" spans="1:61" x14ac:dyDescent="0.3">
       <c r="A37" s="26">
         <v>2011</v>
       </c>
@@ -9689,160 +11055,172 @@
         <f>SUMIF(ventas_año,$A37,ventas_total)</f>
         <v>15082721</v>
       </c>
-      <c r="E37" s="83">
-        <f t="shared" si="64"/>
+      <c r="E37" s="82">
+        <f t="shared" si="76"/>
         <v>2738</v>
       </c>
       <c r="F37" s="18">
-        <f t="shared" si="64"/>
+        <f t="shared" si="76"/>
         <v>4903</v>
       </c>
       <c r="G37" s="18">
-        <f t="shared" si="64"/>
+        <f t="shared" si="76"/>
         <v>13926</v>
       </c>
       <c r="H37" s="18">
-        <f t="shared" si="64"/>
+        <f t="shared" si="76"/>
         <v>129</v>
       </c>
       <c r="I37" s="18">
-        <f t="shared" si="64"/>
+        <f t="shared" si="76"/>
         <v>107946</v>
       </c>
       <c r="J37" s="18">
-        <f t="shared" si="70"/>
+        <f t="shared" si="82"/>
         <v>1193153</v>
       </c>
-      <c r="L37" s="98">
-        <f t="shared" si="65"/>
+      <c r="L37" s="97">
+        <f t="shared" si="77"/>
         <v>844832</v>
       </c>
-      <c r="M37" s="60">
-        <f t="shared" si="65"/>
+      <c r="M37" s="59">
+        <f t="shared" si="77"/>
         <v>483929</v>
       </c>
-      <c r="N37" s="60">
-        <f t="shared" si="65"/>
+      <c r="N37" s="59">
+        <f t="shared" si="77"/>
         <v>12448615</v>
       </c>
-      <c r="O37" s="60">
-        <f t="shared" si="65"/>
+      <c r="O37" s="59">
+        <f t="shared" si="77"/>
         <v>1203910</v>
       </c>
-      <c r="P37" s="60">
-        <f t="shared" si="65"/>
+      <c r="P37" s="59">
+        <f t="shared" si="77"/>
         <v>101435</v>
       </c>
-      <c r="Q37" s="60">
-        <f t="shared" si="71"/>
+      <c r="Q37" s="59">
+        <f t="shared" si="83"/>
         <v>15082721</v>
       </c>
-      <c r="S37" s="91">
-        <f t="shared" si="66"/>
+      <c r="S37" s="90">
+        <f t="shared" si="78"/>
         <v>9886</v>
       </c>
       <c r="T37" s="30">
-        <f t="shared" si="66"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="U37" s="30">
-        <f t="shared" si="66"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="V37" s="30">
-        <f t="shared" si="66"/>
+        <f t="shared" si="78"/>
         <v>107066</v>
       </c>
       <c r="W37" s="30">
-        <f t="shared" si="66"/>
+        <f t="shared" si="78"/>
         <v>9823</v>
       </c>
       <c r="X37" s="30">
-        <f t="shared" si="66"/>
+        <f t="shared" si="78"/>
         <v>2867</v>
       </c>
       <c r="Y37" s="30">
-        <f t="shared" si="72"/>
+        <f t="shared" si="84"/>
         <v>129642</v>
       </c>
-      <c r="AA37" s="105">
-        <f t="shared" si="67"/>
+      <c r="AA37" s="104">
+        <f t="shared" si="79"/>
         <v>9886</v>
       </c>
-      <c r="AB37" s="65">
-        <f t="shared" si="67"/>
+      <c r="AB37" s="64">
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
-      <c r="AC37" s="65">
-        <f t="shared" si="67"/>
+      <c r="AC37" s="64">
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
-      <c r="AD37" s="65">
-        <f t="shared" si="67"/>
+      <c r="AD37" s="64">
+        <f t="shared" si="79"/>
         <v>107066</v>
       </c>
-      <c r="AE37" s="65">
-        <f t="shared" si="67"/>
+      <c r="AE37" s="64">
+        <f t="shared" si="79"/>
         <v>9823</v>
       </c>
-      <c r="AF37" s="65">
-        <f t="shared" si="67"/>
+      <c r="AF37" s="64">
+        <f t="shared" si="79"/>
         <v>2867</v>
       </c>
-      <c r="AG37" s="65">
-        <f t="shared" si="73"/>
+      <c r="AG37" s="64">
+        <f t="shared" si="85"/>
         <v>129642</v>
       </c>
-      <c r="AI37" s="83">
-        <f t="shared" si="68"/>
+      <c r="AI37" s="82">
+        <f t="shared" si="80"/>
         <v>9072</v>
       </c>
       <c r="AJ37" s="18">
-        <f t="shared" si="68"/>
+        <f t="shared" si="80"/>
         <v>107946</v>
       </c>
       <c r="AK37" s="18">
-        <f t="shared" si="68"/>
+        <f t="shared" si="80"/>
         <v>7721</v>
       </c>
       <c r="AL37" s="18">
-        <f t="shared" si="68"/>
+        <f t="shared" si="80"/>
         <v>4903</v>
       </c>
       <c r="AM37" s="18">
-        <f t="shared" si="68"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="AN37" s="18">
-        <f t="shared" si="74"/>
+        <f t="shared" si="86"/>
         <v>129642</v>
       </c>
-      <c r="AP37" s="112">
-        <f t="shared" si="69"/>
+      <c r="AP37" s="111">
+        <f t="shared" si="81"/>
         <v>5532144</v>
       </c>
-      <c r="AQ37" s="45">
-        <f t="shared" si="69"/>
+      <c r="AQ37" s="44">
+        <f t="shared" si="81"/>
         <v>101435</v>
       </c>
-      <c r="AR37" s="45">
-        <f t="shared" si="69"/>
+      <c r="AR37" s="44">
+        <f t="shared" si="81"/>
         <v>8965213</v>
       </c>
-      <c r="AS37" s="45">
-        <f t="shared" si="69"/>
+      <c r="AS37" s="44">
+        <f t="shared" si="81"/>
         <v>483929</v>
       </c>
-      <c r="AT37" s="45">
-        <f t="shared" si="69"/>
+      <c r="AT37" s="44">
+        <f t="shared" si="81"/>
         <v>0</v>
       </c>
-      <c r="AU37" s="45">
-        <f t="shared" si="75"/>
+      <c r="AU37" s="44">
+        <f t="shared" si="87"/>
         <v>15082721</v>
       </c>
-    </row>
-    <row r="38" spans="1:47" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="AW37" s="93"/>
+      <c r="AX37" s="53"/>
+      <c r="AY37" s="53"/>
+      <c r="AZ37" s="53"/>
+      <c r="BA37" s="120"/>
+      <c r="BB37" s="120"/>
+      <c r="BD37" s="93"/>
+      <c r="BE37" s="53"/>
+      <c r="BF37" s="53"/>
+      <c r="BG37" s="53"/>
+      <c r="BH37" s="120"/>
+      <c r="BI37" s="120"/>
+    </row>
+    <row r="38" spans="1:61" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="27">
         <v>2012</v>
       </c>
@@ -9854,323 +11232,347 @@
         <f>SUMIF(ventas_año,$A38,ventas_total)</f>
         <v>11533854</v>
       </c>
-      <c r="E38" s="84">
-        <f t="shared" si="64"/>
+      <c r="E38" s="83">
+        <f t="shared" si="76"/>
         <v>7128</v>
       </c>
       <c r="F38" s="19">
-        <f t="shared" si="64"/>
+        <f t="shared" si="76"/>
         <v>194302</v>
       </c>
       <c r="G38" s="19">
-        <f t="shared" si="64"/>
+        <f t="shared" si="76"/>
         <v>0</v>
       </c>
       <c r="H38" s="19">
-        <f t="shared" si="64"/>
+        <f t="shared" si="76"/>
         <v>1927</v>
       </c>
       <c r="I38" s="19">
-        <f t="shared" si="64"/>
+        <f t="shared" si="76"/>
         <v>1927</v>
       </c>
       <c r="J38" s="19">
-        <f t="shared" si="70"/>
+        <f t="shared" si="82"/>
         <v>1063511</v>
       </c>
-      <c r="L38" s="99">
-        <f t="shared" si="65"/>
+      <c r="L38" s="98">
+        <f t="shared" si="77"/>
         <v>9123918</v>
       </c>
-      <c r="M38" s="61">
-        <f t="shared" si="65"/>
+      <c r="M38" s="60">
+        <f t="shared" si="77"/>
         <v>937562</v>
       </c>
-      <c r="N38" s="61">
-        <f t="shared" si="65"/>
+      <c r="N38" s="60">
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
-      <c r="O38" s="61">
-        <f t="shared" si="65"/>
+      <c r="O38" s="60">
+        <f t="shared" si="77"/>
         <v>923982</v>
       </c>
-      <c r="P38" s="61">
-        <f t="shared" si="65"/>
+      <c r="P38" s="60">
+        <f t="shared" si="77"/>
         <v>548392</v>
       </c>
-      <c r="Q38" s="61">
-        <f t="shared" si="71"/>
+      <c r="Q38" s="60">
+        <f t="shared" si="83"/>
         <v>11533854</v>
       </c>
-      <c r="S38" s="92">
-        <f t="shared" si="66"/>
+      <c r="S38" s="91">
+        <f t="shared" si="78"/>
         <v>1928</v>
       </c>
       <c r="T38" s="31">
-        <f t="shared" si="66"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="U38" s="31">
-        <f t="shared" si="66"/>
+        <f t="shared" si="78"/>
         <v>0</v>
       </c>
       <c r="V38" s="31">
-        <f t="shared" si="66"/>
+        <f t="shared" si="78"/>
         <v>192374</v>
       </c>
       <c r="W38" s="31">
-        <f t="shared" si="66"/>
+        <f t="shared" si="78"/>
         <v>9055</v>
       </c>
       <c r="X38" s="31">
-        <f t="shared" si="66"/>
+        <f t="shared" si="78"/>
         <v>1927</v>
       </c>
       <c r="Y38" s="31">
-        <f t="shared" si="72"/>
+        <f t="shared" si="84"/>
         <v>205284</v>
       </c>
-      <c r="AA38" s="106">
-        <f t="shared" si="67"/>
+      <c r="AA38" s="105">
+        <f t="shared" si="79"/>
         <v>1928</v>
       </c>
-      <c r="AB38" s="66">
-        <f t="shared" si="67"/>
+      <c r="AB38" s="65">
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
-      <c r="AC38" s="66">
-        <f t="shared" si="67"/>
+      <c r="AC38" s="65">
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
-      <c r="AD38" s="66">
-        <f t="shared" si="67"/>
+      <c r="AD38" s="65">
+        <f t="shared" si="79"/>
         <v>192374</v>
       </c>
-      <c r="AE38" s="66">
-        <f t="shared" si="67"/>
+      <c r="AE38" s="65">
+        <f t="shared" si="79"/>
         <v>9055</v>
       </c>
-      <c r="AF38" s="66">
-        <f t="shared" si="67"/>
+      <c r="AF38" s="65">
+        <f t="shared" si="79"/>
         <v>1927</v>
       </c>
-      <c r="AG38" s="66">
-        <f t="shared" si="73"/>
+      <c r="AG38" s="65">
+        <f t="shared" si="85"/>
         <v>205284</v>
       </c>
-      <c r="AI38" s="84">
-        <f t="shared" si="68"/>
+      <c r="AI38" s="83">
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="AJ38" s="19">
-        <f t="shared" si="68"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="AK38" s="19">
-        <f t="shared" si="68"/>
+        <f t="shared" si="80"/>
         <v>3855</v>
       </c>
       <c r="AL38" s="19">
-        <f t="shared" si="68"/>
+        <f t="shared" si="80"/>
         <v>194301</v>
       </c>
       <c r="AM38" s="19">
-        <f t="shared" si="68"/>
+        <f t="shared" si="80"/>
         <v>7128</v>
       </c>
       <c r="AN38" s="19">
-        <f t="shared" si="74"/>
+        <f t="shared" si="86"/>
         <v>205284</v>
       </c>
-      <c r="AP38" s="113">
-        <f t="shared" si="69"/>
+      <c r="AP38" s="112">
+        <f t="shared" si="81"/>
         <v>0</v>
       </c>
-      <c r="AQ38" s="46">
-        <f t="shared" si="69"/>
+      <c r="AQ38" s="45">
+        <f t="shared" si="81"/>
         <v>0</v>
       </c>
-      <c r="AR38" s="46">
-        <f t="shared" si="69"/>
+      <c r="AR38" s="45">
+        <f t="shared" si="81"/>
         <v>1032196</v>
       </c>
-      <c r="AS38" s="46">
-        <f t="shared" si="69"/>
+      <c r="AS38" s="45">
+        <f t="shared" si="81"/>
         <v>1377740</v>
       </c>
-      <c r="AT38" s="46">
-        <f t="shared" si="69"/>
+      <c r="AT38" s="45">
+        <f t="shared" si="81"/>
         <v>9123918</v>
       </c>
-      <c r="AU38" s="46">
-        <f t="shared" si="75"/>
+      <c r="AU38" s="45">
+        <f t="shared" si="87"/>
         <v>11533854</v>
       </c>
-    </row>
-    <row r="39" spans="1:47" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="AW38" s="93"/>
+      <c r="AX38" s="53"/>
+      <c r="AY38" s="53"/>
+      <c r="AZ38" s="53"/>
+      <c r="BA38" s="120"/>
+      <c r="BB38" s="120"/>
+      <c r="BD38" s="93"/>
+      <c r="BE38" s="53"/>
+      <c r="BF38" s="53"/>
+      <c r="BG38" s="53"/>
+      <c r="BH38" s="120"/>
+      <c r="BI38" s="120"/>
+    </row>
+    <row r="39" spans="1:61" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="B39" s="117">
+      <c r="B39" s="116">
         <f>SUM(B34:B38)</f>
         <v>858227</v>
       </c>
-      <c r="C39" s="116">
+      <c r="C39" s="115">
         <f>SUBTOTAL(109,estadisticas!$C$34:$C$38)</f>
         <v>3230017545</v>
       </c>
-      <c r="E39" s="95">
+      <c r="E39" s="94">
         <f>SUM(E34:E38)</f>
         <v>110903</v>
       </c>
-      <c r="F39" s="51">
-        <f t="shared" ref="F39" si="76">SUM(F34:F38)</f>
+      <c r="F39" s="50">
+        <f t="shared" ref="F39" si="88">SUM(F34:F38)</f>
         <v>304519</v>
       </c>
-      <c r="G39" s="51">
-        <f t="shared" ref="G39" si="77">SUM(G34:G38)</f>
+      <c r="G39" s="50">
+        <f t="shared" ref="G39" si="89">SUM(G34:G38)</f>
         <v>118380</v>
       </c>
-      <c r="H39" s="51">
-        <f t="shared" ref="H39" si="78">SUM(H34:H38)</f>
+      <c r="H39" s="50">
+        <f t="shared" ref="H39" si="90">SUM(H34:H38)</f>
         <v>115644</v>
       </c>
-      <c r="I39" s="51">
-        <f t="shared" ref="I39" si="79">SUM(I34:I38)</f>
+      <c r="I39" s="50">
+        <f t="shared" ref="I39" si="91">SUM(I34:I38)</f>
         <v>208781</v>
       </c>
-      <c r="J39" s="118">
-        <f t="shared" ref="J39" si="80">SUM(J34:J38)</f>
+      <c r="J39" s="117">
+        <f t="shared" ref="J39" si="92">SUM(J34:J38)</f>
         <v>6017171</v>
       </c>
-      <c r="L39" s="109">
+      <c r="L39" s="108">
         <f>SUM(L34:L38)</f>
         <v>650543568</v>
       </c>
-      <c r="M39" s="69">
-        <f t="shared" ref="M39" si="81">SUM(M34:M38)</f>
+      <c r="M39" s="68">
+        <f t="shared" ref="M39" si="93">SUM(M34:M38)</f>
         <v>578124392</v>
       </c>
-      <c r="N39" s="69">
-        <f t="shared" ref="N39" si="82">SUM(N34:N38)</f>
+      <c r="N39" s="68">
+        <f t="shared" ref="N39" si="94">SUM(N34:N38)</f>
         <v>690157736</v>
       </c>
-      <c r="O39" s="69">
-        <f t="shared" ref="O39" si="83">SUM(O34:O38)</f>
+      <c r="O39" s="68">
+        <f t="shared" ref="O39" si="95">SUM(O34:O38)</f>
         <v>654943915</v>
       </c>
-      <c r="P39" s="69">
-        <f t="shared" ref="P39" si="84">SUM(P34:P38)</f>
+      <c r="P39" s="68">
+        <f t="shared" ref="P39" si="96">SUM(P34:P38)</f>
         <v>656247934</v>
       </c>
-      <c r="Q39" s="115">
+      <c r="Q39" s="114">
         <f>SUM(Q34:Q38)</f>
         <v>3230017545</v>
       </c>
-      <c r="S39" s="93">
+      <c r="S39" s="92">
         <f>SUM(S34:S38)</f>
         <v>121665</v>
       </c>
       <c r="T39" s="40">
-        <f t="shared" ref="T39:Y39" si="85">SUM(T34:T38)</f>
+        <f t="shared" ref="T39:Y39" si="97">SUM(T34:T38)</f>
         <v>125620</v>
       </c>
       <c r="U39" s="40">
-        <f t="shared" si="85"/>
+        <f t="shared" si="97"/>
         <v>32356</v>
       </c>
       <c r="V39" s="40">
-        <f t="shared" si="85"/>
+        <f t="shared" si="97"/>
         <v>356297</v>
       </c>
       <c r="W39" s="40">
-        <f t="shared" si="85"/>
+        <f t="shared" si="97"/>
         <v>122295</v>
       </c>
       <c r="X39" s="40">
-        <f t="shared" si="85"/>
+        <f t="shared" si="97"/>
         <v>99994</v>
       </c>
       <c r="Y39" s="40">
-        <f t="shared" si="85"/>
+        <f t="shared" si="97"/>
         <v>858227</v>
       </c>
-      <c r="AA39" s="107">
+      <c r="AA39" s="106">
         <f>SUM(AA34:AA38)</f>
         <v>121665</v>
       </c>
-      <c r="AB39" s="67">
-        <f t="shared" ref="AB39" si="86">SUM(AB34:AB38)</f>
+      <c r="AB39" s="66">
+        <f t="shared" ref="AB39" si="98">SUM(AB34:AB38)</f>
         <v>125620</v>
       </c>
-      <c r="AC39" s="67">
-        <f t="shared" ref="AC39" si="87">SUM(AC34:AC38)</f>
+      <c r="AC39" s="66">
+        <f t="shared" ref="AC39" si="99">SUM(AC34:AC38)</f>
         <v>32356</v>
       </c>
-      <c r="AD39" s="67">
-        <f t="shared" ref="AD39" si="88">SUM(AD34:AD38)</f>
+      <c r="AD39" s="66">
+        <f t="shared" ref="AD39" si="100">SUM(AD34:AD38)</f>
         <v>356297</v>
       </c>
-      <c r="AE39" s="67">
-        <f t="shared" ref="AE39" si="89">SUM(AE34:AE38)</f>
+      <c r="AE39" s="66">
+        <f t="shared" ref="AE39" si="101">SUM(AE34:AE38)</f>
         <v>122295</v>
       </c>
-      <c r="AF39" s="67">
-        <f t="shared" ref="AF39" si="90">SUM(AF34:AF38)</f>
+      <c r="AF39" s="66">
+        <f t="shared" ref="AF39" si="102">SUM(AF34:AF38)</f>
         <v>99994</v>
       </c>
-      <c r="AG39" s="115">
-        <f t="shared" ref="AG39" si="91">SUM(AG34:AG38)</f>
+      <c r="AG39" s="114">
+        <f t="shared" ref="AG39" si="103">SUM(AG34:AG38)</f>
         <v>858227</v>
       </c>
-      <c r="AI39" s="95">
+      <c r="AI39" s="94">
         <f>SUM(AI34:AI38)</f>
         <v>110109</v>
       </c>
-      <c r="AJ39" s="51">
-        <f t="shared" ref="AJ39:AN39" si="92">SUM(AJ34:AJ38)</f>
+      <c r="AJ39" s="50">
+        <f t="shared" ref="AJ39:AN39" si="104">SUM(AJ34:AJ38)</f>
         <v>213260</v>
       </c>
-      <c r="AK39" s="51">
-        <f t="shared" si="92"/>
+      <c r="AK39" s="50">
+        <f t="shared" si="104"/>
         <v>116030</v>
       </c>
-      <c r="AL39" s="51">
-        <f t="shared" si="92"/>
+      <c r="AL39" s="50">
+        <f t="shared" si="104"/>
         <v>312792</v>
       </c>
-      <c r="AM39" s="51">
-        <f t="shared" si="92"/>
+      <c r="AM39" s="50">
+        <f t="shared" si="104"/>
         <v>106036</v>
       </c>
-      <c r="AN39" s="118">
-        <f t="shared" si="92"/>
+      <c r="AN39" s="117">
+        <f t="shared" si="104"/>
         <v>858227</v>
       </c>
-      <c r="AP39" s="114">
+      <c r="AP39" s="113">
         <f>SUM(AP34:AP38)</f>
         <v>646106962</v>
       </c>
-      <c r="AQ39" s="49">
-        <f t="shared" ref="AQ39" si="93">SUM(AQ34:AQ38)</f>
+      <c r="AQ39" s="48">
+        <f t="shared" ref="AQ39" si="105">SUM(AQ34:AQ38)</f>
         <v>576804336</v>
       </c>
-      <c r="AR39" s="49">
-        <f t="shared" ref="AR39" si="94">SUM(AR34:AR38)</f>
+      <c r="AR39" s="48">
+        <f t="shared" ref="AR39" si="106">SUM(AR34:AR38)</f>
         <v>687706530</v>
       </c>
-      <c r="AS39" s="49">
-        <f t="shared" ref="AS39" si="95">SUM(AS34:AS38)</f>
+      <c r="AS39" s="48">
+        <f t="shared" ref="AS39" si="107">SUM(AS34:AS38)</f>
         <v>654677692</v>
       </c>
-      <c r="AT39" s="49">
-        <f t="shared" ref="AT39" si="96">SUM(AT34:AT38)</f>
+      <c r="AT39" s="48">
+        <f t="shared" ref="AT39" si="108">SUM(AT34:AT38)</f>
         <v>664722025</v>
       </c>
-      <c r="AU39" s="119">
-        <f t="shared" ref="AU39" si="97">SUM(AU34:AU38)</f>
+      <c r="AU39" s="118">
+        <f t="shared" ref="AU39" si="109">SUM(AU34:AU38)</f>
         <v>3230017545</v>
       </c>
+      <c r="AW39" s="93"/>
+      <c r="AX39" s="53"/>
+      <c r="AY39" s="53"/>
+      <c r="AZ39" s="53"/>
+      <c r="BA39" s="120"/>
+      <c r="BB39" s="120"/>
+      <c r="BD39" s="93"/>
+      <c r="BE39" s="53"/>
+      <c r="BF39" s="53"/>
+      <c r="BG39" s="53"/>
+      <c r="BH39" s="120"/>
+      <c r="BI39" s="120"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/examples/DB_Supermercado.xlsx
+++ b/examples/DB_Supermercado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EducacionIT\Documents\office\Excel\xls-mj15\examples\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30A3AA43-0965-484F-88A4-DE87CEE6109D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6231D298-2DDF-4F12-898F-084AB5DE28D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -439,7 +439,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="136">
+  <cellXfs count="135">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -575,15 +575,14 @@
     <xf numFmtId="44" fontId="8" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="4" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="10" fillId="3" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="10" fillId="5" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="10" fillId="5" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="10" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Énfasis5" xfId="3" builtinId="45"/>
@@ -6459,7 +6458,7 @@
         <f>SUMIF(ventas_producto,I$1,ventas_unidades)</f>
         <v>208781</v>
       </c>
-      <c r="J6" s="131">
+      <c r="J6" s="130">
         <f>SUM(E6:I6)</f>
         <v>858227</v>
       </c>
@@ -6483,7 +6482,7 @@
         <f>SUMIF(ventas_producto,P$1,ventas_total)</f>
         <v>656247934</v>
       </c>
-      <c r="Q6" s="132">
+      <c r="Q6" s="131">
         <f>SUM(L6:P6)</f>
         <v>3230017545</v>
       </c>
@@ -6511,8 +6510,11 @@
         <f t="shared" si="6"/>
         <v>99994</v>
       </c>
-      <c r="Y6" s="131"/>
-      <c r="Z6" s="133"/>
+      <c r="Y6" s="130">
+        <f>SUM(S6:X6)</f>
+        <v>858227</v>
+      </c>
+      <c r="Z6" s="132"/>
       <c r="AA6" s="99">
         <f t="shared" ref="AA6:AF6" si="7">SUMIF(ventas_vendedor,AA$1,ventas_total)</f>
         <v>645115066</v>
@@ -6537,7 +6539,10 @@
         <f t="shared" si="7"/>
         <v>561953724</v>
       </c>
-      <c r="AG6" s="132"/>
+      <c r="AG6" s="131">
+        <f>SUM(AA6:AF6)</f>
+        <v>3230017545</v>
+      </c>
       <c r="AI6" s="84">
         <f>SUMIF(ventas_region,AI$1,ventas_unidades)</f>
         <v>110109</v>
@@ -6558,7 +6563,10 @@
         <f>SUMIF(ventas_region,AM$1,ventas_unidades)</f>
         <v>106036</v>
       </c>
-      <c r="AN6" s="134"/>
+      <c r="AN6" s="134">
+        <f>SUM(AI6:AM6)</f>
+        <v>858227</v>
+      </c>
       <c r="AP6" s="99">
         <f>SUMIF(ventas_region,AP$1,ventas_total)</f>
         <v>646106962</v>
@@ -6579,7 +6587,7 @@
         <f>SUMIF(ventas_region,AT$1,ventas_total)</f>
         <v>664722025</v>
       </c>
-      <c r="AU6" s="135">
+      <c r="AU6" s="133">
         <f>SUM(AP6:AT6)</f>
         <v>3230017545</v>
       </c>
@@ -6603,7 +6611,7 @@
         <f>SUMIF(ventas_año,BA$1,ventas_unidades)</f>
         <v>205284</v>
       </c>
-      <c r="BB6" s="130">
+      <c r="BB6" s="129">
         <f>SUM(AW6:BA6)</f>
         <v>858227</v>
       </c>
@@ -6627,7 +6635,7 @@
         <f>SUMIF(ventas_año,BH$1,ventas_total)</f>
         <v>11533854</v>
       </c>
-      <c r="BI6" s="135">
+      <c r="BI6" s="133">
         <f>SUM(BD6:BH6)</f>
         <v>3230017545</v>
       </c>
@@ -6902,23 +6910,23 @@
         <v>650543568</v>
       </c>
       <c r="AW9" s="81">
-        <f>SUMIFS(ventas_unidades,ventas_producto,$A9,ventas_año,AW$8)</f>
+        <f t="shared" ref="AW9:BA13" si="12">SUMIFS(ventas_unidades,ventas_producto,$A9,ventas_año,AW$8)</f>
         <v>33032</v>
       </c>
       <c r="AX9" s="17">
-        <f>SUMIFS(ventas_unidades,ventas_producto,$A9,ventas_año,AX$8)</f>
+        <f t="shared" si="12"/>
         <v>32671</v>
       </c>
       <c r="AY9" s="17">
-        <f>SUMIFS(ventas_unidades,ventas_producto,$A9,ventas_año,AY$8)</f>
+        <f t="shared" si="12"/>
         <v>35334</v>
       </c>
       <c r="AZ9" s="17">
-        <f>SUMIFS(ventas_unidades,ventas_producto,$A9,ventas_año,AZ$8)</f>
+        <f t="shared" si="12"/>
         <v>2738</v>
       </c>
       <c r="BA9" s="17">
-        <f>SUMIFS(ventas_unidades,ventas_producto,$A9,ventas_año,BA$8)</f>
+        <f t="shared" si="12"/>
         <v>7128</v>
       </c>
       <c r="BB9" s="17">
@@ -6926,23 +6934,23 @@
         <v>110903</v>
       </c>
       <c r="BD9" s="96">
-        <f>SUMIFS(ventas_total,ventas_producto,$A9,ventas_año,BD$8)</f>
+        <f t="shared" ref="BD9:BH13" si="13">SUMIFS(ventas_total,ventas_producto,$A9,ventas_año,BD$8)</f>
         <v>218669111</v>
       </c>
       <c r="BE9" s="58">
-        <f>SUMIFS(ventas_total,ventas_producto,$A9,ventas_año,BE$8)</f>
+        <f t="shared" si="13"/>
         <v>203341463</v>
       </c>
       <c r="BF9" s="58">
-        <f>SUMIFS(ventas_total,ventas_producto,$A9,ventas_año,BF$8)</f>
+        <f t="shared" si="13"/>
         <v>218564244</v>
       </c>
       <c r="BG9" s="58">
-        <f>SUMIFS(ventas_total,ventas_producto,$A9,ventas_año,BG$8)</f>
+        <f t="shared" si="13"/>
         <v>844832</v>
       </c>
       <c r="BH9" s="58">
-        <f>SUMIFS(ventas_total,ventas_producto,$A9,ventas_año,BH$8)</f>
+        <f t="shared" si="13"/>
         <v>9123918</v>
       </c>
       <c r="BI9" s="58">
@@ -7000,7 +7008,7 @@
         <v>16505</v>
       </c>
       <c r="Y10" s="30">
-        <f t="shared" ref="Y10:Y13" si="12">SUM(S10:X10)</f>
+        <f t="shared" ref="Y10:Y13" si="14">SUM(S10:X10)</f>
         <v>304519</v>
       </c>
       <c r="AA10" s="104">
@@ -7028,7 +7036,7 @@
         <v>50806730</v>
       </c>
       <c r="AG10" s="64">
-        <f t="shared" ref="AG10:AG13" si="13">SUM(AA10:AF10)</f>
+        <f t="shared" ref="AG10:AG13" si="15">SUM(AA10:AF10)</f>
         <v>578124392</v>
       </c>
       <c r="AI10" s="82">
@@ -7052,7 +7060,7 @@
         <v>0</v>
       </c>
       <c r="AN10" s="46">
-        <f t="shared" ref="AN10:AN13" si="14">SUM(AI10:AM10)</f>
+        <f t="shared" ref="AN10:AN13" si="16">SUM(AI10:AM10)</f>
         <v>304519</v>
       </c>
       <c r="AP10" s="97">
@@ -7076,55 +7084,55 @@
         <v>0</v>
       </c>
       <c r="AU10" s="69">
-        <f t="shared" ref="AU10:AU13" si="15">SUM(AP10:AT10)</f>
+        <f t="shared" ref="AU10:AU13" si="17">SUM(AP10:AT10)</f>
         <v>578124392</v>
       </c>
       <c r="AW10" s="82">
-        <f>SUMIFS(ventas_unidades,ventas_producto,$A10,ventas_año,AW$8)</f>
+        <f t="shared" si="12"/>
         <v>32696</v>
       </c>
       <c r="AX10" s="46">
-        <f>SUMIFS(ventas_unidades,ventas_producto,$A10,ventas_año,AX$8)</f>
+        <f t="shared" si="12"/>
         <v>31651</v>
       </c>
       <c r="AY10" s="46">
-        <f>SUMIFS(ventas_unidades,ventas_producto,$A10,ventas_año,AY$8)</f>
+        <f t="shared" si="12"/>
         <v>40967</v>
       </c>
       <c r="AZ10" s="46">
-        <f>SUMIFS(ventas_unidades,ventas_producto,$A10,ventas_año,AZ$8)</f>
+        <f t="shared" si="12"/>
         <v>4903</v>
       </c>
       <c r="BA10" s="46">
-        <f>SUMIFS(ventas_unidades,ventas_producto,$A10,ventas_año,BA$8)</f>
+        <f t="shared" si="12"/>
         <v>194302</v>
       </c>
       <c r="BB10" s="46">
-        <f t="shared" ref="BB10:BB13" si="16">SUM(AW10:BA10)</f>
+        <f t="shared" ref="BB10:BB13" si="18">SUM(AW10:BA10)</f>
         <v>304519</v>
       </c>
       <c r="BD10" s="97">
-        <f>SUMIFS(ventas_total,ventas_producto,$A10,ventas_año,BD$8)</f>
+        <f t="shared" si="13"/>
         <v>160364763</v>
       </c>
       <c r="BE10" s="69">
-        <f>SUMIFS(ventas_total,ventas_producto,$A10,ventas_año,BE$8)</f>
+        <f t="shared" si="13"/>
         <v>201880917</v>
       </c>
       <c r="BF10" s="69">
-        <f>SUMIFS(ventas_total,ventas_producto,$A10,ventas_año,BF$8)</f>
+        <f t="shared" si="13"/>
         <v>214457221</v>
       </c>
       <c r="BG10" s="69">
-        <f>SUMIFS(ventas_total,ventas_producto,$A10,ventas_año,BG$8)</f>
+        <f t="shared" si="13"/>
         <v>483929</v>
       </c>
       <c r="BH10" s="69">
-        <f>SUMIFS(ventas_total,ventas_producto,$A10,ventas_año,BH$8)</f>
+        <f t="shared" si="13"/>
         <v>937562</v>
       </c>
       <c r="BI10" s="69">
-        <f t="shared" ref="BI10:BI13" si="17">SUM(BD10:BH10)</f>
+        <f t="shared" ref="BI10:BI13" si="19">SUM(BD10:BH10)</f>
         <v>578124392</v>
       </c>
     </row>
@@ -7178,7 +7186,7 @@
         <v>25030</v>
       </c>
       <c r="Y11" s="31">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>118380</v>
       </c>
       <c r="AA11" s="105">
@@ -7206,7 +7214,7 @@
         <v>167729464</v>
       </c>
       <c r="AG11" s="65">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>690157736</v>
       </c>
       <c r="AI11" s="83">
@@ -7230,7 +7238,7 @@
         <v>0</v>
       </c>
       <c r="AN11" s="47">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>118380</v>
       </c>
       <c r="AP11" s="98">
@@ -7254,55 +7262,55 @@
         <v>0</v>
       </c>
       <c r="AU11" s="70">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>690157736</v>
       </c>
       <c r="AW11" s="83">
-        <f>SUMIFS(ventas_unidades,ventas_producto,$A11,ventas_año,AW$8)</f>
+        <f t="shared" si="12"/>
         <v>39124</v>
       </c>
       <c r="AX11" s="47">
-        <f>SUMIFS(ventas_unidades,ventas_producto,$A11,ventas_año,AX$8)</f>
+        <f t="shared" si="12"/>
         <v>34000</v>
       </c>
       <c r="AY11" s="47">
-        <f>SUMIFS(ventas_unidades,ventas_producto,$A11,ventas_año,AY$8)</f>
+        <f t="shared" si="12"/>
         <v>31330</v>
       </c>
       <c r="AZ11" s="47">
-        <f>SUMIFS(ventas_unidades,ventas_producto,$A11,ventas_año,AZ$8)</f>
+        <f t="shared" si="12"/>
         <v>13926</v>
       </c>
       <c r="BA11" s="47">
-        <f>SUMIFS(ventas_unidades,ventas_producto,$A11,ventas_año,BA$8)</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="BB11" s="47">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>118380</v>
       </c>
       <c r="BD11" s="98">
-        <f>SUMIFS(ventas_total,ventas_producto,$A11,ventas_año,BD$8)</f>
+        <f t="shared" si="13"/>
         <v>220801841</v>
       </c>
       <c r="BE11" s="70">
-        <f>SUMIFS(ventas_total,ventas_producto,$A11,ventas_año,BE$8)</f>
+        <f t="shared" si="13"/>
         <v>239992813</v>
       </c>
       <c r="BF11" s="70">
-        <f>SUMIFS(ventas_total,ventas_producto,$A11,ventas_año,BF$8)</f>
+        <f t="shared" si="13"/>
         <v>216914467</v>
       </c>
       <c r="BG11" s="70">
-        <f>SUMIFS(ventas_total,ventas_producto,$A11,ventas_año,BG$8)</f>
+        <f t="shared" si="13"/>
         <v>12448615</v>
       </c>
       <c r="BH11" s="70">
-        <f>SUMIFS(ventas_total,ventas_producto,$A11,ventas_año,BH$8)</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="BI11" s="70">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>690157736</v>
       </c>
     </row>
@@ -7356,7 +7364,7 @@
         <v>5584</v>
       </c>
       <c r="Y12" s="30">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>115644</v>
       </c>
       <c r="AA12" s="104">
@@ -7384,7 +7392,7 @@
         <v>17788927</v>
       </c>
       <c r="AG12" s="64">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>654943915</v>
       </c>
       <c r="AI12" s="82">
@@ -7408,7 +7416,7 @@
         <v>0</v>
       </c>
       <c r="AN12" s="46">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>115644</v>
       </c>
       <c r="AP12" s="97">
@@ -7432,55 +7440,55 @@
         <v>0</v>
       </c>
       <c r="AU12" s="69">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>654943915</v>
       </c>
       <c r="AW12" s="82">
-        <f>SUMIFS(ventas_unidades,ventas_producto,$A12,ventas_año,AW$8)</f>
+        <f t="shared" si="12"/>
         <v>40573</v>
       </c>
       <c r="AX12" s="46">
-        <f>SUMIFS(ventas_unidades,ventas_producto,$A12,ventas_año,AX$8)</f>
+        <f t="shared" si="12"/>
         <v>39442</v>
       </c>
       <c r="AY12" s="46">
-        <f>SUMIFS(ventas_unidades,ventas_producto,$A12,ventas_año,AY$8)</f>
+        <f t="shared" si="12"/>
         <v>33573</v>
       </c>
       <c r="AZ12" s="46">
-        <f>SUMIFS(ventas_unidades,ventas_producto,$A12,ventas_año,AZ$8)</f>
+        <f t="shared" si="12"/>
         <v>129</v>
       </c>
       <c r="BA12" s="46">
-        <f>SUMIFS(ventas_unidades,ventas_producto,$A12,ventas_año,BA$8)</f>
+        <f t="shared" si="12"/>
         <v>1927</v>
       </c>
       <c r="BB12" s="46">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>115644</v>
       </c>
       <c r="BD12" s="97">
-        <f>SUMIFS(ventas_total,ventas_producto,$A12,ventas_año,BD$8)</f>
+        <f t="shared" si="13"/>
         <v>190929354</v>
       </c>
       <c r="BE12" s="69">
-        <f>SUMIFS(ventas_total,ventas_producto,$A12,ventas_año,BE$8)</f>
+        <f t="shared" si="13"/>
         <v>221383553</v>
       </c>
       <c r="BF12" s="69">
-        <f>SUMIFS(ventas_total,ventas_producto,$A12,ventas_año,BF$8)</f>
+        <f t="shared" si="13"/>
         <v>240503116</v>
       </c>
       <c r="BG12" s="69">
-        <f>SUMIFS(ventas_total,ventas_producto,$A12,ventas_año,BG$8)</f>
+        <f t="shared" si="13"/>
         <v>1203910</v>
       </c>
       <c r="BH12" s="69">
-        <f>SUMIFS(ventas_total,ventas_producto,$A12,ventas_año,BH$8)</f>
+        <f t="shared" si="13"/>
         <v>923982</v>
       </c>
       <c r="BI12" s="69">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>654943915</v>
       </c>
     </row>
@@ -7534,7 +7542,7 @@
         <v>41415</v>
       </c>
       <c r="Y13" s="31">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>208781</v>
       </c>
       <c r="AA13" s="105">
@@ -7562,7 +7570,7 @@
         <v>276189776</v>
       </c>
       <c r="AG13" s="65">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>656247934</v>
       </c>
       <c r="AI13" s="83">
@@ -7586,7 +7594,7 @@
         <v>98908</v>
       </c>
       <c r="AN13" s="47">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>208781</v>
       </c>
       <c r="AP13" s="98">
@@ -7610,55 +7618,55 @@
         <v>655598107</v>
       </c>
       <c r="AU13" s="70">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>656247934</v>
       </c>
       <c r="AW13" s="83">
-        <f>SUMIFS(ventas_unidades,ventas_producto,$A13,ventas_año,AW$8)</f>
+        <f t="shared" si="12"/>
         <v>36557</v>
       </c>
       <c r="AX13" s="47">
-        <f>SUMIFS(ventas_unidades,ventas_producto,$A13,ventas_año,AX$8)</f>
+        <f t="shared" si="12"/>
         <v>28900</v>
       </c>
       <c r="AY13" s="47">
-        <f>SUMIFS(ventas_unidades,ventas_producto,$A13,ventas_año,AY$8)</f>
+        <f t="shared" si="12"/>
         <v>33451</v>
       </c>
       <c r="AZ13" s="47">
-        <f>SUMIFS(ventas_unidades,ventas_producto,$A13,ventas_año,AZ$8)</f>
+        <f t="shared" si="12"/>
         <v>107946</v>
       </c>
       <c r="BA13" s="47">
-        <f>SUMIFS(ventas_unidades,ventas_producto,$A13,ventas_año,BA$8)</f>
+        <f t="shared" si="12"/>
         <v>1927</v>
       </c>
       <c r="BB13" s="47">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>208781</v>
       </c>
       <c r="BD13" s="98">
-        <f>SUMIFS(ventas_total,ventas_producto,$A13,ventas_año,BD$8)</f>
+        <f t="shared" si="13"/>
         <v>216479082</v>
       </c>
       <c r="BE13" s="70">
-        <f>SUMIFS(ventas_total,ventas_producto,$A13,ventas_año,BE$8)</f>
+        <f t="shared" si="13"/>
         <v>240247726</v>
       </c>
       <c r="BF13" s="70">
-        <f>SUMIFS(ventas_total,ventas_producto,$A13,ventas_año,BF$8)</f>
+        <f t="shared" si="13"/>
         <v>198871299</v>
       </c>
       <c r="BG13" s="70">
-        <f>SUMIFS(ventas_total,ventas_producto,$A13,ventas_año,BG$8)</f>
+        <f t="shared" si="13"/>
         <v>101435</v>
       </c>
       <c r="BH13" s="70">
-        <f>SUMIFS(ventas_total,ventas_producto,$A13,ventas_año,BH$8)</f>
+        <f t="shared" si="13"/>
         <v>548392</v>
       </c>
       <c r="BI13" s="70">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>656247934</v>
       </c>
     </row>
@@ -7692,23 +7700,23 @@
         <v>121665</v>
       </c>
       <c r="T14" s="40">
-        <f t="shared" ref="T14:X14" si="18">SUM(T9:T13)</f>
+        <f t="shared" ref="T14:X14" si="20">SUM(T9:T13)</f>
         <v>125620</v>
       </c>
       <c r="U14" s="40">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>32356</v>
       </c>
       <c r="V14" s="40">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>356297</v>
       </c>
       <c r="W14" s="40">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>122295</v>
       </c>
       <c r="X14" s="40">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>99994</v>
       </c>
       <c r="Y14" s="117">
@@ -7720,47 +7728,47 @@
         <v>645115066</v>
       </c>
       <c r="AB14" s="66">
-        <f t="shared" ref="AB14" si="19">SUM(AB9:AB13)</f>
+        <f t="shared" ref="AB14" si="21">SUM(AB9:AB13)</f>
         <v>761464717</v>
       </c>
       <c r="AC14" s="66">
-        <f t="shared" ref="AC14" si="20">SUM(AC9:AC13)</f>
+        <f t="shared" ref="AC14" si="22">SUM(AC9:AC13)</f>
         <v>226722785</v>
       </c>
       <c r="AD14" s="66">
-        <f t="shared" ref="AD14" si="21">SUM(AD9:AD13)</f>
+        <f t="shared" ref="AD14" si="23">SUM(AD9:AD13)</f>
         <v>312257691</v>
       </c>
       <c r="AE14" s="66">
-        <f t="shared" ref="AE14" si="22">SUM(AE9:AE13)</f>
+        <f t="shared" ref="AE14" si="24">SUM(AE9:AE13)</f>
         <v>722503562</v>
       </c>
       <c r="AF14" s="66">
-        <f t="shared" ref="AF14" si="23">SUM(AF9:AF13)</f>
+        <f t="shared" ref="AF14" si="25">SUM(AF9:AF13)</f>
         <v>561953724</v>
       </c>
       <c r="AG14" s="114">
-        <f t="shared" ref="AG14" si="24">SUM(AG9:AG13)</f>
+        <f t="shared" ref="AG14" si="26">SUM(AG9:AG13)</f>
         <v>3230017545</v>
       </c>
       <c r="AI14" s="94">
-        <f t="shared" ref="AI14:AM14" si="25">SUM(AI10:AI13)</f>
+        <f t="shared" ref="AI14:AM14" si="27">SUM(AI10:AI13)</f>
         <v>9072</v>
       </c>
       <c r="AJ14" s="50">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>213260</v>
       </c>
       <c r="AK14" s="50">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>113292</v>
       </c>
       <c r="AL14" s="50">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>312792</v>
       </c>
       <c r="AM14" s="50">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>98908</v>
       </c>
       <c r="AN14" s="117">
@@ -7772,43 +7780,43 @@
         <v>646106962</v>
       </c>
       <c r="AQ14" s="68">
-        <f t="shared" ref="AQ14:AU14" si="26">SUM(AQ9:AQ13)</f>
+        <f t="shared" ref="AQ14:AU14" si="28">SUM(AQ9:AQ13)</f>
         <v>576804336</v>
       </c>
       <c r="AR14" s="68">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>687706530</v>
       </c>
       <c r="AS14" s="68">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>654677692</v>
       </c>
       <c r="AT14" s="68">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>664722025</v>
       </c>
       <c r="AU14" s="114">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>3230017545</v>
       </c>
       <c r="AW14" s="94">
-        <f t="shared" ref="AW14:BA14" si="27">SUM(AW10:AW13)</f>
+        <f t="shared" ref="AW14:BA14" si="29">SUM(AW10:AW13)</f>
         <v>148950</v>
       </c>
       <c r="AX14" s="50">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>133993</v>
       </c>
       <c r="AY14" s="50">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>139321</v>
       </c>
       <c r="AZ14" s="50">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>126904</v>
       </c>
       <c r="BA14" s="50">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>198156</v>
       </c>
       <c r="BB14" s="117">
@@ -7820,23 +7828,23 @@
         <v>1007244151</v>
       </c>
       <c r="BE14" s="68">
-        <f t="shared" ref="BE14:BI14" si="28">SUM(BE9:BE13)</f>
+        <f t="shared" ref="BE14:BI14" si="30">SUM(BE9:BE13)</f>
         <v>1106846472</v>
       </c>
       <c r="BF14" s="68">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>1089310347</v>
       </c>
       <c r="BG14" s="68">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>15082721</v>
       </c>
       <c r="BH14" s="68">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>11533854</v>
       </c>
       <c r="BI14" s="114">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>3230017545</v>
       </c>
     </row>
@@ -7980,31 +7988,31 @@
         <v>28</v>
       </c>
       <c r="B17" s="29">
-        <f t="shared" ref="B17:B22" si="29">SUMIF(ventas_vendedor,$A17,ventas_unidades)</f>
+        <f t="shared" ref="B17:B22" si="31">SUMIF(ventas_vendedor,$A17,ventas_unidades)</f>
         <v>121665</v>
       </c>
       <c r="C17" s="37">
-        <f t="shared" ref="C17:C22" si="30">SUMIF(ventas_vendedor,$A17,ventas_total)</f>
+        <f t="shared" ref="C17:C22" si="32">SUMIF(ventas_vendedor,$A17,ventas_total)</f>
         <v>645115066</v>
       </c>
       <c r="E17" s="81">
-        <f t="shared" ref="E17:I22" si="31">SUMIFS(ventas_unidades,ventas_vendedor,$A17,ventas_producto,E$16)</f>
+        <f t="shared" ref="E17:I22" si="33">SUMIFS(ventas_unidades,ventas_vendedor,$A17,ventas_producto,E$16)</f>
         <v>23075</v>
       </c>
       <c r="F17" s="17">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>14026</v>
       </c>
       <c r="G17" s="17">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>37242</v>
       </c>
       <c r="H17" s="17">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>34352</v>
       </c>
       <c r="I17" s="17">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>12970</v>
       </c>
       <c r="J17" s="17">
@@ -8012,23 +8020,23 @@
         <v>121665</v>
       </c>
       <c r="L17" s="96">
-        <f t="shared" ref="L17:P22" si="32">SUMIFS(ventas_total,ventas_vendedor,$A17,ventas_producto,L$16)</f>
+        <f t="shared" ref="L17:P22" si="34">SUMIFS(ventas_total,ventas_vendedor,$A17,ventas_producto,L$16)</f>
         <v>109144041</v>
       </c>
       <c r="M17" s="58">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>53223672</v>
       </c>
       <c r="N17" s="58">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>240818885</v>
       </c>
       <c r="O17" s="58">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>169977929</v>
       </c>
       <c r="P17" s="58">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>71950539</v>
       </c>
       <c r="Q17" s="58">
@@ -8050,23 +8058,23 @@
       <c r="AF17" s="67"/>
       <c r="AG17" s="67"/>
       <c r="AI17" s="81">
-        <f t="shared" ref="AI17:AM22" si="33">SUMIFS(ventas_unidades,ventas_vendedor,$A17,ventas_region,AI$16)</f>
+        <f t="shared" ref="AI17:AM22" si="35">SUMIFS(ventas_unidades,ventas_vendedor,$A17,ventas_region,AI$16)</f>
         <v>23075</v>
       </c>
       <c r="AJ17" s="17">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>7195</v>
       </c>
       <c r="AK17" s="17">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>39170</v>
       </c>
       <c r="AL17" s="17">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>39255</v>
       </c>
       <c r="AM17" s="17">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>12970</v>
       </c>
       <c r="AN17" s="17">
@@ -8074,23 +8082,23 @@
         <v>121665</v>
       </c>
       <c r="AP17" s="96">
-        <f t="shared" ref="AP17:AT22" si="34">SUMIFS(ventas_total,ventas_vendedor,$A17,ventas_region,AP$16)</f>
+        <f t="shared" ref="AP17:AT22" si="36">SUMIFS(ventas_total,ventas_vendedor,$A17,ventas_region,AP$16)</f>
         <v>109144041</v>
       </c>
       <c r="AQ17" s="58">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>52631529</v>
       </c>
       <c r="AR17" s="58">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>240927099</v>
       </c>
       <c r="AS17" s="58">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>170461858</v>
       </c>
       <c r="AT17" s="58">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>71950539</v>
       </c>
       <c r="AU17" s="58">
@@ -8098,23 +8106,23 @@
         <v>645115066</v>
       </c>
       <c r="AW17" s="81">
-        <f>SUMIFS(ventas_unidades,ventas_vendedor,$A17,ventas_año,AW$16)</f>
+        <f t="shared" ref="AW17:BA22" si="37">SUMIFS(ventas_unidades,ventas_vendedor,$A17,ventas_año,AW$16)</f>
         <v>33623</v>
       </c>
       <c r="AX17" s="17">
-        <f>SUMIFS(ventas_unidades,ventas_vendedor,$A17,ventas_año,AX$16)</f>
+        <f t="shared" si="37"/>
         <v>42339</v>
       </c>
       <c r="AY17" s="17">
-        <f>SUMIFS(ventas_unidades,ventas_vendedor,$A17,ventas_año,AY$16)</f>
+        <f t="shared" si="37"/>
         <v>33889</v>
       </c>
       <c r="AZ17" s="17">
-        <f>SUMIFS(ventas_unidades,ventas_vendedor,$A17,ventas_año,AZ$16)</f>
+        <f t="shared" si="37"/>
         <v>9886</v>
       </c>
       <c r="BA17" s="17">
-        <f>SUMIFS(ventas_unidades,ventas_vendedor,$A17,ventas_año,BA$16)</f>
+        <f t="shared" si="37"/>
         <v>1928</v>
       </c>
       <c r="BB17" s="17">
@@ -8122,23 +8130,23 @@
         <v>121665</v>
       </c>
       <c r="BD17" s="96">
-        <f>SUMIFS(ventas_total,ventas_vendedor,$A17,ventas_año,BD$8)</f>
+        <f t="shared" ref="BD17:BH22" si="38">SUMIFS(ventas_total,ventas_vendedor,$A17,ventas_año,BD$8)</f>
         <v>175048265</v>
       </c>
       <c r="BE17" s="58">
-        <f>SUMIFS(ventas_total,ventas_vendedor,$A17,ventas_año,BE$8)</f>
+        <f t="shared" si="38"/>
         <v>244791087</v>
       </c>
       <c r="BF17" s="58">
-        <f>SUMIFS(ventas_total,ventas_vendedor,$A17,ventas_año,BF$8)</f>
+        <f t="shared" si="38"/>
         <v>216563190</v>
       </c>
       <c r="BG17" s="58">
-        <f>SUMIFS(ventas_total,ventas_vendedor,$A17,ventas_año,BG$8)</f>
+        <f t="shared" si="38"/>
         <v>8604310</v>
       </c>
       <c r="BH17" s="58">
-        <f>SUMIFS(ventas_total,ventas_vendedor,$A17,ventas_año,BH$8)</f>
+        <f t="shared" si="38"/>
         <v>108214</v>
       </c>
       <c r="BI17" s="58">
@@ -8151,59 +8159,59 @@
         <v>8</v>
       </c>
       <c r="B18" s="30">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>125620</v>
       </c>
       <c r="C18" s="38">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>761464717</v>
       </c>
       <c r="E18" s="82">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>27346</v>
       </c>
       <c r="F18" s="18">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>51553</v>
       </c>
       <c r="G18" s="18">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>19565</v>
       </c>
       <c r="H18" s="18">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>12991</v>
       </c>
       <c r="I18" s="18">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>14165</v>
       </c>
       <c r="J18" s="18">
-        <f t="shared" ref="J18:J22" si="35">SUM(E18:I18)</f>
+        <f t="shared" ref="J18:J22" si="39">SUM(E18:I18)</f>
         <v>125620</v>
       </c>
       <c r="L18" s="97">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>193222871</v>
       </c>
       <c r="M18" s="59">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>271532147</v>
       </c>
       <c r="N18" s="59">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>131950052</v>
       </c>
       <c r="O18" s="59">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>75839132</v>
       </c>
       <c r="P18" s="59">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>88920515</v>
       </c>
       <c r="Q18" s="59">
-        <f t="shared" ref="Q18:Q22" si="36">SUM(L18:P18)</f>
+        <f t="shared" ref="Q18:Q22" si="40">SUM(L18:P18)</f>
         <v>761464717</v>
       </c>
       <c r="S18" s="93"/>
@@ -8221,99 +8229,99 @@
       <c r="AF18" s="67"/>
       <c r="AG18" s="67"/>
       <c r="AI18" s="82">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>27346</v>
       </c>
       <c r="AJ18" s="18">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>51553</v>
       </c>
       <c r="AK18" s="18">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>19565</v>
       </c>
       <c r="AL18" s="18">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>12991</v>
       </c>
       <c r="AM18" s="18">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>14165</v>
       </c>
       <c r="AN18" s="18">
-        <f t="shared" ref="AN18:AN22" si="37">SUM(AI18:AM18)</f>
+        <f t="shared" ref="AN18:AN22" si="41">SUM(AI18:AM18)</f>
         <v>125620</v>
       </c>
       <c r="AP18" s="97">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>193222871</v>
       </c>
       <c r="AQ18" s="59">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>271532147</v>
       </c>
       <c r="AR18" s="59">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>131950052</v>
       </c>
       <c r="AS18" s="59">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>75839132</v>
       </c>
       <c r="AT18" s="59">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>88920515</v>
       </c>
       <c r="AU18" s="59">
-        <f t="shared" ref="AU18:AU22" si="38">SUM(AP18:AT18)</f>
+        <f t="shared" ref="AU18:AU22" si="42">SUM(AP18:AT18)</f>
         <v>761464717</v>
       </c>
       <c r="AW18" s="82">
-        <f>SUMIFS(ventas_unidades,ventas_vendedor,$A18,ventas_año,AW$16)</f>
+        <f t="shared" si="37"/>
         <v>45235</v>
       </c>
       <c r="AX18" s="46">
-        <f>SUMIFS(ventas_unidades,ventas_vendedor,$A18,ventas_año,AX$16)</f>
+        <f t="shared" si="37"/>
         <v>39435</v>
       </c>
       <c r="AY18" s="46">
-        <f>SUMIFS(ventas_unidades,ventas_vendedor,$A18,ventas_año,AY$16)</f>
+        <f t="shared" si="37"/>
         <v>40950</v>
       </c>
       <c r="AZ18" s="46">
-        <f>SUMIFS(ventas_unidades,ventas_vendedor,$A18,ventas_año,AZ$16)</f>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="BA18" s="46">
-        <f>SUMIFS(ventas_unidades,ventas_vendedor,$A18,ventas_año,BA$16)</f>
+        <f t="shared" si="37"/>
         <v>0</v>
       </c>
       <c r="BB18" s="46">
-        <f t="shared" ref="BB18:BB21" si="39">SUM(AW18:BA18)</f>
+        <f t="shared" ref="BB18:BB21" si="43">SUM(AW18:BA18)</f>
         <v>125620</v>
       </c>
       <c r="BD18" s="97">
-        <f>SUMIFS(ventas_total,ventas_vendedor,$A18,ventas_año,BD$8)</f>
+        <f t="shared" si="38"/>
         <v>275531995</v>
       </c>
       <c r="BE18" s="69">
-        <f>SUMIFS(ventas_total,ventas_vendedor,$A18,ventas_año,BE$8)</f>
+        <f t="shared" si="38"/>
         <v>271002529</v>
       </c>
       <c r="BF18" s="69">
-        <f>SUMIFS(ventas_total,ventas_vendedor,$A18,ventas_año,BF$8)</f>
+        <f t="shared" si="38"/>
         <v>214930193</v>
       </c>
       <c r="BG18" s="69">
-        <f>SUMIFS(ventas_total,ventas_vendedor,$A18,ventas_año,BG$8)</f>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="BH18" s="69">
-        <f>SUMIFS(ventas_total,ventas_vendedor,$A18,ventas_año,BH$8)</f>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
       <c r="BI18" s="69">
-        <f t="shared" ref="BI18:BI21" si="40">SUM(BD18:BH18)</f>
+        <f t="shared" ref="BI18:BI21" si="44">SUM(BD18:BH18)</f>
         <v>761464717</v>
       </c>
     </row>
@@ -8322,59 +8330,59 @@
         <v>11</v>
       </c>
       <c r="B19" s="31">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>32356</v>
       </c>
       <c r="C19" s="39">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>226722785</v>
       </c>
       <c r="E19" s="83">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>9125</v>
       </c>
       <c r="F19" s="19">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>9023</v>
       </c>
       <c r="G19" s="19">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>6969</v>
       </c>
       <c r="H19" s="19">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>2096</v>
       </c>
       <c r="I19" s="19">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>5143</v>
       </c>
       <c r="J19" s="19">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v>32356</v>
       </c>
       <c r="L19" s="98">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>59797810</v>
       </c>
       <c r="M19" s="60">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>63246530</v>
       </c>
       <c r="N19" s="60">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>40433106</v>
       </c>
       <c r="O19" s="60">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>31378227</v>
       </c>
       <c r="P19" s="60">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>31867112</v>
       </c>
       <c r="Q19" s="60">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v>226722785</v>
       </c>
       <c r="S19" s="93"/>
@@ -8392,99 +8400,99 @@
       <c r="AF19" s="67"/>
       <c r="AG19" s="67"/>
       <c r="AI19" s="83">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>9125</v>
       </c>
       <c r="AJ19" s="19">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>9023</v>
       </c>
       <c r="AK19" s="19">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>6969</v>
       </c>
       <c r="AL19" s="19">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>2096</v>
       </c>
       <c r="AM19" s="19">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>5143</v>
       </c>
       <c r="AN19" s="19">
+        <f t="shared" si="41"/>
+        <v>32356</v>
+      </c>
+      <c r="AP19" s="98">
+        <f t="shared" si="36"/>
+        <v>59797810</v>
+      </c>
+      <c r="AQ19" s="60">
+        <f t="shared" si="36"/>
+        <v>63246530</v>
+      </c>
+      <c r="AR19" s="60">
+        <f t="shared" si="36"/>
+        <v>40433106</v>
+      </c>
+      <c r="AS19" s="60">
+        <f t="shared" si="36"/>
+        <v>31378227</v>
+      </c>
+      <c r="AT19" s="60">
+        <f t="shared" si="36"/>
+        <v>31867112</v>
+      </c>
+      <c r="AU19" s="60">
+        <f t="shared" si="42"/>
+        <v>226722785</v>
+      </c>
+      <c r="AW19" s="83">
         <f t="shared" si="37"/>
+        <v>12423</v>
+      </c>
+      <c r="AX19" s="47">
+        <f t="shared" si="37"/>
+        <v>12194</v>
+      </c>
+      <c r="AY19" s="47">
+        <f t="shared" si="37"/>
+        <v>7739</v>
+      </c>
+      <c r="AZ19" s="47">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="BA19" s="47">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="BB19" s="47">
+        <f t="shared" si="43"/>
         <v>32356</v>
       </c>
-      <c r="AP19" s="98">
-        <f t="shared" si="34"/>
-        <v>59797810</v>
-      </c>
-      <c r="AQ19" s="60">
-        <f t="shared" si="34"/>
-        <v>63246530</v>
-      </c>
-      <c r="AR19" s="60">
-        <f t="shared" si="34"/>
-        <v>40433106</v>
-      </c>
-      <c r="AS19" s="60">
-        <f t="shared" si="34"/>
-        <v>31378227</v>
-      </c>
-      <c r="AT19" s="60">
-        <f t="shared" si="34"/>
-        <v>31867112</v>
-      </c>
-      <c r="AU19" s="60">
+      <c r="BD19" s="98">
         <f t="shared" si="38"/>
-        <v>226722785</v>
-      </c>
-      <c r="AW19" s="83">
-        <f>SUMIFS(ventas_unidades,ventas_vendedor,$A19,ventas_año,AW$16)</f>
-        <v>12423</v>
-      </c>
-      <c r="AX19" s="47">
-        <f>SUMIFS(ventas_unidades,ventas_vendedor,$A19,ventas_año,AX$16)</f>
-        <v>12194</v>
-      </c>
-      <c r="AY19" s="47">
-        <f>SUMIFS(ventas_unidades,ventas_vendedor,$A19,ventas_año,AY$16)</f>
-        <v>7739</v>
-      </c>
-      <c r="AZ19" s="47">
-        <f>SUMIFS(ventas_unidades,ventas_vendedor,$A19,ventas_año,AZ$16)</f>
+        <v>48322205</v>
+      </c>
+      <c r="BE19" s="70">
+        <f t="shared" si="38"/>
+        <v>131956162</v>
+      </c>
+      <c r="BF19" s="70">
+        <f t="shared" si="38"/>
+        <v>46444418</v>
+      </c>
+      <c r="BG19" s="70">
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
-      <c r="BA19" s="47">
-        <f>SUMIFS(ventas_unidades,ventas_vendedor,$A19,ventas_año,BA$16)</f>
+      <c r="BH19" s="70">
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
-      <c r="BB19" s="47">
-        <f t="shared" si="39"/>
-        <v>32356</v>
-      </c>
-      <c r="BD19" s="98">
-        <f>SUMIFS(ventas_total,ventas_vendedor,$A19,ventas_año,BD$8)</f>
-        <v>48322205</v>
-      </c>
-      <c r="BE19" s="70">
-        <f>SUMIFS(ventas_total,ventas_vendedor,$A19,ventas_año,BE$8)</f>
-        <v>131956162</v>
-      </c>
-      <c r="BF19" s="70">
-        <f>SUMIFS(ventas_total,ventas_vendedor,$A19,ventas_año,BF$8)</f>
-        <v>46444418</v>
-      </c>
-      <c r="BG19" s="70">
-        <f>SUMIFS(ventas_total,ventas_vendedor,$A19,ventas_año,BG$8)</f>
-        <v>0</v>
-      </c>
-      <c r="BH19" s="70">
-        <f>SUMIFS(ventas_total,ventas_vendedor,$A19,ventas_año,BH$8)</f>
-        <v>0</v>
-      </c>
       <c r="BI19" s="70">
-        <f t="shared" si="40"/>
+        <f t="shared" si="44"/>
         <v>226722785</v>
       </c>
     </row>
@@ -8493,59 +8501,59 @@
         <v>13</v>
       </c>
       <c r="B20" s="30">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>356297</v>
       </c>
       <c r="C20" s="38">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>312257691</v>
       </c>
       <c r="E20" s="82">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>21722</v>
       </c>
       <c r="F20" s="18">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>197836</v>
       </c>
       <c r="G20" s="18">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>18868</v>
       </c>
       <c r="H20" s="18">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>5457</v>
       </c>
       <c r="I20" s="18">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>112414</v>
       </c>
       <c r="J20" s="18">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v>356297</v>
       </c>
       <c r="L20" s="97">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>135280108</v>
       </c>
       <c r="M20" s="59">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>45710704</v>
       </c>
       <c r="N20" s="59">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>31481567</v>
       </c>
       <c r="O20" s="59">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>23001252</v>
       </c>
       <c r="P20" s="59">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>76784060</v>
       </c>
       <c r="Q20" s="59">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v>312257691</v>
       </c>
       <c r="S20" s="93"/>
@@ -8563,99 +8571,99 @@
       <c r="AF20" s="67"/>
       <c r="AG20" s="67"/>
       <c r="AI20" s="82">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>30665</v>
       </c>
       <c r="AJ20" s="18">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>103585</v>
       </c>
       <c r="AK20" s="18">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>9925</v>
       </c>
       <c r="AL20" s="18">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>197831</v>
       </c>
       <c r="AM20" s="18">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>14291</v>
       </c>
       <c r="AN20" s="18">
+        <f t="shared" si="41"/>
+        <v>356297</v>
+      </c>
+      <c r="AP20" s="97">
+        <f t="shared" si="36"/>
+        <v>139608342</v>
+      </c>
+      <c r="AQ20" s="59">
+        <f t="shared" si="36"/>
+        <v>44964557</v>
+      </c>
+      <c r="AR20" s="59">
+        <f t="shared" si="36"/>
+        <v>27153333</v>
+      </c>
+      <c r="AS20" s="59">
+        <f t="shared" si="36"/>
+        <v>23830600</v>
+      </c>
+      <c r="AT20" s="59">
+        <f t="shared" si="36"/>
+        <v>76700859</v>
+      </c>
+      <c r="AU20" s="59">
+        <f t="shared" si="42"/>
+        <v>312257691</v>
+      </c>
+      <c r="AW20" s="82">
         <f t="shared" si="37"/>
+        <v>20990</v>
+      </c>
+      <c r="AX20" s="46">
+        <f t="shared" si="37"/>
+        <v>11750</v>
+      </c>
+      <c r="AY20" s="46">
+        <f t="shared" si="37"/>
+        <v>24117</v>
+      </c>
+      <c r="AZ20" s="46">
+        <f t="shared" si="37"/>
+        <v>107066</v>
+      </c>
+      <c r="BA20" s="46">
+        <f t="shared" si="37"/>
+        <v>192374</v>
+      </c>
+      <c r="BB20" s="46">
+        <f t="shared" si="43"/>
         <v>356297</v>
       </c>
-      <c r="AP20" s="97">
-        <f t="shared" si="34"/>
-        <v>139608342</v>
-      </c>
-      <c r="AQ20" s="59">
-        <f t="shared" si="34"/>
-        <v>44964557</v>
-      </c>
-      <c r="AR20" s="59">
-        <f t="shared" si="34"/>
-        <v>27153333</v>
-      </c>
-      <c r="AS20" s="59">
-        <f t="shared" si="34"/>
-        <v>23830600</v>
-      </c>
-      <c r="AT20" s="59">
-        <f t="shared" si="34"/>
-        <v>76700859</v>
-      </c>
-      <c r="AU20" s="59">
+      <c r="BD20" s="97">
         <f t="shared" si="38"/>
-        <v>312257691</v>
-      </c>
-      <c r="AW20" s="82">
-        <f>SUMIFS(ventas_unidades,ventas_vendedor,$A20,ventas_año,AW$16)</f>
-        <v>20990</v>
-      </c>
-      <c r="AX20" s="46">
-        <f>SUMIFS(ventas_unidades,ventas_vendedor,$A20,ventas_año,AX$16)</f>
-        <v>11750</v>
-      </c>
-      <c r="AY20" s="46">
-        <f>SUMIFS(ventas_unidades,ventas_vendedor,$A20,ventas_año,AY$16)</f>
-        <v>24117</v>
-      </c>
-      <c r="AZ20" s="46">
-        <f>SUMIFS(ventas_unidades,ventas_vendedor,$A20,ventas_año,AZ$16)</f>
-        <v>107066</v>
-      </c>
-      <c r="BA20" s="46">
-        <f>SUMIFS(ventas_unidades,ventas_vendedor,$A20,ventas_año,BA$16)</f>
-        <v>192374</v>
-      </c>
-      <c r="BB20" s="46">
-        <f t="shared" si="39"/>
-        <v>356297</v>
-      </c>
-      <c r="BD20" s="97">
-        <f>SUMIFS(ventas_total,ventas_vendedor,$A20,ventas_año,BD$8)</f>
         <v>109777406</v>
       </c>
       <c r="BE20" s="69">
-        <f>SUMIFS(ventas_total,ventas_vendedor,$A20,ventas_año,BE$8)</f>
+        <f t="shared" si="38"/>
         <v>63876055</v>
       </c>
       <c r="BF20" s="69">
-        <f>SUMIFS(ventas_total,ventas_vendedor,$A20,ventas_año,BF$8)</f>
+        <f t="shared" si="38"/>
         <v>133363447</v>
       </c>
       <c r="BG20" s="69">
-        <f>SUMIFS(ventas_total,ventas_vendedor,$A20,ventas_año,BG$8)</f>
+        <f t="shared" si="38"/>
         <v>4411435</v>
       </c>
       <c r="BH20" s="69">
-        <f>SUMIFS(ventas_total,ventas_vendedor,$A20,ventas_año,BH$8)</f>
+        <f t="shared" si="38"/>
         <v>829348</v>
       </c>
       <c r="BI20" s="69">
-        <f t="shared" si="40"/>
+        <f t="shared" si="44"/>
         <v>312257691</v>
       </c>
     </row>
@@ -8664,59 +8672,59 @@
         <v>29</v>
       </c>
       <c r="B21" s="31">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>122295</v>
       </c>
       <c r="C21" s="39">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>722503562</v>
       </c>
       <c r="E21" s="83">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>18175</v>
       </c>
       <c r="F21" s="19">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>15576</v>
       </c>
       <c r="G21" s="19">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>10706</v>
       </c>
       <c r="H21" s="19">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>55164</v>
       </c>
       <c r="I21" s="19">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>22674</v>
       </c>
       <c r="J21" s="19">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v>122295</v>
       </c>
       <c r="L21" s="98">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>103659911</v>
       </c>
       <c r="M21" s="60">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>93604609</v>
       </c>
       <c r="N21" s="60">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>77744662</v>
       </c>
       <c r="O21" s="60">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>336958448</v>
       </c>
       <c r="P21" s="60">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>110535932</v>
       </c>
       <c r="Q21" s="60">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v>722503562</v>
       </c>
       <c r="S21" s="93"/>
@@ -8734,99 +8742,99 @@
       <c r="AF21" s="67"/>
       <c r="AG21" s="67"/>
       <c r="AI21" s="83">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>11047</v>
       </c>
       <c r="AJ21" s="19">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>25399</v>
       </c>
       <c r="AK21" s="19">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>12633</v>
       </c>
       <c r="AL21" s="19">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>53237</v>
       </c>
       <c r="AM21" s="19">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>19979</v>
       </c>
       <c r="AN21" s="19">
+        <f t="shared" si="41"/>
+        <v>122295</v>
+      </c>
+      <c r="AP21" s="98">
+        <f t="shared" si="36"/>
+        <v>94535993</v>
+      </c>
+      <c r="AQ21" s="60">
+        <f t="shared" si="36"/>
+        <v>93622843</v>
+      </c>
+      <c r="AR21" s="60">
+        <f t="shared" si="36"/>
+        <v>78668644</v>
+      </c>
+      <c r="AS21" s="60">
+        <f t="shared" si="36"/>
+        <v>336034466</v>
+      </c>
+      <c r="AT21" s="60">
+        <f t="shared" si="36"/>
+        <v>119641616</v>
+      </c>
+      <c r="AU21" s="60">
+        <f t="shared" si="42"/>
+        <v>722503562</v>
+      </c>
+      <c r="AW21" s="83">
         <f t="shared" si="37"/>
+        <v>44558</v>
+      </c>
+      <c r="AX21" s="47">
+        <f t="shared" si="37"/>
+        <v>27319</v>
+      </c>
+      <c r="AY21" s="47">
+        <f t="shared" si="37"/>
+        <v>31540</v>
+      </c>
+      <c r="AZ21" s="47">
+        <f t="shared" si="37"/>
+        <v>9823</v>
+      </c>
+      <c r="BA21" s="47">
+        <f t="shared" si="37"/>
+        <v>9055</v>
+      </c>
+      <c r="BB21" s="47">
+        <f t="shared" si="43"/>
         <v>122295</v>
       </c>
-      <c r="AP21" s="98">
-        <f t="shared" si="34"/>
-        <v>94535993</v>
-      </c>
-      <c r="AQ21" s="60">
-        <f t="shared" si="34"/>
-        <v>93622843</v>
-      </c>
-      <c r="AR21" s="60">
-        <f t="shared" si="34"/>
-        <v>78668644</v>
-      </c>
-      <c r="AS21" s="60">
-        <f t="shared" si="34"/>
-        <v>336034466</v>
-      </c>
-      <c r="AT21" s="60">
-        <f t="shared" si="34"/>
-        <v>119641616</v>
-      </c>
-      <c r="AU21" s="60">
+      <c r="BD21" s="98">
         <f t="shared" si="38"/>
-        <v>722503562</v>
-      </c>
-      <c r="AW21" s="83">
-        <f>SUMIFS(ventas_unidades,ventas_vendedor,$A21,ventas_año,AW$16)</f>
-        <v>44558</v>
-      </c>
-      <c r="AX21" s="47">
-        <f>SUMIFS(ventas_unidades,ventas_vendedor,$A21,ventas_año,AX$16)</f>
-        <v>27319</v>
-      </c>
-      <c r="AY21" s="47">
-        <f>SUMIFS(ventas_unidades,ventas_vendedor,$A21,ventas_año,AY$16)</f>
-        <v>31540</v>
-      </c>
-      <c r="AZ21" s="47">
-        <f>SUMIFS(ventas_unidades,ventas_vendedor,$A21,ventas_año,AZ$16)</f>
-        <v>9823</v>
-      </c>
-      <c r="BA21" s="47">
-        <f>SUMIFS(ventas_unidades,ventas_vendedor,$A21,ventas_año,BA$16)</f>
-        <v>9055</v>
-      </c>
-      <c r="BB21" s="47">
-        <f t="shared" si="39"/>
-        <v>122295</v>
-      </c>
-      <c r="BD21" s="98">
-        <f>SUMIFS(ventas_total,ventas_vendedor,$A21,ventas_año,BD$8)</f>
         <v>223098228</v>
       </c>
       <c r="BE21" s="70">
-        <f>SUMIFS(ventas_total,ventas_vendedor,$A21,ventas_año,BE$8)</f>
+        <f t="shared" si="38"/>
         <v>217807965</v>
       </c>
       <c r="BF21" s="70">
-        <f>SUMIFS(ventas_total,ventas_vendedor,$A21,ventas_año,BF$8)</f>
+        <f t="shared" si="38"/>
         <v>271531235</v>
       </c>
       <c r="BG21" s="70">
-        <f>SUMIFS(ventas_total,ventas_vendedor,$A21,ventas_año,BG$8)</f>
+        <f t="shared" si="38"/>
         <v>18234</v>
       </c>
       <c r="BH21" s="70">
-        <f>SUMIFS(ventas_total,ventas_vendedor,$A21,ventas_año,BH$8)</f>
+        <f t="shared" si="38"/>
         <v>10047900</v>
       </c>
       <c r="BI21" s="70">
-        <f t="shared" si="40"/>
+        <f t="shared" si="44"/>
         <v>722503562</v>
       </c>
     </row>
@@ -8835,59 +8843,59 @@
         <v>30</v>
       </c>
       <c r="B22" s="30">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>99994</v>
       </c>
       <c r="C22" s="38">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>561953724</v>
       </c>
       <c r="E22" s="87">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>11460</v>
       </c>
       <c r="F22" s="51">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>16505</v>
       </c>
       <c r="G22" s="51">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>25030</v>
       </c>
       <c r="H22" s="51">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>5584</v>
       </c>
       <c r="I22" s="51">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>41415</v>
       </c>
       <c r="J22" s="51">
-        <f t="shared" si="35"/>
+        <f t="shared" si="39"/>
         <v>99994</v>
       </c>
       <c r="L22" s="101">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>49438827</v>
       </c>
       <c r="M22" s="57">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>50806730</v>
       </c>
       <c r="N22" s="57">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>167729464</v>
       </c>
       <c r="O22" s="57">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>17788927</v>
       </c>
       <c r="P22" s="57">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>276189776</v>
       </c>
       <c r="Q22" s="57">
-        <f t="shared" si="36"/>
+        <f t="shared" si="40"/>
         <v>561953724</v>
       </c>
       <c r="S22" s="93"/>
@@ -8905,100 +8913,99 @@
       <c r="AF22" s="67"/>
       <c r="AG22" s="67"/>
       <c r="AI22" s="82">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>8851</v>
       </c>
       <c r="AJ22" s="18">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>16505</v>
       </c>
       <c r="AK22" s="18">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>27768</v>
       </c>
       <c r="AL22" s="18">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>7382</v>
       </c>
       <c r="AM22" s="18">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>39488</v>
       </c>
       <c r="AN22" s="18">
+        <f t="shared" si="41"/>
+        <v>99994</v>
+      </c>
+      <c r="AP22" s="97">
+        <f t="shared" si="36"/>
+        <v>49797905</v>
+      </c>
+      <c r="AQ22" s="59">
+        <f t="shared" si="36"/>
+        <v>50806730</v>
+      </c>
+      <c r="AR22" s="59">
+        <f t="shared" si="36"/>
+        <v>168574296</v>
+      </c>
+      <c r="AS22" s="59">
+        <f t="shared" si="36"/>
+        <v>17133409</v>
+      </c>
+      <c r="AT22" s="59">
+        <f t="shared" si="36"/>
+        <v>275641384</v>
+      </c>
+      <c r="AU22" s="59">
+        <f t="shared" si="42"/>
+        <v>561953724</v>
+      </c>
+      <c r="AW22" s="126">
         <f t="shared" si="37"/>
+        <v>25153</v>
+      </c>
+      <c r="AX22" s="78">
+        <f t="shared" si="37"/>
+        <v>33627</v>
+      </c>
+      <c r="AY22" s="78">
+        <f t="shared" si="37"/>
+        <v>36420</v>
+      </c>
+      <c r="AZ22" s="78">
+        <f t="shared" si="37"/>
+        <v>2867</v>
+      </c>
+      <c r="BA22" s="78">
+        <f t="shared" si="37"/>
+        <v>1927</v>
+      </c>
+      <c r="BB22" s="78">
+        <f t="shared" ref="BB22" si="45">SUM(AW22:BA22)</f>
         <v>99994</v>
       </c>
-      <c r="AP22" s="97">
-        <f t="shared" si="34"/>
-        <v>49797905</v>
-      </c>
-      <c r="AQ22" s="59">
-        <f t="shared" si="34"/>
-        <v>50806730</v>
-      </c>
-      <c r="AR22" s="59">
-        <f t="shared" si="34"/>
-        <v>168574296</v>
-      </c>
-      <c r="AS22" s="59">
-        <f t="shared" si="34"/>
-        <v>17133409</v>
-      </c>
-      <c r="AT22" s="59">
-        <f t="shared" si="34"/>
-        <v>275641384</v>
-      </c>
-      <c r="AU22" s="59">
+      <c r="BD22" s="127">
         <f t="shared" si="38"/>
-        <v>561953724</v>
-      </c>
-      <c r="AW22" s="126">
-        <f>SUMIFS(ventas_unidades,ventas_vendedor,$A22,ventas_año,AW$16)</f>
-        <v>25153</v>
-      </c>
-      <c r="AX22" s="78">
-        <f>SUMIFS(ventas_unidades,ventas_vendedor,$A22,ventas_año,AX$16)</f>
-        <v>33627</v>
-      </c>
-      <c r="AY22" s="78">
-        <f>SUMIFS(ventas_unidades,ventas_vendedor,$A22,ventas_año,AY$16)</f>
-        <v>36420</v>
-      </c>
-      <c r="AZ22" s="78">
-        <f>SUMIFS(ventas_unidades,ventas_vendedor,$A22,ventas_año,AZ$16)</f>
-        <v>2867</v>
-      </c>
-      <c r="BA22" s="78">
-        <f>SUMIFS(ventas_unidades,ventas_vendedor,$A22,ventas_año,BA$16)</f>
-        <v>1927</v>
-      </c>
-      <c r="BB22" s="78">
-        <f t="shared" ref="BB22" si="41">SUM(AW22:BA22)</f>
-        <v>99994</v>
-      </c>
-      <c r="BC22" s="127"/>
-      <c r="BD22" s="128">
-        <f>SUMIFS(ventas_total,ventas_vendedor,$A22,ventas_año,BD$8)</f>
         <v>175466052</v>
       </c>
-      <c r="BE22" s="129">
-        <f>SUMIFS(ventas_total,ventas_vendedor,$A22,ventas_año,BE$8)</f>
+      <c r="BE22" s="128">
+        <f t="shared" si="38"/>
         <v>177412674</v>
       </c>
-      <c r="BF22" s="129">
-        <f>SUMIFS(ventas_total,ventas_vendedor,$A22,ventas_año,BF$8)</f>
+      <c r="BF22" s="128">
+        <f t="shared" si="38"/>
         <v>206477864</v>
       </c>
-      <c r="BG22" s="129">
-        <f>SUMIFS(ventas_total,ventas_vendedor,$A22,ventas_año,BG$8)</f>
+      <c r="BG22" s="128">
+        <f t="shared" si="38"/>
         <v>2048742</v>
       </c>
-      <c r="BH22" s="129">
-        <f>SUMIFS(ventas_total,ventas_vendedor,$A22,ventas_año,BH$8)</f>
+      <c r="BH22" s="128">
+        <f t="shared" si="38"/>
         <v>548392</v>
       </c>
-      <c r="BI22" s="129">
-        <f t="shared" ref="BI22" si="42">SUM(BD22:BH22)</f>
+      <c r="BI22" s="128">
+        <f t="shared" ref="BI22" si="46">SUM(BD22:BH22)</f>
         <v>561953724</v>
       </c>
     </row>
@@ -9019,23 +9026,23 @@
         <v>110903</v>
       </c>
       <c r="F23" s="50">
-        <f t="shared" ref="F23:J23" si="43">SUM(F17:F22)</f>
+        <f t="shared" ref="F23:J23" si="47">SUM(F17:F22)</f>
         <v>304519</v>
       </c>
       <c r="G23" s="50">
-        <f t="shared" si="43"/>
+        <f t="shared" si="47"/>
         <v>118380</v>
       </c>
       <c r="H23" s="50">
-        <f t="shared" si="43"/>
+        <f t="shared" si="47"/>
         <v>115644</v>
       </c>
       <c r="I23" s="50">
-        <f t="shared" si="43"/>
+        <f t="shared" si="47"/>
         <v>208781</v>
       </c>
       <c r="J23" s="117">
-        <f t="shared" si="43"/>
+        <f t="shared" si="47"/>
         <v>858227</v>
       </c>
       <c r="L23" s="108">
@@ -9043,23 +9050,23 @@
         <v>650543568</v>
       </c>
       <c r="M23" s="68">
-        <f t="shared" ref="M23:Q23" si="44">SUM(M17:M22)</f>
+        <f t="shared" ref="M23:Q23" si="48">SUM(M17:M22)</f>
         <v>578124392</v>
       </c>
       <c r="N23" s="68">
-        <f t="shared" si="44"/>
+        <f t="shared" si="48"/>
         <v>690157736</v>
       </c>
       <c r="O23" s="68">
-        <f t="shared" si="44"/>
+        <f t="shared" si="48"/>
         <v>654943915</v>
       </c>
       <c r="P23" s="68">
-        <f t="shared" si="44"/>
+        <f t="shared" si="48"/>
         <v>656247934</v>
       </c>
       <c r="Q23" s="114">
-        <f t="shared" si="44"/>
+        <f t="shared" si="48"/>
         <v>3230017545</v>
       </c>
       <c r="S23" s="93"/>
@@ -9081,23 +9088,23 @@
         <v>110109</v>
       </c>
       <c r="AJ23" s="50">
-        <f t="shared" ref="AJ23:AN23" si="45">SUM(AJ17:AJ22)</f>
+        <f t="shared" ref="AJ23:AN23" si="49">SUM(AJ17:AJ22)</f>
         <v>213260</v>
       </c>
       <c r="AK23" s="50">
-        <f t="shared" si="45"/>
+        <f t="shared" si="49"/>
         <v>116030</v>
       </c>
       <c r="AL23" s="50">
-        <f t="shared" si="45"/>
+        <f t="shared" si="49"/>
         <v>312792</v>
       </c>
       <c r="AM23" s="50">
-        <f t="shared" si="45"/>
+        <f t="shared" si="49"/>
         <v>106036</v>
       </c>
       <c r="AN23" s="117">
-        <f t="shared" si="45"/>
+        <f t="shared" si="49"/>
         <v>858227</v>
       </c>
       <c r="AP23" s="108">
@@ -9105,23 +9112,23 @@
         <v>646106962</v>
       </c>
       <c r="AQ23" s="68">
-        <f t="shared" ref="AQ23" si="46">SUM(AQ17:AQ22)</f>
+        <f t="shared" ref="AQ23" si="50">SUM(AQ17:AQ22)</f>
         <v>576804336</v>
       </c>
       <c r="AR23" s="68">
-        <f t="shared" ref="AR23" si="47">SUM(AR17:AR22)</f>
+        <f t="shared" ref="AR23" si="51">SUM(AR17:AR22)</f>
         <v>687706530</v>
       </c>
       <c r="AS23" s="68">
-        <f t="shared" ref="AS23" si="48">SUM(AS17:AS22)</f>
+        <f t="shared" ref="AS23" si="52">SUM(AS17:AS22)</f>
         <v>654677692</v>
       </c>
       <c r="AT23" s="68">
-        <f t="shared" ref="AT23" si="49">SUM(AT17:AT22)</f>
+        <f t="shared" ref="AT23" si="53">SUM(AT17:AT22)</f>
         <v>664722025</v>
       </c>
       <c r="AU23" s="114">
-        <f t="shared" ref="AU23" si="50">SUM(AU17:AU22)</f>
+        <f t="shared" ref="AU23" si="54">SUM(AU17:AU22)</f>
         <v>3230017545</v>
       </c>
       <c r="AW23" s="94">
@@ -9149,27 +9156,27 @@
         <v>758233</v>
       </c>
       <c r="BD23" s="108">
-        <f>SUM(BD17:BD21)</f>
+        <f t="shared" ref="BD23:BI23" si="55">SUM(BD17:BD21)</f>
         <v>831778099</v>
       </c>
       <c r="BE23" s="68">
-        <f>SUM(BE17:BE21)</f>
+        <f t="shared" si="55"/>
         <v>929433798</v>
       </c>
       <c r="BF23" s="68">
-        <f>SUM(BF17:BF21)</f>
+        <f t="shared" si="55"/>
         <v>882832483</v>
       </c>
       <c r="BG23" s="68">
-        <f>SUM(BG17:BG21)</f>
+        <f t="shared" si="55"/>
         <v>13033979</v>
       </c>
       <c r="BH23" s="68">
-        <f>SUM(BH17:BH21)</f>
+        <f t="shared" si="55"/>
         <v>10985462</v>
       </c>
       <c r="BI23" s="114">
-        <f>SUM(BI17:BI21)</f>
+        <f t="shared" si="55"/>
         <v>2668063821</v>
       </c>
     </row>
@@ -9325,47 +9332,47 @@
         <v>646106962</v>
       </c>
       <c r="E26" s="81">
-        <f t="shared" ref="E26:I30" si="51">SUMIFS(ventas_unidades,ventas_region,$A26,ventas_producto,E$25)</f>
+        <f>SUMIFS(ventas_unidades,ventas_region,$A26,ventas_producto,E$25)</f>
         <v>101037</v>
       </c>
       <c r="F26" s="17">
-        <f t="shared" si="51"/>
+        <f>SUMIFS(ventas_unidades,ventas_region,$A26,ventas_producto,F$25)</f>
         <v>0</v>
       </c>
       <c r="G26" s="17">
-        <f t="shared" si="51"/>
+        <f>SUMIFS(ventas_unidades,ventas_region,$A26,ventas_producto,G$25)</f>
         <v>8943</v>
       </c>
       <c r="H26" s="17">
-        <f t="shared" si="51"/>
+        <f>SUMIFS(ventas_unidades,ventas_region,$A26,ventas_producto,H$25)</f>
         <v>129</v>
       </c>
       <c r="I26" s="17">
-        <f t="shared" si="51"/>
+        <f>SUMIFS(ventas_unidades,ventas_region,$A26,ventas_producto,I$25)</f>
         <v>0</v>
       </c>
       <c r="J26" s="17">
-        <f>SUM(E26:I30)</f>
-        <v>858227</v>
+        <f>SUM(E26:I26)</f>
+        <v>110109</v>
       </c>
       <c r="L26" s="96">
-        <f t="shared" ref="L26:P30" si="52">SUMIFS(ventas_total,ventas_region,$A26,ventas_producto,L$25)</f>
+        <f t="shared" ref="L26:P30" si="56">SUMIFS(ventas_total,ventas_region,$A26,ventas_producto,L$25)</f>
         <v>640574818</v>
       </c>
       <c r="M26" s="58">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="N26" s="58">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v>4328234</v>
       </c>
       <c r="O26" s="58">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v>1203910</v>
       </c>
       <c r="P26" s="58">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="Q26" s="58">
@@ -9373,27 +9380,27 @@
         <v>646106962</v>
       </c>
       <c r="S26" s="81">
-        <f t="shared" ref="S26:X30" si="53">SUMIFS(ventas_unidades,ventas_region,$A26,ventas_vendedor,S$25)</f>
+        <f t="shared" ref="S26:X30" si="57">SUMIFS(ventas_unidades,ventas_region,$A26,ventas_vendedor,S$25)</f>
         <v>23075</v>
       </c>
       <c r="T26" s="29">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v>27346</v>
       </c>
       <c r="U26" s="29">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v>9125</v>
       </c>
       <c r="V26" s="17">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v>30665</v>
       </c>
       <c r="W26" s="29">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v>11047</v>
       </c>
       <c r="X26" s="29">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v>8851</v>
       </c>
       <c r="Y26" s="17">
@@ -9401,27 +9408,27 @@
         <v>110109</v>
       </c>
       <c r="AA26" s="96">
-        <f t="shared" ref="AA26:AF30" si="54">SUMIFS(ventas_total,ventas_region,$A26,ventas_vendedor,AA$25)</f>
+        <f t="shared" ref="AA26:AF30" si="58">SUMIFS(ventas_total,ventas_region,$A26,ventas_vendedor,AA$25)</f>
         <v>109144041</v>
       </c>
       <c r="AB26" s="63">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v>193222871</v>
       </c>
       <c r="AC26" s="63">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v>59797810</v>
       </c>
       <c r="AD26" s="58">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v>139608342</v>
       </c>
       <c r="AE26" s="63">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v>94535993</v>
       </c>
       <c r="AF26" s="63">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v>49797905</v>
       </c>
       <c r="AG26" s="58">
@@ -9441,23 +9448,23 @@
       <c r="AT26" s="49"/>
       <c r="AU26" s="49"/>
       <c r="AW26" s="81">
-        <f>SUMIFS(ventas_unidades,ventas_region,$A26,ventas_año,AW$8)</f>
+        <f t="shared" ref="AW26:BA30" si="59">SUMIFS(ventas_unidades,ventas_region,$A26,ventas_año,AW$8)</f>
         <v>33032</v>
       </c>
       <c r="AX26" s="17">
-        <f>SUMIFS(ventas_unidades,ventas_region,$A26,ventas_año,AX$8)</f>
+        <f t="shared" si="59"/>
         <v>32671</v>
       </c>
       <c r="AY26" s="17">
-        <f>SUMIFS(ventas_unidades,ventas_region,$A26,ventas_año,AY$8)</f>
+        <f t="shared" si="59"/>
         <v>35334</v>
       </c>
       <c r="AZ26" s="17">
-        <f>SUMIFS(ventas_unidades,ventas_region,$A26,ventas_año,AZ$8)</f>
+        <f t="shared" si="59"/>
         <v>9072</v>
       </c>
       <c r="BA26" s="17">
-        <f>SUMIFS(ventas_unidades,ventas_region,$A26,ventas_año,BA$8)</f>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="BB26" s="17">
@@ -9465,23 +9472,23 @@
         <v>110109</v>
       </c>
       <c r="BD26" s="96">
-        <f>SUMIFS(ventas_total,ventas_region,$A26,ventas_año,BD$8)</f>
+        <f t="shared" ref="BD26:BH30" si="60">SUMIFS(ventas_total,ventas_region,$A26,ventas_año,BD$8)</f>
         <v>218669111</v>
       </c>
       <c r="BE26" s="58">
-        <f>SUMIFS(ventas_total,ventas_region,$A26,ventas_año,BE$8)</f>
+        <f t="shared" si="60"/>
         <v>203341463</v>
       </c>
       <c r="BF26" s="58">
-        <f>SUMIFS(ventas_total,ventas_region,$A26,ventas_año,BF$8)</f>
+        <f t="shared" si="60"/>
         <v>218564244</v>
       </c>
       <c r="BG26" s="58">
-        <f>SUMIFS(ventas_total,ventas_region,$A26,ventas_año,BG$8)</f>
+        <f t="shared" si="60"/>
         <v>5532144</v>
       </c>
       <c r="BH26" s="58">
-        <f>SUMIFS(ventas_total,ventas_region,$A26,ventas_año,BH$8)</f>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="BI26" s="58">
@@ -9502,107 +9509,107 @@
         <v>576804336</v>
       </c>
       <c r="E27" s="82">
-        <f t="shared" si="51"/>
+        <f>SUMIFS(ventas_unidades,ventas_region,$A27,ventas_producto,E$25)</f>
         <v>0</v>
       </c>
       <c r="F27" s="18">
-        <f t="shared" si="51"/>
+        <f>SUMIFS(ventas_unidades,ventas_region,$A27,ventas_producto,F$25)</f>
         <v>105314</v>
       </c>
       <c r="G27" s="18">
-        <f t="shared" si="51"/>
+        <f>SUMIFS(ventas_unidades,ventas_region,$A27,ventas_producto,G$25)</f>
         <v>0</v>
       </c>
       <c r="H27" s="18">
-        <f t="shared" si="51"/>
+        <f>SUMIFS(ventas_unidades,ventas_region,$A27,ventas_producto,H$25)</f>
         <v>0</v>
       </c>
       <c r="I27" s="18">
-        <f t="shared" si="51"/>
+        <f>SUMIFS(ventas_unidades,ventas_region,$A27,ventas_producto,I$25)</f>
         <v>107946</v>
       </c>
       <c r="J27" s="18">
-        <f t="shared" ref="J27:J30" si="55">SUM(E27:I31)</f>
-        <v>1606345</v>
+        <f t="shared" ref="J27:J30" si="61">SUM(E27:I27)</f>
+        <v>213260</v>
       </c>
       <c r="L27" s="97">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="M27" s="59">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v>576702901</v>
       </c>
       <c r="N27" s="59">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="O27" s="59">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="P27" s="59">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v>101435</v>
       </c>
       <c r="Q27" s="59">
-        <f t="shared" ref="Q27:Q30" si="56">SUM(L27:P27)</f>
+        <f t="shared" ref="Q27:Q30" si="62">SUM(L27:P27)</f>
         <v>576804336</v>
       </c>
       <c r="S27" s="90">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v>7195</v>
       </c>
       <c r="T27" s="30">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v>51553</v>
       </c>
       <c r="U27" s="30">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v>9023</v>
       </c>
       <c r="V27" s="30">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v>103585</v>
       </c>
       <c r="W27" s="30">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v>25399</v>
       </c>
       <c r="X27" s="30">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v>16505</v>
       </c>
       <c r="Y27" s="30">
-        <f t="shared" ref="Y27:Y30" si="57">SUM(S27:X27)</f>
+        <f t="shared" ref="Y27:Y30" si="63">SUM(S27:X27)</f>
         <v>213260</v>
       </c>
       <c r="AA27" s="104">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v>52631529</v>
       </c>
       <c r="AB27" s="64">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v>271532147</v>
       </c>
       <c r="AC27" s="64">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v>63246530</v>
       </c>
       <c r="AD27" s="64">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v>44964557</v>
       </c>
       <c r="AE27" s="64">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v>93622843</v>
       </c>
       <c r="AF27" s="64">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v>50806730</v>
       </c>
       <c r="AG27" s="64">
-        <f t="shared" ref="AG27:AG30" si="58">SUM(AA27:AF27)</f>
+        <f t="shared" ref="AG27:AG30" si="64">SUM(AA27:AF27)</f>
         <v>576804336</v>
       </c>
       <c r="AI27" s="93"/>
@@ -9618,51 +9625,51 @@
       <c r="AT27" s="49"/>
       <c r="AU27" s="49"/>
       <c r="AW27" s="82">
-        <f>SUMIFS(ventas_unidades,ventas_region,$A27,ventas_año,AW$8)</f>
+        <f t="shared" si="59"/>
         <v>32696</v>
       </c>
       <c r="AX27" s="46">
-        <f>SUMIFS(ventas_unidades,ventas_region,$A27,ventas_año,AX$8)</f>
+        <f t="shared" si="59"/>
         <v>31651</v>
       </c>
       <c r="AY27" s="46">
-        <f>SUMIFS(ventas_unidades,ventas_region,$A27,ventas_año,AY$8)</f>
+        <f t="shared" si="59"/>
         <v>40967</v>
       </c>
       <c r="AZ27" s="46">
-        <f>SUMIFS(ventas_unidades,ventas_region,$A27,ventas_año,AZ$8)</f>
+        <f t="shared" si="59"/>
         <v>107946</v>
       </c>
       <c r="BA27" s="46">
-        <f>SUMIFS(ventas_unidades,ventas_region,$A27,ventas_año,BA$8)</f>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="BB27" s="46">
-        <f t="shared" ref="BB27:BB30" si="59">SUM(AW27:BA27)</f>
+        <f t="shared" ref="BB27:BB30" si="65">SUM(AW27:BA27)</f>
         <v>213260</v>
       </c>
       <c r="BD27" s="97">
-        <f>SUMIFS(ventas_total,ventas_region,$A27,ventas_año,BD$8)</f>
+        <f t="shared" si="60"/>
         <v>160364763</v>
       </c>
       <c r="BE27" s="69">
-        <f>SUMIFS(ventas_total,ventas_region,$A27,ventas_año,BE$8)</f>
+        <f t="shared" si="60"/>
         <v>201880917</v>
       </c>
       <c r="BF27" s="69">
-        <f>SUMIFS(ventas_total,ventas_region,$A27,ventas_año,BF$8)</f>
+        <f t="shared" si="60"/>
         <v>214457221</v>
       </c>
       <c r="BG27" s="69">
-        <f>SUMIFS(ventas_total,ventas_region,$A27,ventas_año,BG$8)</f>
+        <f t="shared" si="60"/>
         <v>101435</v>
       </c>
       <c r="BH27" s="69">
-        <f>SUMIFS(ventas_total,ventas_region,$A27,ventas_año,BH$8)</f>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="BI27" s="69">
-        <f t="shared" ref="BI27:BI30" si="60">SUM(BD27:BH27)</f>
+        <f t="shared" ref="BI27:BI30" si="66">SUM(BD27:BH27)</f>
         <v>576804336</v>
       </c>
     </row>
@@ -9679,107 +9686,107 @@
         <v>687706530</v>
       </c>
       <c r="E28" s="83">
-        <f t="shared" si="51"/>
+        <f>SUMIFS(ventas_unidades,ventas_region,$A28,ventas_producto,E$25)</f>
         <v>2738</v>
       </c>
       <c r="F28" s="19">
-        <f t="shared" si="51"/>
+        <f>SUMIFS(ventas_unidades,ventas_region,$A28,ventas_producto,F$25)</f>
         <v>1928</v>
       </c>
       <c r="G28" s="19">
-        <f t="shared" si="51"/>
+        <f>SUMIFS(ventas_unidades,ventas_region,$A28,ventas_producto,G$25)</f>
         <v>109437</v>
       </c>
       <c r="H28" s="19">
-        <f t="shared" si="51"/>
+        <f>SUMIFS(ventas_unidades,ventas_region,$A28,ventas_producto,H$25)</f>
         <v>1927</v>
       </c>
       <c r="I28" s="19">
-        <f t="shared" si="51"/>
+        <f>SUMIFS(ventas_unidades,ventas_region,$A28,ventas_producto,I$25)</f>
         <v>0</v>
       </c>
       <c r="J28" s="19">
-        <f t="shared" si="55"/>
-        <v>1393085</v>
+        <f t="shared" si="61"/>
+        <v>116030</v>
       </c>
       <c r="L28" s="98">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v>844832</v>
       </c>
       <c r="M28" s="60">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v>108214</v>
       </c>
       <c r="N28" s="60">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v>685829502</v>
       </c>
       <c r="O28" s="60">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v>923982</v>
       </c>
       <c r="P28" s="60">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="Q28" s="60">
-        <f t="shared" si="56"/>
+        <f t="shared" si="62"/>
         <v>687706530</v>
       </c>
       <c r="S28" s="91">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v>39170</v>
       </c>
       <c r="T28" s="31">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v>19565</v>
       </c>
       <c r="U28" s="31">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v>6969</v>
       </c>
       <c r="V28" s="31">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v>9925</v>
       </c>
       <c r="W28" s="31">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v>12633</v>
       </c>
       <c r="X28" s="31">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v>27768</v>
       </c>
       <c r="Y28" s="31">
-        <f t="shared" si="57"/>
+        <f t="shared" si="63"/>
         <v>116030</v>
       </c>
       <c r="AA28" s="105">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v>240927099</v>
       </c>
       <c r="AB28" s="65">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v>131950052</v>
       </c>
       <c r="AC28" s="65">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v>40433106</v>
       </c>
       <c r="AD28" s="65">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v>27153333</v>
       </c>
       <c r="AE28" s="65">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v>78668644</v>
       </c>
       <c r="AF28" s="65">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v>168574296</v>
       </c>
       <c r="AG28" s="65">
-        <f t="shared" si="58"/>
+        <f t="shared" si="64"/>
         <v>687706530</v>
       </c>
       <c r="AI28" s="93"/>
@@ -9795,51 +9802,51 @@
       <c r="AT28" s="49"/>
       <c r="AU28" s="49"/>
       <c r="AW28" s="83">
-        <f>SUMIFS(ventas_unidades,ventas_region,$A28,ventas_año,AW$8)</f>
+        <f t="shared" si="59"/>
         <v>39124</v>
       </c>
       <c r="AX28" s="47">
-        <f>SUMIFS(ventas_unidades,ventas_region,$A28,ventas_año,AX$8)</f>
+        <f t="shared" si="59"/>
         <v>34000</v>
       </c>
       <c r="AY28" s="47">
-        <f>SUMIFS(ventas_unidades,ventas_region,$A28,ventas_año,AY$8)</f>
+        <f t="shared" si="59"/>
         <v>31330</v>
       </c>
       <c r="AZ28" s="47">
-        <f>SUMIFS(ventas_unidades,ventas_region,$A28,ventas_año,AZ$8)</f>
+        <f t="shared" si="59"/>
         <v>7721</v>
       </c>
       <c r="BA28" s="47">
-        <f>SUMIFS(ventas_unidades,ventas_region,$A28,ventas_año,BA$8)</f>
+        <f t="shared" si="59"/>
         <v>3855</v>
       </c>
       <c r="BB28" s="47">
-        <f t="shared" si="59"/>
+        <f t="shared" si="65"/>
         <v>116030</v>
       </c>
       <c r="BD28" s="98">
-        <f>SUMIFS(ventas_total,ventas_region,$A28,ventas_año,BD$8)</f>
+        <f t="shared" si="60"/>
         <v>220801841</v>
       </c>
       <c r="BE28" s="70">
-        <f>SUMIFS(ventas_total,ventas_region,$A28,ventas_año,BE$8)</f>
+        <f t="shared" si="60"/>
         <v>239992813</v>
       </c>
       <c r="BF28" s="70">
-        <f>SUMIFS(ventas_total,ventas_region,$A28,ventas_año,BF$8)</f>
+        <f t="shared" si="60"/>
         <v>216914467</v>
       </c>
       <c r="BG28" s="70">
-        <f>SUMIFS(ventas_total,ventas_region,$A28,ventas_año,BG$8)</f>
+        <f t="shared" si="60"/>
         <v>8965213</v>
       </c>
       <c r="BH28" s="70">
-        <f>SUMIFS(ventas_total,ventas_region,$A28,ventas_año,BH$8)</f>
+        <f t="shared" si="60"/>
         <v>1032196</v>
       </c>
       <c r="BI28" s="70">
-        <f t="shared" si="60"/>
+        <f t="shared" si="66"/>
         <v>687706530</v>
       </c>
     </row>
@@ -9856,107 +9863,107 @@
         <v>654677692</v>
       </c>
       <c r="E29" s="82">
-        <f t="shared" si="51"/>
+        <f>SUMIFS(ventas_unidades,ventas_region,$A29,ventas_producto,E$25)</f>
         <v>0</v>
       </c>
       <c r="F29" s="18">
-        <f t="shared" si="51"/>
+        <f>SUMIFS(ventas_unidades,ventas_region,$A29,ventas_producto,F$25)</f>
         <v>197277</v>
       </c>
       <c r="G29" s="18">
-        <f t="shared" si="51"/>
+        <f>SUMIFS(ventas_unidades,ventas_region,$A29,ventas_producto,G$25)</f>
         <v>0</v>
       </c>
       <c r="H29" s="18">
-        <f t="shared" si="51"/>
+        <f>SUMIFS(ventas_unidades,ventas_region,$A29,ventas_producto,H$25)</f>
         <v>113588</v>
       </c>
       <c r="I29" s="18">
-        <f t="shared" si="51"/>
+        <f>SUMIFS(ventas_unidades,ventas_region,$A29,ventas_producto,I$25)</f>
         <v>1927</v>
       </c>
       <c r="J29" s="18">
-        <f t="shared" si="55"/>
-        <v>1277055</v>
+        <f t="shared" si="61"/>
+        <v>312792</v>
       </c>
       <c r="L29" s="97">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="M29" s="59">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v>1313277</v>
       </c>
       <c r="N29" s="59">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="O29" s="59">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v>652816023</v>
       </c>
       <c r="P29" s="59">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v>548392</v>
       </c>
       <c r="Q29" s="59">
-        <f t="shared" si="56"/>
+        <f t="shared" si="62"/>
         <v>654677692</v>
       </c>
       <c r="S29" s="90">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v>39255</v>
       </c>
       <c r="T29" s="30">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v>12991</v>
       </c>
       <c r="U29" s="30">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v>2096</v>
       </c>
       <c r="V29" s="30">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v>197831</v>
       </c>
       <c r="W29" s="30">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v>53237</v>
       </c>
       <c r="X29" s="30">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v>7382</v>
       </c>
       <c r="Y29" s="30">
-        <f t="shared" si="57"/>
+        <f t="shared" si="63"/>
         <v>312792</v>
       </c>
       <c r="AA29" s="104">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v>170461858</v>
       </c>
       <c r="AB29" s="64">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v>75839132</v>
       </c>
       <c r="AC29" s="64">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v>31378227</v>
       </c>
       <c r="AD29" s="64">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v>23830600</v>
       </c>
       <c r="AE29" s="64">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v>336034466</v>
       </c>
       <c r="AF29" s="64">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v>17133409</v>
       </c>
       <c r="AG29" s="64">
-        <f t="shared" si="58"/>
+        <f t="shared" si="64"/>
         <v>654677692</v>
       </c>
       <c r="AI29" s="93"/>
@@ -9972,51 +9979,51 @@
       <c r="AT29" s="49"/>
       <c r="AU29" s="49"/>
       <c r="AW29" s="82">
-        <f>SUMIFS(ventas_unidades,ventas_region,$A29,ventas_año,AW$8)</f>
+        <f t="shared" si="59"/>
         <v>40573</v>
       </c>
       <c r="AX29" s="46">
-        <f>SUMIFS(ventas_unidades,ventas_region,$A29,ventas_año,AX$8)</f>
+        <f t="shared" si="59"/>
         <v>39442</v>
       </c>
       <c r="AY29" s="46">
-        <f>SUMIFS(ventas_unidades,ventas_region,$A29,ventas_año,AY$8)</f>
+        <f t="shared" si="59"/>
         <v>33573</v>
       </c>
       <c r="AZ29" s="46">
-        <f>SUMIFS(ventas_unidades,ventas_region,$A29,ventas_año,AZ$8)</f>
+        <f t="shared" si="59"/>
         <v>4903</v>
       </c>
       <c r="BA29" s="46">
-        <f>SUMIFS(ventas_unidades,ventas_region,$A29,ventas_año,BA$8)</f>
+        <f t="shared" si="59"/>
         <v>194301</v>
       </c>
       <c r="BB29" s="46">
-        <f t="shared" si="59"/>
+        <f t="shared" si="65"/>
         <v>312792</v>
       </c>
       <c r="BD29" s="97">
-        <f>SUMIFS(ventas_total,ventas_region,$A29,ventas_año,BD$8)</f>
+        <f t="shared" si="60"/>
         <v>190929354</v>
       </c>
       <c r="BE29" s="69">
-        <f>SUMIFS(ventas_total,ventas_region,$A29,ventas_año,BE$8)</f>
+        <f t="shared" si="60"/>
         <v>221383553</v>
       </c>
       <c r="BF29" s="69">
-        <f>SUMIFS(ventas_total,ventas_region,$A29,ventas_año,BF$8)</f>
+        <f t="shared" si="60"/>
         <v>240503116</v>
       </c>
       <c r="BG29" s="69">
-        <f>SUMIFS(ventas_total,ventas_region,$A29,ventas_año,BG$8)</f>
+        <f t="shared" si="60"/>
         <v>483929</v>
       </c>
       <c r="BH29" s="69">
-        <f>SUMIFS(ventas_total,ventas_region,$A29,ventas_año,BH$8)</f>
+        <f t="shared" si="60"/>
         <v>1377740</v>
       </c>
       <c r="BI29" s="69">
-        <f t="shared" si="60"/>
+        <f t="shared" si="66"/>
         <v>654677692</v>
       </c>
     </row>
@@ -10033,107 +10040,107 @@
         <v>664722025</v>
       </c>
       <c r="E30" s="83">
-        <f t="shared" si="51"/>
+        <f>SUMIFS(ventas_unidades,ventas_region,$A30,ventas_producto,E$25)</f>
         <v>7128</v>
       </c>
       <c r="F30" s="19">
-        <f t="shared" si="51"/>
+        <f>SUMIFS(ventas_unidades,ventas_region,$A30,ventas_producto,F$25)</f>
         <v>0</v>
       </c>
       <c r="G30" s="19">
-        <f t="shared" si="51"/>
+        <f>SUMIFS(ventas_unidades,ventas_region,$A30,ventas_producto,G$25)</f>
         <v>0</v>
       </c>
       <c r="H30" s="19">
-        <f t="shared" si="51"/>
+        <f>SUMIFS(ventas_unidades,ventas_region,$A30,ventas_producto,H$25)</f>
         <v>0</v>
       </c>
       <c r="I30" s="19">
-        <f t="shared" si="51"/>
+        <f>SUMIFS(ventas_unidades,ventas_region,$A30,ventas_producto,I$25)</f>
         <v>98908</v>
       </c>
       <c r="J30" s="19">
-        <f t="shared" si="55"/>
-        <v>1146245</v>
+        <f t="shared" si="61"/>
+        <v>106036</v>
       </c>
       <c r="L30" s="98">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v>9123918</v>
       </c>
       <c r="M30" s="60">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="N30" s="60">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="O30" s="60">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="P30" s="60">
-        <f t="shared" si="52"/>
+        <f t="shared" si="56"/>
         <v>655598107</v>
       </c>
       <c r="Q30" s="60">
-        <f t="shared" si="56"/>
+        <f t="shared" si="62"/>
         <v>664722025</v>
       </c>
       <c r="S30" s="91">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v>12970</v>
       </c>
       <c r="T30" s="31">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v>14165</v>
       </c>
       <c r="U30" s="31">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v>5143</v>
       </c>
       <c r="V30" s="31">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v>14291</v>
       </c>
       <c r="W30" s="31">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v>19979</v>
       </c>
       <c r="X30" s="31">
-        <f t="shared" si="53"/>
+        <f t="shared" si="57"/>
         <v>39488</v>
       </c>
       <c r="Y30" s="31">
-        <f t="shared" si="57"/>
+        <f t="shared" si="63"/>
         <v>106036</v>
       </c>
       <c r="AA30" s="105">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v>71950539</v>
       </c>
       <c r="AB30" s="65">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v>88920515</v>
       </c>
       <c r="AC30" s="65">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v>31867112</v>
       </c>
       <c r="AD30" s="65">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v>76700859</v>
       </c>
       <c r="AE30" s="65">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v>119641616</v>
       </c>
       <c r="AF30" s="65">
-        <f t="shared" si="54"/>
+        <f t="shared" si="58"/>
         <v>275641384</v>
       </c>
       <c r="AG30" s="65">
-        <f t="shared" si="58"/>
+        <f t="shared" si="64"/>
         <v>664722025</v>
       </c>
       <c r="AI30" s="93"/>
@@ -10149,51 +10156,51 @@
       <c r="AT30" s="49"/>
       <c r="AU30" s="49"/>
       <c r="AW30" s="83">
-        <f>SUMIFS(ventas_unidades,ventas_region,$A30,ventas_año,AW$8)</f>
+        <f t="shared" si="59"/>
         <v>36557</v>
       </c>
       <c r="AX30" s="47">
-        <f>SUMIFS(ventas_unidades,ventas_region,$A30,ventas_año,AX$8)</f>
+        <f t="shared" si="59"/>
         <v>28900</v>
       </c>
       <c r="AY30" s="47">
-        <f>SUMIFS(ventas_unidades,ventas_region,$A30,ventas_año,AY$8)</f>
+        <f t="shared" si="59"/>
         <v>33451</v>
       </c>
       <c r="AZ30" s="47">
-        <f>SUMIFS(ventas_unidades,ventas_region,$A30,ventas_año,AZ$8)</f>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="BA30" s="47">
-        <f>SUMIFS(ventas_unidades,ventas_region,$A30,ventas_año,BA$8)</f>
+        <f t="shared" si="59"/>
         <v>7128</v>
       </c>
       <c r="BB30" s="47">
-        <f t="shared" si="59"/>
+        <f t="shared" si="65"/>
         <v>106036</v>
       </c>
       <c r="BD30" s="98">
-        <f>SUMIFS(ventas_total,ventas_region,$A30,ventas_año,BD$8)</f>
+        <f t="shared" si="60"/>
         <v>216479082</v>
       </c>
       <c r="BE30" s="70">
-        <f>SUMIFS(ventas_total,ventas_region,$A30,ventas_año,BE$8)</f>
+        <f t="shared" si="60"/>
         <v>240247726</v>
       </c>
       <c r="BF30" s="70">
-        <f>SUMIFS(ventas_total,ventas_region,$A30,ventas_año,BF$8)</f>
+        <f t="shared" si="60"/>
         <v>198871299</v>
       </c>
       <c r="BG30" s="70">
-        <f>SUMIFS(ventas_total,ventas_region,$A30,ventas_año,BG$8)</f>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="BH30" s="70">
-        <f>SUMIFS(ventas_total,ventas_region,$A30,ventas_año,BH$8)</f>
+        <f t="shared" si="60"/>
         <v>9123918</v>
       </c>
       <c r="BI30" s="70">
-        <f t="shared" si="60"/>
+        <f t="shared" si="66"/>
         <v>664722025</v>
       </c>
     </row>
@@ -10214,47 +10221,47 @@
         <v>110903</v>
       </c>
       <c r="F31" s="50">
-        <f t="shared" ref="F31:J31" si="61">SUM(F26:F30)</f>
+        <f t="shared" ref="F31:J31" si="67">SUM(F26:F30)</f>
         <v>304519</v>
       </c>
       <c r="G31" s="50">
-        <f t="shared" si="61"/>
+        <f t="shared" si="67"/>
         <v>118380</v>
       </c>
       <c r="H31" s="50">
-        <f t="shared" si="61"/>
+        <f t="shared" si="67"/>
         <v>115644</v>
       </c>
       <c r="I31" s="50">
-        <f t="shared" si="61"/>
+        <f t="shared" si="67"/>
         <v>208781</v>
       </c>
       <c r="J31" s="117">
-        <f t="shared" si="61"/>
-        <v>6280957</v>
+        <f t="shared" si="67"/>
+        <v>858227</v>
       </c>
       <c r="L31" s="108">
         <f>SUM(L26:L30)</f>
         <v>650543568</v>
       </c>
       <c r="M31" s="68">
-        <f t="shared" ref="M31" si="62">SUM(M26:M30)</f>
+        <f t="shared" ref="M31" si="68">SUM(M26:M30)</f>
         <v>578124392</v>
       </c>
       <c r="N31" s="68">
-        <f t="shared" ref="N31" si="63">SUM(N26:N30)</f>
+        <f t="shared" ref="N31" si="69">SUM(N26:N30)</f>
         <v>690157736</v>
       </c>
       <c r="O31" s="68">
-        <f t="shared" ref="O31" si="64">SUM(O26:O30)</f>
+        <f t="shared" ref="O31" si="70">SUM(O26:O30)</f>
         <v>654943915</v>
       </c>
       <c r="P31" s="68">
-        <f t="shared" ref="P31" si="65">SUM(P26:P30)</f>
+        <f t="shared" ref="P31" si="71">SUM(P26:P30)</f>
         <v>656247934</v>
       </c>
       <c r="Q31" s="114">
-        <f t="shared" ref="Q31" si="66">SUM(Q26:Q30)</f>
+        <f t="shared" ref="Q31" si="72">SUM(Q26:Q30)</f>
         <v>3230017545</v>
       </c>
       <c r="S31" s="92">
@@ -10262,27 +10269,27 @@
         <v>121665</v>
       </c>
       <c r="T31" s="40">
-        <f t="shared" ref="T31:Y31" si="67">SUM(T26:T30)</f>
+        <f t="shared" ref="T31:Y31" si="73">SUM(T26:T30)</f>
         <v>125620</v>
       </c>
       <c r="U31" s="40">
-        <f t="shared" si="67"/>
+        <f t="shared" si="73"/>
         <v>32356</v>
       </c>
       <c r="V31" s="40">
-        <f t="shared" si="67"/>
+        <f t="shared" si="73"/>
         <v>356297</v>
       </c>
       <c r="W31" s="40">
-        <f t="shared" si="67"/>
+        <f t="shared" si="73"/>
         <v>122295</v>
       </c>
       <c r="X31" s="40">
-        <f t="shared" si="67"/>
+        <f t="shared" si="73"/>
         <v>99994</v>
       </c>
       <c r="Y31" s="40">
-        <f t="shared" si="67"/>
+        <f t="shared" si="73"/>
         <v>858227</v>
       </c>
       <c r="AA31" s="106">
@@ -10290,27 +10297,27 @@
         <v>645115066</v>
       </c>
       <c r="AB31" s="66">
-        <f t="shared" ref="AB31" si="68">SUM(AB26:AB30)</f>
+        <f t="shared" ref="AB31" si="74">SUM(AB26:AB30)</f>
         <v>761464717</v>
       </c>
       <c r="AC31" s="66">
-        <f t="shared" ref="AC31" si="69">SUM(AC26:AC30)</f>
+        <f t="shared" ref="AC31" si="75">SUM(AC26:AC30)</f>
         <v>226722785</v>
       </c>
       <c r="AD31" s="66">
-        <f t="shared" ref="AD31" si="70">SUM(AD26:AD30)</f>
+        <f t="shared" ref="AD31" si="76">SUM(AD26:AD30)</f>
         <v>312257691</v>
       </c>
       <c r="AE31" s="66">
-        <f t="shared" ref="AE31" si="71">SUM(AE26:AE30)</f>
+        <f t="shared" ref="AE31" si="77">SUM(AE26:AE30)</f>
         <v>722503562</v>
       </c>
       <c r="AF31" s="66">
-        <f t="shared" ref="AF31" si="72">SUM(AF26:AF30)</f>
+        <f t="shared" ref="AF31" si="78">SUM(AF26:AF30)</f>
         <v>561953724</v>
       </c>
       <c r="AG31" s="114">
-        <f t="shared" ref="AG31" si="73">SUM(AG26:AG30)</f>
+        <f t="shared" ref="AG31" si="79">SUM(AG26:AG30)</f>
         <v>3230017545</v>
       </c>
       <c r="AI31" s="93"/>
@@ -10326,23 +10333,23 @@
       <c r="AT31" s="49"/>
       <c r="AU31" s="49"/>
       <c r="AW31" s="94">
-        <f t="shared" ref="AW31:BA31" si="74">SUM(AW27:AW30)</f>
+        <f t="shared" ref="AW31:BA31" si="80">SUM(AW27:AW30)</f>
         <v>148950</v>
       </c>
       <c r="AX31" s="50">
-        <f t="shared" si="74"/>
+        <f t="shared" si="80"/>
         <v>133993</v>
       </c>
       <c r="AY31" s="50">
-        <f t="shared" si="74"/>
+        <f t="shared" si="80"/>
         <v>139321</v>
       </c>
       <c r="AZ31" s="50">
-        <f t="shared" si="74"/>
+        <f t="shared" si="80"/>
         <v>120570</v>
       </c>
       <c r="BA31" s="50">
-        <f t="shared" si="74"/>
+        <f t="shared" si="80"/>
         <v>205284</v>
       </c>
       <c r="BB31" s="117">
@@ -10354,23 +10361,23 @@
         <v>1007244151</v>
       </c>
       <c r="BE31" s="68">
-        <f t="shared" ref="BE31:BI31" si="75">SUM(BE26:BE30)</f>
+        <f t="shared" ref="BE31:BI31" si="81">SUM(BE26:BE30)</f>
         <v>1106846472</v>
       </c>
       <c r="BF31" s="68">
-        <f t="shared" si="75"/>
+        <f t="shared" si="81"/>
         <v>1089310347</v>
       </c>
       <c r="BG31" s="68">
-        <f t="shared" si="75"/>
+        <f t="shared" si="81"/>
         <v>15082721</v>
       </c>
       <c r="BH31" s="68">
-        <f t="shared" si="75"/>
+        <f t="shared" si="81"/>
         <v>11533854</v>
       </c>
       <c r="BI31" s="114">
-        <f t="shared" si="75"/>
+        <f t="shared" si="81"/>
         <v>3230017545</v>
       </c>
     </row>
@@ -10525,47 +10532,47 @@
         <v>1007244151</v>
       </c>
       <c r="E34" s="81">
-        <f t="shared" ref="E34:I38" si="76">SUMIFS(ventas_unidades,ventas_año,$A34,ventas_producto,E$25)</f>
+        <f t="shared" ref="E34:I38" si="82">SUMIFS(ventas_unidades,ventas_año,$A34,ventas_producto,E$25)</f>
         <v>33032</v>
       </c>
       <c r="F34" s="17">
-        <f t="shared" si="76"/>
+        <f t="shared" si="82"/>
         <v>32696</v>
       </c>
       <c r="G34" s="17">
-        <f t="shared" si="76"/>
+        <f t="shared" si="82"/>
         <v>39124</v>
       </c>
       <c r="H34" s="17">
-        <f t="shared" si="76"/>
+        <f t="shared" si="82"/>
         <v>40573</v>
       </c>
       <c r="I34" s="17">
-        <f t="shared" si="76"/>
+        <f t="shared" si="82"/>
         <v>36557</v>
       </c>
       <c r="J34" s="17">
-        <f>SUM(E34:I38)</f>
-        <v>858227</v>
+        <f>SUM(E34:I34)</f>
+        <v>181982</v>
       </c>
       <c r="L34" s="96">
-        <f t="shared" ref="L34:P38" si="77">SUMIFS(ventas_total,ventas_año,$A34,ventas_producto,L$25)</f>
+        <f t="shared" ref="L34:P38" si="83">SUMIFS(ventas_total,ventas_año,$A34,ventas_producto,L$25)</f>
         <v>218669111</v>
       </c>
       <c r="M34" s="58">
-        <f t="shared" si="77"/>
+        <f t="shared" si="83"/>
         <v>160364763</v>
       </c>
       <c r="N34" s="58">
-        <f t="shared" si="77"/>
+        <f t="shared" si="83"/>
         <v>220801841</v>
       </c>
       <c r="O34" s="58">
-        <f t="shared" si="77"/>
+        <f t="shared" si="83"/>
         <v>190929354</v>
       </c>
       <c r="P34" s="58">
-        <f t="shared" si="77"/>
+        <f t="shared" si="83"/>
         <v>216479082</v>
       </c>
       <c r="Q34" s="58">
@@ -10573,27 +10580,27 @@
         <v>1007244151</v>
       </c>
       <c r="S34" s="89">
-        <f t="shared" ref="S34:X38" si="78">SUMIFS(ventas_unidades,ventas_año,$A34,ventas_vendedor,S$33)</f>
+        <f t="shared" ref="S34:X38" si="84">SUMIFS(ventas_unidades,ventas_año,$A34,ventas_vendedor,S$33)</f>
         <v>33623</v>
       </c>
       <c r="T34" s="29">
-        <f t="shared" si="78"/>
+        <f t="shared" si="84"/>
         <v>45235</v>
       </c>
       <c r="U34" s="29">
-        <f t="shared" si="78"/>
+        <f t="shared" si="84"/>
         <v>12423</v>
       </c>
       <c r="V34" s="29">
-        <f t="shared" si="78"/>
+        <f t="shared" si="84"/>
         <v>20990</v>
       </c>
       <c r="W34" s="29">
-        <f t="shared" si="78"/>
+        <f t="shared" si="84"/>
         <v>44558</v>
       </c>
       <c r="X34" s="29">
-        <f t="shared" si="78"/>
+        <f t="shared" si="84"/>
         <v>25153</v>
       </c>
       <c r="Y34" s="29">
@@ -10601,27 +10608,27 @@
         <v>181982</v>
       </c>
       <c r="AA34" s="103">
-        <f t="shared" ref="AA34:AF38" si="79">SUMIFS(ventas_unidades,ventas_año,$A34,ventas_vendedor,AA$33)</f>
+        <f t="shared" ref="AA34:AF38" si="85">SUMIFS(ventas_unidades,ventas_año,$A34,ventas_vendedor,AA$33)</f>
         <v>33623</v>
       </c>
       <c r="AB34" s="63">
-        <f t="shared" si="79"/>
+        <f t="shared" si="85"/>
         <v>45235</v>
       </c>
       <c r="AC34" s="63">
-        <f t="shared" si="79"/>
+        <f t="shared" si="85"/>
         <v>12423</v>
       </c>
       <c r="AD34" s="63">
-        <f t="shared" si="79"/>
+        <f t="shared" si="85"/>
         <v>20990</v>
       </c>
       <c r="AE34" s="63">
-        <f t="shared" si="79"/>
+        <f t="shared" si="85"/>
         <v>44558</v>
       </c>
       <c r="AF34" s="63">
-        <f t="shared" si="79"/>
+        <f t="shared" si="85"/>
         <v>25153</v>
       </c>
       <c r="AG34" s="63">
@@ -10629,23 +10636,23 @@
         <v>181982</v>
       </c>
       <c r="AI34" s="81">
-        <f t="shared" ref="AI34:AM38" si="80">SUMIFS(ventas_unidades,ventas_año,$A34,ventas_region,AI$33)</f>
+        <f t="shared" ref="AI34:AM38" si="86">SUMIFS(ventas_unidades,ventas_año,$A34,ventas_region,AI$33)</f>
         <v>33032</v>
       </c>
       <c r="AJ34" s="17">
-        <f t="shared" si="80"/>
+        <f t="shared" si="86"/>
         <v>32696</v>
       </c>
       <c r="AK34" s="17">
-        <f t="shared" si="80"/>
+        <f t="shared" si="86"/>
         <v>39124</v>
       </c>
       <c r="AL34" s="17">
-        <f t="shared" si="80"/>
+        <f t="shared" si="86"/>
         <v>40573</v>
       </c>
       <c r="AM34" s="17">
-        <f t="shared" si="80"/>
+        <f t="shared" si="86"/>
         <v>36557</v>
       </c>
       <c r="AN34" s="17">
@@ -10653,23 +10660,23 @@
         <v>181982</v>
       </c>
       <c r="AP34" s="110">
-        <f t="shared" ref="AP34:AT38" si="81">SUMIFS(ventas_total,ventas_año,$A34,ventas_region,AP$33)</f>
+        <f t="shared" ref="AP34:AT38" si="87">SUMIFS(ventas_total,ventas_año,$A34,ventas_region,AP$33)</f>
         <v>218669111</v>
       </c>
       <c r="AQ34" s="41">
-        <f t="shared" si="81"/>
+        <f t="shared" si="87"/>
         <v>160364763</v>
       </c>
       <c r="AR34" s="41">
-        <f t="shared" si="81"/>
+        <f t="shared" si="87"/>
         <v>220801841</v>
       </c>
       <c r="AS34" s="41">
-        <f t="shared" si="81"/>
+        <f t="shared" si="87"/>
         <v>190929354</v>
       </c>
       <c r="AT34" s="41">
-        <f t="shared" si="81"/>
+        <f t="shared" si="87"/>
         <v>216479082</v>
       </c>
       <c r="AU34" s="41">
@@ -10702,155 +10709,155 @@
         <v>1106846472</v>
       </c>
       <c r="E35" s="82">
-        <f t="shared" si="76"/>
+        <f t="shared" si="82"/>
         <v>32671</v>
       </c>
       <c r="F35" s="18">
-        <f t="shared" si="76"/>
+        <f t="shared" si="82"/>
         <v>31651</v>
       </c>
       <c r="G35" s="18">
-        <f t="shared" si="76"/>
+        <f t="shared" si="82"/>
         <v>34000</v>
       </c>
       <c r="H35" s="18">
-        <f t="shared" si="76"/>
+        <f t="shared" si="82"/>
         <v>39442</v>
       </c>
       <c r="I35" s="18">
-        <f t="shared" si="76"/>
+        <f t="shared" si="82"/>
         <v>28900</v>
       </c>
       <c r="J35" s="18">
-        <f t="shared" ref="J35:J38" si="82">SUM(E35:I39)</f>
-        <v>1534472</v>
+        <f t="shared" ref="J35:J38" si="88">SUM(E35:I35)</f>
+        <v>166664</v>
       </c>
       <c r="L35" s="97">
-        <f t="shared" si="77"/>
+        <f t="shared" si="83"/>
         <v>203341463</v>
       </c>
       <c r="M35" s="59">
-        <f t="shared" si="77"/>
+        <f t="shared" si="83"/>
         <v>201880917</v>
       </c>
       <c r="N35" s="59">
-        <f t="shared" si="77"/>
+        <f t="shared" si="83"/>
         <v>239992813</v>
       </c>
       <c r="O35" s="59">
-        <f t="shared" si="77"/>
+        <f t="shared" si="83"/>
         <v>221383553</v>
       </c>
       <c r="P35" s="59">
-        <f t="shared" si="77"/>
+        <f t="shared" si="83"/>
         <v>240247726</v>
       </c>
       <c r="Q35" s="59">
-        <f t="shared" ref="Q35:Q38" si="83">SUM(L35:P35)</f>
+        <f t="shared" ref="Q35:Q38" si="89">SUM(L35:P35)</f>
         <v>1106846472</v>
       </c>
       <c r="S35" s="90">
-        <f t="shared" si="78"/>
+        <f t="shared" si="84"/>
         <v>42339</v>
       </c>
       <c r="T35" s="30">
-        <f t="shared" si="78"/>
+        <f t="shared" si="84"/>
         <v>39435</v>
       </c>
       <c r="U35" s="30">
-        <f t="shared" si="78"/>
+        <f t="shared" si="84"/>
         <v>12194</v>
       </c>
       <c r="V35" s="30">
-        <f t="shared" si="78"/>
+        <f t="shared" si="84"/>
         <v>11750</v>
       </c>
       <c r="W35" s="30">
-        <f t="shared" si="78"/>
+        <f t="shared" si="84"/>
         <v>27319</v>
       </c>
       <c r="X35" s="30">
-        <f t="shared" si="78"/>
+        <f t="shared" si="84"/>
         <v>33627</v>
       </c>
       <c r="Y35" s="30">
-        <f t="shared" ref="Y35:Y38" si="84">SUM(S35:X35)</f>
+        <f t="shared" ref="Y35:Y38" si="90">SUM(S35:X35)</f>
         <v>166664</v>
       </c>
       <c r="AA35" s="104">
-        <f t="shared" si="79"/>
+        <f t="shared" si="85"/>
         <v>42339</v>
       </c>
       <c r="AB35" s="64">
-        <f t="shared" si="79"/>
+        <f t="shared" si="85"/>
         <v>39435</v>
       </c>
       <c r="AC35" s="64">
-        <f t="shared" si="79"/>
+        <f t="shared" si="85"/>
         <v>12194</v>
       </c>
       <c r="AD35" s="64">
-        <f t="shared" si="79"/>
+        <f t="shared" si="85"/>
         <v>11750</v>
       </c>
       <c r="AE35" s="64">
-        <f t="shared" si="79"/>
+        <f t="shared" si="85"/>
         <v>27319</v>
       </c>
       <c r="AF35" s="64">
-        <f t="shared" si="79"/>
+        <f t="shared" si="85"/>
         <v>33627</v>
       </c>
       <c r="AG35" s="64">
-        <f t="shared" ref="AG35:AG38" si="85">SUM(AA35:AF35)</f>
+        <f t="shared" ref="AG35:AG38" si="91">SUM(AA35:AF35)</f>
         <v>166664</v>
       </c>
       <c r="AI35" s="82">
-        <f t="shared" si="80"/>
+        <f t="shared" si="86"/>
         <v>32671</v>
       </c>
       <c r="AJ35" s="18">
-        <f t="shared" si="80"/>
+        <f t="shared" si="86"/>
         <v>31651</v>
       </c>
       <c r="AK35" s="18">
-        <f t="shared" si="80"/>
+        <f t="shared" si="86"/>
         <v>34000</v>
       </c>
       <c r="AL35" s="18">
-        <f t="shared" si="80"/>
+        <f t="shared" si="86"/>
         <v>39442</v>
       </c>
       <c r="AM35" s="18">
-        <f t="shared" si="80"/>
+        <f t="shared" si="86"/>
         <v>28900</v>
       </c>
       <c r="AN35" s="18">
-        <f t="shared" ref="AN35:AN38" si="86">SUM(AI35:AM35)</f>
+        <f t="shared" ref="AN35:AN38" si="92">SUM(AI35:AM35)</f>
         <v>166664</v>
       </c>
       <c r="AP35" s="111">
-        <f t="shared" si="81"/>
+        <f t="shared" si="87"/>
         <v>203341463</v>
       </c>
       <c r="AQ35" s="44">
-        <f t="shared" si="81"/>
+        <f t="shared" si="87"/>
         <v>201880917</v>
       </c>
       <c r="AR35" s="44">
-        <f t="shared" si="81"/>
+        <f t="shared" si="87"/>
         <v>239992813</v>
       </c>
       <c r="AS35" s="44">
-        <f t="shared" si="81"/>
+        <f t="shared" si="87"/>
         <v>221383553</v>
       </c>
       <c r="AT35" s="44">
-        <f t="shared" si="81"/>
+        <f t="shared" si="87"/>
         <v>240247726</v>
       </c>
       <c r="AU35" s="44">
-        <f t="shared" ref="AU35:AU38" si="87">SUM(AP35:AT35)</f>
+        <f t="shared" ref="AU35:AU38" si="93">SUM(AP35:AT35)</f>
         <v>1106846472</v>
       </c>
       <c r="AW35" s="93"/>
@@ -10879,155 +10886,155 @@
         <v>1089310347</v>
       </c>
       <c r="E36" s="83">
-        <f t="shared" si="76"/>
+        <f t="shared" si="82"/>
         <v>35334</v>
       </c>
       <c r="F36" s="19">
-        <f t="shared" si="76"/>
+        <f t="shared" si="82"/>
         <v>40967</v>
       </c>
       <c r="G36" s="19">
-        <f t="shared" si="76"/>
+        <f t="shared" si="82"/>
         <v>31330</v>
       </c>
       <c r="H36" s="19">
-        <f t="shared" si="76"/>
+        <f t="shared" si="82"/>
         <v>33573</v>
       </c>
       <c r="I36" s="19">
-        <f t="shared" si="76"/>
+        <f t="shared" si="82"/>
         <v>33451</v>
       </c>
       <c r="J36" s="19">
-        <f t="shared" si="82"/>
-        <v>1367808</v>
+        <f t="shared" si="88"/>
+        <v>174655</v>
       </c>
       <c r="L36" s="98">
-        <f t="shared" si="77"/>
+        <f t="shared" si="83"/>
         <v>218564244</v>
       </c>
       <c r="M36" s="60">
-        <f t="shared" si="77"/>
+        <f t="shared" si="83"/>
         <v>214457221</v>
       </c>
       <c r="N36" s="60">
-        <f t="shared" si="77"/>
+        <f t="shared" si="83"/>
         <v>216914467</v>
       </c>
       <c r="O36" s="60">
-        <f t="shared" si="77"/>
+        <f t="shared" si="83"/>
         <v>240503116</v>
       </c>
       <c r="P36" s="60">
-        <f t="shared" si="77"/>
+        <f t="shared" si="83"/>
         <v>198871299</v>
       </c>
       <c r="Q36" s="60">
-        <f t="shared" si="83"/>
+        <f t="shared" si="89"/>
         <v>1089310347</v>
       </c>
       <c r="S36" s="91">
-        <f t="shared" si="78"/>
+        <f t="shared" si="84"/>
         <v>33889</v>
       </c>
       <c r="T36" s="31">
-        <f t="shared" si="78"/>
+        <f t="shared" si="84"/>
         <v>40950</v>
       </c>
       <c r="U36" s="31">
-        <f t="shared" si="78"/>
+        <f t="shared" si="84"/>
         <v>7739</v>
       </c>
       <c r="V36" s="31">
-        <f t="shared" si="78"/>
+        <f t="shared" si="84"/>
         <v>24117</v>
       </c>
       <c r="W36" s="31">
-        <f t="shared" si="78"/>
+        <f t="shared" si="84"/>
         <v>31540</v>
       </c>
       <c r="X36" s="31">
-        <f t="shared" si="78"/>
+        <f t="shared" si="84"/>
         <v>36420</v>
       </c>
       <c r="Y36" s="31">
-        <f t="shared" si="84"/>
+        <f t="shared" si="90"/>
         <v>174655</v>
       </c>
       <c r="AA36" s="105">
-        <f t="shared" si="79"/>
+        <f t="shared" si="85"/>
         <v>33889</v>
       </c>
       <c r="AB36" s="65">
-        <f t="shared" si="79"/>
+        <f t="shared" si="85"/>
         <v>40950</v>
       </c>
       <c r="AC36" s="65">
-        <f t="shared" si="79"/>
+        <f t="shared" si="85"/>
         <v>7739</v>
       </c>
       <c r="AD36" s="65">
-        <f t="shared" si="79"/>
+        <f t="shared" si="85"/>
         <v>24117</v>
       </c>
       <c r="AE36" s="65">
-        <f t="shared" si="79"/>
+        <f t="shared" si="85"/>
         <v>31540</v>
       </c>
       <c r="AF36" s="65">
-        <f t="shared" si="79"/>
+        <f t="shared" si="85"/>
         <v>36420</v>
       </c>
       <c r="AG36" s="65">
-        <f t="shared" si="85"/>
+        <f t="shared" si="91"/>
         <v>174655</v>
       </c>
       <c r="AI36" s="83">
-        <f t="shared" si="80"/>
+        <f t="shared" si="86"/>
         <v>35334</v>
       </c>
       <c r="AJ36" s="19">
-        <f t="shared" si="80"/>
+        <f t="shared" si="86"/>
         <v>40967</v>
       </c>
       <c r="AK36" s="19">
-        <f t="shared" si="80"/>
+        <f t="shared" si="86"/>
         <v>31330</v>
       </c>
       <c r="AL36" s="19">
-        <f t="shared" si="80"/>
+        <f t="shared" si="86"/>
         <v>33573</v>
       </c>
       <c r="AM36" s="19">
-        <f t="shared" si="80"/>
+        <f t="shared" si="86"/>
         <v>33451</v>
       </c>
       <c r="AN36" s="19">
-        <f t="shared" si="86"/>
+        <f t="shared" si="92"/>
         <v>174655</v>
       </c>
       <c r="AP36" s="112">
-        <f t="shared" si="81"/>
+        <f t="shared" si="87"/>
         <v>218564244</v>
       </c>
       <c r="AQ36" s="45">
-        <f t="shared" si="81"/>
+        <f t="shared" si="87"/>
         <v>214457221</v>
       </c>
       <c r="AR36" s="45">
-        <f t="shared" si="81"/>
+        <f t="shared" si="87"/>
         <v>216914467</v>
       </c>
       <c r="AS36" s="45">
-        <f t="shared" si="81"/>
+        <f t="shared" si="87"/>
         <v>240503116</v>
       </c>
       <c r="AT36" s="45">
-        <f t="shared" si="81"/>
+        <f t="shared" si="87"/>
         <v>198871299</v>
       </c>
       <c r="AU36" s="45">
-        <f t="shared" si="87"/>
+        <f t="shared" si="93"/>
         <v>1089310347</v>
       </c>
       <c r="AW36" s="93"/>
@@ -11056,155 +11063,155 @@
         <v>15082721</v>
       </c>
       <c r="E37" s="82">
-        <f t="shared" si="76"/>
+        <f t="shared" si="82"/>
         <v>2738</v>
       </c>
       <c r="F37" s="18">
-        <f t="shared" si="76"/>
+        <f t="shared" si="82"/>
         <v>4903</v>
       </c>
       <c r="G37" s="18">
-        <f t="shared" si="76"/>
+        <f t="shared" si="82"/>
         <v>13926</v>
       </c>
       <c r="H37" s="18">
-        <f t="shared" si="76"/>
+        <f t="shared" si="82"/>
         <v>129</v>
       </c>
       <c r="I37" s="18">
-        <f t="shared" si="76"/>
+        <f t="shared" si="82"/>
         <v>107946</v>
       </c>
       <c r="J37" s="18">
-        <f t="shared" si="82"/>
-        <v>1193153</v>
+        <f t="shared" si="88"/>
+        <v>129642</v>
       </c>
       <c r="L37" s="97">
-        <f t="shared" si="77"/>
+        <f t="shared" si="83"/>
         <v>844832</v>
       </c>
       <c r="M37" s="59">
-        <f t="shared" si="77"/>
+        <f t="shared" si="83"/>
         <v>483929</v>
       </c>
       <c r="N37" s="59">
-        <f t="shared" si="77"/>
+        <f t="shared" si="83"/>
         <v>12448615</v>
       </c>
       <c r="O37" s="59">
-        <f t="shared" si="77"/>
+        <f t="shared" si="83"/>
         <v>1203910</v>
       </c>
       <c r="P37" s="59">
-        <f t="shared" si="77"/>
+        <f t="shared" si="83"/>
         <v>101435</v>
       </c>
       <c r="Q37" s="59">
-        <f t="shared" si="83"/>
+        <f t="shared" si="89"/>
         <v>15082721</v>
       </c>
       <c r="S37" s="90">
-        <f t="shared" si="78"/>
+        <f t="shared" si="84"/>
         <v>9886</v>
       </c>
       <c r="T37" s="30">
-        <f t="shared" si="78"/>
+        <f t="shared" si="84"/>
         <v>0</v>
       </c>
       <c r="U37" s="30">
-        <f t="shared" si="78"/>
+        <f t="shared" si="84"/>
         <v>0</v>
       </c>
       <c r="V37" s="30">
-        <f t="shared" si="78"/>
+        <f t="shared" si="84"/>
         <v>107066</v>
       </c>
       <c r="W37" s="30">
-        <f t="shared" si="78"/>
+        <f t="shared" si="84"/>
         <v>9823</v>
       </c>
       <c r="X37" s="30">
-        <f t="shared" si="78"/>
+        <f t="shared" si="84"/>
         <v>2867</v>
       </c>
       <c r="Y37" s="30">
-        <f t="shared" si="84"/>
+        <f t="shared" si="90"/>
         <v>129642</v>
       </c>
       <c r="AA37" s="104">
-        <f t="shared" si="79"/>
+        <f t="shared" si="85"/>
         <v>9886</v>
       </c>
       <c r="AB37" s="64">
-        <f t="shared" si="79"/>
+        <f t="shared" si="85"/>
         <v>0</v>
       </c>
       <c r="AC37" s="64">
-        <f t="shared" si="79"/>
+        <f t="shared" si="85"/>
         <v>0</v>
       </c>
       <c r="AD37" s="64">
-        <f t="shared" si="79"/>
+        <f t="shared" si="85"/>
         <v>107066</v>
       </c>
       <c r="AE37" s="64">
-        <f t="shared" si="79"/>
+        <f t="shared" si="85"/>
         <v>9823</v>
       </c>
       <c r="AF37" s="64">
-        <f t="shared" si="79"/>
+        <f t="shared" si="85"/>
         <v>2867</v>
       </c>
       <c r="AG37" s="64">
-        <f t="shared" si="85"/>
+        <f t="shared" si="91"/>
         <v>129642</v>
       </c>
       <c r="AI37" s="82">
-        <f t="shared" si="80"/>
+        <f t="shared" si="86"/>
         <v>9072</v>
       </c>
       <c r="AJ37" s="18">
-        <f t="shared" si="80"/>
+        <f t="shared" si="86"/>
         <v>107946</v>
       </c>
       <c r="AK37" s="18">
-        <f t="shared" si="80"/>
+        <f t="shared" si="86"/>
         <v>7721</v>
       </c>
       <c r="AL37" s="18">
-        <f t="shared" si="80"/>
+        <f t="shared" si="86"/>
         <v>4903</v>
       </c>
       <c r="AM37" s="18">
-        <f t="shared" si="80"/>
+        <f t="shared" si="86"/>
         <v>0</v>
       </c>
       <c r="AN37" s="18">
-        <f t="shared" si="86"/>
+        <f t="shared" si="92"/>
         <v>129642</v>
       </c>
       <c r="AP37" s="111">
-        <f t="shared" si="81"/>
+        <f t="shared" si="87"/>
         <v>5532144</v>
       </c>
       <c r="AQ37" s="44">
-        <f t="shared" si="81"/>
+        <f t="shared" si="87"/>
         <v>101435</v>
       </c>
       <c r="AR37" s="44">
-        <f t="shared" si="81"/>
+        <f t="shared" si="87"/>
         <v>8965213</v>
       </c>
       <c r="AS37" s="44">
-        <f t="shared" si="81"/>
+        <f t="shared" si="87"/>
         <v>483929</v>
       </c>
       <c r="AT37" s="44">
-        <f t="shared" si="81"/>
+        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="AU37" s="44">
-        <f t="shared" si="87"/>
+        <f t="shared" si="93"/>
         <v>15082721</v>
       </c>
       <c r="AW37" s="93"/>
@@ -11233,155 +11240,155 @@
         <v>11533854</v>
       </c>
       <c r="E38" s="83">
-        <f t="shared" si="76"/>
+        <f t="shared" si="82"/>
         <v>7128</v>
       </c>
       <c r="F38" s="19">
-        <f t="shared" si="76"/>
+        <f t="shared" si="82"/>
         <v>194302</v>
       </c>
       <c r="G38" s="19">
-        <f t="shared" si="76"/>
+        <f t="shared" si="82"/>
         <v>0</v>
       </c>
       <c r="H38" s="19">
-        <f t="shared" si="76"/>
+        <f t="shared" si="82"/>
         <v>1927</v>
       </c>
       <c r="I38" s="19">
-        <f t="shared" si="76"/>
+        <f t="shared" si="82"/>
         <v>1927</v>
       </c>
       <c r="J38" s="19">
-        <f t="shared" si="82"/>
-        <v>1063511</v>
+        <f t="shared" si="88"/>
+        <v>205284</v>
       </c>
       <c r="L38" s="98">
-        <f t="shared" si="77"/>
+        <f t="shared" si="83"/>
         <v>9123918</v>
       </c>
       <c r="M38" s="60">
-        <f t="shared" si="77"/>
+        <f t="shared" si="83"/>
         <v>937562</v>
       </c>
       <c r="N38" s="60">
-        <f t="shared" si="77"/>
+        <f t="shared" si="83"/>
         <v>0</v>
       </c>
       <c r="O38" s="60">
-        <f t="shared" si="77"/>
+        <f t="shared" si="83"/>
         <v>923982</v>
       </c>
       <c r="P38" s="60">
-        <f t="shared" si="77"/>
+        <f t="shared" si="83"/>
         <v>548392</v>
       </c>
       <c r="Q38" s="60">
-        <f t="shared" si="83"/>
+        <f t="shared" si="89"/>
         <v>11533854</v>
       </c>
       <c r="S38" s="91">
-        <f t="shared" si="78"/>
+        <f t="shared" si="84"/>
         <v>1928</v>
       </c>
       <c r="T38" s="31">
-        <f t="shared" si="78"/>
+        <f t="shared" si="84"/>
         <v>0</v>
       </c>
       <c r="U38" s="31">
-        <f t="shared" si="78"/>
+        <f t="shared" si="84"/>
         <v>0</v>
       </c>
       <c r="V38" s="31">
-        <f t="shared" si="78"/>
+        <f t="shared" si="84"/>
         <v>192374</v>
       </c>
       <c r="W38" s="31">
-        <f t="shared" si="78"/>
+        <f t="shared" si="84"/>
         <v>9055</v>
       </c>
       <c r="X38" s="31">
-        <f t="shared" si="78"/>
+        <f t="shared" si="84"/>
         <v>1927</v>
       </c>
       <c r="Y38" s="31">
-        <f t="shared" si="84"/>
+        <f t="shared" si="90"/>
         <v>205284</v>
       </c>
       <c r="AA38" s="105">
-        <f t="shared" si="79"/>
+        <f t="shared" si="85"/>
         <v>1928</v>
       </c>
       <c r="AB38" s="65">
-        <f t="shared" si="79"/>
+        <f t="shared" si="85"/>
         <v>0</v>
       </c>
       <c r="AC38" s="65">
-        <f t="shared" si="79"/>
+        <f t="shared" si="85"/>
         <v>0</v>
       </c>
       <c r="AD38" s="65">
-        <f t="shared" si="79"/>
+        <f t="shared" si="85"/>
         <v>192374</v>
       </c>
       <c r="AE38" s="65">
-        <f t="shared" si="79"/>
+        <f t="shared" si="85"/>
         <v>9055</v>
       </c>
       <c r="AF38" s="65">
-        <f t="shared" si="79"/>
+        <f t="shared" si="85"/>
         <v>1927</v>
       </c>
       <c r="AG38" s="65">
-        <f t="shared" si="85"/>
+        <f t="shared" si="91"/>
         <v>205284</v>
       </c>
       <c r="AI38" s="83">
-        <f t="shared" si="80"/>
+        <f t="shared" si="86"/>
         <v>0</v>
       </c>
       <c r="AJ38" s="19">
-        <f t="shared" si="80"/>
+        <f t="shared" si="86"/>
         <v>0</v>
       </c>
       <c r="AK38" s="19">
-        <f t="shared" si="80"/>
+        <f t="shared" si="86"/>
         <v>3855</v>
       </c>
       <c r="AL38" s="19">
-        <f t="shared" si="80"/>
+        <f t="shared" si="86"/>
         <v>194301</v>
       </c>
       <c r="AM38" s="19">
-        <f t="shared" si="80"/>
+        <f t="shared" si="86"/>
         <v>7128</v>
       </c>
       <c r="AN38" s="19">
-        <f t="shared" si="86"/>
+        <f t="shared" si="92"/>
         <v>205284</v>
       </c>
       <c r="AP38" s="112">
-        <f t="shared" si="81"/>
+        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="AQ38" s="45">
-        <f t="shared" si="81"/>
+        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="AR38" s="45">
-        <f t="shared" si="81"/>
+        <f t="shared" si="87"/>
         <v>1032196</v>
       </c>
       <c r="AS38" s="45">
-        <f t="shared" si="81"/>
+        <f t="shared" si="87"/>
         <v>1377740</v>
       </c>
       <c r="AT38" s="45">
-        <f t="shared" si="81"/>
+        <f t="shared" si="87"/>
         <v>9123918</v>
       </c>
       <c r="AU38" s="45">
-        <f t="shared" si="87"/>
+        <f t="shared" si="93"/>
         <v>11533854</v>
       </c>
       <c r="AW38" s="93"/>
@@ -11414,43 +11421,43 @@
         <v>110903</v>
       </c>
       <c r="F39" s="50">
-        <f t="shared" ref="F39" si="88">SUM(F34:F38)</f>
+        <f t="shared" ref="F39" si="94">SUM(F34:F38)</f>
         <v>304519</v>
       </c>
       <c r="G39" s="50">
-        <f t="shared" ref="G39" si="89">SUM(G34:G38)</f>
+        <f t="shared" ref="G39" si="95">SUM(G34:G38)</f>
         <v>118380</v>
       </c>
       <c r="H39" s="50">
-        <f t="shared" ref="H39" si="90">SUM(H34:H38)</f>
+        <f t="shared" ref="H39" si="96">SUM(H34:H38)</f>
         <v>115644</v>
       </c>
       <c r="I39" s="50">
-        <f t="shared" ref="I39" si="91">SUM(I34:I38)</f>
+        <f t="shared" ref="I39" si="97">SUM(I34:I38)</f>
         <v>208781</v>
       </c>
       <c r="J39" s="117">
-        <f t="shared" ref="J39" si="92">SUM(J34:J38)</f>
-        <v>6017171</v>
+        <f t="shared" ref="J39" si="98">SUM(J34:J38)</f>
+        <v>858227</v>
       </c>
       <c r="L39" s="108">
         <f>SUM(L34:L38)</f>
         <v>650543568</v>
       </c>
       <c r="M39" s="68">
-        <f t="shared" ref="M39" si="93">SUM(M34:M38)</f>
+        <f t="shared" ref="M39" si="99">SUM(M34:M38)</f>
         <v>578124392</v>
       </c>
       <c r="N39" s="68">
-        <f t="shared" ref="N39" si="94">SUM(N34:N38)</f>
+        <f t="shared" ref="N39" si="100">SUM(N34:N38)</f>
         <v>690157736</v>
       </c>
       <c r="O39" s="68">
-        <f t="shared" ref="O39" si="95">SUM(O34:O38)</f>
+        <f t="shared" ref="O39" si="101">SUM(O34:O38)</f>
         <v>654943915</v>
       </c>
       <c r="P39" s="68">
-        <f t="shared" ref="P39" si="96">SUM(P34:P38)</f>
+        <f t="shared" ref="P39" si="102">SUM(P34:P38)</f>
         <v>656247934</v>
       </c>
       <c r="Q39" s="114">
@@ -11462,27 +11469,27 @@
         <v>121665</v>
       </c>
       <c r="T39" s="40">
-        <f t="shared" ref="T39:Y39" si="97">SUM(T34:T38)</f>
+        <f t="shared" ref="T39:Y39" si="103">SUM(T34:T38)</f>
         <v>125620</v>
       </c>
       <c r="U39" s="40">
-        <f t="shared" si="97"/>
+        <f t="shared" si="103"/>
         <v>32356</v>
       </c>
       <c r="V39" s="40">
-        <f t="shared" si="97"/>
+        <f t="shared" si="103"/>
         <v>356297</v>
       </c>
       <c r="W39" s="40">
-        <f t="shared" si="97"/>
+        <f t="shared" si="103"/>
         <v>122295</v>
       </c>
       <c r="X39" s="40">
-        <f t="shared" si="97"/>
+        <f t="shared" si="103"/>
         <v>99994</v>
       </c>
       <c r="Y39" s="40">
-        <f t="shared" si="97"/>
+        <f t="shared" si="103"/>
         <v>858227</v>
       </c>
       <c r="AA39" s="106">
@@ -11490,27 +11497,27 @@
         <v>121665</v>
       </c>
       <c r="AB39" s="66">
-        <f t="shared" ref="AB39" si="98">SUM(AB34:AB38)</f>
+        <f t="shared" ref="AB39" si="104">SUM(AB34:AB38)</f>
         <v>125620</v>
       </c>
       <c r="AC39" s="66">
-        <f t="shared" ref="AC39" si="99">SUM(AC34:AC38)</f>
+        <f t="shared" ref="AC39" si="105">SUM(AC34:AC38)</f>
         <v>32356</v>
       </c>
       <c r="AD39" s="66">
-        <f t="shared" ref="AD39" si="100">SUM(AD34:AD38)</f>
+        <f t="shared" ref="AD39" si="106">SUM(AD34:AD38)</f>
         <v>356297</v>
       </c>
       <c r="AE39" s="66">
-        <f t="shared" ref="AE39" si="101">SUM(AE34:AE38)</f>
+        <f t="shared" ref="AE39" si="107">SUM(AE34:AE38)</f>
         <v>122295</v>
       </c>
       <c r="AF39" s="66">
-        <f t="shared" ref="AF39" si="102">SUM(AF34:AF38)</f>
+        <f t="shared" ref="AF39" si="108">SUM(AF34:AF38)</f>
         <v>99994</v>
       </c>
       <c r="AG39" s="114">
-        <f t="shared" ref="AG39" si="103">SUM(AG34:AG38)</f>
+        <f t="shared" ref="AG39" si="109">SUM(AG34:AG38)</f>
         <v>858227</v>
       </c>
       <c r="AI39" s="94">
@@ -11518,23 +11525,23 @@
         <v>110109</v>
       </c>
       <c r="AJ39" s="50">
-        <f t="shared" ref="AJ39:AN39" si="104">SUM(AJ34:AJ38)</f>
+        <f t="shared" ref="AJ39:AN39" si="110">SUM(AJ34:AJ38)</f>
         <v>213260</v>
       </c>
       <c r="AK39" s="50">
-        <f t="shared" si="104"/>
+        <f t="shared" si="110"/>
         <v>116030</v>
       </c>
       <c r="AL39" s="50">
-        <f t="shared" si="104"/>
+        <f t="shared" si="110"/>
         <v>312792</v>
       </c>
       <c r="AM39" s="50">
-        <f t="shared" si="104"/>
+        <f t="shared" si="110"/>
         <v>106036</v>
       </c>
       <c r="AN39" s="117">
-        <f t="shared" si="104"/>
+        <f t="shared" si="110"/>
         <v>858227</v>
       </c>
       <c r="AP39" s="113">
@@ -11542,23 +11549,23 @@
         <v>646106962</v>
       </c>
       <c r="AQ39" s="48">
-        <f t="shared" ref="AQ39" si="105">SUM(AQ34:AQ38)</f>
+        <f t="shared" ref="AQ39" si="111">SUM(AQ34:AQ38)</f>
         <v>576804336</v>
       </c>
       <c r="AR39" s="48">
-        <f t="shared" ref="AR39" si="106">SUM(AR34:AR38)</f>
+        <f t="shared" ref="AR39" si="112">SUM(AR34:AR38)</f>
         <v>687706530</v>
       </c>
       <c r="AS39" s="48">
-        <f t="shared" ref="AS39" si="107">SUM(AS34:AS38)</f>
+        <f t="shared" ref="AS39" si="113">SUM(AS34:AS38)</f>
         <v>654677692</v>
       </c>
       <c r="AT39" s="48">
-        <f t="shared" ref="AT39" si="108">SUM(AT34:AT38)</f>
+        <f t="shared" ref="AT39" si="114">SUM(AT34:AT38)</f>
         <v>664722025</v>
       </c>
       <c r="AU39" s="118">
-        <f t="shared" ref="AU39" si="109">SUM(AU34:AU38)</f>
+        <f t="shared" ref="AU39" si="115">SUM(AU34:AU38)</f>
         <v>3230017545</v>
       </c>
       <c r="AW39" s="93"/>

--- a/examples/DB_Supermercado.xlsx
+++ b/examples/DB_Supermercado.xlsx
@@ -8,17 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EducacionIT\Documents\office\Excel\xls-mj15\examples\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6231D298-2DDF-4F12-898F-084AB5DE28D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B21AB4E-B473-4246-8337-6D7FFB61AAE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ventas" sheetId="6" r:id="rId1"/>
     <sheet name="listas" sheetId="7" state="hidden" r:id="rId2"/>
     <sheet name="estadisticas" sheetId="8" r:id="rId3"/>
+    <sheet name="comisiones" sheetId="9" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ventas!$A:$G</definedName>
+    <definedName name="vendedores">estadisticas!$A$16:$C$23</definedName>
     <definedName name="ventas_año">ventas!$B:$B</definedName>
     <definedName name="ventas_producto">ventas!$C:$C</definedName>
     <definedName name="ventas_region">ventas!$G:$G</definedName>
@@ -64,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="989" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1001" uniqueCount="57">
   <si>
     <t>Mes</t>
   </si>
@@ -211,6 +213,30 @@
   </si>
   <si>
     <t>UNIDADES</t>
+  </si>
+  <si>
+    <t>Comision</t>
+  </si>
+  <si>
+    <t>porcentaje</t>
+  </si>
+  <si>
+    <t>objetivo</t>
+  </si>
+  <si>
+    <t>valor</t>
+  </si>
+  <si>
+    <t>unidad</t>
+  </si>
+  <si>
+    <t>venta</t>
+  </si>
+  <si>
+    <t>cumple</t>
+  </si>
+  <si>
+    <t>Objetivos</t>
   </si>
 </sst>
 </file>
@@ -439,7 +465,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="135">
+  <cellXfs count="138">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -583,6 +609,9 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="165" fontId="10" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="10" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Énfasis5" xfId="3" builtinId="45"/>
@@ -8497,7 +8526,7 @@
       </c>
     </row>
     <row r="20" spans="1:61" x14ac:dyDescent="0.3">
-      <c r="A20" s="26" t="s">
+      <c r="A20" s="5" t="s">
         <v>13</v>
       </c>
       <c r="B20" s="30">
@@ -9332,23 +9361,23 @@
         <v>646106962</v>
       </c>
       <c r="E26" s="81">
-        <f>SUMIFS(ventas_unidades,ventas_region,$A26,ventas_producto,E$25)</f>
+        <f t="shared" ref="E26:I30" si="56">SUMIFS(ventas_unidades,ventas_region,$A26,ventas_producto,E$25)</f>
         <v>101037</v>
       </c>
       <c r="F26" s="17">
-        <f>SUMIFS(ventas_unidades,ventas_region,$A26,ventas_producto,F$25)</f>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="G26" s="17">
-        <f>SUMIFS(ventas_unidades,ventas_region,$A26,ventas_producto,G$25)</f>
+        <f t="shared" si="56"/>
         <v>8943</v>
       </c>
       <c r="H26" s="17">
-        <f>SUMIFS(ventas_unidades,ventas_region,$A26,ventas_producto,H$25)</f>
+        <f t="shared" si="56"/>
         <v>129</v>
       </c>
       <c r="I26" s="17">
-        <f>SUMIFS(ventas_unidades,ventas_region,$A26,ventas_producto,I$25)</f>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="J26" s="17">
@@ -9356,23 +9385,23 @@
         <v>110109</v>
       </c>
       <c r="L26" s="96">
-        <f t="shared" ref="L26:P30" si="56">SUMIFS(ventas_total,ventas_region,$A26,ventas_producto,L$25)</f>
+        <f t="shared" ref="L26:P30" si="57">SUMIFS(ventas_total,ventas_region,$A26,ventas_producto,L$25)</f>
         <v>640574818</v>
       </c>
       <c r="M26" s="58">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="N26" s="58">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>4328234</v>
       </c>
       <c r="O26" s="58">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>1203910</v>
       </c>
       <c r="P26" s="58">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>0</v>
       </c>
       <c r="Q26" s="58">
@@ -9380,27 +9409,27 @@
         <v>646106962</v>
       </c>
       <c r="S26" s="81">
-        <f t="shared" ref="S26:X30" si="57">SUMIFS(ventas_unidades,ventas_region,$A26,ventas_vendedor,S$25)</f>
+        <f t="shared" ref="S26:X30" si="58">SUMIFS(ventas_unidades,ventas_region,$A26,ventas_vendedor,S$25)</f>
         <v>23075</v>
       </c>
       <c r="T26" s="29">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>27346</v>
       </c>
       <c r="U26" s="29">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>9125</v>
       </c>
       <c r="V26" s="17">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>30665</v>
       </c>
       <c r="W26" s="29">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>11047</v>
       </c>
       <c r="X26" s="29">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>8851</v>
       </c>
       <c r="Y26" s="17">
@@ -9408,27 +9437,27 @@
         <v>110109</v>
       </c>
       <c r="AA26" s="96">
-        <f t="shared" ref="AA26:AF30" si="58">SUMIFS(ventas_total,ventas_region,$A26,ventas_vendedor,AA$25)</f>
+        <f t="shared" ref="AA26:AF30" si="59">SUMIFS(ventas_total,ventas_region,$A26,ventas_vendedor,AA$25)</f>
         <v>109144041</v>
       </c>
       <c r="AB26" s="63">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>193222871</v>
       </c>
       <c r="AC26" s="63">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>59797810</v>
       </c>
       <c r="AD26" s="58">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>139608342</v>
       </c>
       <c r="AE26" s="63">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>94535993</v>
       </c>
       <c r="AF26" s="63">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>49797905</v>
       </c>
       <c r="AG26" s="58">
@@ -9448,23 +9477,23 @@
       <c r="AT26" s="49"/>
       <c r="AU26" s="49"/>
       <c r="AW26" s="81">
-        <f t="shared" ref="AW26:BA30" si="59">SUMIFS(ventas_unidades,ventas_region,$A26,ventas_año,AW$8)</f>
+        <f t="shared" ref="AW26:BA30" si="60">SUMIFS(ventas_unidades,ventas_region,$A26,ventas_año,AW$8)</f>
         <v>33032</v>
       </c>
       <c r="AX26" s="17">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>32671</v>
       </c>
       <c r="AY26" s="17">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>35334</v>
       </c>
       <c r="AZ26" s="17">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>9072</v>
       </c>
       <c r="BA26" s="17">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="BB26" s="17">
@@ -9472,23 +9501,23 @@
         <v>110109</v>
       </c>
       <c r="BD26" s="96">
-        <f t="shared" ref="BD26:BH30" si="60">SUMIFS(ventas_total,ventas_region,$A26,ventas_año,BD$8)</f>
+        <f t="shared" ref="BD26:BH30" si="61">SUMIFS(ventas_total,ventas_region,$A26,ventas_año,BD$8)</f>
         <v>218669111</v>
       </c>
       <c r="BE26" s="58">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>203341463</v>
       </c>
       <c r="BF26" s="58">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>218564244</v>
       </c>
       <c r="BG26" s="58">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>5532144</v>
       </c>
       <c r="BH26" s="58">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>0</v>
       </c>
       <c r="BI26" s="58">
@@ -9509,107 +9538,107 @@
         <v>576804336</v>
       </c>
       <c r="E27" s="82">
-        <f>SUMIFS(ventas_unidades,ventas_region,$A27,ventas_producto,E$25)</f>
-        <v>0</v>
-      </c>
-      <c r="F27" s="18">
-        <f>SUMIFS(ventas_unidades,ventas_region,$A27,ventas_producto,F$25)</f>
-        <v>105314</v>
-      </c>
-      <c r="G27" s="18">
-        <f>SUMIFS(ventas_unidades,ventas_region,$A27,ventas_producto,G$25)</f>
-        <v>0</v>
-      </c>
-      <c r="H27" s="18">
-        <f>SUMIFS(ventas_unidades,ventas_region,$A27,ventas_producto,H$25)</f>
-        <v>0</v>
-      </c>
-      <c r="I27" s="18">
-        <f>SUMIFS(ventas_unidades,ventas_region,$A27,ventas_producto,I$25)</f>
-        <v>107946</v>
-      </c>
-      <c r="J27" s="18">
-        <f t="shared" ref="J27:J30" si="61">SUM(E27:I27)</f>
-        <v>213260</v>
-      </c>
-      <c r="L27" s="97">
         <f t="shared" si="56"/>
         <v>0</v>
       </c>
-      <c r="M27" s="59">
+      <c r="F27" s="18">
         <f t="shared" si="56"/>
-        <v>576702901</v>
-      </c>
-      <c r="N27" s="59">
+        <v>105314</v>
+      </c>
+      <c r="G27" s="18">
         <f t="shared" si="56"/>
         <v>0</v>
       </c>
-      <c r="O27" s="59">
+      <c r="H27" s="18">
         <f t="shared" si="56"/>
         <v>0</v>
       </c>
+      <c r="I27" s="18">
+        <f t="shared" si="56"/>
+        <v>107946</v>
+      </c>
+      <c r="J27" s="18">
+        <f t="shared" ref="J27:J30" si="62">SUM(E27:I27)</f>
+        <v>213260</v>
+      </c>
+      <c r="L27" s="97">
+        <f t="shared" si="57"/>
+        <v>0</v>
+      </c>
+      <c r="M27" s="59">
+        <f t="shared" si="57"/>
+        <v>576702901</v>
+      </c>
+      <c r="N27" s="59">
+        <f t="shared" si="57"/>
+        <v>0</v>
+      </c>
+      <c r="O27" s="59">
+        <f t="shared" si="57"/>
+        <v>0</v>
+      </c>
       <c r="P27" s="59">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>101435</v>
       </c>
       <c r="Q27" s="59">
-        <f t="shared" ref="Q27:Q30" si="62">SUM(L27:P27)</f>
+        <f t="shared" ref="Q27:Q30" si="63">SUM(L27:P27)</f>
         <v>576804336</v>
       </c>
       <c r="S27" s="90">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>7195</v>
       </c>
       <c r="T27" s="30">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>51553</v>
       </c>
       <c r="U27" s="30">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>9023</v>
       </c>
       <c r="V27" s="30">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>103585</v>
       </c>
       <c r="W27" s="30">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>25399</v>
       </c>
       <c r="X27" s="30">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>16505</v>
       </c>
       <c r="Y27" s="30">
-        <f t="shared" ref="Y27:Y30" si="63">SUM(S27:X27)</f>
+        <f t="shared" ref="Y27:Y30" si="64">SUM(S27:X27)</f>
         <v>213260</v>
       </c>
       <c r="AA27" s="104">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>52631529</v>
       </c>
       <c r="AB27" s="64">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>271532147</v>
       </c>
       <c r="AC27" s="64">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>63246530</v>
       </c>
       <c r="AD27" s="64">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>44964557</v>
       </c>
       <c r="AE27" s="64">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>93622843</v>
       </c>
       <c r="AF27" s="64">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>50806730</v>
       </c>
       <c r="AG27" s="64">
-        <f t="shared" ref="AG27:AG30" si="64">SUM(AA27:AF27)</f>
+        <f t="shared" ref="AG27:AG30" si="65">SUM(AA27:AF27)</f>
         <v>576804336</v>
       </c>
       <c r="AI27" s="93"/>
@@ -9625,51 +9654,51 @@
       <c r="AT27" s="49"/>
       <c r="AU27" s="49"/>
       <c r="AW27" s="82">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>32696</v>
       </c>
       <c r="AX27" s="46">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>31651</v>
       </c>
       <c r="AY27" s="46">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>40967</v>
       </c>
       <c r="AZ27" s="46">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>107946</v>
       </c>
       <c r="BA27" s="46">
-        <f t="shared" si="59"/>
-        <v>0</v>
-      </c>
-      <c r="BB27" s="46">
-        <f t="shared" ref="BB27:BB30" si="65">SUM(AW27:BA27)</f>
-        <v>213260</v>
-      </c>
-      <c r="BD27" s="97">
-        <f t="shared" si="60"/>
-        <v>160364763</v>
-      </c>
-      <c r="BE27" s="69">
-        <f t="shared" si="60"/>
-        <v>201880917</v>
-      </c>
-      <c r="BF27" s="69">
-        <f t="shared" si="60"/>
-        <v>214457221</v>
-      </c>
-      <c r="BG27" s="69">
-        <f t="shared" si="60"/>
-        <v>101435</v>
-      </c>
-      <c r="BH27" s="69">
         <f t="shared" si="60"/>
         <v>0</v>
       </c>
+      <c r="BB27" s="46">
+        <f t="shared" ref="BB27:BB30" si="66">SUM(AW27:BA27)</f>
+        <v>213260</v>
+      </c>
+      <c r="BD27" s="97">
+        <f t="shared" si="61"/>
+        <v>160364763</v>
+      </c>
+      <c r="BE27" s="69">
+        <f t="shared" si="61"/>
+        <v>201880917</v>
+      </c>
+      <c r="BF27" s="69">
+        <f t="shared" si="61"/>
+        <v>214457221</v>
+      </c>
+      <c r="BG27" s="69">
+        <f t="shared" si="61"/>
+        <v>101435</v>
+      </c>
+      <c r="BH27" s="69">
+        <f t="shared" si="61"/>
+        <v>0</v>
+      </c>
       <c r="BI27" s="69">
-        <f t="shared" ref="BI27:BI30" si="66">SUM(BD27:BH27)</f>
+        <f t="shared" ref="BI27:BI30" si="67">SUM(BD27:BH27)</f>
         <v>576804336</v>
       </c>
     </row>
@@ -9686,107 +9715,107 @@
         <v>687706530</v>
       </c>
       <c r="E28" s="83">
-        <f>SUMIFS(ventas_unidades,ventas_region,$A28,ventas_producto,E$25)</f>
+        <f t="shared" si="56"/>
         <v>2738</v>
       </c>
       <c r="F28" s="19">
-        <f>SUMIFS(ventas_unidades,ventas_region,$A28,ventas_producto,F$25)</f>
+        <f t="shared" si="56"/>
         <v>1928</v>
       </c>
       <c r="G28" s="19">
-        <f>SUMIFS(ventas_unidades,ventas_region,$A28,ventas_producto,G$25)</f>
+        <f t="shared" si="56"/>
         <v>109437</v>
       </c>
       <c r="H28" s="19">
-        <f>SUMIFS(ventas_unidades,ventas_region,$A28,ventas_producto,H$25)</f>
+        <f t="shared" si="56"/>
         <v>1927</v>
       </c>
       <c r="I28" s="19">
-        <f>SUMIFS(ventas_unidades,ventas_region,$A28,ventas_producto,I$25)</f>
-        <v>0</v>
-      </c>
-      <c r="J28" s="19">
-        <f t="shared" si="61"/>
-        <v>116030</v>
-      </c>
-      <c r="L28" s="98">
-        <f t="shared" si="56"/>
-        <v>844832</v>
-      </c>
-      <c r="M28" s="60">
-        <f t="shared" si="56"/>
-        <v>108214</v>
-      </c>
-      <c r="N28" s="60">
-        <f t="shared" si="56"/>
-        <v>685829502</v>
-      </c>
-      <c r="O28" s="60">
-        <f t="shared" si="56"/>
-        <v>923982</v>
-      </c>
-      <c r="P28" s="60">
         <f t="shared" si="56"/>
         <v>0</v>
       </c>
+      <c r="J28" s="19">
+        <f t="shared" si="62"/>
+        <v>116030</v>
+      </c>
+      <c r="L28" s="98">
+        <f t="shared" si="57"/>
+        <v>844832</v>
+      </c>
+      <c r="M28" s="60">
+        <f t="shared" si="57"/>
+        <v>108214</v>
+      </c>
+      <c r="N28" s="60">
+        <f t="shared" si="57"/>
+        <v>685829502</v>
+      </c>
+      <c r="O28" s="60">
+        <f t="shared" si="57"/>
+        <v>923982</v>
+      </c>
+      <c r="P28" s="60">
+        <f t="shared" si="57"/>
+        <v>0</v>
+      </c>
       <c r="Q28" s="60">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>687706530</v>
       </c>
       <c r="S28" s="91">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>39170</v>
       </c>
       <c r="T28" s="31">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>19565</v>
       </c>
       <c r="U28" s="31">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>6969</v>
       </c>
       <c r="V28" s="31">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>9925</v>
       </c>
       <c r="W28" s="31">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>12633</v>
       </c>
       <c r="X28" s="31">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>27768</v>
       </c>
       <c r="Y28" s="31">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>116030</v>
       </c>
       <c r="AA28" s="105">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>240927099</v>
       </c>
       <c r="AB28" s="65">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>131950052</v>
       </c>
       <c r="AC28" s="65">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>40433106</v>
       </c>
       <c r="AD28" s="65">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>27153333</v>
       </c>
       <c r="AE28" s="65">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>78668644</v>
       </c>
       <c r="AF28" s="65">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>168574296</v>
       </c>
       <c r="AG28" s="65">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>687706530</v>
       </c>
       <c r="AI28" s="93"/>
@@ -9802,51 +9831,51 @@
       <c r="AT28" s="49"/>
       <c r="AU28" s="49"/>
       <c r="AW28" s="83">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>39124</v>
       </c>
       <c r="AX28" s="47">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>34000</v>
       </c>
       <c r="AY28" s="47">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>31330</v>
       </c>
       <c r="AZ28" s="47">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>7721</v>
       </c>
       <c r="BA28" s="47">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>3855</v>
       </c>
       <c r="BB28" s="47">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>116030</v>
       </c>
       <c r="BD28" s="98">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>220801841</v>
       </c>
       <c r="BE28" s="70">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>239992813</v>
       </c>
       <c r="BF28" s="70">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>216914467</v>
       </c>
       <c r="BG28" s="70">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>8965213</v>
       </c>
       <c r="BH28" s="70">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>1032196</v>
       </c>
       <c r="BI28" s="70">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>687706530</v>
       </c>
     </row>
@@ -9863,107 +9892,107 @@
         <v>654677692</v>
       </c>
       <c r="E29" s="82">
-        <f>SUMIFS(ventas_unidades,ventas_region,$A29,ventas_producto,E$25)</f>
-        <v>0</v>
-      </c>
-      <c r="F29" s="18">
-        <f>SUMIFS(ventas_unidades,ventas_region,$A29,ventas_producto,F$25)</f>
-        <v>197277</v>
-      </c>
-      <c r="G29" s="18">
-        <f>SUMIFS(ventas_unidades,ventas_region,$A29,ventas_producto,G$25)</f>
-        <v>0</v>
-      </c>
-      <c r="H29" s="18">
-        <f>SUMIFS(ventas_unidades,ventas_region,$A29,ventas_producto,H$25)</f>
-        <v>113588</v>
-      </c>
-      <c r="I29" s="18">
-        <f>SUMIFS(ventas_unidades,ventas_region,$A29,ventas_producto,I$25)</f>
-        <v>1927</v>
-      </c>
-      <c r="J29" s="18">
-        <f t="shared" si="61"/>
-        <v>312792</v>
-      </c>
-      <c r="L29" s="97">
         <f t="shared" si="56"/>
         <v>0</v>
       </c>
-      <c r="M29" s="59">
+      <c r="F29" s="18">
         <f t="shared" si="56"/>
-        <v>1313277</v>
-      </c>
-      <c r="N29" s="59">
+        <v>197277</v>
+      </c>
+      <c r="G29" s="18">
         <f t="shared" si="56"/>
         <v>0</v>
       </c>
+      <c r="H29" s="18">
+        <f t="shared" si="56"/>
+        <v>113588</v>
+      </c>
+      <c r="I29" s="18">
+        <f t="shared" si="56"/>
+        <v>1927</v>
+      </c>
+      <c r="J29" s="18">
+        <f t="shared" si="62"/>
+        <v>312792</v>
+      </c>
+      <c r="L29" s="97">
+        <f t="shared" si="57"/>
+        <v>0</v>
+      </c>
+      <c r="M29" s="59">
+        <f t="shared" si="57"/>
+        <v>1313277</v>
+      </c>
+      <c r="N29" s="59">
+        <f t="shared" si="57"/>
+        <v>0</v>
+      </c>
       <c r="O29" s="59">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>652816023</v>
       </c>
       <c r="P29" s="59">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>548392</v>
       </c>
       <c r="Q29" s="59">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>654677692</v>
       </c>
       <c r="S29" s="90">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>39255</v>
       </c>
       <c r="T29" s="30">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>12991</v>
       </c>
       <c r="U29" s="30">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>2096</v>
       </c>
       <c r="V29" s="30">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>197831</v>
       </c>
       <c r="W29" s="30">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>53237</v>
       </c>
       <c r="X29" s="30">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>7382</v>
       </c>
       <c r="Y29" s="30">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>312792</v>
       </c>
       <c r="AA29" s="104">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>170461858</v>
       </c>
       <c r="AB29" s="64">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>75839132</v>
       </c>
       <c r="AC29" s="64">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>31378227</v>
       </c>
       <c r="AD29" s="64">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>23830600</v>
       </c>
       <c r="AE29" s="64">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>336034466</v>
       </c>
       <c r="AF29" s="64">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>17133409</v>
       </c>
       <c r="AG29" s="64">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>654677692</v>
       </c>
       <c r="AI29" s="93"/>
@@ -9979,51 +10008,51 @@
       <c r="AT29" s="49"/>
       <c r="AU29" s="49"/>
       <c r="AW29" s="82">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>40573</v>
       </c>
       <c r="AX29" s="46">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>39442</v>
       </c>
       <c r="AY29" s="46">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>33573</v>
       </c>
       <c r="AZ29" s="46">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>4903</v>
       </c>
       <c r="BA29" s="46">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>194301</v>
       </c>
       <c r="BB29" s="46">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>312792</v>
       </c>
       <c r="BD29" s="97">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>190929354</v>
       </c>
       <c r="BE29" s="69">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>221383553</v>
       </c>
       <c r="BF29" s="69">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>240503116</v>
       </c>
       <c r="BG29" s="69">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>483929</v>
       </c>
       <c r="BH29" s="69">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>1377740</v>
       </c>
       <c r="BI29" s="69">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>654677692</v>
       </c>
     </row>
@@ -10040,107 +10069,107 @@
         <v>664722025</v>
       </c>
       <c r="E30" s="83">
-        <f>SUMIFS(ventas_unidades,ventas_region,$A30,ventas_producto,E$25)</f>
+        <f t="shared" si="56"/>
         <v>7128</v>
       </c>
       <c r="F30" s="19">
-        <f>SUMIFS(ventas_unidades,ventas_region,$A30,ventas_producto,F$25)</f>
-        <v>0</v>
-      </c>
-      <c r="G30" s="19">
-        <f>SUMIFS(ventas_unidades,ventas_region,$A30,ventas_producto,G$25)</f>
-        <v>0</v>
-      </c>
-      <c r="H30" s="19">
-        <f>SUMIFS(ventas_unidades,ventas_region,$A30,ventas_producto,H$25)</f>
-        <v>0</v>
-      </c>
-      <c r="I30" s="19">
-        <f>SUMIFS(ventas_unidades,ventas_region,$A30,ventas_producto,I$25)</f>
-        <v>98908</v>
-      </c>
-      <c r="J30" s="19">
-        <f t="shared" si="61"/>
-        <v>106036</v>
-      </c>
-      <c r="L30" s="98">
-        <f t="shared" si="56"/>
-        <v>9123918</v>
-      </c>
-      <c r="M30" s="60">
         <f t="shared" si="56"/>
         <v>0</v>
       </c>
-      <c r="N30" s="60">
+      <c r="G30" s="19">
         <f t="shared" si="56"/>
         <v>0</v>
       </c>
-      <c r="O30" s="60">
+      <c r="H30" s="19">
         <f t="shared" si="56"/>
         <v>0</v>
       </c>
+      <c r="I30" s="19">
+        <f t="shared" si="56"/>
+        <v>98908</v>
+      </c>
+      <c r="J30" s="19">
+        <f t="shared" si="62"/>
+        <v>106036</v>
+      </c>
+      <c r="L30" s="98">
+        <f t="shared" si="57"/>
+        <v>9123918</v>
+      </c>
+      <c r="M30" s="60">
+        <f t="shared" si="57"/>
+        <v>0</v>
+      </c>
+      <c r="N30" s="60">
+        <f t="shared" si="57"/>
+        <v>0</v>
+      </c>
+      <c r="O30" s="60">
+        <f t="shared" si="57"/>
+        <v>0</v>
+      </c>
       <c r="P30" s="60">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>655598107</v>
       </c>
       <c r="Q30" s="60">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>664722025</v>
       </c>
       <c r="S30" s="91">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>12970</v>
       </c>
       <c r="T30" s="31">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>14165</v>
       </c>
       <c r="U30" s="31">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>5143</v>
       </c>
       <c r="V30" s="31">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>14291</v>
       </c>
       <c r="W30" s="31">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>19979</v>
       </c>
       <c r="X30" s="31">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>39488</v>
       </c>
       <c r="Y30" s="31">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>106036</v>
       </c>
       <c r="AA30" s="105">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>71950539</v>
       </c>
       <c r="AB30" s="65">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>88920515</v>
       </c>
       <c r="AC30" s="65">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>31867112</v>
       </c>
       <c r="AD30" s="65">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>76700859</v>
       </c>
       <c r="AE30" s="65">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>119641616</v>
       </c>
       <c r="AF30" s="65">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>275641384</v>
       </c>
       <c r="AG30" s="65">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>664722025</v>
       </c>
       <c r="AI30" s="93"/>
@@ -10156,51 +10185,51 @@
       <c r="AT30" s="49"/>
       <c r="AU30" s="49"/>
       <c r="AW30" s="83">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>36557</v>
       </c>
       <c r="AX30" s="47">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>28900</v>
       </c>
       <c r="AY30" s="47">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>33451</v>
       </c>
       <c r="AZ30" s="47">
-        <f t="shared" si="59"/>
-        <v>0</v>
-      </c>
-      <c r="BA30" s="47">
-        <f t="shared" si="59"/>
-        <v>7128</v>
-      </c>
-      <c r="BB30" s="47">
-        <f t="shared" si="65"/>
-        <v>106036</v>
-      </c>
-      <c r="BD30" s="98">
-        <f t="shared" si="60"/>
-        <v>216479082</v>
-      </c>
-      <c r="BE30" s="70">
-        <f t="shared" si="60"/>
-        <v>240247726</v>
-      </c>
-      <c r="BF30" s="70">
-        <f t="shared" si="60"/>
-        <v>198871299</v>
-      </c>
-      <c r="BG30" s="70">
         <f t="shared" si="60"/>
         <v>0</v>
       </c>
+      <c r="BA30" s="47">
+        <f t="shared" si="60"/>
+        <v>7128</v>
+      </c>
+      <c r="BB30" s="47">
+        <f t="shared" si="66"/>
+        <v>106036</v>
+      </c>
+      <c r="BD30" s="98">
+        <f t="shared" si="61"/>
+        <v>216479082</v>
+      </c>
+      <c r="BE30" s="70">
+        <f t="shared" si="61"/>
+        <v>240247726</v>
+      </c>
+      <c r="BF30" s="70">
+        <f t="shared" si="61"/>
+        <v>198871299</v>
+      </c>
+      <c r="BG30" s="70">
+        <f t="shared" si="61"/>
+        <v>0</v>
+      </c>
       <c r="BH30" s="70">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>9123918</v>
       </c>
       <c r="BI30" s="70">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>664722025</v>
       </c>
     </row>
@@ -10221,23 +10250,23 @@
         <v>110903</v>
       </c>
       <c r="F31" s="50">
-        <f t="shared" ref="F31:J31" si="67">SUM(F26:F30)</f>
+        <f t="shared" ref="F31:J31" si="68">SUM(F26:F30)</f>
         <v>304519</v>
       </c>
       <c r="G31" s="50">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>118380</v>
       </c>
       <c r="H31" s="50">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>115644</v>
       </c>
       <c r="I31" s="50">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>208781</v>
       </c>
       <c r="J31" s="117">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>858227</v>
       </c>
       <c r="L31" s="108">
@@ -10245,23 +10274,23 @@
         <v>650543568</v>
       </c>
       <c r="M31" s="68">
-        <f t="shared" ref="M31" si="68">SUM(M26:M30)</f>
+        <f t="shared" ref="M31" si="69">SUM(M26:M30)</f>
         <v>578124392</v>
       </c>
       <c r="N31" s="68">
-        <f t="shared" ref="N31" si="69">SUM(N26:N30)</f>
+        <f t="shared" ref="N31" si="70">SUM(N26:N30)</f>
         <v>690157736</v>
       </c>
       <c r="O31" s="68">
-        <f t="shared" ref="O31" si="70">SUM(O26:O30)</f>
+        <f t="shared" ref="O31" si="71">SUM(O26:O30)</f>
         <v>654943915</v>
       </c>
       <c r="P31" s="68">
-        <f t="shared" ref="P31" si="71">SUM(P26:P30)</f>
+        <f t="shared" ref="P31" si="72">SUM(P26:P30)</f>
         <v>656247934</v>
       </c>
       <c r="Q31" s="114">
-        <f t="shared" ref="Q31" si="72">SUM(Q26:Q30)</f>
+        <f t="shared" ref="Q31" si="73">SUM(Q26:Q30)</f>
         <v>3230017545</v>
       </c>
       <c r="S31" s="92">
@@ -10269,27 +10298,27 @@
         <v>121665</v>
       </c>
       <c r="T31" s="40">
-        <f t="shared" ref="T31:Y31" si="73">SUM(T26:T30)</f>
+        <f t="shared" ref="T31:Y31" si="74">SUM(T26:T30)</f>
         <v>125620</v>
       </c>
       <c r="U31" s="40">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>32356</v>
       </c>
       <c r="V31" s="40">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>356297</v>
       </c>
       <c r="W31" s="40">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>122295</v>
       </c>
       <c r="X31" s="40">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>99994</v>
       </c>
       <c r="Y31" s="40">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>858227</v>
       </c>
       <c r="AA31" s="106">
@@ -10297,27 +10326,27 @@
         <v>645115066</v>
       </c>
       <c r="AB31" s="66">
-        <f t="shared" ref="AB31" si="74">SUM(AB26:AB30)</f>
+        <f t="shared" ref="AB31" si="75">SUM(AB26:AB30)</f>
         <v>761464717</v>
       </c>
       <c r="AC31" s="66">
-        <f t="shared" ref="AC31" si="75">SUM(AC26:AC30)</f>
+        <f t="shared" ref="AC31" si="76">SUM(AC26:AC30)</f>
         <v>226722785</v>
       </c>
       <c r="AD31" s="66">
-        <f t="shared" ref="AD31" si="76">SUM(AD26:AD30)</f>
+        <f t="shared" ref="AD31" si="77">SUM(AD26:AD30)</f>
         <v>312257691</v>
       </c>
       <c r="AE31" s="66">
-        <f t="shared" ref="AE31" si="77">SUM(AE26:AE30)</f>
+        <f t="shared" ref="AE31" si="78">SUM(AE26:AE30)</f>
         <v>722503562</v>
       </c>
       <c r="AF31" s="66">
-        <f t="shared" ref="AF31" si="78">SUM(AF26:AF30)</f>
+        <f t="shared" ref="AF31" si="79">SUM(AF26:AF30)</f>
         <v>561953724</v>
       </c>
       <c r="AG31" s="114">
-        <f t="shared" ref="AG31" si="79">SUM(AG26:AG30)</f>
+        <f t="shared" ref="AG31" si="80">SUM(AG26:AG30)</f>
         <v>3230017545</v>
       </c>
       <c r="AI31" s="93"/>
@@ -10333,23 +10362,23 @@
       <c r="AT31" s="49"/>
       <c r="AU31" s="49"/>
       <c r="AW31" s="94">
-        <f t="shared" ref="AW31:BA31" si="80">SUM(AW27:AW30)</f>
+        <f t="shared" ref="AW31:BA31" si="81">SUM(AW27:AW30)</f>
         <v>148950</v>
       </c>
       <c r="AX31" s="50">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>133993</v>
       </c>
       <c r="AY31" s="50">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>139321</v>
       </c>
       <c r="AZ31" s="50">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>120570</v>
       </c>
       <c r="BA31" s="50">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>205284</v>
       </c>
       <c r="BB31" s="117">
@@ -10361,23 +10390,23 @@
         <v>1007244151</v>
       </c>
       <c r="BE31" s="68">
-        <f t="shared" ref="BE31:BI31" si="81">SUM(BE26:BE30)</f>
+        <f t="shared" ref="BE31:BI31" si="82">SUM(BE26:BE30)</f>
         <v>1106846472</v>
       </c>
       <c r="BF31" s="68">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>1089310347</v>
       </c>
       <c r="BG31" s="68">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>15082721</v>
       </c>
       <c r="BH31" s="68">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>11533854</v>
       </c>
       <c r="BI31" s="114">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>3230017545</v>
       </c>
     </row>
@@ -10532,23 +10561,23 @@
         <v>1007244151</v>
       </c>
       <c r="E34" s="81">
-        <f t="shared" ref="E34:I38" si="82">SUMIFS(ventas_unidades,ventas_año,$A34,ventas_producto,E$25)</f>
+        <f t="shared" ref="E34:I38" si="83">SUMIFS(ventas_unidades,ventas_año,$A34,ventas_producto,E$25)</f>
         <v>33032</v>
       </c>
       <c r="F34" s="17">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>32696</v>
       </c>
       <c r="G34" s="17">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>39124</v>
       </c>
       <c r="H34" s="17">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>40573</v>
       </c>
       <c r="I34" s="17">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>36557</v>
       </c>
       <c r="J34" s="17">
@@ -10556,23 +10585,23 @@
         <v>181982</v>
       </c>
       <c r="L34" s="96">
-        <f t="shared" ref="L34:P38" si="83">SUMIFS(ventas_total,ventas_año,$A34,ventas_producto,L$25)</f>
+        <f t="shared" ref="L34:P38" si="84">SUMIFS(ventas_total,ventas_año,$A34,ventas_producto,L$25)</f>
         <v>218669111</v>
       </c>
       <c r="M34" s="58">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>160364763</v>
       </c>
       <c r="N34" s="58">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>220801841</v>
       </c>
       <c r="O34" s="58">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>190929354</v>
       </c>
       <c r="P34" s="58">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>216479082</v>
       </c>
       <c r="Q34" s="58">
@@ -10580,27 +10609,27 @@
         <v>1007244151</v>
       </c>
       <c r="S34" s="89">
-        <f t="shared" ref="S34:X38" si="84">SUMIFS(ventas_unidades,ventas_año,$A34,ventas_vendedor,S$33)</f>
+        <f t="shared" ref="S34:X38" si="85">SUMIFS(ventas_unidades,ventas_año,$A34,ventas_vendedor,S$33)</f>
         <v>33623</v>
       </c>
       <c r="T34" s="29">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>45235</v>
       </c>
       <c r="U34" s="29">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>12423</v>
       </c>
       <c r="V34" s="29">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>20990</v>
       </c>
       <c r="W34" s="29">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>44558</v>
       </c>
       <c r="X34" s="29">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>25153</v>
       </c>
       <c r="Y34" s="29">
@@ -10608,27 +10637,27 @@
         <v>181982</v>
       </c>
       <c r="AA34" s="103">
-        <f t="shared" ref="AA34:AF38" si="85">SUMIFS(ventas_unidades,ventas_año,$A34,ventas_vendedor,AA$33)</f>
+        <f t="shared" ref="AA34:AF38" si="86">SUMIFS(ventas_unidades,ventas_año,$A34,ventas_vendedor,AA$33)</f>
         <v>33623</v>
       </c>
       <c r="AB34" s="63">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>45235</v>
       </c>
       <c r="AC34" s="63">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>12423</v>
       </c>
       <c r="AD34" s="63">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>20990</v>
       </c>
       <c r="AE34" s="63">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>44558</v>
       </c>
       <c r="AF34" s="63">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>25153</v>
       </c>
       <c r="AG34" s="63">
@@ -10636,23 +10665,23 @@
         <v>181982</v>
       </c>
       <c r="AI34" s="81">
-        <f t="shared" ref="AI34:AM38" si="86">SUMIFS(ventas_unidades,ventas_año,$A34,ventas_region,AI$33)</f>
+        <f t="shared" ref="AI34:AM38" si="87">SUMIFS(ventas_unidades,ventas_año,$A34,ventas_region,AI$33)</f>
         <v>33032</v>
       </c>
       <c r="AJ34" s="17">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>32696</v>
       </c>
       <c r="AK34" s="17">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>39124</v>
       </c>
       <c r="AL34" s="17">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>40573</v>
       </c>
       <c r="AM34" s="17">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>36557</v>
       </c>
       <c r="AN34" s="17">
@@ -10660,23 +10689,23 @@
         <v>181982</v>
       </c>
       <c r="AP34" s="110">
-        <f t="shared" ref="AP34:AT38" si="87">SUMIFS(ventas_total,ventas_año,$A34,ventas_region,AP$33)</f>
+        <f t="shared" ref="AP34:AT38" si="88">SUMIFS(ventas_total,ventas_año,$A34,ventas_region,AP$33)</f>
         <v>218669111</v>
       </c>
       <c r="AQ34" s="41">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>160364763</v>
       </c>
       <c r="AR34" s="41">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>220801841</v>
       </c>
       <c r="AS34" s="41">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>190929354</v>
       </c>
       <c r="AT34" s="41">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>216479082</v>
       </c>
       <c r="AU34" s="41">
@@ -10709,155 +10738,155 @@
         <v>1106846472</v>
       </c>
       <c r="E35" s="82">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>32671</v>
       </c>
       <c r="F35" s="18">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>31651</v>
       </c>
       <c r="G35" s="18">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>34000</v>
       </c>
       <c r="H35" s="18">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>39442</v>
       </c>
       <c r="I35" s="18">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>28900</v>
       </c>
       <c r="J35" s="18">
-        <f t="shared" ref="J35:J38" si="88">SUM(E35:I35)</f>
+        <f t="shared" ref="J35:J38" si="89">SUM(E35:I35)</f>
         <v>166664</v>
       </c>
       <c r="L35" s="97">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>203341463</v>
       </c>
       <c r="M35" s="59">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>201880917</v>
       </c>
       <c r="N35" s="59">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>239992813</v>
       </c>
       <c r="O35" s="59">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>221383553</v>
       </c>
       <c r="P35" s="59">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>240247726</v>
       </c>
       <c r="Q35" s="59">
-        <f t="shared" ref="Q35:Q38" si="89">SUM(L35:P35)</f>
+        <f t="shared" ref="Q35:Q38" si="90">SUM(L35:P35)</f>
         <v>1106846472</v>
       </c>
       <c r="S35" s="90">
-        <f t="shared" si="84"/>
-        <v>42339</v>
-      </c>
-      <c r="T35" s="30">
-        <f t="shared" si="84"/>
-        <v>39435</v>
-      </c>
-      <c r="U35" s="30">
-        <f t="shared" si="84"/>
-        <v>12194</v>
-      </c>
-      <c r="V35" s="30">
-        <f t="shared" si="84"/>
-        <v>11750</v>
-      </c>
-      <c r="W35" s="30">
-        <f t="shared" si="84"/>
-        <v>27319</v>
-      </c>
-      <c r="X35" s="30">
-        <f t="shared" si="84"/>
-        <v>33627</v>
-      </c>
-      <c r="Y35" s="30">
-        <f t="shared" ref="Y35:Y38" si="90">SUM(S35:X35)</f>
-        <v>166664</v>
-      </c>
-      <c r="AA35" s="104">
         <f t="shared" si="85"/>
         <v>42339</v>
       </c>
-      <c r="AB35" s="64">
+      <c r="T35" s="30">
         <f t="shared" si="85"/>
         <v>39435</v>
       </c>
-      <c r="AC35" s="64">
+      <c r="U35" s="30">
         <f t="shared" si="85"/>
         <v>12194</v>
       </c>
-      <c r="AD35" s="64">
+      <c r="V35" s="30">
         <f t="shared" si="85"/>
         <v>11750</v>
       </c>
-      <c r="AE35" s="64">
+      <c r="W35" s="30">
         <f t="shared" si="85"/>
         <v>27319</v>
       </c>
-      <c r="AF35" s="64">
+      <c r="X35" s="30">
         <f t="shared" si="85"/>
         <v>33627</v>
       </c>
+      <c r="Y35" s="30">
+        <f t="shared" ref="Y35:Y38" si="91">SUM(S35:X35)</f>
+        <v>166664</v>
+      </c>
+      <c r="AA35" s="104">
+        <f t="shared" si="86"/>
+        <v>42339</v>
+      </c>
+      <c r="AB35" s="64">
+        <f t="shared" si="86"/>
+        <v>39435</v>
+      </c>
+      <c r="AC35" s="64">
+        <f t="shared" si="86"/>
+        <v>12194</v>
+      </c>
+      <c r="AD35" s="64">
+        <f t="shared" si="86"/>
+        <v>11750</v>
+      </c>
+      <c r="AE35" s="64">
+        <f t="shared" si="86"/>
+        <v>27319</v>
+      </c>
+      <c r="AF35" s="64">
+        <f t="shared" si="86"/>
+        <v>33627</v>
+      </c>
       <c r="AG35" s="64">
-        <f t="shared" ref="AG35:AG38" si="91">SUM(AA35:AF35)</f>
+        <f t="shared" ref="AG35:AG38" si="92">SUM(AA35:AF35)</f>
         <v>166664</v>
       </c>
       <c r="AI35" s="82">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>32671</v>
       </c>
       <c r="AJ35" s="18">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>31651</v>
       </c>
       <c r="AK35" s="18">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>34000</v>
       </c>
       <c r="AL35" s="18">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>39442</v>
       </c>
       <c r="AM35" s="18">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>28900</v>
       </c>
       <c r="AN35" s="18">
-        <f t="shared" ref="AN35:AN38" si="92">SUM(AI35:AM35)</f>
+        <f t="shared" ref="AN35:AN38" si="93">SUM(AI35:AM35)</f>
         <v>166664</v>
       </c>
       <c r="AP35" s="111">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>203341463</v>
       </c>
       <c r="AQ35" s="44">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>201880917</v>
       </c>
       <c r="AR35" s="44">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>239992813</v>
       </c>
       <c r="AS35" s="44">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>221383553</v>
       </c>
       <c r="AT35" s="44">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>240247726</v>
       </c>
       <c r="AU35" s="44">
-        <f t="shared" ref="AU35:AU38" si="93">SUM(AP35:AT35)</f>
+        <f t="shared" ref="AU35:AU38" si="94">SUM(AP35:AT35)</f>
         <v>1106846472</v>
       </c>
       <c r="AW35" s="93"/>
@@ -10886,155 +10915,155 @@
         <v>1089310347</v>
       </c>
       <c r="E36" s="83">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>35334</v>
       </c>
       <c r="F36" s="19">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>40967</v>
       </c>
       <c r="G36" s="19">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>31330</v>
       </c>
       <c r="H36" s="19">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>33573</v>
       </c>
       <c r="I36" s="19">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>33451</v>
       </c>
       <c r="J36" s="19">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>174655</v>
       </c>
       <c r="L36" s="98">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>218564244</v>
       </c>
       <c r="M36" s="60">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>214457221</v>
       </c>
       <c r="N36" s="60">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>216914467</v>
       </c>
       <c r="O36" s="60">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>240503116</v>
       </c>
       <c r="P36" s="60">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>198871299</v>
       </c>
       <c r="Q36" s="60">
-        <f t="shared" si="89"/>
+        <f t="shared" si="90"/>
         <v>1089310347</v>
       </c>
       <c r="S36" s="91">
-        <f t="shared" si="84"/>
-        <v>33889</v>
-      </c>
-      <c r="T36" s="31">
-        <f t="shared" si="84"/>
-        <v>40950</v>
-      </c>
-      <c r="U36" s="31">
-        <f t="shared" si="84"/>
-        <v>7739</v>
-      </c>
-      <c r="V36" s="31">
-        <f t="shared" si="84"/>
-        <v>24117</v>
-      </c>
-      <c r="W36" s="31">
-        <f t="shared" si="84"/>
-        <v>31540</v>
-      </c>
-      <c r="X36" s="31">
-        <f t="shared" si="84"/>
-        <v>36420</v>
-      </c>
-      <c r="Y36" s="31">
-        <f t="shared" si="90"/>
-        <v>174655</v>
-      </c>
-      <c r="AA36" s="105">
         <f t="shared" si="85"/>
         <v>33889</v>
       </c>
-      <c r="AB36" s="65">
+      <c r="T36" s="31">
         <f t="shared" si="85"/>
         <v>40950</v>
       </c>
-      <c r="AC36" s="65">
+      <c r="U36" s="31">
         <f t="shared" si="85"/>
         <v>7739</v>
       </c>
-      <c r="AD36" s="65">
+      <c r="V36" s="31">
         <f t="shared" si="85"/>
         <v>24117</v>
       </c>
-      <c r="AE36" s="65">
+      <c r="W36" s="31">
         <f t="shared" si="85"/>
         <v>31540</v>
       </c>
-      <c r="AF36" s="65">
+      <c r="X36" s="31">
         <f t="shared" si="85"/>
         <v>36420</v>
       </c>
-      <c r="AG36" s="65">
+      <c r="Y36" s="31">
         <f t="shared" si="91"/>
         <v>174655</v>
       </c>
-      <c r="AI36" s="83">
+      <c r="AA36" s="105">
         <f t="shared" si="86"/>
-        <v>35334</v>
-      </c>
-      <c r="AJ36" s="19">
+        <v>33889</v>
+      </c>
+      <c r="AB36" s="65">
         <f t="shared" si="86"/>
-        <v>40967</v>
-      </c>
-      <c r="AK36" s="19">
+        <v>40950</v>
+      </c>
+      <c r="AC36" s="65">
         <f t="shared" si="86"/>
-        <v>31330</v>
-      </c>
-      <c r="AL36" s="19">
+        <v>7739</v>
+      </c>
+      <c r="AD36" s="65">
         <f t="shared" si="86"/>
-        <v>33573</v>
-      </c>
-      <c r="AM36" s="19">
+        <v>24117</v>
+      </c>
+      <c r="AE36" s="65">
         <f t="shared" si="86"/>
-        <v>33451</v>
-      </c>
-      <c r="AN36" s="19">
+        <v>31540</v>
+      </c>
+      <c r="AF36" s="65">
+        <f t="shared" si="86"/>
+        <v>36420</v>
+      </c>
+      <c r="AG36" s="65">
         <f t="shared" si="92"/>
         <v>174655</v>
       </c>
+      <c r="AI36" s="83">
+        <f t="shared" si="87"/>
+        <v>35334</v>
+      </c>
+      <c r="AJ36" s="19">
+        <f t="shared" si="87"/>
+        <v>40967</v>
+      </c>
+      <c r="AK36" s="19">
+        <f t="shared" si="87"/>
+        <v>31330</v>
+      </c>
+      <c r="AL36" s="19">
+        <f t="shared" si="87"/>
+        <v>33573</v>
+      </c>
+      <c r="AM36" s="19">
+        <f t="shared" si="87"/>
+        <v>33451</v>
+      </c>
+      <c r="AN36" s="19">
+        <f t="shared" si="93"/>
+        <v>174655</v>
+      </c>
       <c r="AP36" s="112">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>218564244</v>
       </c>
       <c r="AQ36" s="45">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>214457221</v>
       </c>
       <c r="AR36" s="45">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>216914467</v>
       </c>
       <c r="AS36" s="45">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>240503116</v>
       </c>
       <c r="AT36" s="45">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>198871299</v>
       </c>
       <c r="AU36" s="45">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>1089310347</v>
       </c>
       <c r="AW36" s="93"/>
@@ -11063,155 +11092,155 @@
         <v>15082721</v>
       </c>
       <c r="E37" s="82">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>2738</v>
       </c>
       <c r="F37" s="18">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>4903</v>
       </c>
       <c r="G37" s="18">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>13926</v>
       </c>
       <c r="H37" s="18">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>129</v>
       </c>
       <c r="I37" s="18">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>107946</v>
       </c>
       <c r="J37" s="18">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>129642</v>
       </c>
       <c r="L37" s="97">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>844832</v>
       </c>
       <c r="M37" s="59">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>483929</v>
       </c>
       <c r="N37" s="59">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>12448615</v>
       </c>
       <c r="O37" s="59">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>1203910</v>
       </c>
       <c r="P37" s="59">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>101435</v>
       </c>
       <c r="Q37" s="59">
-        <f t="shared" si="89"/>
+        <f t="shared" si="90"/>
         <v>15082721</v>
       </c>
       <c r="S37" s="90">
-        <f t="shared" si="84"/>
-        <v>9886</v>
-      </c>
-      <c r="T37" s="30">
-        <f t="shared" si="84"/>
-        <v>0</v>
-      </c>
-      <c r="U37" s="30">
-        <f t="shared" si="84"/>
-        <v>0</v>
-      </c>
-      <c r="V37" s="30">
-        <f t="shared" si="84"/>
-        <v>107066</v>
-      </c>
-      <c r="W37" s="30">
-        <f t="shared" si="84"/>
-        <v>9823</v>
-      </c>
-      <c r="X37" s="30">
-        <f t="shared" si="84"/>
-        <v>2867</v>
-      </c>
-      <c r="Y37" s="30">
-        <f t="shared" si="90"/>
-        <v>129642</v>
-      </c>
-      <c r="AA37" s="104">
         <f t="shared" si="85"/>
         <v>9886</v>
       </c>
-      <c r="AB37" s="64">
+      <c r="T37" s="30">
         <f t="shared" si="85"/>
         <v>0</v>
       </c>
-      <c r="AC37" s="64">
+      <c r="U37" s="30">
         <f t="shared" si="85"/>
         <v>0</v>
       </c>
-      <c r="AD37" s="64">
+      <c r="V37" s="30">
         <f t="shared" si="85"/>
         <v>107066</v>
       </c>
-      <c r="AE37" s="64">
+      <c r="W37" s="30">
         <f t="shared" si="85"/>
         <v>9823</v>
       </c>
-      <c r="AF37" s="64">
+      <c r="X37" s="30">
         <f t="shared" si="85"/>
         <v>2867</v>
       </c>
-      <c r="AG37" s="64">
+      <c r="Y37" s="30">
         <f t="shared" si="91"/>
         <v>129642</v>
       </c>
-      <c r="AI37" s="82">
+      <c r="AA37" s="104">
         <f t="shared" si="86"/>
-        <v>9072</v>
-      </c>
-      <c r="AJ37" s="18">
-        <f t="shared" si="86"/>
-        <v>107946</v>
-      </c>
-      <c r="AK37" s="18">
-        <f t="shared" si="86"/>
-        <v>7721</v>
-      </c>
-      <c r="AL37" s="18">
-        <f t="shared" si="86"/>
-        <v>4903</v>
-      </c>
-      <c r="AM37" s="18">
+        <v>9886</v>
+      </c>
+      <c r="AB37" s="64">
         <f t="shared" si="86"/>
         <v>0</v>
       </c>
-      <c r="AN37" s="18">
+      <c r="AC37" s="64">
+        <f t="shared" si="86"/>
+        <v>0</v>
+      </c>
+      <c r="AD37" s="64">
+        <f t="shared" si="86"/>
+        <v>107066</v>
+      </c>
+      <c r="AE37" s="64">
+        <f t="shared" si="86"/>
+        <v>9823</v>
+      </c>
+      <c r="AF37" s="64">
+        <f t="shared" si="86"/>
+        <v>2867</v>
+      </c>
+      <c r="AG37" s="64">
         <f t="shared" si="92"/>
         <v>129642</v>
       </c>
-      <c r="AP37" s="111">
+      <c r="AI37" s="82">
         <f t="shared" si="87"/>
-        <v>5532144</v>
-      </c>
-      <c r="AQ37" s="44">
+        <v>9072</v>
+      </c>
+      <c r="AJ37" s="18">
         <f t="shared" si="87"/>
-        <v>101435</v>
-      </c>
-      <c r="AR37" s="44">
+        <v>107946</v>
+      </c>
+      <c r="AK37" s="18">
         <f t="shared" si="87"/>
-        <v>8965213</v>
-      </c>
-      <c r="AS37" s="44">
+        <v>7721</v>
+      </c>
+      <c r="AL37" s="18">
         <f t="shared" si="87"/>
-        <v>483929</v>
-      </c>
-      <c r="AT37" s="44">
+        <v>4903</v>
+      </c>
+      <c r="AM37" s="18">
         <f t="shared" si="87"/>
         <v>0</v>
       </c>
+      <c r="AN37" s="18">
+        <f t="shared" si="93"/>
+        <v>129642</v>
+      </c>
+      <c r="AP37" s="111">
+        <f t="shared" si="88"/>
+        <v>5532144</v>
+      </c>
+      <c r="AQ37" s="44">
+        <f t="shared" si="88"/>
+        <v>101435</v>
+      </c>
+      <c r="AR37" s="44">
+        <f t="shared" si="88"/>
+        <v>8965213</v>
+      </c>
+      <c r="AS37" s="44">
+        <f t="shared" si="88"/>
+        <v>483929</v>
+      </c>
+      <c r="AT37" s="44">
+        <f t="shared" si="88"/>
+        <v>0</v>
+      </c>
       <c r="AU37" s="44">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>15082721</v>
       </c>
       <c r="AW37" s="93"/>
@@ -11240,155 +11269,155 @@
         <v>11533854</v>
       </c>
       <c r="E38" s="83">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>7128</v>
       </c>
       <c r="F38" s="19">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>194302</v>
       </c>
       <c r="G38" s="19">
-        <f t="shared" si="82"/>
-        <v>0</v>
-      </c>
-      <c r="H38" s="19">
-        <f t="shared" si="82"/>
-        <v>1927</v>
-      </c>
-      <c r="I38" s="19">
-        <f t="shared" si="82"/>
-        <v>1927</v>
-      </c>
-      <c r="J38" s="19">
-        <f t="shared" si="88"/>
-        <v>205284</v>
-      </c>
-      <c r="L38" s="98">
-        <f t="shared" si="83"/>
-        <v>9123918</v>
-      </c>
-      <c r="M38" s="60">
-        <f t="shared" si="83"/>
-        <v>937562</v>
-      </c>
-      <c r="N38" s="60">
         <f t="shared" si="83"/>
         <v>0</v>
       </c>
-      <c r="O38" s="60">
+      <c r="H38" s="19">
         <f t="shared" si="83"/>
-        <v>923982</v>
-      </c>
-      <c r="P38" s="60">
+        <v>1927</v>
+      </c>
+      <c r="I38" s="19">
         <f t="shared" si="83"/>
-        <v>548392</v>
-      </c>
-      <c r="Q38" s="60">
+        <v>1927</v>
+      </c>
+      <c r="J38" s="19">
         <f t="shared" si="89"/>
-        <v>11533854</v>
-      </c>
-      <c r="S38" s="91">
+        <v>205284</v>
+      </c>
+      <c r="L38" s="98">
         <f t="shared" si="84"/>
-        <v>1928</v>
-      </c>
-      <c r="T38" s="31">
+        <v>9123918</v>
+      </c>
+      <c r="M38" s="60">
+        <f t="shared" si="84"/>
+        <v>937562</v>
+      </c>
+      <c r="N38" s="60">
         <f t="shared" si="84"/>
         <v>0</v>
       </c>
-      <c r="U38" s="31">
+      <c r="O38" s="60">
         <f t="shared" si="84"/>
-        <v>0</v>
-      </c>
-      <c r="V38" s="31">
+        <v>923982</v>
+      </c>
+      <c r="P38" s="60">
         <f t="shared" si="84"/>
-        <v>192374</v>
-      </c>
-      <c r="W38" s="31">
-        <f t="shared" si="84"/>
-        <v>9055</v>
-      </c>
-      <c r="X38" s="31">
-        <f t="shared" si="84"/>
-        <v>1927</v>
-      </c>
-      <c r="Y38" s="31">
+        <v>548392</v>
+      </c>
+      <c r="Q38" s="60">
         <f t="shared" si="90"/>
-        <v>205284</v>
-      </c>
-      <c r="AA38" s="105">
+        <v>11533854</v>
+      </c>
+      <c r="S38" s="91">
         <f t="shared" si="85"/>
         <v>1928</v>
       </c>
-      <c r="AB38" s="65">
+      <c r="T38" s="31">
         <f t="shared" si="85"/>
         <v>0</v>
       </c>
-      <c r="AC38" s="65">
+      <c r="U38" s="31">
         <f t="shared" si="85"/>
         <v>0</v>
       </c>
-      <c r="AD38" s="65">
+      <c r="V38" s="31">
         <f t="shared" si="85"/>
         <v>192374</v>
       </c>
-      <c r="AE38" s="65">
+      <c r="W38" s="31">
         <f t="shared" si="85"/>
         <v>9055</v>
       </c>
-      <c r="AF38" s="65">
+      <c r="X38" s="31">
         <f t="shared" si="85"/>
         <v>1927</v>
       </c>
-      <c r="AG38" s="65">
+      <c r="Y38" s="31">
         <f t="shared" si="91"/>
         <v>205284</v>
       </c>
-      <c r="AI38" s="83">
+      <c r="AA38" s="105">
+        <f t="shared" si="86"/>
+        <v>1928</v>
+      </c>
+      <c r="AB38" s="65">
         <f t="shared" si="86"/>
         <v>0</v>
       </c>
-      <c r="AJ38" s="19">
+      <c r="AC38" s="65">
         <f t="shared" si="86"/>
         <v>0</v>
       </c>
-      <c r="AK38" s="19">
+      <c r="AD38" s="65">
         <f t="shared" si="86"/>
-        <v>3855</v>
-      </c>
-      <c r="AL38" s="19">
+        <v>192374</v>
+      </c>
+      <c r="AE38" s="65">
         <f t="shared" si="86"/>
-        <v>194301</v>
-      </c>
-      <c r="AM38" s="19">
+        <v>9055</v>
+      </c>
+      <c r="AF38" s="65">
         <f t="shared" si="86"/>
-        <v>7128</v>
-      </c>
-      <c r="AN38" s="19">
+        <v>1927</v>
+      </c>
+      <c r="AG38" s="65">
         <f t="shared" si="92"/>
         <v>205284</v>
       </c>
-      <c r="AP38" s="112">
+      <c r="AI38" s="83">
         <f t="shared" si="87"/>
         <v>0</v>
       </c>
-      <c r="AQ38" s="45">
+      <c r="AJ38" s="19">
         <f t="shared" si="87"/>
         <v>0</v>
       </c>
+      <c r="AK38" s="19">
+        <f t="shared" si="87"/>
+        <v>3855</v>
+      </c>
+      <c r="AL38" s="19">
+        <f t="shared" si="87"/>
+        <v>194301</v>
+      </c>
+      <c r="AM38" s="19">
+        <f t="shared" si="87"/>
+        <v>7128</v>
+      </c>
+      <c r="AN38" s="19">
+        <f t="shared" si="93"/>
+        <v>205284</v>
+      </c>
+      <c r="AP38" s="112">
+        <f t="shared" si="88"/>
+        <v>0</v>
+      </c>
+      <c r="AQ38" s="45">
+        <f t="shared" si="88"/>
+        <v>0</v>
+      </c>
       <c r="AR38" s="45">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>1032196</v>
       </c>
       <c r="AS38" s="45">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>1377740</v>
       </c>
       <c r="AT38" s="45">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>9123918</v>
       </c>
       <c r="AU38" s="45">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>11533854</v>
       </c>
       <c r="AW38" s="93"/>
@@ -11421,23 +11450,23 @@
         <v>110903</v>
       </c>
       <c r="F39" s="50">
-        <f t="shared" ref="F39" si="94">SUM(F34:F38)</f>
+        <f t="shared" ref="F39" si="95">SUM(F34:F38)</f>
         <v>304519</v>
       </c>
       <c r="G39" s="50">
-        <f t="shared" ref="G39" si="95">SUM(G34:G38)</f>
+        <f t="shared" ref="G39" si="96">SUM(G34:G38)</f>
         <v>118380</v>
       </c>
       <c r="H39" s="50">
-        <f t="shared" ref="H39" si="96">SUM(H34:H38)</f>
+        <f t="shared" ref="H39" si="97">SUM(H34:H38)</f>
         <v>115644</v>
       </c>
       <c r="I39" s="50">
-        <f t="shared" ref="I39" si="97">SUM(I34:I38)</f>
+        <f t="shared" ref="I39" si="98">SUM(I34:I38)</f>
         <v>208781</v>
       </c>
       <c r="J39" s="117">
-        <f t="shared" ref="J39" si="98">SUM(J34:J38)</f>
+        <f t="shared" ref="J39" si="99">SUM(J34:J38)</f>
         <v>858227</v>
       </c>
       <c r="L39" s="108">
@@ -11445,19 +11474,19 @@
         <v>650543568</v>
       </c>
       <c r="M39" s="68">
-        <f t="shared" ref="M39" si="99">SUM(M34:M38)</f>
+        <f t="shared" ref="M39" si="100">SUM(M34:M38)</f>
         <v>578124392</v>
       </c>
       <c r="N39" s="68">
-        <f t="shared" ref="N39" si="100">SUM(N34:N38)</f>
+        <f t="shared" ref="N39" si="101">SUM(N34:N38)</f>
         <v>690157736</v>
       </c>
       <c r="O39" s="68">
-        <f t="shared" ref="O39" si="101">SUM(O34:O38)</f>
+        <f t="shared" ref="O39" si="102">SUM(O34:O38)</f>
         <v>654943915</v>
       </c>
       <c r="P39" s="68">
-        <f t="shared" ref="P39" si="102">SUM(P34:P38)</f>
+        <f t="shared" ref="P39" si="103">SUM(P34:P38)</f>
         <v>656247934</v>
       </c>
       <c r="Q39" s="114">
@@ -11469,27 +11498,27 @@
         <v>121665</v>
       </c>
       <c r="T39" s="40">
-        <f t="shared" ref="T39:Y39" si="103">SUM(T34:T38)</f>
+        <f t="shared" ref="T39:Y39" si="104">SUM(T34:T38)</f>
         <v>125620</v>
       </c>
       <c r="U39" s="40">
-        <f t="shared" si="103"/>
+        <f t="shared" si="104"/>
         <v>32356</v>
       </c>
       <c r="V39" s="40">
-        <f t="shared" si="103"/>
+        <f t="shared" si="104"/>
         <v>356297</v>
       </c>
       <c r="W39" s="40">
-        <f t="shared" si="103"/>
+        <f t="shared" si="104"/>
         <v>122295</v>
       </c>
       <c r="X39" s="40">
-        <f t="shared" si="103"/>
+        <f t="shared" si="104"/>
         <v>99994</v>
       </c>
       <c r="Y39" s="40">
-        <f t="shared" si="103"/>
+        <f t="shared" si="104"/>
         <v>858227</v>
       </c>
       <c r="AA39" s="106">
@@ -11497,27 +11526,27 @@
         <v>121665</v>
       </c>
       <c r="AB39" s="66">
-        <f t="shared" ref="AB39" si="104">SUM(AB34:AB38)</f>
+        <f t="shared" ref="AB39" si="105">SUM(AB34:AB38)</f>
         <v>125620</v>
       </c>
       <c r="AC39" s="66">
-        <f t="shared" ref="AC39" si="105">SUM(AC34:AC38)</f>
+        <f t="shared" ref="AC39" si="106">SUM(AC34:AC38)</f>
         <v>32356</v>
       </c>
       <c r="AD39" s="66">
-        <f t="shared" ref="AD39" si="106">SUM(AD34:AD38)</f>
+        <f t="shared" ref="AD39" si="107">SUM(AD34:AD38)</f>
         <v>356297</v>
       </c>
       <c r="AE39" s="66">
-        <f t="shared" ref="AE39" si="107">SUM(AE34:AE38)</f>
+        <f t="shared" ref="AE39" si="108">SUM(AE34:AE38)</f>
         <v>122295</v>
       </c>
       <c r="AF39" s="66">
-        <f t="shared" ref="AF39" si="108">SUM(AF34:AF38)</f>
+        <f t="shared" ref="AF39" si="109">SUM(AF34:AF38)</f>
         <v>99994</v>
       </c>
       <c r="AG39" s="114">
-        <f t="shared" ref="AG39" si="109">SUM(AG34:AG38)</f>
+        <f t="shared" ref="AG39" si="110">SUM(AG34:AG38)</f>
         <v>858227</v>
       </c>
       <c r="AI39" s="94">
@@ -11525,23 +11554,23 @@
         <v>110109</v>
       </c>
       <c r="AJ39" s="50">
-        <f t="shared" ref="AJ39:AN39" si="110">SUM(AJ34:AJ38)</f>
+        <f t="shared" ref="AJ39:AN39" si="111">SUM(AJ34:AJ38)</f>
         <v>213260</v>
       </c>
       <c r="AK39" s="50">
-        <f t="shared" si="110"/>
+        <f t="shared" si="111"/>
         <v>116030</v>
       </c>
       <c r="AL39" s="50">
-        <f t="shared" si="110"/>
+        <f t="shared" si="111"/>
         <v>312792</v>
       </c>
       <c r="AM39" s="50">
-        <f t="shared" si="110"/>
+        <f t="shared" si="111"/>
         <v>106036</v>
       </c>
       <c r="AN39" s="117">
-        <f t="shared" si="110"/>
+        <f t="shared" si="111"/>
         <v>858227</v>
       </c>
       <c r="AP39" s="113">
@@ -11549,23 +11578,23 @@
         <v>646106962</v>
       </c>
       <c r="AQ39" s="48">
-        <f t="shared" ref="AQ39" si="111">SUM(AQ34:AQ38)</f>
+        <f t="shared" ref="AQ39" si="112">SUM(AQ34:AQ38)</f>
         <v>576804336</v>
       </c>
       <c r="AR39" s="48">
-        <f t="shared" ref="AR39" si="112">SUM(AR34:AR38)</f>
+        <f t="shared" ref="AR39" si="113">SUM(AR34:AR38)</f>
         <v>687706530</v>
       </c>
       <c r="AS39" s="48">
-        <f t="shared" ref="AS39" si="113">SUM(AS34:AS38)</f>
+        <f t="shared" ref="AS39" si="114">SUM(AS34:AS38)</f>
         <v>654677692</v>
       </c>
       <c r="AT39" s="48">
-        <f t="shared" ref="AT39" si="114">SUM(AT34:AT38)</f>
+        <f t="shared" ref="AT39" si="115">SUM(AT34:AT38)</f>
         <v>664722025</v>
       </c>
       <c r="AU39" s="118">
-        <f t="shared" ref="AU39" si="115">SUM(AU34:AU38)</f>
+        <f t="shared" ref="AU39" si="116">SUM(AU34:AU38)</f>
         <v>3230017545</v>
       </c>
       <c r="AW39" s="93"/>
@@ -11584,4 +11613,124 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DAD1870-E097-4F50-A371-71EFC7F222CC}">
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="2" customWidth="1"/>
+    <col min="5" max="5" width="16.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="135" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B2" s="3">
+        <v>100000</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="51">
+        <f>IFERROR(VLOOKUP($E$1,vendedores,MATCH($D2,estadisticas!$A$16:$C$16,0),FALSE),"seleccione un vendedor")</f>
+        <v>99994</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B3" s="3">
+        <v>500000000</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E3" s="137">
+        <f>IFERROR(VLOOKUP($E$1,vendedores,MATCH($D3,estadisticas!$A$16:$C$16,0),FALSE),"seleccione un vendedor")</f>
+        <v>561953724</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D4" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E4">
+        <f>IF(AND(E2&gt;=B2,E3&gt;=B3),2,IF(OR(E2&gt;=B2,E3&gt;=B3),1,0))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E5" s="1">
+        <f>E3*VLOOKUP(E4,A5:B8,2,FALSE)</f>
+        <v>84293058.599999994</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>0</v>
+      </c>
+      <c r="B6" s="136">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>1</v>
+      </c>
+      <c r="B7" s="136">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>2</v>
+      </c>
+      <c r="B8" s="136">
+        <v>0.2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Vendedor No encontrado" error="Ingrese un nombre de vendedor que se encuentre registrado" xr:uid="{0AD58637-BCDD-4A9E-8D99-B372B763A97D}">
+          <x14:formula1>
+            <xm:f>listas!$B$2:$B$7</xm:f>
+          </x14:formula1>
+          <xm:sqref>E1</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
 </file>